--- a/Vocabulary/IT_vocab/IT_vocab.xlsx
+++ b/Vocabulary/IT_vocab/IT_vocab.xlsx
@@ -24,1978 +24,1978 @@
     <t>word,reading,meaning,type,level,example,exampleMeaning,courseId,lessonId,lessonTitle</t>
   </si>
   <si>
-    <t>パソコン,ぱそこん,máy tính,名詞,N5,会社で毎日パソコンを使って仕事をします,Hằng ngày tôi dùng máy tính để làm việc ở công ty,tu-vung-cntt,lesson-01,Bài 1: Thiết bị và khái niệm cơ bản</t>
-  </si>
-  <si>
-    <t>ファイル,ふぁいる,tệp tin,名詞,N5,このファイルを先に開いて内容を確認してください,Hãy mở tệp này trước và kiểm tra nội dung,tu-vung-cntt,lesson-01,Bài 1: Thiết bị và khái niệm cơ bản</t>
-  </si>
-  <si>
-    <t>フォルダ,ふぉるだ,thư mục,名詞,N5,資料はこのフォルダの中に保存してあります,Tài liệu được lưu trong thư mục này,tu-vung-cntt,lesson-01,Bài 1: Thiết bị và khái niệm cơ bản</t>
-  </si>
-  <si>
-    <t>保存,ほぞん,lưu dữ liệu,名詞,N5,作業が終わったら必ず保存してください,Sau khi làm xong hãy nhớ lưu lại,tu-vung-cntt,lesson-01,Bài 1: Thiết bị và khái niệm cơ bản</t>
-  </si>
-  <si>
-    <t>削除,さくじょ,xóa,名詞,N4,不要なファイルは昨日全部削除しました,Hôm qua tôi đã xóa toàn bộ tệp không cần thiết,tu-vung-cntt,lesson-01,Bài 1: Thiết bị và khái niệm cơ bản</t>
-  </si>
-  <si>
-    <t>検索,けんさく,tìm kiếm,名詞,N4,必要な資料を社内システムで検索します,Tôi tìm tài liệu cần thiết trên hệ thống nội bộ,tu-vung-cntt,lesson-01,Bài 1: Thiết bị và khái niệm cơ bản</t>
-  </si>
-  <si>
-    <t>画面,がめん,màn hình,名詞,N4,画面が暗いので明るさを上げてください,Màn hình tối nên hãy tăng độ sáng,tu-vung-cntt,lesson-01,Bài 1: Thiết bị và khái niệm cơ bản</t>
-  </si>
-  <si>
-    <t>入力,にゅうりょく,nhập dữ liệu,名詞,N4,名前と住所を正しく入力してください,Hãy nhập đúng họ tên và địa chỉ,tu-vung-cntt,lesson-01,Bài 1: Thiết bị và khái niệm cơ bản</t>
-  </si>
-  <si>
-    <t>出力,しゅつりょく,xuất dữ liệu,名詞,N4,結果をPDFで出力して共有しました,Tôi đã xuất kết quả thành PDF và chia sẻ,tu-vung-cntt,lesson-01,Bài 1: Thiết bị và khái niệm cơ bản</t>
-  </si>
-  <si>
-    <t>印刷,いんさつ,in,名詞,N4,この資料を二部印刷してください,Hãy in tài liệu này thành hai bản,tu-vung-cntt,lesson-01,Bài 1: Thiết bị và khái niệm cơ bản</t>
-  </si>
-  <si>
-    <t>接続,せつぞく,kết nối,名詞,N3,サーバーとの接続をもう一度確認してください,Hãy kiểm tra lại kết nối với máy chủ,tu-vung-cntt,lesson-01,Bài 1: Thiết bị và khái niệm cơ bản</t>
-  </si>
-  <si>
-    <t>更新,こうしん,cập nhật,名詞,N3,システムを最新の状態に更新しました,Tôi đã cập nhật hệ thống lên phiên bản mới nhất,tu-vung-cntt,lesson-01,Bài 1: Thiết bị và khái niệm cơ bản</t>
-  </si>
-  <si>
-    <t>設定,せってい,cài đặt,名詞,N3,ネットワークの設定を変更しました,Tôi đã thay đổi cài đặt mạng,tu-vung-cntt,lesson-01,Bài 1: Thiết bị và khái niệm cơ bản</t>
-  </si>
-  <si>
-    <t>共有,きょうゆう,chia sẻ,名詞,N3,完成した資料をチーム全員へ共有しました,Tôi đã chia sẻ tài liệu hoàn thành cho cả nhóm,tu-vung-cntt,lesson-01,Bài 1: Thiết bị và khái niệm cơ bản</t>
-  </si>
-  <si>
-    <t>管理,かんり,quản lý,名詞,N3,私は毎日サーバーを管理しています,Tôi quản lý máy chủ mỗi ngày,tu-vung-cntt,lesson-01,Bài 1: Thiết bị và khái niệm cơ bản</t>
-  </si>
-  <si>
-    <t>サーバー,さーばー,máy chủ,名詞,N3,新しいサーバーは昨日から正常に動いています,Máy chủ mới đã hoạt động bình thường từ hôm qua,tu-vung-cntt,lesson-02,Bài 2: Hệ thống và phát triển phần mềm</t>
-  </si>
-  <si>
-    <t>ネットワーク,ねっとわーく,mạng,名詞,N3,ネットワークに問題がないか確認してください,Hãy kiểm tra xem mạng có vấn đề không,tu-vung-cntt,lesson-02,Bài 2: Hệ thống và phát triển phần mềm</t>
-  </si>
-  <si>
-    <t>データベース,でーたべーす,cơ sở dữ liệu,名詞,N3,顧客情報はデータベースに保存されています,Thông tin khách hàng được lưu trong cơ sở dữ liệu,tu-vung-cntt,lesson-02,Bài 2: Hệ thống và phát triển phần mềm</t>
-  </si>
-  <si>
-    <t>プログラム,ぷろぐらむ,chương trình,名詞,N3,このプログラムは毎朝自動で実行されます,Chương trình này tự động chạy mỗi sáng,tu-vung-cntt,lesson-02,Bài 2: Hệ thống và phát triển phần mềm</t>
-  </si>
-  <si>
-    <t>ソフトウェア,そふとうぇあ,phần mềm,名詞,N3,新しいソフトウェアを今日インストールしました,Hôm nay tôi đã cài phần mềm mới,tu-vung-cntt,lesson-02,Bài 2: Hệ thống và phát triển phần mềm</t>
-  </si>
-  <si>
-    <t>ハードウェア,はーどうぇあ,phần cứng,名詞,N3,ハードウェアの故障を詳しく調べています,Chúng tôi đang kiểm tra kỹ lỗi phần cứng,tu-vung-cntt,lesson-02,Bài 2: Hệ thống và phát triển phần mềm</t>
-  </si>
-  <si>
-    <t>開発,かいはつ,phát triển,名詞,N3,新しいシステムの開発を担当しています,Tôi phụ trách phát triển hệ thống mới,tu-vung-cntt,lesson-02,Bài 2: Hệ thống và phát triển phần mềm</t>
-  </si>
-  <si>
-    <t>運用,うんよう,vận hành,名詞,N3,サービスの運用は二十四時間続きます,Dịch vụ được vận hành hai mươi bốn giờ,tu-vung-cntt,lesson-02,Bài 2: Hệ thống và phát triển phần mềm</t>
-  </si>
-  <si>
-    <t>障害,しょうがい,sự cố,名詞,N3,障害が発生したので原因を調査しています,Đã xảy ra sự cố nên đang điều tra nguyên nhân,tu-vung-cntt,lesson-02,Bài 2: Hệ thống và phát triển phần mềm</t>
-  </si>
-  <si>
-    <t>復旧,ふっきゅう,khôi phục,名詞,N3,システムは一時間で復旧しました,Hệ thống đã được khôi phục trong một giờ,tu-vung-cntt,lesson-02,Bài 2: Hệ thống và phát triển phần mềm</t>
-  </si>
-  <si>
-    <t>保守,ほしゅ,bảo trì,名詞,N3,毎週日曜日にサーバーを保守します,Mỗi Chủ nhật chúng tôi bảo trì máy chủ,tu-vung-cntt,lesson-02,Bài 2: Hệ thống và phát triển phần mềm</t>
-  </si>
-  <si>
-    <t>暗号化,あんごうか,mã hóa,名詞,N3,重要なデータは暗号化して送信します,Dữ liệu quan trọng được mã hóa trước khi gửi,tu-vung-cntt,lesson-02,Bài 2: Hệ thống và phát triển phần mềm</t>
-  </si>
-  <si>
-    <t>認証,にんしょう,xác thực,名詞,N3,利用者は認証の後でログインできます,Người dùng có thể đăng nhập sau khi xác thực,tu-vung-cntt,lesson-02,Bài 2: Hệ thống và phát triển phần mềm</t>
-  </si>
-  <si>
-    <t>監視,かんし,giám sát,名詞,N3,システムを夜間も継続して監視しています,Chúng tôi tiếp tục giám sát hệ thống cả ban đêm,tu-vung-cntt,lesson-02,Bài 2: Hệ thống và phát triển phần mềm</t>
-  </si>
-  <si>
-    <t>バックアップ,ばっくあっぷ,sao lưu,名詞,N3,毎日自動でバックアップを作成しています,Hệ thống tự động tạo bản sao lưu mỗi ngày,tu-vung-cntt,lesson-02,Bài 2: Hệ thống và phát triển phần mềm</t>
-  </si>
-  <si>
-    <t>ログイン,ろぐいん,đăng nhập,名詞,N5,朝会社に着いたらすぐログインします,Sáng đến công ty tôi đăng nhập ngay,tu-vung-cntt,lesson-03,Bài 3: Internet và bảo mật</t>
-  </si>
-  <si>
-    <t>ログアウト,ろぐあうと,đăng xuất,名詞,N5,帰る前に必ずログアウトしてください,Hãy nhớ đăng xuất trước khi về,tu-vung-cntt,lesson-03,Bài 3: Internet và bảo mật</t>
-  </si>
-  <si>
-    <t>メール,めーる,email,名詞,N5,お客様からメールが届きました,Tôi đã nhận được email từ khách hàng,tu-vung-cntt,lesson-03,Bài 3: Internet và bảo mật</t>
-  </si>
-  <si>
-    <t>パスワード,ぱすわーど,mật khẩu,名詞,N5,パスワードは他の人に教えません,Tôi không tiết lộ mật khẩu cho người khác,tu-vung-cntt,lesson-03,Bài 3: Internet và bảo mật</t>
-  </si>
-  <si>
-    <t>ユーザー,ゆーざー,người dùng,名詞,N4,新しいユーザーを追加しました,Tôi đã thêm người dùng mới,tu-vung-cntt,lesson-03,Bài 3: Internet và bảo mật</t>
-  </si>
-  <si>
-    <t>アカウント,あかうんと,tài khoản,名詞,N4,このアカウントはまだ利用できます,Tài khoản này vẫn có thể sử dụng,tu-vung-cntt,lesson-03,Bài 3: Internet và bảo mật</t>
-  </si>
-  <si>
-    <t>ブラウザ,ぶらうざ,trình duyệt,名詞,N4,ブラウザを最新版に更新してください,Hãy cập nhật trình duyệt lên phiên bản mới nhất,tu-vung-cntt,lesson-03,Bài 3: Internet và bảo mật</t>
-  </si>
-  <si>
-    <t>ウェブサイト,うぇぶさいと,trang web,名詞,N4,会社のウェブサイトを毎日確認します,Tôi kiểm tra trang web công ty mỗi ngày,tu-vung-cntt,lesson-03,Bài 3: Internet và bảo mật</t>
-  </si>
-  <si>
-    <t>ダウンロード,だうんろーど,tải xuống,名詞,N4,必要な資料をダウンロードしました,Tôi đã tải xuống tài liệu cần thiết,tu-vung-cntt,lesson-03,Bài 3: Internet và bảo mật</t>
-  </si>
-  <si>
-    <t>アップロード,あっぷろーど,tải lên,名詞,N4,完成したファイルをアップロードしてください,Hãy tải lên tệp đã hoàn thành,tu-vung-cntt,lesson-03,Bài 3: Internet và bảo mật</t>
-  </si>
-  <si>
-    <t>アクセス,あくせす,truy cập,名詞,N3,このフォルダには誰でもアクセスできます,Mọi người đều có thể truy cập thư mục này,tu-vung-cntt,lesson-03,Bài 3: Internet và bảo mật</t>
-  </si>
-  <si>
-    <t>通信,つうしん,giao tiếp dữ liệu,名詞,N3,通信速度が急に遅くなりました,Tốc độ truyền dữ liệu đột nhiên chậm lại,tu-vung-cntt,lesson-03,Bài 3: Internet và bảo mật</t>
-  </si>
-  <si>
-    <t>セキュリティ,せきゅりてぃ,bảo mật,名詞,N3,セキュリティを強化する必要があります,Cần tăng cường bảo mật,tu-vung-cntt,lesson-03,Bài 3: Internet và bảo mật</t>
-  </si>
-  <si>
-    <t>ウイルス,ういるす,vi rút máy tính,名詞,N3,ウイルスを検出したので削除しました,Tôi đã phát hiện và xóa vi rút,tu-vung-cntt,lesson-03,Bài 3: Internet và bảo mật</t>
-  </si>
-  <si>
-    <t>ファイアウォール,ふぁいあうぉーる,tường lửa,名詞,N3,ファイアウォールの設定を確認してください,Hãy kiểm tra cài đặt tường lửa,tu-vung-cntt,lesson-03,Bài 3: Internet và bảo mật</t>
-  </si>
-  <si>
-    <t>エラー,えらー,lỗi,名詞,N5,システムにエラーが表示されました,Hệ thống đã hiển thị lỗi,tu-vung-cntt,lesson-04,Bài 4: Lập trình và xử lý sự cố</t>
-  </si>
-  <si>
-    <t>修正,しゅうせい,sửa chữa,名詞,N4,見つかった問題をすぐ修正しました,Tôi đã sửa ngay vấn đề được phát hiện,tu-vung-cntt,lesson-04,Bài 4: Lập trình và xử lý sự cố</t>
-  </si>
-  <si>
-    <t>確認,かくにん,kiểm tra xác nhận,名詞,N4,変更した内容をもう一度確認してください,Hãy kiểm tra lại nội dung đã thay đổi,tu-vung-cntt,lesson-04,Bài 4: Lập trình và xử lý sự cố</t>
-  </si>
-  <si>
-    <t>実行,じっこう,thực thi,名詞,N4,プログラムを実行して結果を確認します,Tôi chạy chương trình và kiểm tra kết quả,tu-vung-cntt,lesson-04,Bài 4: Lập trình và xử lý sự cố</t>
-  </si>
-  <si>
-    <t>停止,ていし,dừng,名詞,N4,サービスを一時停止しました,Dịch vụ đã được tạm dừng,tu-vung-cntt,lesson-04,Bài 4: Lập trình và xử lý sự cố</t>
-  </si>
-  <si>
-    <t>再起動,さいきどう,khởi động lại,名詞,N4,サーバーを再起動してみてください,Hãy thử khởi động lại máy chủ,tu-vung-cntt,lesson-04,Bài 4: Lập trình và xử lý sự cố</t>
-  </si>
-  <si>
-    <t>起動,きどう,khởi động,名詞,N4,パソコンは正常に起動しました,Máy tính đã khởi động bình thường,tu-vung-cntt,lesson-04,Bài 4: Lập trình và xử lý sự cố</t>
-  </si>
-  <si>
-    <t>終了,しゅうりょう,kết thúc,名詞,N4,作業が終わったらアプリを終了します,Sau khi xong việc tôi sẽ đóng ứng dụng,tu-vung-cntt,lesson-04,Bài 4: Lập trình và xử lý sự cố</t>
-  </si>
-  <si>
-    <t>処理,しょり,xử lý,名詞,N3,大量のデータを高速で処理できます,Có thể xử lý lượng lớn dữ liệu với tốc độ cao,tu-vung-cntt,lesson-04,Bài 4: Lập trình và xử lý sự cố</t>
-  </si>
-  <si>
-    <t>自動化,じどうか,tự động hóa,名詞,N3,定型作業を自動化しました,Tôi đã tự động hóa các công việc lặp lại,tu-vung-cntt,lesson-04,Bài 4: Lập trình và xử lý sự cố</t>
-  </si>
-  <si>
-    <t>最適化,さいてきか,tối ưu hóa,名詞,N3,システムの性能を最適化しています,Chúng tôi đang tối ưu hiệu năng hệ thống,tu-vung-cntt,lesson-04,Bài 4: Lập trình và xử lý sự cố</t>
-  </si>
-  <si>
-    <t>開く,ひらく,mở,動詞,N5,このファイルを開いて内容を読んでください,Hãy mở tệp này và đọc nội dung,tu-vung-cntt,lesson-04,Bài 4: Lập trình và xử lý sự cố</t>
-  </si>
-  <si>
-    <t>閉じる,とじる,đóng,動詞,N5,使い終わったら画面を閉じてください,Sau khi dùng xong hãy đóng màn hình,tu-vung-cntt,lesson-04,Bài 4: Lập trình và xử lý sự cố</t>
-  </si>
-  <si>
-    <t>送信,そうしん,gửi,名詞,N4,資料をお客様へ送信しました,Tôi đã gửi tài liệu cho khách hàng,tu-vung-cntt,lesson-04,Bài 4: Lập trình và xử lý sự cố</t>
-  </si>
-  <si>
-    <t>受信,じゅしん,nhận,名詞,N4,新しいデータを正常に受信しました,Hệ thống đã nhận dữ liệu mới thành công,tu-vung-cntt,lesson-04,Bài 4: Lập trình và xử lý sự cố</t>
-  </si>
-  <si>
-    <t>プリンター,ぷりんたー,máy in,名詞,N5,プリンターで会議資料を印刷しました,Tôi đã in tài liệu cuộc họp bằng máy in,tu-vung-cntt,lesson-05,Bài 5: Thiết bị và văn phòng IT</t>
-  </si>
-  <si>
-    <t>スキャナー,すきゃなー,máy quét,名詞,N5,契約書をスキャナーで読み取りました,Tôi đã quét hợp đồng bằng máy quét,tu-vung-cntt,lesson-05,Bài 5: Thiết bị và văn phòng IT</t>
-  </si>
-  <si>
-    <t>キーボード,きーぼーど,bàn phím,名詞,N5,キーボードの一部のキーが反応しません,Một số phím trên bàn phím không phản hồi,tu-vung-cntt,lesson-05,Bài 5: Thiết bị và văn phòng IT</t>
-  </si>
-  <si>
-    <t>マウス,まうす,chuột máy tính,名詞,N5,新しいマウスはとても使いやすいです,Chuột mới rất dễ sử dụng,tu-vung-cntt,lesson-05,Bài 5: Thiết bị và văn phòng IT</t>
-  </si>
-  <si>
-    <t>ケーブル,けーぶる,cáp,名詞,N4,ネットワークケーブルを交換してください,Hãy thay dây cáp mạng,tu-vung-cntt,lesson-05,Bài 5: Thiết bị và văn phòng IT</t>
-  </si>
-  <si>
-    <t>モニター,もにたー,màn hình,名詞,N4,モニターを二台使って作業しています,Tôi làm việc với hai màn hình,tu-vung-cntt,lesson-05,Bài 5: Thiết bị và văn phòng IT</t>
-  </si>
-  <si>
-    <t>電源,でんげん,nguồn điện,名詞,N4,電源が入らないので確認してください,Hãy kiểm tra vì máy không lên nguồn,tu-vung-cntt,lesson-05,Bài 5: Thiết bị và văn phòng IT</t>
-  </si>
-  <si>
-    <t>電源を入れる,でんげんをいれる,bật nguồn,表現,N4,作業を始める前に電源を入れてください,Hãy bật nguồn trước khi bắt đầu làm việc,tu-vung-cntt,lesson-05,Bài 5: Thiết bị và văn phòng IT</t>
-  </si>
-  <si>
-    <t>電源を切る,でんげんをきる,tắt nguồn,表現,N4,帰る前に電源を切ってください,Hãy tắt nguồn trước khi ra về,tu-vung-cntt,lesson-05,Bài 5: Thiết bị và văn phòng IT</t>
-  </si>
-  <si>
-    <t>故障,こしょう,hỏng hóc,名詞,N3,プリンターが故障したので修理を依頼しました,Máy in bị hỏng nên tôi đã yêu cầu sửa chữa,tu-vung-cntt,lesson-05,Bài 5: Thiết bị và văn phòng IT</t>
-  </si>
-  <si>
-    <t>交換,こうかん,thay thế,名詞,N3,古いディスクを新しい物へ交換しました,Tôi đã thay ổ đĩa cũ bằng ổ mới,tu-vung-cntt,lesson-05,Bài 5: Thiết bị và văn phòng IT</t>
-  </si>
-  <si>
-    <t>点検,てんけん,kiểm tra bảo dưỡng,名詞,N3,毎月機器を点検しています,Chúng tôi kiểm tra thiết bị mỗi tháng,tu-vung-cntt,lesson-05,Bài 5: Thiết bị và văn phòng IT</t>
-  </si>
-  <si>
-    <t>修理,しゅうり,sửa chữa,名詞,N3,壊れたパソコンを修理しました,Tôi đã sửa chiếc máy tính bị hỏng,tu-vung-cntt,lesson-05,Bài 5: Thiết bị và văn phòng IT</t>
-  </si>
-  <si>
-    <t>部品,ぶひん,linh kiện,名詞,N3,必要な部品がまだ届いていません,Linh kiện cần thiết vẫn chưa được giao tới,tu-vung-cntt,lesson-05,Bài 5: Thiết bị và văn phòng IT</t>
-  </si>
-  <si>
-    <t>機器,きき,thiết bị,名詞,N3,新しい機器を会議室へ設置しました,Tôi đã lắp đặt thiết bị mới trong phòng họp,tu-vung-cntt,lesson-05,Bài 5: Thiết bị và văn phòng IT</t>
-  </si>
-  <si>
-    <t>コード,こーど,mã nguồn,名詞,N4,コードを変更する前に確認してください,Hãy kiểm tra trước khi sửa mã nguồn,tu-vung-cntt,lesson-06,Bài 6: Lập trình và phát triển phần mềm</t>
-  </si>
-  <si>
-    <t>変数,へんすう,biến,名詞,N3,変数の名前を分かりやすくしてください,Hãy đặt tên biến dễ hiểu hơn,tu-vung-cntt,lesson-06,Bài 6: Lập trình và phát triển phần mềm</t>
-  </si>
-  <si>
-    <t>関数,かんすう,hàm,名詞,N3,この関数はデータを並べ替えます,Hàm này sắp xếp dữ liệu,tu-vung-cntt,lesson-06,Bài 6: Lập trình và phát triển phần mềm</t>
-  </si>
-  <si>
-    <t>配列,はいれつ,mảng,名詞,N3,配列の要素を一つずつ表示します,Hiển thị từng phần tử của mảng,tu-vung-cntt,lesson-06,Bài 6: Lập trình và phát triển phần mềm</t>
-  </si>
-  <si>
-    <t>文字列,もじれつ,chuỗi ký tự,名詞,N3,文字列の長さを確認してください,Hãy kiểm tra độ dài chuỗi ký tự,tu-vung-cntt,lesson-06,Bài 6: Lập trình và phát triển phần mềm</t>
-  </si>
-  <si>
-    <t>仕様,しよう,đặc tả yêu cầu,名詞,N3,仕様を読んでから開発を始めます,Tôi đọc đặc tả trước khi bắt đầu phát triển,tu-vung-cntt,lesson-06,Bài 6: Lập trình và phát triển phần mềm</t>
-  </si>
-  <si>
-    <t>設計,せっけい,thiết kế,名詞,N3,設計が終わってから実装します,Sau khi thiết kế xong mới tiến hành lập trình,tu-vung-cntt,lesson-06,Bài 6: Lập trình và phát triển phần mềm</t>
-  </si>
-  <si>
-    <t>実装,じっそう,triển khai lập trình,名詞,N3,新しい機能を実装しました,Tôi đã triển khai tính năng mới,tu-vung-cntt,lesson-06,Bài 6: Lập trình và phát triển phần mềm</t>
-  </si>
-  <si>
-    <t>試験,しけん,kiểm thử,名詞,N3,試験の結果に問題はありません,Kết quả kiểm thử không có vấn đề,tu-vung-cntt,lesson-06,Bài 6: Lập trình và phát triển phần mềm</t>
-  </si>
-  <si>
-    <t>デバッグ,でばっぐ,gỡ lỗi,名詞,N3,一日中デバッグを続けました,Tôi đã gỡ lỗi suốt cả ngày,tu-vung-cntt,lesson-06,Bài 6: Lập trình và phát triển phần mềm</t>
-  </si>
-  <si>
-    <t>不具合,ふぐあい,lỗi phần mềm,名詞,N3,不具合の原因を調査しています,Chúng tôi đang điều tra nguyên nhân lỗi phần mềm,tu-vung-cntt,lesson-06,Bài 6: Lập trình và phát triển phần mềm</t>
-  </si>
-  <si>
-    <t>品質,ひんしつ,chất lượng,名詞,N3,品質を高めるために改善します,Chúng tôi cải tiến để nâng cao chất lượng,tu-vung-cntt,lesson-06,Bài 6: Lập trình và phát triển phần mềm</t>
-  </si>
-  <si>
-    <t>納期,のうき,thời hạn giao,名詞,N3,納期までに作業を完了します,Tôi sẽ hoàn thành công việc trước thời hạn,tu-vung-cntt,lesson-06,Bài 6: Lập trình và phát triển phần mềm</t>
-  </si>
-  <si>
-    <t>担当者,たんとうしゃ,người phụ trách,名詞,N3,担当者へ直接連絡してください,Hãy liên hệ trực tiếp với người phụ trách,tu-vung-cntt,lesson-06,Bài 6: Lập trình và phát triển phần mềm</t>
-  </si>
-  <si>
-    <t>改善,かいぜん,cải tiến,名詞,N3,利用者の意見を参考に改善しました,Chúng tôi đã cải tiến dựa trên ý kiến người dùng,tu-vung-cntt,lesson-06,Bài 6: Lập trình và phát triển phần mềm</t>
-  </si>
-  <si>
-    <t>画面共有,がめんきょうゆう,chia sẻ màn hình,名詞,N4,会議で画面共有を使って説明しました,Tôi đã dùng chia sẻ màn hình để giải thích trong cuộc họp,tu-vung-cntt,lesson-07,Bài 7: Họp trực tuyến và làm việc nhóm</t>
-  </si>
-  <si>
-    <t>オンライン会議,おんらいんかいぎ,họp trực tuyến,名詞,N4,今日はオンライン会議が三回あります,Hôm nay có ba cuộc họp trực tuyến,tu-vung-cntt,lesson-07,Bài 7: Họp trực tuyến và làm việc nhóm</t>
-  </si>
-  <si>
-    <t>チャット,ちゃっと,trò chuyện trực tuyến,名詞,N5,分からないことはチャットで質問してください,Nếu không hiểu hãy hỏi qua chat,tu-vung-cntt,lesson-07,Bài 7: Họp trực tuyến và làm việc nhóm</t>
-  </si>
-  <si>
-    <t>通知,つうち,thông báo,名詞,N4,新しい通知がスマートフォンに届きました,Một thông báo mới đã đến điện thoại,tu-vung-cntt,lesson-07,Bài 7: Họp trực tuyến và làm việc nhóm</t>
-  </si>
-  <si>
-    <t>参加,さんか,tham gia,名詞,N4,全員が会議に参加しました,Mọi người đều đã tham gia cuộc họp,tu-vung-cntt,lesson-07,Bài 7: Họp trực tuyến và làm việc nhóm</t>
-  </si>
-  <si>
-    <t>退出,たいしゅつ,rời khỏi,名詞,N3,会議が終わったので退出しました,Cuộc họp kết thúc nên tôi đã rời phòng họp,tu-vung-cntt,lesson-07,Bài 7: Họp trực tuyến và làm việc nhóm</t>
-  </si>
-  <si>
-    <t>共有する,きょうゆうする,chia sẻ,動詞,N4,資料を全員と共有してください,Hãy chia sẻ tài liệu với mọi người,tu-vung-cntt,lesson-07,Bài 7: Họp trực tuyến và làm việc nhóm</t>
-  </si>
-  <si>
-    <t>招待,しょうたい,lời mời,名詞,N3,会議の招待をメールで送りました,Tôi đã gửi lời mời họp qua email,tu-vung-cntt,lesson-07,Bài 7: Họp trực tuyến và làm việc nhóm</t>
-  </si>
-  <si>
-    <t>会議室,かいぎしつ,phòng họp,名詞,N5,午後は会議室で打ち合わせをします,Chiều nay chúng tôi họp tại phòng họp,tu-vung-cntt,lesson-07,Bài 7: Họp trực tuyến và làm việc nhóm</t>
-  </si>
-  <si>
-    <t>録画,ろくが,ghi hình,名詞,N3,重要な説明を録画しました,Tôi đã ghi hình phần giải thích quan trọng,tu-vung-cntt,lesson-07,Bài 7: Họp trực tuyến và làm việc nhóm</t>
-  </si>
-  <si>
-    <t>録音,ろくおん,ghi âm,名詞,N3,会議の内容を録音しています,Nội dung cuộc họp đang được ghi âm,tu-vung-cntt,lesson-07,Bài 7: Họp trực tuyến và làm việc nhóm</t>
-  </si>
-  <si>
-    <t>発言,はつげん,phát biểu,名詞,N3,質問があれば自由に発言してください,Nếu có câu hỏi hãy phát biểu tự do,tu-vung-cntt,lesson-07,Bài 7: Họp trực tuyến và làm việc nhóm</t>
-  </si>
-  <si>
-    <t>議事録,ぎじろく,biên bản cuộc họp,名詞,N3,議事録を午後までに作成します,Tôi sẽ hoàn thành biên bản cuộc họp trước chiều,tu-vung-cntt,lesson-07,Bài 7: Họp trực tuyến và làm việc nhóm</t>
-  </si>
-  <si>
-    <t>共同作業,きょうどうさぎょう,làm việc nhóm,名詞,N3,共同作業で効率が上がりました,Làm việc nhóm đã nâng cao hiệu quả,tu-vung-cntt,lesson-07,Bài 7: Họp trực tuyến và làm việc nhóm</t>
-  </si>
-  <si>
-    <t>担当,たんとう,phụ trách,名詞,N3,私はネットワーク担当です,Tôi phụ trách mảng mạng,tu-vung-cntt,lesson-07,Bài 7: Họp trực tuyến và làm việc nhóm</t>
-  </si>
-  <si>
-    <t>利用者,りようしゃ,người sử dụng,名詞,N4,利用者から多くの質問が届きました,Đã nhận được nhiều câu hỏi từ người dùng,tu-vung-cntt,lesson-08,Bài 8: Hỗ trợ người dùng</t>
-  </si>
-  <si>
-    <t>問い合わせ,といあわせ,yêu cầu hỗ trợ,名詞,N3,問い合わせにすぐ対応しました,Tôi đã phản hồi yêu cầu hỗ trợ ngay lập tức,tu-vung-cntt,lesson-08,Bài 8: Hỗ trợ người dùng</t>
-  </si>
-  <si>
-    <t>対応,たいおう,xử lý hỗ trợ,名詞,N3,問題に迅速に対応してください,Hãy xử lý vấn đề một cách nhanh chóng,tu-vung-cntt,lesson-08,Bài 8: Hỗ trợ người dùng</t>
-  </si>
-  <si>
-    <t>受付,うけつけ,tiếp nhận,名詞,N3,朝から多くの依頼を受付しました,Từ sáng đã tiếp nhận nhiều yêu cầu,tu-vung-cntt,lesson-08,Bài 8: Hỗ trợ người dùng</t>
-  </si>
-  <si>
-    <t>依頼,いらい,yêu cầu,名詞,N3,新しい依頼を確認してください,Hãy kiểm tra yêu cầu mới,tu-vung-cntt,lesson-08,Bài 8: Hỗ trợ người dùng</t>
-  </si>
-  <si>
-    <t>解決,かいけつ,giải quyết,名詞,N3,問題を十分で解決しました,Tôi đã giải quyết vấn đề trong mười phút,tu-vung-cntt,lesson-08,Bài 8: Hỗ trợ người dùng</t>
-  </si>
-  <si>
-    <t>原因,げんいん,nguyên nhân,名詞,N3,原因を詳しく調査しています,Chúng tôi đang điều tra chi tiết nguyên nhân,tu-vung-cntt,lesson-08,Bài 8: Hỗ trợ người dùng</t>
-  </si>
-  <si>
-    <t>現象,げんしょう,hiện tượng,名詞,N3,同じ現象が何度も発生しました,Hiện tượng tương tự đã xảy ra nhiều lần,tu-vung-cntt,lesson-08,Bài 8: Hỗ trợ người dùng</t>
-  </si>
-  <si>
-    <t>報告,ほうこく,báo cáo,名詞,N3,結果を上司へ報告しました,Tôi đã báo cáo kết quả với cấp trên,tu-vung-cntt,lesson-08,Bài 8: Hỗ trợ người dùng</t>
-  </si>
-  <si>
-    <t>連絡,れんらく,liên lạc,名詞,N4,担当者へすぐ連絡してください,Hãy liên lạc ngay với người phụ trách,tu-vung-cntt,lesson-08,Bài 8: Hỗ trợ người dùng</t>
-  </si>
-  <si>
-    <t>説明,せつめい,giải thích,名詞,N4,操作方法を分かりやすく説明しました,Tôi đã giải thích cách sử dụng một cách dễ hiểu,tu-vung-cntt,lesson-08,Bài 8: Hỗ trợ người dùng</t>
-  </si>
-  <si>
-    <t>操作,そうさ,thao tác,名詞,N4,操作はとても簡単です,Thao tác rất đơn giản,tu-vung-cntt,lesson-08,Bài 8: Hỗ trợ người dùng</t>
-  </si>
-  <si>
-    <t>案内,あんない,hướng dẫn,名詞,N3,利用者へ手順を案内しました,Tôi đã hướng dẫn các bước cho người dùng,tu-vung-cntt,lesson-08,Bài 8: Hỗ trợ người dùng</t>
-  </si>
-  <si>
-    <t>手順,てじゅん,các bước thực hiện,名詞,N3,手順どおりに設定してください,Hãy cài đặt theo đúng các bước,tu-vung-cntt,lesson-08,Bài 8: Hỗ trợ người dùng</t>
-  </si>
-  <si>
-    <t>完了,かんりょう,hoàn tất,名詞,N3,設定は予定どおり完了しました,Việc cài đặt đã hoàn tất đúng kế hoạch,tu-vung-cntt,lesson-08,Bài 8: Hỗ trợ người dùng</t>
-  </si>
-  <si>
-    <t>エクスプローラー,えくすぷろーらー,File Explorer,名詞,N4,エクスプローラーで共有フォルダを開いてください,Hãy mở thư mục chia sẻ bằng File Explorer,tu-vung-cntt,lesson-09,Bài 9: Windows và File Explorer</t>
-  </si>
-  <si>
-    <t>デスクトップ,ですくとっぷ,màn hình Desktop,名詞,N5,デスクトップに新しいフォルダを作りました,Tôi đã tạo một thư mục mới trên Desktop,tu-vung-cntt,lesson-09,Bài 9: Windows và File Explorer</t>
-  </si>
-  <si>
-    <t>ごみ箱,ごみばこ,thùng rác,名詞,N5,不要なファイルをごみ箱へ移動しました,Tôi đã chuyển tệp không cần thiết vào thùng rác,tu-vung-cntt,lesson-09,Bài 9: Windows và File Explorer</t>
-  </si>
-  <si>
-    <t>コピー,こぴー,sao chép,名詞,N5,このファイルをUSBへコピーしてください,Hãy sao chép tệp này vào USB,tu-vung-cntt,lesson-09,Bài 9: Windows và File Explorer</t>
-  </si>
-  <si>
-    <t>貼り付け,はりつけ,dán,名詞,N4,コピーした内容をここへ貼り付けます,Tôi dán nội dung đã sao chép vào đây,tu-vung-cntt,lesson-09,Bài 9: Windows và File Explorer</t>
-  </si>
-  <si>
-    <t>移動,いどう,di chuyển,名詞,N4,ファイルを別のフォルダへ移動しました,Tôi đã di chuyển tệp sang thư mục khác,tu-vung-cntt,lesson-09,Bài 9: Windows và File Explorer</t>
-  </si>
-  <si>
-    <t>名前変更,なまえへんこう,đổi tên,名詞,N3,ファイルの名前変更を行いました,Tôi đã đổi tên tệp,tu-vung-cntt,lesson-09,Bài 9: Windows và File Explorer</t>
-  </si>
-  <si>
-    <t>圧縮,あっしゅく,nén tệp,名詞,N3,大きなファイルを圧縮しました,Tôi đã nén tệp có dung lượng lớn,tu-vung-cntt,lesson-09,Bài 9: Windows và File Explorer</t>
-  </si>
-  <si>
-    <t>展開,てんかい,giải nén,名詞,N3,ZIPファイルを展開してください,Hãy giải nén tệp ZIP,tu-vung-cntt,lesson-09,Bài 9: Windows và File Explorer</t>
-  </si>
-  <si>
-    <t>ショートカット,しょーとかっと,lối tắt,名詞,N4,デスクトップにショートカットを作成しました,Tôi đã tạo lối tắt trên Desktop,tu-vung-cntt,lesson-09,Bài 9: Windows và File Explorer</t>
-  </si>
-  <si>
-    <t>ドライブ,どらいぶ,ổ đĩa,名詞,N4,Dドライブの空き容量を確認してください,Hãy kiểm tra dung lượng trống của ổ D,tu-vung-cntt,lesson-09,Bài 9: Windows và File Explorer</t>
-  </si>
-  <si>
-    <t>容量,ようりょう,dung lượng,名詞,N3,ディスクの容量が不足しています,Dung lượng ổ đĩa đang không đủ,tu-vung-cntt,lesson-09,Bài 9: Windows và File Explorer</t>
-  </si>
-  <si>
-    <t>読み取り専用,よみとりせんよう,chỉ đọc,名詞,N3,このファイルは読み取り専用です,Tệp này đang ở chế độ chỉ đọc,tu-vung-cntt,lesson-09,Bài 9: Windows và File Explorer</t>
-  </si>
-  <si>
-    <t>隠しファイル,かくしふぁいる,tệp ẩn,名詞,N3,隠しファイルを表示してください,Hãy hiển thị các tệp ẩn,tu-vung-cntt,lesson-09,Bài 9: Windows và File Explorer</t>
-  </si>
-  <si>
-    <t>権限,けんげん,quyền truy cập,名詞,N3,フォルダの権限を変更しました,Tôi đã thay đổi quyền của thư mục,tu-vung-cntt,lesson-09,Bài 9: Windows và File Explorer</t>
-  </si>
-  <si>
-    <t>ドメイン,どめいん,domain,名詞,N3,新しいパソコンをドメインへ参加させました,Tôi đã đưa máy tính mới vào domain,tu-vung-cntt,lesson-10,Bài 10: Domain và Active Directory</t>
-  </si>
-  <si>
-    <t>参加する,さんかする,tham gia,動詞,N4,パソコンを会社のドメインへ参加します,Tôi sẽ cho máy tính tham gia domain của công ty,tu-vung-cntt,lesson-10,Bài 10: Domain và Active Directory</t>
-  </si>
-  <si>
-    <t>離脱する,りだつする,rời khỏi,動詞,N3,古いパソコンをドメインから離脱しました,Tôi đã đưa máy tính cũ ra khỏi domain,tu-vung-cntt,lesson-10,Bài 10: Domain và Active Directory</t>
-  </si>
-  <si>
-    <t>管理者,かんりしゃ,quản trị viên,名詞,N3,管理者だけ設定を変更できます,Chỉ quản trị viên mới có thể thay đổi cài đặt,tu-vung-cntt,lesson-10,Bài 10: Domain và Active Directory</t>
-  </si>
-  <si>
-    <t>管理者権限,かんりしゃけんげん,quyền quản trị,名詞,N3,管理者権限で実行してください,Hãy chạy bằng quyền quản trị,tu-vung-cntt,lesson-10,Bài 10: Domain và Active Directory</t>
-  </si>
-  <si>
-    <t>利用権限,りようけんげん,quyền sử dụng,名詞,N3,利用権限を追加しました,Tôi đã thêm quyền sử dụng,tu-vung-cntt,lesson-10,Bài 10: Domain và Active Directory</t>
-  </si>
-  <si>
-    <t>組織単位,そしきたんい,OU; đơn vị tổ chức,名詞,N3,利用者を組織単位へ移動しました,Tôi đã chuyển người dùng vào OU,tu-vung-cntt,lesson-10,Bài 10: Domain và Active Directory</t>
-  </si>
-  <si>
-    <t>グループ,ぐるーぷ,nhóm,名詞,N5,新しいグループを作成しました,Tôi đã tạo một nhóm mới,tu-vung-cntt,lesson-10,Bài 10: Domain và Active Directory</t>
-  </si>
-  <si>
-    <t>追加,ついか,thêm,名詞,N4,利用者をグループへ追加しました,Tôi đã thêm người dùng vào nhóm,tu-vung-cntt,lesson-10,Bài 10: Domain và Active Directory</t>
-  </si>
-  <si>
-    <t>削除する,さくじょする,xóa,動詞,N4,不要なアカウントを削除しました,Tôi đã xóa tài khoản không cần thiết,tu-vung-cntt,lesson-10,Bài 10: Domain và Active Directory</t>
-  </si>
-  <si>
-    <t>有効化,ゆうこうか,kích hoạt,名詞,N3,アカウントを有効化しました,Tôi đã kích hoạt tài khoản,tu-vung-cntt,lesson-10,Bài 10: Domain và Active Directory</t>
-  </si>
-  <si>
-    <t>無効化,むこうか,vô hiệu hóa,名詞,N3,退職者のアカウントを無効化しました,Tôi đã vô hiệu hóa tài khoản của nhân viên nghỉ việc,tu-vung-cntt,lesson-10,Bài 10: Domain và Active Directory</t>
-  </si>
-  <si>
-    <t>パスワード変更,ぱすわーどへんこう,đổi mật khẩu,名詞,N4,利用者のパスワード変更を行いました,Tôi đã đổi mật khẩu cho người dùng,tu-vung-cntt,lesson-10,Bài 10: Domain và Active Directory</t>
-  </si>
-  <si>
-    <t>ロック,ろっく,khóa tài khoản,名詞,N3,アカウントがロックされました,Tài khoản đã bị khóa,tu-vung-cntt,lesson-10,Bài 10: Domain và Active Directory</t>
-  </si>
-  <si>
-    <t>ロック解除,ろっくかいじょ,mở khóa tài khoản,名詞,N3,管理者がロック解除しました,Quản trị viên đã mở khóa tài khoản,tu-vung-cntt,lesson-10,Bài 10: Domain và Active Directory</t>
-  </si>
-  <si>
-    <t>IPアドレス,あいぴーあどれす,địa chỉ IP,名詞,N4,IPアドレスを確認してから接続してください,Hãy kiểm tra địa chỉ IP trước khi kết nối,tu-vung-cntt,lesson-11,Bài 11: Mạng máy tính cơ bản</t>
-  </si>
-  <si>
-    <t>DNS,でぃーえぬえす,DNS,名詞,N3,DNSの設定が正しいか確認しました,Tôi đã kiểm tra cài đặt DNS có đúng hay không,tu-vung-cntt,lesson-11,Bài 11: Mạng máy tính cơ bản</t>
-  </si>
-  <si>
-    <t>DHCP,でぃーえいちしーぴー,DHCP,名詞,N3,DHCPからIPアドレスを取得しました,Máy đã nhận địa chỉ IP từ DHCP,tu-vung-cntt,lesson-11,Bài 11: Mạng máy tính cơ bản</t>
-  </si>
-  <si>
-    <t>ルーター,るーたー,bộ định tuyến,名詞,N4,ルーターを再起動してください,Hãy khởi động lại bộ định tuyến,tu-vung-cntt,lesson-11,Bài 11: Mạng máy tính cơ bản</t>
-  </si>
-  <si>
-    <t>スイッチ,すいっち,bộ chuyển mạch,名詞,N4,新しいスイッチを設置しました,Tôi đã lắp đặt bộ chuyển mạch mới,tu-vung-cntt,lesson-11,Bài 11: Mạng máy tính cơ bản</t>
-  </si>
-  <si>
-    <t>LAN,らん,mạng LAN,名詞,N4,LANケーブルを交換しました,Tôi đã thay cáp LAN,tu-vung-cntt,lesson-11,Bài 11: Mạng máy tính cơ bản</t>
-  </si>
-  <si>
-    <t>無線LAN,むせんらん,mạng không dây,名詞,N3,無線LANへ正常に接続できました,Đã kết nối thành công vào mạng không dây,tu-vung-cntt,lesson-11,Bài 11: Mạng máy tính cơ bản</t>
-  </si>
-  <si>
-    <t>有線,ゆうせん,kết nối có dây,名詞,N3,有線のほうが通信は安定しています,Kết nối có dây ổn định hơn,tu-vung-cntt,lesson-11,Bài 11: Mạng máy tính cơ bản</t>
-  </si>
-  <si>
-    <t>無線,むせん,kết nối không dây,名詞,N3,無線でインターネットを利用しています,Tôi sử dụng Internet qua kết nối không dây,tu-vung-cntt,lesson-11,Bài 11: Mạng máy tính cơ bản</t>
-  </si>
-  <si>
-    <t>通信速度,つうしんそくど,tốc độ truyền,名詞,N3,通信速度を測定してください,Hãy đo tốc độ truyền mạng,tu-vung-cntt,lesson-11,Bài 11: Mạng máy tính cơ bản</t>
-  </si>
-  <si>
-    <t>遅延,ちえん,độ trễ,名詞,N3,遅延が大きいので確認します,Độ trễ cao nên tôi sẽ kiểm tra,tu-vung-cntt,lesson-11,Bài 11: Mạng máy tính cơ bản</t>
-  </si>
-  <si>
-    <t>接続先,せつぞくさき,điểm kết nối,名詞,N3,接続先を間違えないでください,Hãy đừng nhầm điểm kết nối,tu-vung-cntt,lesson-11,Bài 11: Mạng máy tính cơ bản</t>
-  </si>
-  <si>
-    <t>固定IP,こていあいぴー,IP tĩnh,名詞,N3,サーバーは固定IPを使用しています,Máy chủ đang dùng IP tĩnh,tu-vung-cntt,lesson-11,Bài 11: Mạng máy tính cơ bản</t>
-  </si>
-  <si>
-    <t>動的IP,どうてきあいぴー,IP động,名詞,N3,この端末は動的IPです,Thiết bị này sử dụng IP động,tu-vung-cntt,lesson-11,Bài 11: Mạng máy tính cơ bản</t>
-  </si>
-  <si>
-    <t>疎通確認,そつうかくにん,kiểm tra kết nối,名詞,N3,サーバーとの疎通確認を行いました,Tôi đã kiểm tra kết nối với máy chủ,tu-vung-cntt,lesson-11,Bài 11: Mạng máy tính cơ bản</t>
-  </si>
-  <si>
-    <t>ping,ぴんぐ,lệnh ping,名詞,N4,pingでサーバーとの通信を確認します,Tôi kiểm tra kết nối tới máy chủ bằng ping,tu-vung-cntt,lesson-12,Bài 12: Công cụ kiểm tra mạng</t>
-  </si>
-  <si>
-    <t>応答,おうとう,phản hồi,名詞,N3,サーバーから応答がありません,Không có phản hồi từ máy chủ,tu-vung-cntt,lesson-12,Bài 12: Công cụ kiểm tra mạng</t>
-  </si>
-  <si>
-    <t>パケット,ぱけっと,gói tin,名詞,N3,パケットが途中で失われました,Gói tin đã bị mất trên đường truyền,tu-vung-cntt,lesson-12,Bài 12: Công cụ kiểm tra mạng</t>
-  </si>
-  <si>
-    <t>ポート,ぽーと,cổng mạng,名詞,N3,ポート番号を確認してください,Hãy kiểm tra số cổng mạng,tu-vung-cntt,lesson-12,Bài 12: Công cụ kiểm tra mạng</t>
-  </si>
-  <si>
-    <t>ポート番号,ぽーとばんごう,số cổng,名詞,N3,FTPは二十一番のポート番号を使います,FTP sử dụng cổng số hai mươi mốt,tu-vung-cntt,lesson-12,Bài 12: Công cụ kiểm tra mạng</t>
-  </si>
-  <si>
-    <t>タイムアウト,たいむあうと,hết thời gian chờ,名詞,N3,接続がタイムアウトしました,Kết nối đã bị hết thời gian chờ,tu-vung-cntt,lesson-12,Bài 12: Công cụ kiểm tra mạng</t>
-  </si>
-  <si>
-    <t>経路,けいろ,tuyến đường truyền,名詞,N3,通信経路を調査しています,Chúng tôi đang kiểm tra tuyến truyền dữ liệu,tu-vung-cntt,lesson-12,Bài 12: Công cụ kiểm tra mạng</t>
-  </si>
-  <si>
-    <t>tracert,とれーさーと,lệnh tracert,名詞,N3,tracertで通信経路を確認しました,Tôi đã kiểm tra tuyến truyền bằng tracert,tu-vung-cntt,lesson-12,Bài 12: Công cụ kiểm tra mạng</t>
-  </si>
-  <si>
-    <t>nslookup,えぬえするっくあっぷ,lệnh nslookup,名詞,N3,nslookupでDNSを確認してください,Hãy kiểm tra DNS bằng nslookup,tu-vung-cntt,lesson-12,Bài 12: Công cụ kiểm tra mạng</t>
-  </si>
-  <si>
-    <t>ipconfig,あいぴーこんふぃぐ,lệnh ipconfig,名詞,N3,ipconfigで設定を確認しました,Tôi đã kiểm tra cấu hình bằng ipconfig,tu-vung-cntt,lesson-12,Bài 12: Công cụ kiểm tra mạng</t>
-  </si>
-  <si>
-    <t>更新する,こうしんする,làm mới,動詞,N4,IPアドレスを更新してください,Hãy làm mới địa chỉ IP,tu-vung-cntt,lesson-12,Bài 12: Công cụ kiểm tra mạng</t>
-  </si>
-  <si>
-    <t>解放する,かいほうする,giải phóng,動詞,N3,現在のIPアドレスを解放しました,Tôi đã giải phóng địa chỉ IP hiện tại,tu-vung-cntt,lesson-12,Bài 12: Công cụ kiểm tra mạng</t>
-  </si>
-  <si>
-    <t>接続不能,せつぞくふのう,không thể kết nối,名詞,N3,現在サーバーは接続不能です,Hiện tại không thể kết nối tới máy chủ,tu-vung-cntt,lesson-12,Bài 12: Công cụ kiểm tra mạng</t>
-  </si>
-  <si>
-    <t>通信障害,つうしんしょうがい,sự cố mạng,名詞,N3,通信障害の原因を調査しています,Chúng tôi đang điều tra nguyên nhân sự cố mạng,tu-vung-cntt,lesson-12,Bài 12: Công cụ kiểm tra mạng</t>
-  </si>
-  <si>
-    <t>復旧作業,ふっきゅうさぎょう,công việc khôi phục,名詞,N3,復旧作業はもうすぐ完了します,Công việc khôi phục sẽ sớm hoàn tất,tu-vung-cntt,lesson-12,Bài 12: Công cụ kiểm tra mạng</t>
-  </si>
-  <si>
-    <t>共有フォルダ,きょうゆうふぉるだ,thư mục chia sẻ,名詞,N4,共有フォルダへ資料を保存してください,Hãy lưu tài liệu vào thư mục chia sẻ,tu-vung-cntt,lesson-13,Bài 13: File Server và chia sẻ dữ liệu</t>
-  </si>
-  <si>
-    <t>共有設定,きょうゆうせってい,cài đặt chia sẻ,名詞,N3,共有設定を変更しました,Tôi đã thay đổi cài đặt chia sẻ,tu-vung-cntt,lesson-13,Bài 13: File Server và chia sẻ dữ liệu</t>
-  </si>
-  <si>
-    <t>アクセス権,あくせすけん,quyền truy cập,名詞,N3,アクセス権を利用者へ追加しました,Tôi đã cấp quyền truy cập cho người dùng,tu-vung-cntt,lesson-13,Bài 13: File Server và chia sẻ dữ liệu</t>
-  </si>
-  <si>
-    <t>読み取り権限,よみとりけんげん,quyền đọc,名詞,N3,読み取り権限だけ設定しました,Tôi chỉ cấp quyền đọc,tu-vung-cntt,lesson-13,Bài 13: File Server và chia sẻ dữ liệu</t>
-  </si>
-  <si>
-    <t>書き込み権限,かきこみけんげん,quyền ghi,名詞,N3,書き込み権限を許可してください,Hãy cấp quyền ghi,tu-vung-cntt,lesson-13,Bài 13: File Server và chia sẻ dữ liệu</t>
-  </si>
-  <si>
-    <t>フルコントロール,ふるこんとろーる,toàn quyền,名詞,N3,管理者にフルコントロールを付与しました,Tôi đã cấp toàn quyền cho quản trị viên,tu-vung-cntt,lesson-13,Bài 13: File Server và chia sẻ dữ liệu</t>
-  </si>
-  <si>
-    <t>アクセス拒否,あくせすきょひ,từ chối truy cập,名詞,N3,アクセス拒否の設定を確認してください,Hãy kiểm tra cài đặt từ chối truy cập,tu-vung-cntt,lesson-13,Bài 13: File Server và chia sẻ dữ liệu</t>
-  </si>
-  <si>
-    <t>ネットワークドライブ,ねっとわーくどらいぶ,ổ đĩa mạng,名詞,N3,ネットワークドライブを割り当てました,Tôi đã ánh xạ ổ đĩa mạng,tu-vung-cntt,lesson-13,Bài 13: File Server và chia sẻ dữ liệu</t>
-  </si>
-  <si>
-    <t>割り当てる,わりあてる,ánh xạ; gán,動詞,N3,Zドライブを割り当てました,Tôi đã ánh xạ ổ Z,tu-vung-cntt,lesson-13,Bài 13: File Server và chia sẻ dữ liệu</t>
-  </si>
-  <si>
-    <t>ファイルサーバー,ふぁいるさーばー,file server,名詞,N3,ファイルサーバーへ接続してください,Hãy kết nối tới file server,tu-vung-cntt,lesson-13,Bài 13: File Server và chia sẻ dữ liệu</t>
-  </si>
-  <si>
-    <t>保存先,ほぞんさき,vị trí lưu,名詞,N3,保存先を間違えないでください,Hãy đừng chọn sai vị trí lưu,tu-vung-cntt,lesson-13,Bài 13: File Server và chia sẻ dữ liệu</t>
-  </si>
-  <si>
-    <t>空き容量,あきようりょう,dung lượng trống,名詞,N3,空き容量が少なくなっています,Dung lượng trống đang còn ít,tu-vung-cntt,lesson-13,Bài 13: File Server và chia sẻ dữ liệu</t>
-  </si>
-  <si>
-    <t>使用容量,しようようりょう,dung lượng đã dùng,名詞,N3,使用容量を毎週確認します,Tôi kiểm tra dung lượng đã sử dụng mỗi tuần,tu-vung-cntt,lesson-13,Bài 13: File Server và chia sẻ dữ liệu</t>
-  </si>
-  <si>
-    <t>所有者,しょゆうしゃ,chủ sở hữu,名詞,N3,フォルダの所有者を変更しました,Tôi đã thay đổi chủ sở hữu thư mục,tu-vung-cntt,lesson-13,Bài 13: File Server và chia sẻ dữ liệu</t>
-  </si>
-  <si>
-    <t>アクセスログ,あくせすろぐ,nhật ký truy cập,名詞,N3,アクセスログを確認しています,Tôi đang kiểm tra nhật ký truy cập,tu-vung-cntt,lesson-13,Bài 13: File Server và chia sẻ dữ liệu</t>
-  </si>
-  <si>
-    <t>FTP,えふてぃーぴー,FTP,名詞,N3,FTPでファイルを送信しました,Tôi đã gửi tệp qua FTP,tu-vung-cntt,lesson-14,Bài 14: FTP và truyền tệp</t>
-  </si>
-  <si>
-    <t>FileZilla,ふぁいるじら,FileZilla,名詞,N3,FileZillaでサーバーへ接続します,Tôi kết nối tới máy chủ bằng FileZilla,tu-vung-cntt,lesson-14,Bài 14: FTP và truyền tệp</t>
-  </si>
-  <si>
-    <t>FTPサーバー,えふてぃーぴーさーばー,máy chủ FTP,名詞,N3,FTPサーバーが正常に動作しています,Máy chủ FTP đang hoạt động bình thường,tu-vung-cntt,lesson-14,Bài 14: FTP và truyền tệp</t>
-  </si>
-  <si>
-    <t>転送,てんそう,truyền tệp,名詞,N3,大きなファイルを転送しています,Tôi đang truyền tệp có dung lượng lớn,tu-vung-cntt,lesson-14,Bài 14: FTP và truyền tệp</t>
-  </si>
-  <si>
-    <t>転送速度,てんそうそくど,tốc độ truyền,名詞,N3,転送速度が遅くなりました,Tốc độ truyền đã chậm lại,tu-vung-cntt,lesson-14,Bài 14: FTP và truyền tệp</t>
-  </si>
-  <si>
-    <t>アップロードする,あっぷろーどする,tải lên,動詞,N4,ファイルをサーバーへアップロードしました,Tôi đã tải tệp lên máy chủ,tu-vung-cntt,lesson-14,Bài 14: FTP và truyền tệp</t>
-  </si>
-  <si>
-    <t>ダウンロードする,だうんろーどする,tải xuống,動詞,N4,最新の資料をダウンロードしました,Tôi đã tải xuống tài liệu mới nhất,tu-vung-cntt,lesson-14,Bài 14: FTP và truyền tệp</t>
-  </si>
-  <si>
-    <t>転送完了,てんそうかんりょう,truyền xong,名詞,N3,転送完了の通知が表示されました,Thông báo truyền tệp hoàn tất đã hiển thị,tu-vung-cntt,lesson-14,Bài 14: FTP và truyền tệp</t>
-  </si>
-  <si>
-    <t>認証情報,にんしょうじょうほう,thông tin xác thực,名詞,N3,認証情報を入力してください,Hãy nhập thông tin xác thực,tu-vung-cntt,lesson-14,Bài 14: FTP và truyền tệp</t>
-  </si>
-  <si>
-    <t>接続情報,せつぞくじょうほう,thông tin kết nối,名詞,N3,接続情報を確認しました,Tôi đã kiểm tra thông tin kết nối,tu-vung-cntt,lesson-14,Bài 14: FTP và truyền tệp</t>
-  </si>
-  <si>
-    <t>ホスト名,ほすとめい,tên máy chủ,名詞,N3,ホスト名を正しく入力してください,Hãy nhập đúng tên máy chủ,tu-vung-cntt,lesson-14,Bài 14: FTP và truyền tệp</t>
-  </si>
-  <si>
-    <t>ユーザー名,ゆーざーめい,tên người dùng,名詞,N4,ユーザー名を忘れました,Tôi đã quên tên người dùng,tu-vung-cntt,lesson-14,Bài 14: FTP và truyền tệp</t>
-  </si>
-  <si>
-    <t>接続成功,せつぞくせいこう,kết nối thành công,名詞,N3,サーバーへの接続成功を確認しました,Tôi đã xác nhận kết nối thành công tới máy chủ,tu-vung-cntt,lesson-14,Bài 14: FTP và truyền tệp</t>
-  </si>
-  <si>
-    <t>接続失敗,せつぞくしっぱい,kết nối thất bại,名詞,N3,接続失敗の原因を調査しています,Chúng tôi đang điều tra nguyên nhân kết nối thất bại,tu-vung-cntt,lesson-14,Bài 14: FTP và truyền tệp</t>
-  </si>
-  <si>
-    <t>再接続,さいせつぞく,kết nối lại,名詞,N3,数分後に再接続してください,Hãy kết nối lại sau vài phút,tu-vung-cntt,lesson-14,Bài 14: FTP và truyền tệp</t>
-  </si>
-  <si>
-    <t>Windows Server,うぃんどうずさーばー,Windows Server,名詞,N3,Windows Serverを再起動しました,Tôi đã khởi động lại Windows Server,tu-vung-cntt,lesson-15,Bài 15: Windows Server cơ bản</t>
-  </si>
-  <si>
-    <t>Active Directory,あくてぃぶでぃれくとり,Active Directory,名詞,N3,Active Directoryで利用者を管理します,Quản lý người dùng bằng Active Directory,tu-vung-cntt,lesson-15,Bài 15: Windows Server cơ bản</t>
-  </si>
-  <si>
-    <t>ドメインコントローラー,どめいんこんとろーらー,Domain Controller,名詞,N3,新しいドメインコントローラーを追加しました,Tôi đã thêm Domain Controller mới,tu-vung-cntt,lesson-15,Bài 15: Windows Server cơ bản</t>
-  </si>
-  <si>
-    <t>レプリケーション,れぷりけーしょん,sao chép đồng bộ,名詞,N3,レプリケーションが正常に完了しました,Việc đồng bộ sao chép đã hoàn tất,tu-vung-cntt,lesson-15,Bài 15: Windows Server cơ bản</t>
-  </si>
-  <si>
-    <t>役割,やくわり,vai trò,名詞,N3,新しい役割をサーバーへ追加しました,Tôi đã thêm vai trò mới cho máy chủ,tu-vung-cntt,lesson-15,Bài 15: Windows Server cơ bản</t>
-  </si>
-  <si>
-    <t>機能,きのう,tính năng,名詞,N3,必要な機能を有効化してください,Hãy kích hoạt tính năng cần thiết,tu-vung-cntt,lesson-15,Bài 15: Windows Server cơ bản</t>
-  </si>
-  <si>
-    <t>イベントビューアー,いべんとびゅーあー,Event Viewer,名詞,N3,イベントビューアーでエラーを確認しました,Tôi đã kiểm tra lỗi bằng Event Viewer,tu-vung-cntt,lesson-15,Bài 15: Windows Server cơ bản</t>
-  </si>
-  <si>
-    <t>イベントログ,いべんとろぐ,nhật ký sự kiện,名詞,N3,イベントログを毎日確認しています,Tôi kiểm tra nhật ký sự kiện mỗi ngày,tu-vung-cntt,lesson-15,Bài 15: Windows Server cơ bản</t>
-  </si>
-  <si>
-    <t>サービス,さーびす,dịch vụ,名詞,N4,サービスが停止しています,Dịch vụ đang dừng hoạt động,tu-vung-cntt,lesson-15,Bài 15: Windows Server cơ bản</t>
-  </si>
-  <si>
-    <t>開始する,かいしする,khởi động,動詞,N4,サービスを開始してください,Hãy khởi động dịch vụ,tu-vung-cntt,lesson-15,Bài 15: Windows Server cơ bản</t>
-  </si>
-  <si>
-    <t>停止する,ていしする,dừng,動詞,N4,不要なサービスを停止しました,Tôi đã dừng dịch vụ không cần thiết,tu-vung-cntt,lesson-15,Bài 15: Windows Server cơ bản</t>
-  </si>
-  <si>
-    <t>自動起動,じどうきどう,khởi động tự động,名詞,N3,サービスを自動起動に設定しました,Tôi đã đặt dịch vụ khởi động tự động,tu-vung-cntt,lesson-15,Bài 15: Windows Server cơ bản</t>
-  </si>
-  <si>
-    <t>手動起動,しゅどうきどう,khởi động thủ công,名詞,N3,このサービスは手動起動です,Dịch vụ này khởi động thủ công,tu-vung-cntt,lesson-15,Bài 15: Windows Server cơ bản</t>
-  </si>
-  <si>
-    <t>サーバー名,さーばーめい,tên máy chủ,名詞,N3,サーバー名を変更しました,Tôi đã đổi tên máy chủ,tu-vung-cntt,lesson-15,Bài 15: Windows Server cơ bản</t>
-  </si>
-  <si>
-    <t>ホスト,ほすと,máy chủ; host,名詞,N3,ホストへ正常に接続しました,Tôi đã kết nối thành công tới host,tu-vung-cntt,lesson-15,Bài 15: Windows Server cơ bản</t>
-  </si>
-  <si>
-    <t>リモートデスクトップ,りもーとですくとっぷ,Remote Desktop,名詞,N3,リモートデスクトップで接続します,Tôi kết nối bằng Remote Desktop,tu-vung-cntt,lesson-16,Bài 16: Quản trị từ xa</t>
-  </si>
-  <si>
-    <t>リモート接続,りもーとせつぞく,kết nối từ xa,名詞,N3,リモート接続が切断されました,Kết nối từ xa đã bị ngắt,tu-vung-cntt,lesson-16,Bài 16: Quản trị từ xa</t>
-  </si>
-  <si>
-    <t>資格情報,しかくじょうほう,thông tin xác thực,名詞,N3,資格情報を保存しました,Tôi đã lưu thông tin xác thực,tu-vung-cntt,lesson-16,Bài 16: Quản trị từ xa</t>
-  </si>
-  <si>
-    <t>ログオン,ろぐおん,đăng nhập hệ thống,名詞,N3,ログオンできませんでした,Không thể đăng nhập hệ thống,tu-vung-cntt,lesson-16,Bài 16: Quản trị từ xa</t>
-  </si>
-  <si>
-    <t>ログオフ,ろぐおふ,đăng xuất hệ thống,名詞,N3,作業後にログオフしてください,Hãy đăng xuất sau khi hoàn thành công việc,tu-vung-cntt,lesson-16,Bài 16: Quản trị từ xa</t>
-  </si>
-  <si>
-    <t>セッション,せっしょん,phiên làm việc,名詞,N3,古いセッションを終了しました,Tôi đã kết thúc phiên làm việc cũ,tu-vung-cntt,lesson-16,Bài 16: Quản trị từ xa</t>
-  </si>
-  <si>
-    <t>切断,せつだん,ngắt kết nối,名詞,N3,ネットワークが突然切断されました,Mạng đã bị ngắt kết nối đột ngột,tu-vung-cntt,lesson-16,Bài 16: Quản trị từ xa</t>
-  </si>
-  <si>
-    <t>再接続する,さいせつぞくする,kết nối lại,動詞,N3,数分後に再接続してください,Hãy kết nối lại sau vài phút,tu-vung-cntt,lesson-16,Bài 16: Quản trị từ xa</t>
-  </si>
-  <si>
-    <t>管理ツール,かんりつーる,công cụ quản trị,名詞,N3,管理ツールを開いてください,Hãy mở công cụ quản trị,tu-vung-cntt,lesson-16,Bài 16: Quản trị từ xa</t>
-  </si>
-  <si>
-    <t>サーバーマネージャー,さーばーまねーじゃー,Server Manager,名詞,N3,サーバーマネージャーで設定を確認します,Tôi kiểm tra cài đặt bằng Server Manager,tu-vung-cntt,lesson-16,Bài 16: Quản trị từ xa</t>
-  </si>
-  <si>
-    <t>PowerShell,ぱわーしぇる,PowerShell,名詞,N3,PowerShellで設定を変更しました,Tôi đã thay đổi cài đặt bằng PowerShell,tu-vung-cntt,lesson-16,Bài 16: Quản trị từ xa</t>
-  </si>
-  <si>
-    <t>コマンドプロンプト,こまんどぷろんぷと,Command Prompt,名詞,N3,コマンドプロンプトを管理者で開きます,Tôi mở Command Prompt bằng quyền quản trị,tu-vung-cntt,lesson-16,Bài 16: Quản trị từ xa</t>
-  </si>
-  <si>
-    <t>実行する,じっこうする,thực thi,動詞,N4,このコマンドを実行してください,Hãy thực thi lệnh này,tu-vung-cntt,lesson-16,Bài 16: Quản trị từ xa</t>
-  </si>
-  <si>
-    <t>管理コンソール,かんりこんそーる,bảng điều khiển quản trị,名詞,N3,管理コンソールへログインしました,Tôi đã đăng nhập vào bảng điều khiển quản trị,tu-vung-cntt,lesson-16,Bài 16: Quản trị từ xa</t>
-  </si>
-  <si>
-    <t>管理画面,かんりがめん,màn hình quản trị,名詞,N3,管理画面から利用者を追加します,Tôi thêm người dùng từ màn hình quản trị,tu-vung-cntt,lesson-16,Bài 16: Quản trị từ xa</t>
-  </si>
-  <si>
-    <t>接続先サーバー,せつぞくさきさーばー,máy chủ đích,名詞,N3,接続先サーバーを選択してください,Hãy chọn máy chủ cần kết nối,tu-vung-cntt,lesson-16,Bài 16: Quản trị từ xa</t>
-  </si>
-  <si>
-    <t>Microsoft 365,まいくろそふとさんろくご,Microsoft 365,名詞,N3,Microsoft 365で毎日の業務を行います,Tôi làm việc hằng ngày bằng Microsoft 365,tu-vung-cntt,lesson-17,Bài 17: Microsoft 365 và Outlook</t>
-  </si>
-  <si>
-    <t>Outlook,あうとるっく,Outlook,名詞,N3,Outlookで会議の予定を確認しました,Tôi đã kiểm tra lịch họp bằng Outlook,tu-vung-cntt,lesson-17,Bài 17: Microsoft 365 và Outlook</t>
-  </si>
-  <si>
-    <t>受信トレイ,じゅしんとれい,hộp thư đến,名詞,N3,受信トレイに新しいメールがあります,Có email mới trong hộp thư đến,tu-vung-cntt,lesson-17,Bài 17: Microsoft 365 và Outlook</t>
-  </si>
-  <si>
-    <t>送信済み,そうしんずみ,thư đã gửi,名詞,N3,送信済みフォルダを確認してください,Hãy kiểm tra thư mục thư đã gửi,tu-vung-cntt,lesson-17,Bài 17: Microsoft 365 và Outlook</t>
-  </si>
-  <si>
-    <t>下書き,したがき,thư nháp,名詞,N3,メールを下書きとして保存しました,Tôi đã lưu email dưới dạng bản nháp,tu-vung-cntt,lesson-17,Bài 17: Microsoft 365 và Outlook</t>
-  </si>
-  <si>
-    <t>添付ファイル,てんぷふぁいる,tệp đính kèm,名詞,N3,添付ファイルを忘れないでください,Đừng quên tệp đính kèm,tu-vung-cntt,lesson-17,Bài 17: Microsoft 365 và Outlook</t>
-  </si>
-  <si>
-    <t>件名,けんめい,tiêu đề email,名詞,N3,件名を分かりやすく書いてください,Hãy viết tiêu đề rõ ràng,tu-vung-cntt,lesson-17,Bài 17: Microsoft 365 và Outlook</t>
-  </si>
-  <si>
-    <t>宛先,あてさき,người nhận,名詞,N3,宛先を確認して送信してください,Hãy kiểm tra người nhận trước khi gửi,tu-vung-cntt,lesson-17,Bài 17: Microsoft 365 và Outlook</t>
-  </si>
-  <si>
-    <t>CC,しーしー,CC,名詞,N3,CCに上司を追加しました,Tôi đã thêm cấp trên vào CC,tu-vung-cntt,lesson-17,Bài 17: Microsoft 365 và Outlook</t>
-  </si>
-  <si>
-    <t>BCC,びーしーしー,BCC,名詞,N3,BCCで送信してください,Hãy gửi bằng BCC,tu-vung-cntt,lesson-17,Bài 17: Microsoft 365 và Outlook</t>
-  </si>
-  <si>
-    <t>予定表,よていひょう,lịch làm việc,名詞,N3,予定表へ会議を追加しました,Tôi đã thêm cuộc họp vào lịch,tu-vung-cntt,lesson-17,Bài 17: Microsoft 365 và Outlook</t>
-  </si>
-  <si>
-    <t>会議依頼,かいぎいらい,lời mời họp,名詞,N2,会議依頼を全員へ送りました,Tôi đã gửi lời mời họp cho mọi người,tu-vung-cntt,lesson-17,Bài 17: Microsoft 365 và Outlook</t>
-  </si>
-  <si>
-    <t>予定,よてい,kế hoạch; lịch hẹn,名詞,N4,午後の予定を変更しました,Tôi đã thay đổi lịch buổi chiều,tu-vung-cntt,lesson-17,Bài 17: Microsoft 365 và Outlook</t>
-  </si>
-  <si>
-    <t>返信,へんしん,trả lời,名詞,N4,メールへ返信してください,Hãy trả lời email,tu-vung-cntt,lesson-17,Bài 17: Microsoft 365 và Outlook</t>
-  </si>
-  <si>
-    <t>転送する,てんそうする,chuyển tiếp,動詞,N4,このメールを転送してください,Hãy chuyển tiếp email này,tu-vung-cntt,lesson-17,Bài 17: Microsoft 365 và Outlook</t>
-  </si>
-  <si>
-    <t>Microsoft Teams,まいくろそふとちーむず,Microsoft Teams,名詞,N3,Microsoft Teamsで会議を始めます,Tôi bắt đầu cuộc họp bằng Microsoft Teams,tu-vung-cntt,lesson-18,Bài 18: Microsoft Teams</t>
-  </si>
-  <si>
-    <t>チーム,ちーむ,nhóm,名詞,N5,新しいチームを作成しました,Tôi đã tạo nhóm mới,tu-vung-cntt,lesson-18,Bài 18: Microsoft Teams</t>
-  </si>
-  <si>
-    <t>チャネル,ちゃねる,kênh,名詞,N3,開発チャネルへ参加しました,Tôi đã tham gia kênh phát triển,tu-vung-cntt,lesson-18,Bài 18: Microsoft Teams</t>
-  </si>
-  <si>
-    <t>投稿,とうこう,bài đăng,名詞,N3,新しい投稿を確認してください,Hãy kiểm tra bài đăng mới,tu-vung-cntt,lesson-18,Bài 18: Microsoft Teams</t>
-  </si>
-  <si>
-    <t>メンション,めんしょん,nhắc tên,名詞,N2,重要なのでメンションしました,Vì quan trọng nên tôi đã nhắc tên,tu-vung-cntt,lesson-18,Bài 18: Microsoft Teams</t>
-  </si>
-  <si>
-    <t>既読,きどく,đã đọc,名詞,N2,メッセージは既読になりました,Tin nhắn đã được đọc,tu-vung-cntt,lesson-18,Bài 18: Microsoft Teams</t>
-  </si>
-  <si>
-    <t>未読,みどく,chưa đọc,名詞,N2,未読メッセージが五件あります,Có năm tin nhắn chưa đọc,tu-vung-cntt,lesson-18,Bài 18: Microsoft Teams</t>
-  </si>
-  <si>
-    <t>通話,つうわ,cuộc gọi,名詞,N3,Teamsで通話を開始しました,Tôi đã bắt đầu cuộc gọi trên Teams,tu-vung-cntt,lesson-18,Bài 18: Microsoft Teams</t>
-  </si>
-  <si>
-    <t>ビデオ会議,びでおかいぎ,họp video,名詞,N3,ビデオ会議に参加してください,Hãy tham gia cuộc họp video,tu-vung-cntt,lesson-18,Bài 18: Microsoft Teams</t>
-  </si>
-  <si>
-    <t>背景,はいけい,hình nền,名詞,N2,背景をぼかしました,Tôi đã làm mờ hình nền,tu-vung-cntt,lesson-18,Bài 18: Microsoft Teams</t>
-  </si>
-  <si>
-    <t>マイク,まいく,micro,名詞,N5,マイクをオンにしてください,Hãy bật micro,tu-vung-cntt,lesson-18,Bài 18: Microsoft Teams</t>
-  </si>
-  <si>
-    <t>カメラ,かめら,camera,名詞,N5,カメラをオフにしました,Tôi đã tắt camera,tu-vung-cntt,lesson-18,Bài 18: Microsoft Teams</t>
-  </si>
-  <si>
-    <t>ミュート,みゅーと,tắt tiếng,名詞,N3,発表中はミュートにしてください,Hãy tắt tiếng khi người khác trình bày,tu-vung-cntt,lesson-18,Bài 18: Microsoft Teams</t>
-  </si>
-  <si>
-    <t>画面録画,がめんろくが,ghi màn hình,名詞,N2,画面録画を保存しました,Tôi đã lưu bản ghi màn hình,tu-vung-cntt,lesson-18,Bài 18: Microsoft Teams</t>
-  </si>
-  <si>
-    <t>共同編集,きょうどうへんしゅう,chỉnh sửa cộng tác,名詞,N2,資料を共同編集しています,Chúng tôi đang cùng chỉnh sửa tài liệu,tu-vung-cntt,lesson-18,Bài 18: Microsoft Teams</t>
-  </si>
-  <si>
-    <t>Google Workspace,ぐーぐるわーくすぺーす,Google Workspace,名詞,N3,Google Workspaceを会社で利用しています,Công ty đang sử dụng Google Workspace,tu-vung-cntt,lesson-19,Bài 19: Google Workspace</t>
-  </si>
-  <si>
-    <t>Gmail,じーめーる,Gmail,名詞,N5,Gmailでお客様へ返信しました,Tôi đã trả lời khách hàng bằng Gmail,tu-vung-cntt,lesson-19,Bài 19: Google Workspace</t>
-  </si>
-  <si>
-    <t>Google Drive,ぐーぐるどらいぶ,Google Drive,名詞,N5,資料をGoogle Driveへ保存しました,Tôi đã lưu tài liệu lên Google Drive,tu-vung-cntt,lesson-19,Bài 19: Google Workspace</t>
-  </si>
-  <si>
-    <t>Google Docs,ぐーぐるどきゅめんと,Google Docs,名詞,N3,Google Docsで報告書を作成します,Tôi tạo báo cáo bằng Google Docs,tu-vung-cntt,lesson-19,Bài 19: Google Workspace</t>
-  </si>
-  <si>
-    <t>Google Sheets,ぐーぐるしーつ,Google Sheets,名詞,N3,Google Sheetsで売上を管理しています,Tôi quản lý doanh thu bằng Google Sheets,tu-vung-cntt,lesson-19,Bài 19: Google Workspace</t>
-  </si>
-  <si>
-    <t>Google Slides,ぐーぐるすらいど,Google Slides,名詞,N3,Google Slidesで発表資料を作りました,Tôi đã tạo slide thuyết trình bằng Google Slides,tu-vung-cntt,lesson-19,Bài 19: Google Workspace</t>
-  </si>
-  <si>
-    <t>Google Meet,ぐーぐるみーと,Google Meet,名詞,N3,Google Meetで会議を始めます,Tôi bắt đầu cuộc họp bằng Google Meet,tu-vung-cntt,lesson-19,Bài 19: Google Workspace</t>
-  </si>
-  <si>
-    <t>共有リンク,きょうゆうりんく,liên kết chia sẻ,名詞,N3,共有リンクを送ってください,Hãy gửi liên kết chia sẻ,tu-vung-cntt,lesson-19,Bài 19: Google Workspace</t>
-  </si>
-  <si>
-    <t>閲覧権限,えつらんけんげん,quyền xem,名詞,N2,閲覧権限だけ設定しました,Tôi chỉ cấp quyền xem,tu-vung-cntt,lesson-19,Bài 19: Google Workspace</t>
-  </si>
-  <si>
-    <t>編集権限,へんしゅうけんげん,quyền chỉnh sửa,名詞,N2,編集権限を追加しました,Tôi đã cấp quyền chỉnh sửa,tu-vung-cntt,lesson-19,Bài 19: Google Workspace</t>
-  </si>
-  <si>
-    <t>コメント,こめんと,bình luận,名詞,N4,コメントを追加してください,Hãy thêm bình luận,tu-vung-cntt,lesson-19,Bài 19: Google Workspace</t>
-  </si>
-  <si>
-    <t>履歴,りれき,lịch sử,名詞,N2,変更履歴を確認しました,Tôi đã kiểm tra lịch sử thay đổi,tu-vung-cntt,lesson-19,Bài 19: Google Workspace</t>
-  </si>
-  <si>
-    <t>版,ばん,phiên bản,名詞,N2,以前の版へ戻しました,Tôi đã quay lại phiên bản trước,tu-vung-cntt,lesson-19,Bài 19: Google Workspace</t>
-  </si>
-  <si>
-    <t>同期,どうき,đồng bộ,名詞,N2,ファイルを自動同期しています,Tệp đang được đồng bộ tự động,tu-vung-cntt,lesson-19,Bài 19: Google Workspace</t>
-  </si>
-  <si>
-    <t>オフライン,おふらいん,ngoại tuyến,名詞,N4,オフラインでも編集できます,Có thể chỉnh sửa ngay cả khi ngoại tuyến,tu-vung-cntt,lesson-19,Bài 19: Google Workspace</t>
-  </si>
-  <si>
-    <t>プリンターキュー,ぷりんたーきゅー,hàng đợi in,名詞,N2,プリンターキューを確認してください,Hãy kiểm tra hàng đợi in,tu-vung-cntt,lesson-20,Bài 20: Máy in và Scan</t>
-  </si>
-  <si>
-    <t>印刷ジョブ,いんさつじょぶ,tác vụ in,名詞,N2,印刷ジョブを削除しました,Tôi đã xóa tác vụ in,tu-vung-cntt,lesson-20,Bài 20: Máy in và Scan</t>
-  </si>
-  <si>
-    <t>印刷待ち,いんさつまち,đang chờ in,名詞,N2,印刷待ちの状態が続いています,Trạng thái chờ in vẫn tiếp tục,tu-vung-cntt,lesson-20,Bài 20: Máy in và Scan</t>
-  </si>
-  <si>
-    <t>紙詰まり,かみづまり,kẹt giấy,名詞,N2,紙詰まりを取り除きました,Tôi đã xử lý tình trạng kẹt giấy,tu-vung-cntt,lesson-20,Bài 20: Máy in và Scan</t>
-  </si>
-  <si>
-    <t>トナー,となー,mực toner,名詞,N3,トナーを交換してください,Hãy thay hộp mực toner,tu-vung-cntt,lesson-20,Bài 20: Máy in và Scan</t>
-  </si>
-  <si>
-    <t>インク,いんく,mực in,名詞,N4,インクがなくなりました,Mực in đã hết,tu-vung-cntt,lesson-20,Bài 20: Máy in và Scan</t>
-  </si>
-  <si>
-    <t>給紙,きゅうし,cấp giấy,名詞,N2,給紙トレイを確認してください,Hãy kiểm tra khay cấp giấy,tu-vung-cntt,lesson-20,Bài 20: Máy in và Scan</t>
-  </si>
-  <si>
-    <t>両面印刷,りょうめんいんさつ,in hai mặt,名詞,N2,両面印刷を選択しました,Tôi đã chọn chế độ in hai mặt,tu-vung-cntt,lesson-20,Bài 20: Máy in và Scan</t>
-  </si>
-  <si>
-    <t>カラー印刷,からーいんさつ,in màu,名詞,N3,カラー印刷は禁止されています,In màu bị cấm,tu-vung-cntt,lesson-20,Bài 20: Máy in và Scan</t>
-  </si>
-  <si>
-    <t>白黒印刷,しろくろいんさつ,in trắng đen,名詞,N3,白黒印刷を利用してください,Hãy sử dụng chế độ in trắng đen,tu-vung-cntt,lesson-20,Bài 20: Máy in và Scan</t>
-  </si>
-  <si>
-    <t>複合機,ふくごうき,máy đa chức năng,名詞,N2,複合機でコピーしました,Tôi đã sao chép bằng máy đa chức năng,tu-vung-cntt,lesson-20,Bài 20: Máy in và Scan</t>
-  </si>
-  <si>
-    <t>スキャンする,すきゃんする,quét tài liệu,動詞,N4,契約書をPDFへスキャンしました,Tôi đã quét hợp đồng thành PDF,tu-vung-cntt,lesson-20,Bài 20: Máy in và Scan</t>
-  </si>
-  <si>
-    <t>ADF,えーでぃーえふ,bộ nạp giấy tự động,名詞,N1,ADFに原稿を入れてください,Hãy đặt tài liệu vào bộ nạp giấy tự động,tu-vung-cntt,lesson-20,Bài 20: Máy in và Scan</t>
-  </si>
-  <si>
-    <t>解像度,かいぞうど,độ phân giải,名詞,N2,解像度を三百dpiに設定しました,Tôi đã đặt độ phân giải thành ba trăm dpi,tu-vung-cntt,lesson-20,Bài 20: Máy in và Scan</t>
-  </si>
-  <si>
-    <t>OCR,おーしーあー,nhận dạng ký tự quang học,名詞,N1,OCRで文字を認識しました,Tôi đã nhận dạng văn bản bằng OCR,tu-vung-cntt,lesson-20,Bài 20: Máy in và Scan</t>
-  </si>
-  <si>
-    <t>TWAIN,ついん,chuẩn giao tiếp máy quét,名詞,N1,TWAINドライバーをインストールしてください,Hãy cài đặt trình điều khiển TWAIN,tu-vung-cntt,lesson-21,Bài 21: Scan và Driver</t>
-  </si>
-  <si>
-    <t>WIA,だぶりゅーあいえー,Windows Image Acquisition,名詞,N1,WIAサービスを再起動しました,Tôi đã khởi động lại dịch vụ WIA,tu-vung-cntt,lesson-21,Bài 21: Scan và Driver</t>
-  </si>
-  <si>
-    <t>ドライバー,どらいばー,trình điều khiển,名詞,N3,最新のドライバーをインストールしました,Tôi đã cài đặt trình điều khiển mới nhất,tu-vung-cntt,lesson-21,Bài 21: Scan và Driver</t>
-  </si>
-  <si>
-    <t>プリンタードライバー,ぷりんたーどらいばー,trình điều khiển máy in,名詞,N2,プリンタードライバーを更新してください,Hãy cập nhật trình điều khiển máy in,tu-vung-cntt,lesson-21,Bài 21: Scan và Driver</t>
-  </si>
-  <si>
-    <t>スキャナードライバー,すきゃなーどらいばー,trình điều khiển máy quét,名詞,N2,スキャナードライバーを再インストールしました,Tôi đã cài đặt lại trình điều khiển máy quét,tu-vung-cntt,lesson-21,Bài 21: Scan và Driver</t>
-  </si>
-  <si>
-    <t>デバイスマネージャー,でばいすまねーじゃー,Device Manager,名詞,N2,デバイスマネージャーを開いてください,Hãy mở Device Manager,tu-vung-cntt,lesson-21,Bài 21: Scan và Driver</t>
-  </si>
-  <si>
-    <t>認識する,にんしきする,nhận diện,動詞,N3,パソコンが機器を認識しません,Máy tính không nhận diện thiết bị,tu-vung-cntt,lesson-21,Bài 21: Scan và Driver</t>
-  </si>
-  <si>
-    <t>検出する,けんしゅつする,phát hiện,動詞,N2,新しい機器を検出しました,Tôi đã phát hiện thiết bị mới,tu-vung-cntt,lesson-21,Bài 21: Scan và Driver</t>
-  </si>
-  <si>
-    <t>更新する,こうしんする,cập nhật,動詞,N4,ドライバーを更新してください,Hãy cập nhật trình điều khiển,tu-vung-cntt,lesson-21,Bài 21: Scan và Driver</t>
-  </si>
-  <si>
-    <t>再インストールする,さいいんすとーるする,cài đặt lại,動詞,N3,ソフトを再インストールしました,Tôi đã cài đặt lại phần mềm,tu-vung-cntt,lesson-21,Bài 21: Scan và Driver</t>
-  </si>
-  <si>
-    <t>互換性,ごかんせい,tính tương thích,名詞,N1,互換性を確認してください,Hãy kiểm tra tính tương thích,tu-vung-cntt,lesson-21,Bài 21: Scan và Driver</t>
-  </si>
-  <si>
-    <t>署名,しょめい,chữ ký số,名詞,N1,署名済みドライバーを使用します,Sử dụng trình điều khiển đã được ký số,tu-vung-cntt,lesson-21,Bài 21: Scan và Driver</t>
-  </si>
-  <si>
-    <t>ファームウェア,ふぁーむうぇあ,firmware,名詞,N1,ファームウェアを更新しました,Tôi đã cập nhật firmware,tu-vung-cntt,lesson-21,Bài 21: Scan và Driver</t>
-  </si>
-  <si>
-    <t>バージョン,ばーじょん,phiên bản,名詞,N4,最新版のバージョンを使っています,Tôi đang sử dụng phiên bản mới nhất,tu-vung-cntt,lesson-21,Bài 21: Scan và Driver</t>
-  </si>
-  <si>
-    <t>互換モード,ごかんもーど,chế độ tương thích,名詞,N1,互換モードで実行しました,Tôi đã chạy ở chế độ tương thích,tu-vung-cntt,lesson-21,Bài 21: Scan và Driver</t>
-  </si>
-  <si>
-    <t>ウイルス,ういるす,virus máy tính,名詞,N4,ウイルスが検出されました,Đã phát hiện virus máy tính,tu-vung-cntt,lesson-22,Bài 22: Bảo mật và Antivirus</t>
-  </si>
-  <si>
-    <t>マルウェア,まるうぇあ,mã độc,名詞,N2,マルウェアを削除しました,Tôi đã xóa mã độc,tu-vung-cntt,lesson-22,Bài 22: Bảo mật và Antivirus</t>
-  </si>
-  <si>
-    <t>ランサムウェア,らんさむうぇあ,mã độc tống tiền,名詞,N1,ランサムウェアの攻撃を受けました,Hệ thống đã bị tấn công bởi ransomware,tu-vung-cntt,lesson-22,Bài 22: Bảo mật và Antivirus</t>
-  </si>
-  <si>
-    <t>スパイウェア,すぱいうぇあ,phần mềm gián điệp,名詞,N1,スパイウェアが見つかりました,Đã phát hiện phần mềm gián điệp,tu-vung-cntt,lesson-22,Bài 22: Bảo mật và Antivirus</t>
-  </si>
-  <si>
-    <t>ウイルス対策ソフト,ういるすたいさくそふと,phần mềm diệt virus,名詞,N2,ウイルス対策ソフトを更新しました,Tôi đã cập nhật phần mềm diệt virus,tu-vung-cntt,lesson-22,Bài 22: Bảo mật và Antivirus</t>
-  </si>
-  <si>
-    <t>リアルタイム保護,りあるたいむほご,bảo vệ thời gian thực,名詞,N1,リアルタイム保護を有効にしました,Tôi đã bật bảo vệ thời gian thực,tu-vung-cntt,lesson-22,Bài 22: Bảo mật và Antivirus</t>
-  </si>
-  <si>
-    <t>隔離する,かくりする,cách ly,動詞,N2,感染したファイルを隔離しました,Tôi đã cách ly tệp bị nhiễm,tu-vung-cntt,lesson-22,Bài 22: Bảo mật và Antivirus</t>
-  </si>
-  <si>
-    <t>感染,かんせん,lây nhiễm,名詞,N2,システムが感染しました,Hệ thống đã bị lây nhiễm,tu-vung-cntt,lesson-22,Bài 22: Bảo mật và Antivirus</t>
-  </si>
-  <si>
-    <t>駆除する,くじょする,loại bỏ; diệt,動詞,N1,ウイルスを完全に駆除しました,Tôi đã loại bỏ hoàn toàn virus,tu-vung-cntt,lesson-22,Bài 22: Bảo mật và Antivirus</t>
-  </si>
-  <si>
-    <t>脆弱性,ぜいじゃくせい,lỗ hổng bảo mật,名詞,N1,脆弱性を修正しました,Tôi đã vá lỗ hổng bảo mật,tu-vung-cntt,lesson-22,Bài 22: Bảo mật và Antivirus</t>
-  </si>
-  <si>
-    <t>セキュリティパッチ,せきゅりてぃぱっち,bản vá bảo mật,名詞,N1,セキュリティパッチを適用しました,Tôi đã áp dụng bản vá bảo mật,tu-vung-cntt,lesson-22,Bài 22: Bảo mật và Antivirus</t>
-  </si>
-  <si>
-    <t>不正アクセス,ふせいあくせす,truy cập trái phép,名詞,N1,不正アクセスを検知しました,Đã phát hiện truy cập trái phép,tu-vung-cntt,lesson-22,Bài 22: Bảo mật và Antivirus</t>
-  </si>
-  <si>
-    <t>侵入,しんにゅう,xâm nhập,名詞,N1,外部からの侵入を防ぎます,Ngăn chặn sự xâm nhập từ bên ngoài,tu-vung-cntt,lesson-22,Bài 22: Bảo mật và Antivirus</t>
-  </si>
-  <si>
-    <t>暗号化する,あんごうかする,mã hóa,動詞,N2,重要なデータを暗号化しました,Tôi đã mã hóa dữ liệu quan trọng,tu-vung-cntt,lesson-22,Bài 22: Bảo mật và Antivirus</t>
-  </si>
-  <si>
-    <t>復号する,ふくごうする,giải mã,動詞,N1,暗号を復号できません,Không thể giải mã dữ liệu đã mã hóa,tu-vung-cntt,lesson-22,Bài 22: Bảo mật và Antivirus</t>
-  </si>
-  <si>
-    <t>バックアップ,ばっくあっぷ,sao lưu,名詞,N3,毎日バックアップを実行しています,Tôi thực hiện sao lưu mỗi ngày,tu-vung-cntt,lesson-23,Bài 23: Backup và Recovery</t>
-  </si>
-  <si>
-    <t>復元,ふくげん,khôi phục,名詞,N2,バックアップから復元しました,Tôi đã khôi phục từ bản sao lưu,tu-vung-cntt,lesson-23,Bài 23: Backup và Recovery</t>
-  </si>
-  <si>
-    <t>リストア,りすとあ,phục hồi dữ liệu,名詞,N2,データをリストアしています,Tôi đang phục hồi dữ liệu,tu-vung-cntt,lesson-23,Bài 23: Backup và Recovery</t>
-  </si>
-  <si>
-    <t>増分バックアップ,ぞうぶんばっくあっぷ,sao lưu gia tăng,名詞,N1,増分バックアップを設定しました,Tôi đã cấu hình sao lưu gia tăng,tu-vung-cntt,lesson-23,Bài 23: Backup và Recovery</t>
-  </si>
-  <si>
-    <t>完全バックアップ,かんぜんばっくあっぷ,sao lưu toàn bộ,名詞,N2,完全バックアップを毎週実行します,Tôi thực hiện sao lưu toàn bộ mỗi tuần,tu-vung-cntt,lesson-23,Bài 23: Backup và Recovery</t>
-  </si>
-  <si>
-    <t>差分バックアップ,さぶんばっくあっぷ,sao lưu khác biệt,名詞,N1,差分バックアップを利用しています,Tôi đang sử dụng sao lưu khác biệt,tu-vung-cntt,lesson-23,Bài 23: Backup và Recovery</t>
-  </si>
-  <si>
-    <t>復元ポイント,ふくげんぽいんと,điểm khôi phục,名詞,N2,復元ポイントを作成しました,Tôi đã tạo điểm khôi phục,tu-vung-cntt,lesson-23,Bài 23: Backup và Recovery</t>
-  </si>
-  <si>
-    <t>スナップショット,すなっぷしょっと,ảnh chụp trạng thái,名詞,N1,仮想マシンのスナップショットを作成しました,Tôi đã tạo snapshot của máy ảo,tu-vung-cntt,lesson-23,Bài 23: Backup và Recovery</t>
-  </si>
-  <si>
-    <t>世代管理,せだいかんり,quản lý phiên bản sao lưu,名詞,N1,世代管理を有効にしました,Tôi đã bật quản lý phiên bản sao lưu,tu-vung-cntt,lesson-23,Bài 23: Backup và Recovery</t>
-  </si>
-  <si>
-    <t>保存期間,ほぞんきかん,thời gian lưu trữ,名詞,N2,保存期間を一年に設定しました,Tôi đã đặt thời gian lưu trữ là một năm,tu-vung-cntt,lesson-23,Bài 23: Backup và Recovery</t>
-  </si>
-  <si>
-    <t>バックアップ先,ばっくあっぷさき,vị trí sao lưu,名詞,N2,バックアップ先を変更してください,Hãy thay đổi nơi lưu bản sao lưu,tu-vung-cntt,lesson-23,Bài 23: Backup và Recovery</t>
-  </si>
-  <si>
-    <t>災害復旧,さいがいふっきゅう,khôi phục sau thảm họa,名詞,N1,災害復旧計画を作成しました,Tôi đã lập kế hoạch khôi phục sau thảm họa,tu-vung-cntt,lesson-23,Bài 23: Backup và Recovery</t>
-  </si>
-  <si>
-    <t>可用性,かようせい,tính sẵn sàng,名詞,N1,システムの可用性を向上させます,Nâng cao tính sẵn sàng của hệ thống,tu-vung-cntt,lesson-23,Bài 23: Backup và Recovery</t>
-  </si>
-  <si>
-    <t>冗長化,じょうちょうか,dự phòng hệ thống,名詞,N1,サーバーを冗長化しました,Tôi đã triển khai dự phòng máy chủ,tu-vung-cntt,lesson-23,Bài 23: Backup và Recovery</t>
-  </si>
-  <si>
-    <t>障害復旧,しょうがいふっきゅう,khôi phục sự cố,名詞,N1,障害復旧を開始しました,Tôi đã bắt đầu khôi phục sự cố,tu-vung-cntt,lesson-23,Bài 23: Backup và Recovery</t>
-  </si>
-  <si>
-    <t>Git,ぎっと,Git,名詞,N3,Gitでソースコードを管理します,Tôi quản lý mã nguồn bằng Git,tu-vung-cntt,lesson-24,Bài 24: Git và GitHub</t>
-  </si>
-  <si>
-    <t>GitHub,ぎっとはぶ,GitHub,名詞,N3,GitHubへコードを公開しました,Tôi đã đưa mã nguồn lên GitHub,tu-vung-cntt,lesson-24,Bài 24: Git và GitHub</t>
-  </si>
-  <si>
-    <t>リポジトリ,りぽじとり,kho mã nguồn,名詞,N2,新しいリポジトリを作成しました,Tôi đã tạo kho mã nguồn mới,tu-vung-cntt,lesson-24,Bài 24: Git và GitHub</t>
-  </si>
-  <si>
-    <t>コミット,こみっと,commit,名詞,N3,変更をコミットしました,Tôi đã commit các thay đổi,tu-vung-cntt,lesson-24,Bài 24: Git và GitHub</t>
-  </si>
-  <si>
-    <t>プッシュ,ぷっしゅ,push,名詞,N3,変更をリモートへプッシュしました,Tôi đã push thay đổi lên máy chủ,tu-vung-cntt,lesson-24,Bài 24: Git và GitHub</t>
-  </si>
-  <si>
-    <t>プル,ぷる,pull,名詞,N3,最新の変更をプルしてください,Hãy pull các thay đổi mới nhất,tu-vung-cntt,lesson-24,Bài 24: Git và GitHub</t>
-  </si>
-  <si>
-    <t>フェッチ,ふぇっち,fetch,名詞,N1,リモートからフェッチしました,Tôi đã fetch dữ liệu từ máy chủ,tu-vung-cntt,lesson-24,Bài 24: Git và GitHub</t>
-  </si>
-  <si>
-    <t>ブランチ,ぶらんち,nhánh,名詞,N3,新しいブランチを作成しました,Tôi đã tạo nhánh mới,tu-vung-cntt,lesson-24,Bài 24: Git và GitHub</t>
-  </si>
-  <si>
-    <t>マージ,まーじ,merge,名詞,N2,ブランチをマージしました,Tôi đã gộp các nhánh,tu-vung-cntt,lesson-24,Bài 24: Git và GitHub</t>
-  </si>
-  <si>
-    <t>マージコンフリクト,まーじこんふりくと,xung đột khi merge,名詞,N1,マージコンフリクトを解決しました,Tôi đã giải quyết xung đột khi merge,tu-vung-cntt,lesson-24,Bài 24: Git và GitHub</t>
-  </si>
-  <si>
-    <t>クローン,くろーん,clone,名詞,N2,リポジトリをクローンしました,Tôi đã clone kho mã nguồn,tu-vung-cntt,lesson-24,Bài 24: Git và GitHub</t>
-  </si>
-  <si>
-    <t>プルリクエスト,ぷるりくえすと,pull request,名詞,N1,プルリクエストを作成しました,Tôi đã tạo pull request,tu-vung-cntt,lesson-24,Bài 24: Git và GitHub</t>
-  </si>
-  <si>
-    <t>レビュー,れびゅー,review mã nguồn,名詞,N2,コードレビューをお願いします,Hãy review mã nguồn giúp tôi,tu-vung-cntt,lesson-24,Bài 24: Git và GitHub</t>
-  </si>
-  <si>
-    <t>コンフリクト,こんふりくと,xung đột,名詞,N2,コンフリクトを修正しました,Tôi đã sửa xung đột,tu-vung-cntt,lesson-24,Bài 24: Git và GitHub</t>
-  </si>
-  <si>
-    <t>チェックアウト,ちぇっくあうと,checkout,名詞,N1,別のブランチへチェックアウトしました,Tôi đã checkout sang nhánh khác,tu-vung-cntt,lesson-24,Bài 24: Git và GitHub</t>
-  </si>
-  <si>
-    <t>データベース,でーたべーす,cơ sở dữ liệu,名詞,N3,データベースへ接続しました,Tôi đã kết nối tới cơ sở dữ liệu,tu-vung-cntt,lesson-25,Bài 25: SQL và Database</t>
-  </si>
-  <si>
-    <t>DBMS,でぃーびーえむえす,hệ quản trị cơ sở dữ liệu,名詞,N1,DBMSを更新しました,Tôi đã cập nhật hệ quản trị cơ sở dữ liệu,tu-vung-cntt,lesson-25,Bài 25: SQL và Database</t>
-  </si>
-  <si>
-    <t>テーブル,てーぶる,bảng dữ liệu,名詞,N3,新しいテーブルを作成しました,Tôi đã tạo bảng mới,tu-vung-cntt,lesson-25,Bài 25: SQL và Database</t>
-  </si>
-  <si>
-    <t>レコード,れこーど,bản ghi,名詞,N3,レコードを追加しました,Tôi đã thêm bản ghi,tu-vung-cntt,lesson-25,Bài 25: SQL và Database</t>
-  </si>
-  <si>
-    <t>カラム,からむ,cột dữ liệu,名詞,N2,カラム名を変更しました,Tôi đã đổi tên cột,tu-vung-cntt,lesson-25,Bài 25: SQL và Database</t>
-  </si>
-  <si>
-    <t>主キー,しゅきー,khóa chính,名詞,N2,主キーを設定してください,Hãy thiết lập khóa chính,tu-vung-cntt,lesson-25,Bài 25: SQL và Database</t>
-  </si>
-  <si>
-    <t>外部キー,がいぶきー,khóa ngoại,名詞,N1,外部キーを追加しました,Tôi đã thêm khóa ngoại,tu-vung-cntt,lesson-25,Bài 25: SQL và Database</t>
-  </si>
-  <si>
-    <t>インデックス,chỉ mục,名詞,N2,インデックスを作成しました,Tôi đã tạo chỉ mục,tu-vung-cntt,lesson-25,Bài 25: SQL và Database</t>
-  </si>
-  <si>
-    <t>クエリ,くえり,truy vấn,名詞,N3,クエリを実行しました,Tôi đã thực thi truy vấn,tu-vung-cntt,lesson-25,Bài 25: SQL và Database</t>
-  </si>
-  <si>
-    <t>SQL,えすきゅーえる,SQL,名詞,N3,SQLを勉強しています,Tôi đang học SQL,tu-vung-cntt,lesson-25,Bài 25: SQL và Database</t>
-  </si>
-  <si>
-    <t>SELECT,せれくと,lệnh SELECT,名詞,N3,SELECT文を実行しました,Tôi đã chạy câu lệnh SELECT,tu-vung-cntt,lesson-25,Bài 25: SQL và Database</t>
-  </si>
-  <si>
-    <t>INSERT,いんさーと,lệnh INSERT,名詞,N3,INSERT文でデータを追加しました,Tôi đã thêm dữ liệu bằng INSERT,tu-vung-cntt,lesson-25,Bài 25: SQL và Database</t>
-  </si>
-  <si>
-    <t>UPDATE,あっぷでーと,lệnh UPDATE,名詞,N3,UPDATE文を実行しました,Tôi đã thực thi câu lệnh UPDATE,tu-vung-cntt,lesson-25,Bài 25: SQL và Database</t>
-  </si>
-  <si>
-    <t>DELETE,でりーと,lệnh DELETE,名詞,N3,不要なデータをDELETEしました,Tôi đã xóa dữ liệu không cần thiết,tu-vung-cntt,lesson-25,Bài 25: SQL và Database</t>
-  </si>
-  <si>
-    <t>JOIN,じょいん,lệnh JOIN,名詞,N2,JOINで二つの表を結合しました,Tôi đã nối hai bảng bằng JOIN,tu-vung-cntt,lesson-25,Bài 25: SQL và Database</t>
-  </si>
-  <si>
-    <t>トランザクション,とらんざくしょん,giao dịch,名詞,N1,トランザクションを開始しました,Tôi đã bắt đầu giao dịch,tu-vung-cntt,lesson-26,Bài 26: SQL nâng cao</t>
-  </si>
-  <si>
-    <t>コミット,こみっと,xác nhận giao dịch,名詞,N1,トランザクションをコミットしました,Tôi đã commit giao dịch,tu-vung-cntt,lesson-26,Bài 26: SQL nâng cao</t>
-  </si>
-  <si>
-    <t>ロールバック,ろーるばっく,hoàn tác giao dịch,名詞,N1,ロールバックを実行しました,Tôi đã rollback giao dịch,tu-vung-cntt,lesson-26,Bài 26: SQL nâng cao</t>
-  </si>
-  <si>
-    <t>ビュー,びゅー,khung nhìn,名詞,N2,ビューを作成しました,Tôi đã tạo view,tu-vung-cntt,lesson-26,Bài 26: SQL nâng cao</t>
-  </si>
-  <si>
-    <t>ストアドプロシージャ,すとあどぷろしーじゃ,stored procedure,名詞,N1,ストアドプロシージャを実行しました,Tôi đã chạy stored procedure,tu-vung-cntt,lesson-26,Bài 26: SQL nâng cao</t>
-  </si>
-  <si>
-    <t>トリガー,とりがー,trigger,名詞,N1,トリガーを追加しました,Tôi đã thêm trigger,tu-vung-cntt,lesson-26,Bài 26: SQL nâng cao</t>
-  </si>
-  <si>
-    <t>正規化,せいきか,chuẩn hóa dữ liệu,名詞,N1,データベースを正規化しました,Tôi đã chuẩn hóa cơ sở dữ liệu,tu-vung-cntt,lesson-26,Bài 26: SQL nâng cao</t>
-  </si>
-  <si>
-    <t>制約,せいやく,ràng buộc,名詞,N2,制約を追加してください,Hãy thêm ràng buộc,tu-vung-cntt,lesson-26,Bài 26: SQL nâng cao</t>
-  </si>
-  <si>
-    <t>一意制約,ゆいいせいやく,ràng buộc duy nhất,名詞,N1,一意制約を設定しました,Tôi đã thiết lập ràng buộc duy nhất,tu-vung-cntt,lesson-26,Bài 26: SQL nâng cao</t>
-  </si>
-  <si>
-    <t>NULL,なる,giá trị NULL,名詞,N2,NULLは許可されていません,Không cho phép giá trị NULL,tu-vung-cntt,lesson-26,Bài 26: SQL nâng cao</t>
-  </si>
-  <si>
-    <t>デッドロック,でっどろっく,bế tắc giao dịch,名詞,N1,デッドロックが発生しました,Đã xảy ra deadlock,tu-vung-cntt,lesson-26,Bài 26: SQL nâng cao</t>
-  </si>
-  <si>
-    <t>最適化,さいてきか,tối ưu hóa,名詞,N1,クエリを最適化しました,Tôi đã tối ưu hóa truy vấn,tu-vung-cntt,lesson-26,Bài 26: SQL nâng cao</t>
-  </si>
-  <si>
-    <t>実行計画,じっこうけいかく,kế hoạch thực thi,名詞,N1,実行計画を分析しました,Tôi đã phân tích execution plan,tu-vung-cntt,lesson-26,Bài 26: SQL nâng cao</t>
-  </si>
-  <si>
-    <t>Linux,りなっくす,Linux,名詞,N3,Linuxサーバーを管理しています,Tôi đang quản lý máy chủ Linux,tu-vung-cntt,lesson-27,Bài 27: Linux cơ bản</t>
-  </si>
-  <si>
-    <t>ディストリビューション,でぃすとりびゅーしょん,bản phân phối Linux,名詞,N1,Ubuntuは人気のディストリビューションです,Ubuntu là bản phân phối phổ biến,tu-vung-cntt,lesson-27,Bài 27: Linux cơ bản</t>
-  </si>
-  <si>
-    <t>Ubuntu,うぶんとぅ,Ubuntu,名詞,N3,Ubuntuをインストールしました,Tôi đã cài Ubuntu,tu-vung-cntt,lesson-27,Bài 27: Linux cơ bản</t>
-  </si>
-  <si>
-    <t>CentOS,せんとおーえす,CentOS,名詞,N2,CentOSを使用しています,Tôi đang sử dụng CentOS,tu-vung-cntt,lesson-27,Bài 27: Linux cơ bản</t>
-  </si>
-  <si>
-    <t>ターミナル,たーみなる,terminal,名詞,N3,ターミナルを開いてください,Hãy mở terminal,tu-vung-cntt,lesson-27,Bài 27: Linux cơ bản</t>
-  </si>
-  <si>
-    <t>シェル,しぇる,shell,名詞,N2,Bashシェルを使っています,Tôi đang sử dụng Bash shell,tu-vung-cntt,lesson-27,Bài 27: Linux cơ bản</t>
-  </si>
-  <si>
-    <t>Bash,ばっしゅ,Bash,名詞,N2,Bashでスクリプトを書きます,Tôi viết script bằng Bash,tu-vung-cntt,lesson-27,Bài 27: Linux cơ bản</t>
-  </si>
-  <si>
-    <t>コマンド,こまんど,lệnh,名詞,N5,コマンドを入力してください,Hãy nhập lệnh,tu-vung-cntt,lesson-27,Bài 27: Linux cơ bản</t>
-  </si>
-  <si>
-    <t>ディレクトリ,でぃれくとり,thư mục,名詞,N3,ディレクトリを移動しました,Tôi đã chuyển thư mục,tu-vung-cntt,lesson-27,Bài 27: Linux cơ bản</t>
-  </si>
-  <si>
-    <t>カレントディレクトリ,かれんとでぃれくとり,thư mục hiện tại,名詞,N2,カレントディレクトリを確認します,Tôi kiểm tra thư mục hiện tại,tu-vung-cntt,lesson-27,Bài 27: Linux cơ bản</t>
-  </si>
-  <si>
-    <t>権限,けんげん,quyền,名詞,N3,権限を変更しました,Tôi đã thay đổi quyền,tu-vung-cntt,lesson-27,Bài 27: Linux cơ bản</t>
-  </si>
-  <si>
-    <t>所有者,しょゆうしゃ,chủ sở hữu,名詞,N3,所有者を変更してください,Hãy thay đổi chủ sở hữu,tu-vung-cntt,lesson-27,Bài 27: Linux cơ bản</t>
-  </si>
-  <si>
-    <t>chmod,ちゃもっど,lệnh chmod,名詞,N2,chmodで権限を変更しました,Tôi đã thay đổi quyền bằng chmod,tu-vung-cntt,lesson-27,Bài 27: Linux cơ bản</t>
-  </si>
-  <si>
-    <t>chown,ちゃうん,lệnh chown,名詞,N2,chownを実行しました,Tôi đã thực hiện lệnh chown,tu-vung-cntt,lesson-27,Bài 27: Linux cơ bản</t>
-  </si>
-  <si>
-    <t>sudo,すどう,lệnh sudo,名詞,N3,sudoでコマンドを実行しました,Tôi đã chạy lệnh bằng sudo,tu-vung-cntt,lesson-27,Bài 27: Linux cơ bản</t>
-  </si>
-  <si>
-    <t>root,るーと,tài khoản root,名詞,N3,rootでログインしました,Tôi đã đăng nhập bằng tài khoản root,tu-vung-cntt,lesson-28,Bài 28: Linux nâng cao</t>
-  </si>
-  <si>
-    <t>パーミッション,ぱーみっしょん,permission,名詞,N2,パーミッションを確認しました,Tôi đã kiểm tra permission,tu-vung-cntt,lesson-28,Bài 28: Linux nâng cao</t>
-  </si>
-  <si>
-    <t>プロセス,ぷろせす,tiến trình,名詞,N2,不要なプロセスを終了しました,Tôi đã kết thúc tiến trình không cần thiết,tu-vung-cntt,lesson-28,Bài 28: Linux nâng cao</t>
-  </si>
-  <si>
-    <t>デーモン,でーもん,daemon,名詞,N1,デーモンが起動しています,Daemon đang chạy,tu-vung-cntt,lesson-28,Bài 28: Linux nâng cao</t>
-  </si>
-  <si>
-    <t>systemctl,しすてむしーてぃーえる,lệnh systemctl,名詞,N1,systemctlでサービスを再起動しました,Tôi đã khởi động lại dịch vụ bằng systemctl,tu-vung-cntt,lesson-28,Bài 28: Linux nâng cao</t>
-  </si>
-  <si>
-    <t>cron,くろん,cron,名詞,N1,cronで自動実行を設定しました,Tôi đã thiết lập chạy tự động bằng cron,tu-vung-cntt,lesson-28,Bài 28: Linux nâng cao</t>
-  </si>
-  <si>
-    <t>crontab,くろんたぶ,bảng lịch cron,名詞,N1,crontabを編集しました,Tôi đã chỉnh sửa crontab,tu-vung-cntt,lesson-28,Bài 28: Linux nâng cao</t>
-  </si>
-  <si>
-    <t>grep,ぐれっぷ,lệnh grep,名詞,N2,grepで文字列を検索しました,Tôi đã tìm chuỗi bằng grep,tu-vung-cntt,lesson-28,Bài 28: Linux nâng cao</t>
-  </si>
-  <si>
-    <t>find,ふぁいんど,lệnh find,名詞,N3,findでファイルを検索しました,Tôi đã tìm tệp bằng find,tu-vung-cntt,lesson-28,Bài 28: Linux nâng cao</t>
-  </si>
-  <si>
-    <t>vi,ゔぃーあい,trình soạn thảo vi,名詞,N2,viで設定ファイルを編集しました,Tôi đã chỉnh sửa tệp cấu hình bằng vi,tu-vung-cntt,lesson-28,Bài 28: Linux nâng cao</t>
-  </si>
-  <si>
-    <t>vim,ゔぃむ,trình soạn thảo Vim,名詞,N2,vimでスクリプトを書いています,Tôi đang viết script bằng Vim,tu-vung-cntt,lesson-28,Bài 28: Linux nâng cao</t>
-  </si>
-  <si>
-    <t>シンボリックリンク,しんぼりっくりんく,liên kết tượng trưng,名詞,N1,シンボリックリンクを作成しました,Tôi đã tạo symbolic link,tu-vung-cntt,lesson-28,Bài 28: Linux nâng cao</t>
-  </si>
-  <si>
-    <t>パイプ,ぱいぷ,pipe,名詞,N2,パイプで結果を渡しました,Tôi đã truyền kết quả bằng pipe,tu-vung-cntt,lesson-28,Bài 28: Linux nâng cao</t>
-  </si>
-  <si>
-    <t>リダイレクト,りだいれくと,chuyển hướng,名詞,N2,出力をファイルへリダイレクトしました,Tôi đã chuyển hướng đầu ra vào tệp,tu-vung-cntt,lesson-28,Bài 28: Linux nâng cao</t>
-  </si>
-  <si>
-    <t>AWS,えーだぶりゅーえす,AWS,名詞,N3,AWSでシステムを運用しています,Tôi đang vận hành hệ thống trên AWS,tu-vung-cntt,lesson-29,Bài 29: Cloud Computing</t>
-  </si>
-  <si>
-    <t>Microsoft Azure,まいくろそふとあじゅーる,Microsoft Azure,名詞,N3,Azureへ仮想マシンを作成しました,Tôi đã tạo máy ảo trên Azure,tu-vung-cntt,lesson-29,Bài 29: Cloud Computing</t>
-  </si>
-  <si>
-    <t>Google Cloud,ぐーぐるくらうど,Google Cloud,名詞,N3,Google Cloudを勉強しています,Tôi đang học Google Cloud,tu-vung-cntt,lesson-29,Bài 29: Cloud Computing</t>
-  </si>
-  <si>
-    <t>クラウド,くらうど,điện toán đám mây,名詞,N3,クラウドへデータを移行しました,Tôi đã chuyển dữ liệu lên đám mây,tu-vung-cntt,lesson-29,Bài 29: Cloud Computing</t>
-  </si>
-  <si>
-    <t>オンプレミス,おんぷれみす,hạ tầng tại chỗ,名詞,N1,オンプレミス環境を運用しています,Tôi đang vận hành hạ tầng tại chỗ,tu-vung-cntt,lesson-29,Bài 29: Cloud Computing</t>
-  </si>
-  <si>
-    <t>仮想マシン,かそうましん,máy ảo,名詞,N2,仮想マシンを起動しました,Tôi đã khởi động máy ảo,tu-vung-cntt,lesson-29,Bài 29: Cloud Computing</t>
-  </si>
-  <si>
-    <t>インスタンス,いんすたんす,instance,名詞,N2,新しいインスタンスを作成しました,Tôi đã tạo instance mới,tu-vung-cntt,lesson-29,Bài 29: Cloud Computing</t>
-  </si>
-  <si>
-    <t>ストレージ,すとれーじ,lưu trữ,名詞,N3,クラウドストレージを利用しています,Tôi đang sử dụng lưu trữ đám mây,tu-vung-cntt,lesson-29,Bài 29: Cloud Computing</t>
-  </si>
-  <si>
-    <t>オブジェクトストレージ,おぶじぇくとすとれーじ,lưu trữ đối tượng,名詞,N1,オブジェクトストレージへ保存しました,Tôi đã lưu vào object storage,tu-vung-cntt,lesson-29,Bài 29: Cloud Computing</t>
-  </si>
-  <si>
-    <t>バケット,ばけっと,bucket,名詞,N1,新しいバケットを作成しました,Tôi đã tạo bucket mới,tu-vung-cntt,lesson-29,Bài 29: Cloud Computing</t>
-  </si>
-  <si>
-    <t>リージョン,りーじょん,vùng dữ liệu,名詞,N2,東京リージョンを選択しました,Tôi đã chọn vùng Tokyo,tu-vung-cntt,lesson-29,Bài 29: Cloud Computing</t>
-  </si>
-  <si>
-    <t>アベイラビリティゾーン,あべいらびりてぃぞーん,vùng khả dụng,名詞,N1,別のアベイラビリティゾーンへ配置しました,Tôi đã triển khai sang vùng khả dụng khác,tu-vung-cntt,lesson-29,Bài 29: Cloud Computing</t>
-  </si>
-  <si>
-    <t>スケーリング,すけーりんぐ,mở rộng quy mô,名詞,N1,自動スケーリングを設定しました,Tôi đã thiết lập tự động mở rộng,tu-vung-cntt,lesson-29,Bài 29: Cloud Computing</t>
-  </si>
-  <si>
-    <t>ロードバランサー,ろーどばらんさー,bộ cân bằng tải,名詞,N1,ロードバランサーを導入しました,Tôi đã triển khai bộ cân bằng tải,tu-vung-cntt,lesson-29,Bài 29: Cloud Computing</t>
-  </si>
-  <si>
-    <t>クラウド移行,くらうどいこう,di chuyển lên cloud,名詞,N1,クラウド移行を計画しています,Tôi đang lên kế hoạch chuyển lên cloud,tu-vung-cntt,lesson-29,Bài 29: Cloud Computing</t>
-  </si>
-  <si>
-    <t>AI,えーあい,trí tuệ nhân tạo,名詞,N4,AIを仕事で活用しています,Tôi đang ứng dụng AI trong công việc,tu-vung-cntt,lesson-30,Bài 30: AI và Machine Learning</t>
-  </si>
-  <si>
-    <t>人工知能,じんこうちのう,trí tuệ nhân tạo,名詞,N2,人工知能について学んでいます,Tôi đang học về trí tuệ nhân tạo,tu-vung-cntt,lesson-30,Bài 30: AI và Machine Learning</t>
-  </si>
-  <si>
-    <t>機械学習,きかいがくしゅう,máy học,名詞,N2,機械学習モデルを開発しました,Tôi đã phát triển mô hình machine learning,tu-vung-cntt,lesson-30,Bài 30: AI và Machine Learning</t>
-  </si>
-  <si>
-    <t>深層学習,しんそうがくしゅう,học sâu,名詞,N1,深層学習を研究しています,Tôi đang nghiên cứu deep learning,tu-vung-cntt,lesson-30,Bài 30: AI và Machine Learning</t>
-  </si>
-  <si>
-    <t>ニューラルネットワーク,にゅーらるねっとわーく,mạng nơ ron,名詞,N1,ニューラルネットワークを学習しました,Tôi đã huấn luyện mạng nơ ron,tu-vung-cntt,lesson-30,Bài 30: AI và Machine Learning</t>
-  </si>
-  <si>
-    <t>モデル,もでる,mô hình,名詞,N3,新しいモデルを評価しました,Tôi đã đánh giá mô hình mới,tu-vung-cntt,lesson-30,Bài 30: AI và Machine Learning</t>
-  </si>
-  <si>
-    <t>学習データ,がくしゅうでーた,dữ liệu huấn luyện,名詞,N2,学習データを追加しました,Tôi đã bổ sung dữ liệu huấn luyện,tu-vung-cntt,lesson-30,Bài 30: AI và Machine Learning</t>
-  </si>
-  <si>
-    <t>推論,すいろん,suy luận AI,名詞,N1,モデルで推論を実行しました,Tôi đã chạy suy luận bằng mô hình,tu-vung-cntt,lesson-30,Bài 30: AI và Machine Learning</t>
-  </si>
-  <si>
-    <t>精度,せいど,độ chính xác,名詞,N2,モデルの精度が向上しました,Độ chính xác của mô hình đã được cải thiện,tu-vung-cntt,lesson-30,Bài 30: AI và Machine Learning</t>
-  </si>
-  <si>
-    <t>訓練する,くんれんする,huấn luyện,動詞,N2,モデルを訓練しています,Tôi đang huấn luyện mô hình,tu-vung-cntt,lesson-30,Bài 30: AI và Machine Learning</t>
-  </si>
-  <si>
-    <t>推論する,すいろんする,suy luận,動詞,N1,画像から結果を推論しました,Tôi đã suy luận kết quả từ hình ảnh,tu-vung-cntt,lesson-30,Bài 30: AI và Machine Learning</t>
-  </si>
-  <si>
-    <t>特徴量,とくちょうりょう,đặc trưng dữ liệu,名詞,N1,特徴量を抽出しました,Tôi đã trích xuất đặc trưng dữ liệu,tu-vung-cntt,lesson-30,Bài 30: AI và Machine Learning</t>
-  </si>
-  <si>
-    <t>データセット,でーたせっと,tập dữ liệu,名詞,N2,データセットを分割しました,Tôi đã chia tập dữ liệu,tu-vung-cntt,lesson-30,Bài 30: AI và Machine Learning</t>
-  </si>
-  <si>
-    <t>過学習,かがくしゅう,quá khớp,名詞,N1,モデルが過学習しています,Mô hình đang bị overfitting,tu-vung-cntt,lesson-30,Bài 30: AI và Machine Learning</t>
-  </si>
-  <si>
-    <t>汎化性能,はんかせいのう,khả năng tổng quát hóa,名詞,N1,汎化性能を改善しました,Tôi đã cải thiện khả năng tổng quát hóa,tu-vung-cntt,lesson-30,Bài 30: AI và Machine Learning</t>
-  </si>
-  <si>
-    <t>フロントエンド,ふろんとえんど,frontend,名詞,N2,フロントエンドを担当しています,Tôi phụ trách frontend,tu-vung-cntt,lesson-31,Bài 31: Phát triển phần mềm hiện đại</t>
-  </si>
-  <si>
-    <t>バックエンド,ばっくえんど,backend,名詞,N2,バックエンドを開発しています,Tôi đang phát triển backend,tu-vung-cntt,lesson-31,Bài 31: Phát triển phần mềm hiện đại</t>
-  </si>
-  <si>
-    <t>フルスタック,ふるすたっく,full stack,名詞,N1,フルスタック開発者を目指しています,Tôi đang hướng tới trở thành full stack developer,tu-vung-cntt,lesson-31,Bài 31: Phát triển phần mềm hiện đại</t>
-  </si>
-  <si>
-    <t>API,えーぴーあい,API,名詞,N3,APIを利用して連携しました,Tôi đã tích hợp bằng API,tu-vung-cntt,lesson-31,Bài 31: Phát triển phần mềm hiện đại</t>
-  </si>
-  <si>
-    <t>REST API,れすとえーぴーあい,REST API,名詞,N2,REST APIを設計しました,Tôi đã thiết kế REST API,tu-vung-cntt,lesson-31,Bài 31: Phát triển phần mềm hiện đại</t>
-  </si>
-  <si>
-    <t>JSON,じぇいそん,JSON,名詞,N3,JSON形式で送信しました,Tôi đã gửi dưới định dạng JSON,tu-vung-cntt,lesson-31,Bài 31: Phát triển phần mềm hiện đại</t>
-  </si>
-  <si>
-    <t>XML,えっくすえむえる,XML,名詞,N2,XMLファイルを解析しました,Tôi đã phân tích tệp XML,tu-vung-cntt,lesson-31,Bài 31: Phát triển phần mềm hiện đại</t>
-  </si>
-  <si>
-    <t>SDK,えすでぃーけー,SDK,名詞,N2,SDKを導入しました,Tôi đã tích hợp SDK,tu-vung-cntt,lesson-31,Bài 31: Phát triển phần mềm hiện đại</t>
-  </si>
-  <si>
-    <t>ライブラリ,らいぶらり,thư viện,名詞,N3,新しいライブラリを追加しました,Tôi đã thêm thư viện mới,tu-vung-cntt,lesson-31,Bài 31: Phát triển phần mềm hiện đại</t>
-  </si>
-  <si>
-    <t>フレームワーク,ふれーむわーく,framework,名詞,N2,新しいフレームワークを勉強しています,Tôi đang học framework mới,tu-vung-cntt,lesson-31,Bài 31: Phát triển phần mềm hiện đại</t>
-  </si>
-  <si>
-    <t>デバッグ,でばっぐ,gỡ lỗi,名詞,N3,プログラムをデバッグしました,Tôi đã gỡ lỗi chương trình,tu-vung-cntt,lesson-31,Bài 31: Phát triển phần mềm hiện đại</t>
-  </si>
-  <si>
-    <t>ビルド,びるど,build,名詞,N2,プロジェクトをビルドしました,Tôi đã build dự án,tu-vung-cntt,lesson-31,Bài 31: Phát triển phần mềm hiện đại</t>
-  </si>
-  <si>
-    <t>デプロイ,でぷろい,triển khai,名詞,N2,本番環境へデプロイしました,Tôi đã triển khai lên môi trường production,tu-vung-cntt,lesson-31,Bài 31: Phát triển phần mềm hiện đại</t>
-  </si>
-  <si>
-    <t>CI,しーあい,Continuous Integration,名詞,N1,CIを導入しました,Tôi đã triển khai CI,tu-vung-cntt,lesson-31,Bài 31: Phát triển phần mềm hiện đại</t>
-  </si>
-  <si>
-    <t>CD,しーでぃー,Continuous Delivery,名詞,N1,CDを自動化しました,Tôi đã tự động hóa CD,tu-vung-cntt,lesson-31,Bài 31: Phát triển phần mềm hiện đại</t>
-  </si>
-  <si>
-    <t>DevOps,でぶおぷす,DevOps,名詞,N1,DevOpsを実践しています,Tôi đang áp dụng DevOps,tu-vung-cntt,lesson-32,Bài 32: DevOps và Container</t>
-  </si>
-  <si>
-    <t>Docker,どっかー,Docker,名詞,N2,Dockerで環境を構築しました,Tôi đã xây dựng môi trường bằng Docker,tu-vung-cntt,lesson-32,Bài 32: DevOps và Container</t>
-  </si>
-  <si>
-    <t>コンテナ,こんてな,container,名詞,N2,コンテナを起動しました,Tôi đã khởi động container,tu-vung-cntt,lesson-32,Bài 32: DevOps và Container</t>
-  </si>
-  <si>
-    <t>Kubernetes,くばねてす,Kubernetes,名詞,N1,Kubernetesを学習しています,Tôi đang học Kubernetes,tu-vung-cntt,lesson-32,Bài 32: DevOps và Container</t>
-  </si>
-  <si>
-    <t>イメージ,いめーじ,image Docker,名詞,N2,Dockerイメージを作成しました,Tôi đã tạo Docker image,tu-vung-cntt,lesson-32,Bài 32: DevOps và Container</t>
-  </si>
-  <si>
-    <t>レジストリ,れじすとり,registry,名詞,N1,レジストリへイメージを保存しました,Tôi đã lưu image vào registry,tu-vung-cntt,lesson-32,Bài 32: DevOps và Container</t>
-  </si>
-  <si>
-    <t>パイプライン,ぱいぷらいん,pipeline,名詞,N1,CIパイプラインを作成しました,Tôi đã tạo pipeline CI,tu-vung-cntt,lesson-32,Bài 32: DevOps và Container</t>
-  </si>
-  <si>
-    <t>自動化,じどうか,tự động hóa,名詞,N2,業務を自動化しています,Tôi đang tự động hóa công việc,tu-vung-cntt,lesson-32,Bài 32: DevOps và Container</t>
-  </si>
-  <si>
-    <t>監視,かんし,giám sát,名詞,N2,サーバーを二十四時間監視しています,Tôi giám sát máy chủ hai mươi bốn giờ,tu-vung-cntt,lesson-32,Bài 32: DevOps và Container</t>
-  </si>
-  <si>
-    <t>ログ収集,ろぐしゅうしゅう,thu thập log,名詞,N1,ログ収集を自動化しました,Tôi đã tự động hóa việc thu thập log,tu-vung-cntt,lesson-32,Bài 32: DevOps và Container</t>
-  </si>
-  <si>
-    <t>アラート,あらーと,cảnh báo,名詞,N2,障害アラートを受信しました,Tôi đã nhận cảnh báo sự cố,tu-vung-cntt,lesson-32,Bài 32: DevOps và Container</t>
-  </si>
-  <si>
-    <t>Prometheus,ぷろめてうす,Prometheus,名詞,N1,Prometheusで監視しています,Tôi đang giám sát bằng Prometheus,tu-vung-cntt,lesson-32,Bài 32: DevOps và Container</t>
-  </si>
-  <si>
-    <t>Grafana,ぐらふぁな,Grafana,名詞,N1,Grafanaでダッシュボードを表示します,Tôi hiển thị dashboard bằng Grafana,tu-vung-cntt,lesson-32,Bài 32: DevOps và Container</t>
-  </si>
-  <si>
-    <t>Ansible,あんしぶる,Ansible,名詞,N1,Ansibleで構成管理を行います,Tôi quản lý cấu hình bằng Ansible,tu-vung-cntt,lesson-32,Bài 32: DevOps và Container</t>
-  </si>
-  <si>
-    <t>Terraform,てらふぉーむ,Terraform,名詞,N1,Terraformで環境を構築しました,Tôi đã xây dựng hạ tầng bằng Terraform,tu-vung-cntt,lesson-32,Bài 32: DevOps và Container</t>
-  </si>
-  <si>
-    <t>要件定義,ようけんていぎ,phân tích yêu cầu,名詞,N2,要件定義を開始しました,Tôi đã bắt đầu phân tích yêu cầu,tu-vung-cntt,lesson-33,Bài 33: Quy trình phát triển phần mềm</t>
-  </si>
-  <si>
-    <t>基本設計,きほんせっけい,thiết kế cơ bản,名詞,N2,基本設計を作成しました,Tôi đã hoàn thành thiết kế cơ bản,tu-vung-cntt,lesson-33,Bài 33: Quy trình phát triển phần mềm</t>
-  </si>
-  <si>
-    <t>詳細設計,しょうさいせっけい,thiết kế chi tiết,名詞,N2,詳細設計を確認してください,Hãy kiểm tra thiết kế chi tiết,tu-vung-cntt,lesson-33,Bài 33: Quy trình phát triển phần mềm</t>
-  </si>
-  <si>
-    <t>実装,じっそう,triển khai lập trình,名詞,N2,実装を担当しています,Tôi phụ trách triển khai lập trình,tu-vung-cntt,lesson-33,Bài 33: Quy trình phát triển phần mềm</t>
-  </si>
-  <si>
-    <t>単体テスト,たんたいてすと,kiểm thử đơn vị,名詞,N2,単体テストを実施しました,Tôi đã thực hiện kiểm thử đơn vị,tu-vung-cntt,lesson-33,Bài 33: Quy trình phát triển phần mềm</t>
-  </si>
-  <si>
-    <t>結合テスト,けつごうてすと,kiểm thử tích hợp,名詞,N2,結合テストを開始しました,Tôi đã bắt đầu kiểm thử tích hợp,tu-vung-cntt,lesson-33,Bài 33: Quy trình phát triển phần mềm</t>
-  </si>
-  <si>
-    <t>総合テスト,そうごうてすと,kiểm thử hệ thống,名詞,N2,総合テストを完了しました,Tôi đã hoàn thành kiểm thử hệ thống,tu-vung-cntt,lesson-33,Bài 33: Quy trình phát triển phần mềm</t>
-  </si>
-  <si>
-    <t>受け入れテスト,うけいれてすと,kiểm thử chấp nhận,名詞,N1,受け入れテストを実施しました,Tôi đã thực hiện kiểm thử chấp nhận,tu-vung-cntt,lesson-33,Bài 33: Quy trình phát triển phần mềm</t>
-  </si>
-  <si>
-    <t>リリース,りりーす,phát hành,名詞,N3,来週システムをリリースします,Tuần sau sẽ phát hành hệ thống,tu-vung-cntt,lesson-33,Bài 33: Quy trình phát triển phần mềm</t>
-  </si>
-  <si>
-    <t>保守,ほしゅ,bảo trì,名詞,N2,システム保守を担当しています,Tôi phụ trách bảo trì hệ thống,tu-vung-cntt,lesson-33,Bài 33: Quy trình phát triển phần mềm</t>
-  </si>
-  <si>
-    <t>運用,うんよう,vận hành,名詞,N2,本番環境を運用しています,Tôi đang vận hành môi trường production,tu-vung-cntt,lesson-33,Bài 33: Quy trình phát triển phần mềm</t>
-  </si>
-  <si>
-    <t>改修,かいしゅう,cải tiến hệ thống,名詞,N1,システムを改修しました,Tôi đã cải tiến hệ thống,tu-vung-cntt,lesson-33,Bài 33: Quy trình phát triển phần mềm</t>
-  </si>
-  <si>
-    <t>仕様書,しようしょ,tài liệu đặc tả,名詞,N2,仕様書を更新しました,Tôi đã cập nhật tài liệu đặc tả,tu-vung-cntt,lesson-33,Bài 33: Quy trình phát triển phần mềm</t>
-  </si>
-  <si>
-    <t>設計書,せっけいしょ,tài liệu thiết kế,名詞,N2,設計書を共有しました,Tôi đã chia sẻ tài liệu thiết kế,tu-vung-cntt,lesson-33,Bài 33: Quy trình phát triển phần mềm</t>
-  </si>
-  <si>
-    <t>納品,のうひん,bàn giao sản phẩm,名詞,N1,予定通り納品しました,Tôi đã bàn giao đúng tiến độ,tu-vung-cntt,lesson-33,Bài 33: Quy trình phát triển phần mềm</t>
-  </si>
-  <si>
-    <t>アジャイル,あじゃいる,Agile,名詞,N2,アジャイル開発を採用しています,Tôi đang áp dụng phát triển Agile,tu-vung-cntt,lesson-34,Bài 34: Agile và Scrum</t>
-  </si>
-  <si>
-    <t>スクラム,すくらむ,Scrum,名詞,N2,スクラムで開発しています,Tôi phát triển theo Scrum,tu-vung-cntt,lesson-34,Bài 34: Agile và Scrum</t>
-  </si>
-  <si>
-    <t>スプリント,すぷりんと,sprint,名詞,N2,二週間のスプリントを開始しました,Tôi đã bắt đầu sprint hai tuần,tu-vung-cntt,lesson-34,Bài 34: Agile và Scrum</t>
-  </si>
-  <si>
-    <t>プロダクトバックログ,ぷろだくとばっくろぐ,product backlog,名詞,N1,バックログを更新しました,Tôi đã cập nhật product backlog,tu-vung-cntt,lesson-34,Bài 34: Agile và Scrum</t>
-  </si>
-  <si>
-    <t>スプリントバックログ,すぷりんとばっくろぐ,sprint backlog,名詞,N1,スプリントバックログを確認します,Tôi kiểm tra sprint backlog,tu-vung-cntt,lesson-34,Bài 34: Agile và Scrum</t>
-  </si>
-  <si>
-    <t>ユーザーストーリー,ゆーざーすとーりー,user story,名詞,N1,ユーザーストーリーを書きました,Tôi đã viết user story,tu-vung-cntt,lesson-34,Bài 34: Agile và Scrum</t>
-  </si>
-  <si>
-    <t>タスク,たすく,công việc,名詞,N5,今日のタスクを終えました,Tôi đã hoàn thành công việc hôm nay,tu-vung-cntt,lesson-34,Bài 34: Agile và Scrum</t>
-  </si>
-  <si>
-    <t>進捗,しんちょく,tiến độ,名詞,N2,進捗を毎日報告します,Tôi báo cáo tiến độ hằng ngày,tu-vung-cntt,lesson-34,Bài 34: Agile và Scrum</t>
-  </si>
-  <si>
-    <t>朝会,あさかい,họp đầu ngày,名詞,N2,朝会に参加してください,Hãy tham gia cuộc họp đầu ngày,tu-vung-cntt,lesson-34,Bài 34: Agile và Scrum</t>
-  </si>
-  <si>
-    <t>ふりかえり,ふりかえり,họp retrospective,名詞,N2,スプリント後にふりかえりを行います,Chúng tôi họp retrospective sau sprint,tu-vung-cntt,lesson-34,Bài 34: Agile và Scrum</t>
-  </si>
-  <si>
-    <t>優先順位,ゆうせんじゅんい,mức ưu tiên,名詞,N2,優先順位を変更しました,Tôi đã thay đổi mức ưu tiên,tu-vung-cntt,lesson-34,Bài 34: Agile và Scrum</t>
-  </si>
-  <si>
-    <t>見積もり,みつもり,ước lượng,名詞,N2,工数を見積もりました,Tôi đã ước lượng khối lượng công việc,tu-vung-cntt,lesson-34,Bài 34: Agile và Scrum</t>
-  </si>
-  <si>
-    <t>工数,こうすう,khối lượng công việc,名詞,N1,工数を削減しました,Tôi đã giảm khối lượng công việc,tu-vung-cntt,lesson-34,Bài 34: Agile và Scrum</t>
-  </si>
-  <si>
-    <t>バーンダウンチャート,ばーんだうんちゃーと,biểu đồ burndown,名詞,N1,バーンダウンチャートを確認しました,Tôi đã kiểm tra biểu đồ burndown,tu-vung-cntt,lesson-34,Bài 34: Agile và Scrum</t>
-  </si>
-  <si>
-    <t>スクラムマスター,すくらむますたー,Scrum Master,名詞,N1,スクラムマスターと相談しました,Tôi đã trao đổi với Scrum Master,tu-vung-cntt,lesson-34,Bài 34: Agile và Scrum</t>
-  </si>
-  <si>
-    <t>ブリッジSE,ぶりっじえすいー,BrSE,名詞,N2,ブリッジSEとして働いています,Tôi làm việc với vai trò BrSE,tu-vung-cntt,lesson-35,Bài 35: Thuật ngữ IT công ty Nhật</t>
-  </si>
-  <si>
-    <t>オフショア,おふしょあ,offshore,名詞,N2,オフショア開発を担当しています,Tôi phụ trách phát triển offshore,tu-vung-cntt,lesson-35,Bài 35: Thuật ngữ IT công ty Nhật</t>
-  </si>
-  <si>
-    <t>ニアショア,にあしょあ,nearshore,名詞,N1,ニアショア開発を検討しています,Chúng tôi đang xem xét phát triển nearshore,tu-vung-cntt,lesson-35,Bài 35: Thuật ngữ IT công ty Nhật</t>
-  </si>
-  <si>
-    <t>客先,きゃくさき,khách hàng,名詞,N2,客先へ訪問しました,Tôi đã đến công ty khách hàng,tu-vung-cntt,lesson-35,Bài 35: Thuật ngữ IT công ty Nhật</t>
-  </si>
-  <si>
-    <t>顧客,こきゃく,khách hàng,名詞,N3,顧客へ報告しました,Tôi đã báo cáo với khách hàng,tu-vung-cntt,lesson-35,Bài 35: Thuật ngữ IT công ty Nhật</t>
-  </si>
-  <si>
-    <t>仕様変更,しようへんこう,thay đổi yêu cầu,名詞,N2,仕様変更がありました,Yêu cầu đã có thay đổi,tu-vung-cntt,lesson-35,Bài 35: Thuật ngữ IT công ty Nhật</t>
-  </si>
-  <si>
-    <t>障害票,しょうがいひょう,phiếu lỗi,名詞,N1,障害票を登録しました,Tôi đã tạo phiếu lỗi,tu-vung-cntt,lesson-35,Bài 35: Thuật ngữ IT công ty Nhật</t>
-  </si>
-  <si>
-    <t>課題管理,かだいかんり,quản lý vấn đề,名詞,N1,課題管理を行っています,Tôi đang quản lý các vấn đề,tu-vung-cntt,lesson-35,Bài 35: Thuật ngữ IT công ty Nhật</t>
-  </si>
-  <si>
-    <t>担当者,たんとうしゃ,người phụ trách,名詞,N3,担当者へ連絡しました,Tôi đã liên hệ người phụ trách,tu-vung-cntt,lesson-35,Bài 35: Thuật ngữ IT công ty Nhật</t>
-  </si>
-  <si>
-    <t>承認,しょうにん,phê duyệt,名詞,N2,上司の承認を受けました,Tôi đã nhận được phê duyệt của cấp trên,tu-vung-cntt,lesson-35,Bài 35: Thuật ngữ IT công ty Nhật</t>
-  </si>
-  <si>
-    <t>稼働,かどう,vận hành,名詞,N1,システムが正常に稼働しています,Hệ thống đang vận hành bình thường,tu-vung-cntt,lesson-35,Bài 35: Thuật ngữ IT công ty Nhật</t>
-  </si>
-  <si>
-    <t>納期,のうき,hạn giao hàng,名詞,N2,納期を守ってください,Hãy đảm bảo đúng thời hạn giao hàng,tu-vung-cntt,lesson-35,Bài 35: Thuật ngữ IT công ty Nhật</t>
-  </si>
-  <si>
-    <t>品質保証,ひんしつほしょう,đảm bảo chất lượng,名詞,N1,品質保証を強化しました,Tôi đã tăng cường đảm bảo chất lượng,tu-vung-cntt,lesson-35,Bài 35: Thuật ngữ IT công ty Nhật</t>
-  </si>
-  <si>
-    <t>品質管理,ひんしつかんり,quản lý chất lượng,名詞,N1,品質管理を担当しています,Tôi phụ trách quản lý chất lượng,tu-vung-cntt,lesson-35,Bài 35: Thuật ngữ IT công ty Nhật</t>
-  </si>
-  <si>
-    <t>検収,けんしゅう,nghiệm thu,名詞,N1,検収が完了しました,Việc nghiệm thu đã hoàn tất,tu-vung-cntt,lesson-35,Bài 35: Thuật ngữ IT công ty Nhật</t>
-  </si>
-  <si>
-    <t>報告,ほうこく,báo cáo,名詞,N4,毎日進捗を報告します,Tôi báo cáo tiến độ hằng ngày,tu-vung-cntt,lesson-36,Bài 36: Giao tiếp trong công ty IT Nhật</t>
-  </si>
-  <si>
-    <t>連絡,れんらく,liên lạc,名詞,N4,問題があれば連絡してください,Hãy liên lạc nếu có vấn đề,tu-vung-cntt,lesson-36,Bài 36: Giao tiếp trong công ty IT Nhật</t>
-  </si>
-  <si>
-    <t>相談,そうだん,trao đổi; tham khảo ý kiến,名詞,N4,困ったら相談してください,Hãy trao đổi nếu gặp khó khăn,tu-vung-cntt,lesson-36,Bài 36: Giao tiếp trong công ty IT Nhật</t>
-  </si>
-  <si>
-    <t>確認,かくにん,xác nhận,名詞,N4,内容を確認してください,Hãy xác nhận nội dung,tu-vung-cntt,lesson-36,Bài 36: Giao tiếp trong công ty IT Nhật</t>
-  </si>
-  <si>
-    <t>依頼,いらい,yêu cầu,名詞,N3,作業を依頼しました,Tôi đã yêu cầu thực hiện công việc,tu-vung-cntt,lesson-36,Bài 36: Giao tiếp trong công ty IT Nhật</t>
-  </si>
-  <si>
-    <t>対応,たいおう,xử lý; ứng phó,名詞,N3,すぐに対応します,Tôi sẽ xử lý ngay lập tức,tu-vung-cntt,lesson-36,Bài 36: Giao tiếp trong công ty IT Nhật</t>
-  </si>
-  <si>
-    <t>共有,きょうゆう,chia sẻ,名詞,N3,情報を共有してください,Hãy chia sẻ thông tin,tu-vung-cntt,lesson-36,Bài 36: Giao tiếp trong công ty IT Nhật</t>
-  </si>
-  <si>
-    <t>引き継ぎ,ひきつぎ,bàn giao công việc,名詞,N2,引き継ぎ資料を作成しました,Tôi đã tạo tài liệu bàn giao,tu-vung-cntt,lesson-36,Bài 36: Giao tiếp trong công ty IT Nhật</t>
-  </si>
-  <si>
-    <t>期限,きげん,hạn chót,名詞,N3,期限までに提出してください,Hãy nộp trước thời hạn,tu-vung-cntt,lesson-36,Bài 36: Giao tiếp trong công ty IT Nhật</t>
-  </si>
-  <si>
-    <t>進行状況,しんこうじょうきょう,tình hình tiến độ,名詞,N2,進行状況を確認しました,Tôi đã kiểm tra tình hình tiến độ,tu-vung-cntt,lesson-36,Bài 36: Giao tiếp trong công ty IT Nhật</t>
-  </si>
-  <si>
-    <t>遅延,ちえん,chậm tiến độ,名詞,N2,納期に遅延が発生しました,Đã xảy ra chậm tiến độ giao hàng,tu-vung-cntt,lesson-36,Bài 36: Giao tiếp trong công ty IT Nhật</t>
-  </si>
-  <si>
-    <t>原因,げんいん,nguyên nhân,名詞,N3,原因を調査しています,Tôi đang điều tra nguyên nhân,tu-vung-cntt,lesson-36,Bài 36: Giao tiếp trong công ty IT Nhật</t>
-  </si>
-  <si>
-    <t>対策,たいさく,biện pháp đối phó,名詞,N2,再発防止の対策を考えます,Chúng tôi sẽ đưa ra biện pháp ngăn tái diễn,tu-vung-cntt,lesson-36,Bài 36: Giao tiếp trong công ty IT Nhật</t>
-  </si>
-  <si>
-    <t>再発防止,さいはつぼうし,ngăn tái diễn,名詞,N1,再発防止策を実施しました,Tôi đã thực hiện biện pháp ngăn tái diễn,tu-vung-cntt,lesson-36,Bài 36: Giao tiếp trong công ty IT Nhật</t>
-  </si>
-  <si>
-    <t>議事録,ぎじろく,biên bản cuộc họp,名詞,N2,議事録を全員へ共有しました,Tôi đã chia sẻ biên bản cuộc họp cho mọi người,tu-vung-cntt,lesson-36,Bài 36: Giao tiếp trong công ty IT Nhật</t>
-  </si>
-  <si>
-    <t>リファクタリング,りふぁくたりんぐ,tái cấu trúc mã nguồn,名詞,N1,コードをリファクタリングしました,Tôi đã tái cấu trúc mã nguồn,tu-vung-cntt,lesson-37,Bài 37: Chất lượng phần mềm</t>
-  </si>
-  <si>
-    <t>技術的負債,ぎじゅつてきふさい,nợ kỹ thuật,名詞,N1,技術的負債を減らします,Chúng tôi sẽ giảm nợ kỹ thuật,tu-vung-cntt,lesson-37,Bài 37: Chất lượng phần mềm</t>
-  </si>
-  <si>
-    <t>コードレビュー,こーどれびゅー,review mã nguồn,名詞,N2,コードレビューを実施しました,Tôi đã thực hiện review mã nguồn,tu-vung-cntt,lesson-37,Bài 37: Chất lượng phần mềm</t>
-  </si>
-  <si>
-    <t>静的解析,せいてきかいせき,phân tích tĩnh,名詞,N1,静的解析ツールを実行しました,Tôi đã chạy công cụ phân tích tĩnh,tu-vung-cntt,lesson-37,Bài 37: Chất lượng phần mềm</t>
-  </si>
-  <si>
-    <t>単体試験,たんたいしけん,kiểm thử đơn vị,名詞,N2,単体試験を自動化しました,Tôi đã tự động hóa kiểm thử đơn vị,tu-vung-cntt,lesson-37,Bài 37: Chất lượng phần mềm</t>
-  </si>
-  <si>
-    <t>回帰テスト,かいきてすと,kiểm thử hồi quy,名詞,N1,回帰テストを実施しました,Tôi đã thực hiện kiểm thử hồi quy,tu-vung-cntt,lesson-37,Bài 37: Chất lượng phần mềm</t>
-  </si>
-  <si>
-    <t>品質,ひんしつ,chất lượng,名詞,N3,品質を改善しています,Tôi đang cải thiện chất lượng,tu-vung-cntt,lesson-37,Bài 37: Chất lượng phần mềm</t>
-  </si>
-  <si>
-    <t>保守性,ほしゅせい,khả năng bảo trì,名詞,N1,保守性を向上させました,Tôi đã nâng cao khả năng bảo trì,tu-vung-cntt,lesson-37,Bài 37: Chất lượng phần mềm</t>
-  </si>
-  <si>
-    <t>可読性,かどくせい,khả năng đọc hiểu mã,名詞,N1,コードの可読性を高めました,Tôi đã cải thiện khả năng đọc của mã,tu-vung-cntt,lesson-37,Bài 37: Chất lượng phần mềm</t>
-  </si>
-  <si>
-    <t>再利用性,さいりようせい,khả năng tái sử dụng,名詞,N1,再利用性を意識して設計しました,Tôi thiết kế chú trọng khả năng tái sử dụng,tu-vung-cntt,lesson-37,Bài 37: Chất lượng phần mềm</t>
-  </si>
-  <si>
-    <t>例外処理,れいがいしょり,xử lý ngoại lệ,名詞,N1,例外処理を追加しました,Tôi đã bổ sung xử lý ngoại lệ,tu-vung-cntt,lesson-37,Bài 37: Chất lượng phần mềm</t>
-  </si>
-  <si>
-    <t>ログ出力,ろぐしゅつりょく,xuất log,名詞,N2,ログ出力を有効にしました,Tôi đã bật ghi log,tu-vung-cntt,lesson-37,Bài 37: Chất lượng phần mềm</t>
-  </si>
-  <si>
-    <t>コーディング規約,こーでぃんぐきやく,quy chuẩn lập trình,名詞,N1,コーディング規約を守ってください,Hãy tuân thủ quy chuẩn lập trình,tu-vung-cntt,lesson-37,Bài 37: Chất lượng phần mềm</t>
-  </si>
-  <si>
-    <t>テストケース,てすとけーす,test case,名詞,N2,テストケースを追加しました,Tôi đã bổ sung test case,tu-vung-cntt,lesson-37,Bài 37: Chất lượng phần mềm</t>
-  </si>
-  <si>
-    <t>不具合修正,ふぐあいしゅうせい,sửa lỗi,名詞,N2,不具合修正が完了しました,Việc sửa lỗi đã hoàn tất,tu-vung-cntt,lesson-37,Bài 37: Chất lượng phần mềm</t>
-  </si>
-  <si>
-    <t>マイクロサービス,まいくろさーびす,microservice,名詞,N1,マイクロサービスへ移行しました,Tôi đã chuyển sang kiến trúc microservice,tu-vung-cntt,lesson-38,Bài 38: Kiến trúc hệ thống</t>
-  </si>
-  <si>
-    <t>モノリス,ものりす,monolith,名詞,N1,モノリス構成を採用しています,Tôi đang sử dụng kiến trúc monolith,tu-vung-cntt,lesson-38,Bài 38: Kiến trúc hệ thống</t>
-  </si>
-  <si>
-    <t>アーキテクチャ,あーきてくちゃ,kiến trúc hệ thống,名詞,N2,システムアーキテクチャを設計しました,Tôi đã thiết kế kiến trúc hệ thống,tu-vung-cntt,lesson-38,Bài 38: Kiến trúc hệ thống</t>
-  </si>
-  <si>
-    <t>モジュール,もじゅーる,module,名詞,N2,モジュールを分割しました,Tôi đã tách các module,tu-vung-cntt,lesson-38,Bài 38: Kiến trúc hệ thống</t>
-  </si>
-  <si>
-    <t>ミドルウェア,みどるうぇあ,middleware,名詞,N1,ミドルウェアを更新しました,Tôi đã cập nhật middleware,tu-vung-cntt,lesson-38,Bài 38: Kiến trúc hệ thống</t>
-  </si>
-  <si>
-    <t>キャッシュ,きゃっしゅ,bộ nhớ đệm,名詞,N2,キャッシュを削除しました,Tôi đã xóa bộ nhớ đệm,tu-vung-cntt,lesson-38,Bài 38: Kiến trúc hệ thống</t>
-  </si>
-  <si>
-    <t>メッセージキュー,めっせーじきゅー,hàng đợi thông điệp,名詞,N1,メッセージキューを導入しました,Tôi đã triển khai message queue,tu-vung-cntt,lesson-38,Bài 38: Kiến trúc hệ thống</t>
-  </si>
-  <si>
-    <t>負荷分散,ふかぶんさん,cân bằng tải,名詞,N1,負荷分散を設定しました,Tôi đã cấu hình cân bằng tải,tu-vung-cntt,lesson-38,Bài 38: Kiến trúc hệ thống</t>
-  </si>
-  <si>
-    <t>冗長構成,じょうちょうこうせい,kiến trúc dự phòng,名詞,N1,冗長構成を構築しました,Tôi đã xây dựng kiến trúc dự phòng,tu-vung-cntt,lesson-38,Bài 38: Kiến trúc hệ thống</t>
-  </si>
-  <si>
-    <t>高可用性,こうかようせい,tính sẵn sàng cao,名詞,N1,高可用性を実現しました,Tôi đã đạt được tính sẵn sàng cao,tu-vung-cntt,lesson-38,Bài 38: Kiến trúc hệ thống</t>
-  </si>
-  <si>
-    <t>スループット,するーぷっと,thông lượng,名詞,N1,スループットを改善しました,Tôi đã cải thiện thông lượng,tu-vung-cntt,lesson-38,Bài 38: Kiến trúc hệ thống</t>
-  </si>
-  <si>
-    <t>レイテンシ,れいてんし,độ trễ,名詞,N1,レイテンシが増加しました,Độ trễ đã tăng lên,tu-vung-cntt,lesson-38,Bài 38: Kiến trúc hệ thống</t>
-  </si>
-  <si>
-    <t>ボトルネック,ぼとるねっく,điểm nghẽn,名詞,N1,ボトルネックを特定しました,Tôi đã xác định điểm nghẽn,tu-vung-cntt,lesson-38,Bài 38: Kiến trúc hệ thống</t>
-  </si>
-  <si>
-    <t>スケーラビリティ,すけーらびりてぃ,khả năng mở rộng,名詞,N1,スケーラビリティを向上させました,Tôi đã nâng cao khả năng mở rộng,tu-vung-cntt,lesson-38,Bài 38: Kiến trúc hệ thống</t>
-  </si>
-  <si>
-    <t>可観測性,かかんそくせい,khả năng quan sát hệ thống,名詞,N1,可観測性を強化しました,Tôi đã tăng cường khả năng quan sát hệ thống,tu-vung-cntt,lesson-38,Bài 38: Kiến trúc hệ thống</t>
-  </si>
-  <si>
-    <t>敬語,けいご,kính ngữ,名詞,N3,敬語を正しく使ってください,Hãy sử dụng kính ngữ đúng cách,tu-vung-cntt,lesson-39,Bài 39: Giao tiếp với khách hàng Nhật</t>
-  </si>
-  <si>
-    <t>お世話になっております,おせわになっております,Xin cảm ơn quý vị luôn hỗ trợ,表現,N3,お世話になっておりますよろしくお願いいたします,Xin cảm ơn quý vị đã luôn hỗ trợ,tu-vung-cntt,lesson-39,Bài 39: Giao tiếp với khách hàng Nhật</t>
-  </si>
-  <si>
-    <t>承知しました,しょうちしました,Đã hiểu,表現,N3,内容を承知しました,Tôi đã hiểu nội dung,tu-vung-cntt,lesson-39,Bài 39: Giao tiếp với khách hàng Nhật</t>
-  </si>
-  <si>
-    <t>かしこまりました,かしこまりました,Vâng tôi đã rõ,表現,N2,かしこまりました対応いたします,Vâng tôi sẽ xử lý,tu-vung-cntt,lesson-39,Bài 39: Giao tiếp với khách hàng Nhật</t>
-  </si>
-  <si>
-    <t>恐れ入ります,おそれいります,Xin phép; làm phiền,表現,N2,恐れ入りますがご確認ください,Xin phiền quý vị xác nhận,tu-vung-cntt,lesson-39,Bài 39: Giao tiếp với khách hàng Nhật</t>
-  </si>
-  <si>
-    <t>申し訳ございません,もうしわけございません,Thành thật xin lỗi,表現,N2,申し訳ございませんすぐ対応します,Thành thật xin lỗi chúng tôi sẽ xử lý ngay,tu-vung-cntt,lesson-39,Bài 39: Giao tiếp với khách hàng Nhật</t>
-  </si>
-  <si>
-    <t>ご確認ください,ごかくにんください,Xin vui lòng xác nhận,表現,N3,添付資料をご確認ください,Xin vui lòng xác nhận tài liệu đính kèm,tu-vung-cntt,lesson-39,Bài 39: Giao tiếp với khách hàng Nhật</t>
-  </si>
-  <si>
-    <t>ご対応ありがとうございます,ごたいおうありがとうございます,Cảm ơn đã hỗ trợ,表現,N2,ご対応ありがとうございます,Cảm ơn vì đã hỗ trợ,tu-vung-cntt,lesson-39,Bài 39: Giao tiếp với khách hàng Nhật</t>
-  </si>
-  <si>
-    <t>少々お待ちください,しょうしょうおまちください,Xin vui lòng chờ một chút,表現,N3,少々お待ちください確認します,Xin vui lòng chờ tôi kiểm tra,tu-vung-cntt,lesson-39,Bài 39: Giao tiếp với khách hàng Nhật</t>
-  </si>
-  <si>
-    <t>よろしくお願いいたします,よろしくおねがいいたします,Mong nhận được sự giúp đỡ,表現,N4,今後ともよろしくお願いいたします,Mong tiếp tục nhận được sự hỗ trợ,tu-vung-cntt,lesson-39,Bài 39: Giao tiếp với khách hàng Nhật</t>
-  </si>
-  <si>
-    <t>ご連絡いたします,ごれんらくいたします,Tôi sẽ liên hệ,表現,N2,後ほどご連絡いたします,Tôi sẽ liên hệ sau,tu-vung-cntt,lesson-39,Bài 39: Giao tiếp với khách hàng Nhật</t>
-  </si>
-  <si>
-    <t>ご回答,ごかいとう,phản hồi,名詞,N2,ご回答をお待ちしております,Chúng tôi đang chờ phản hồi,tu-vung-cntt,lesson-39,Bài 39: Giao tiếp với khách hàng Nhật</t>
-  </si>
-  <si>
-    <t>ご協力,ごきょうりょく,sự hợp tác,名詞,N3,ご協力ありがとうございます,Cảm ơn sự hợp tác của quý vị,tu-vung-cntt,lesson-39,Bài 39: Giao tiếp với khách hàng Nhật</t>
-  </si>
-  <si>
-    <t>至急,しきゅう,khẩn cấp,副詞,N2,至急ご対応をお願いいたします,Xin vui lòng xử lý khẩn cấp,tu-vung-cntt,lesson-39,Bài 39: Giao tiếp với khách hàng Nhật</t>
-  </si>
-  <si>
-    <t>折り返し,おりかえし,gọi lại; phản hồi lại,名詞,N2,折り返しご連絡します,Tôi sẽ liên hệ lại,tu-vung-cntt,lesson-39,Bài 39: Giao tiếp với khách hàng Nhật</t>
-  </si>
-  <si>
-    <t>稟議,りんぎ,đề xuất phê duyệt nội bộ,名詞,N1,稟議を提出しました,Tôi đã gửi đề xuất phê duyệt,tu-vung-cntt,lesson-40,Bài 40: Doanh nghiệp Nhật Bản</t>
-  </si>
-  <si>
-    <t>稟議書,りんぎしょ,tài liệu xin phê duyệt,名詞,N1,稟議書を作成しました,Tôi đã tạo tài liệu xin phê duyệt,tu-vung-cntt,lesson-40,Bài 40: Doanh nghiệp Nhật Bản</t>
-  </si>
-  <si>
-    <t>決裁,けっさい,phê duyệt cuối cùng,名詞,N1,決裁が完了しました,Việc phê duyệt cuối cùng đã hoàn tất,tu-vung-cntt,lesson-40,Bài 40: Doanh nghiệp Nhật Bản</t>
-  </si>
-  <si>
-    <t>承認フロー,しょうにんふろー,quy trình phê duyệt,名詞,N1,承認フローを変更しました,Tôi đã thay đổi quy trình phê duyệt,tu-vung-cntt,lesson-40,Bài 40: Doanh nghiệp Nhật Bản</t>
-  </si>
-  <si>
-    <t>業務改善,ぎょうむかいぜん,cải tiến nghiệp vụ,名詞,N1,業務改善を提案しました,Tôi đã đề xuất cải tiến nghiệp vụ,tu-vung-cntt,lesson-40,Bài 40: Doanh nghiệp Nhật Bản</t>
-  </si>
-  <si>
-    <t>標準化,ひょうじゅんか,tiêu chuẩn hóa,名詞,N1,業務を標準化しました,Tôi đã tiêu chuẩn hóa quy trình,tu-vung-cntt,lesson-40,Bài 40: Doanh nghiệp Nhật Bản</t>
-  </si>
-  <si>
-    <t>手順書,てじゅんしょ,tài liệu hướng dẫn quy trình,名詞,N2,手順書を更新しました,Tôi đã cập nhật tài liệu hướng dẫn,tu-vung-cntt,lesson-40,Bài 40: Doanh nghiệp Nhật Bản</t>
-  </si>
-  <si>
-    <t>業務フロー,ぎょうむふろー,quy trình nghiệp vụ,名詞,N1,業務フローを見直しました,Tôi đã rà soát quy trình nghiệp vụ,tu-vung-cntt,lesson-40,Bài 40: Doanh nghiệp Nhật Bản</t>
-  </si>
-  <si>
-    <t>標準手順書,ひょうじゅんてじゅんしょ,tài liệu quy trình chuẩn,名詞,N1,標準手順書を共有しました,Tôi đã chia sẻ tài liệu quy trình chuẩn,tu-vung-cntt,lesson-40,Bài 40: Doanh nghiệp Nhật Bản</t>
-  </si>
-  <si>
-    <t>引合い,ひきあい,yêu cầu báo giá,名詞,N1,新しい引合いが届きました,Đã nhận được yêu cầu báo giá mới,tu-vung-cntt,lesson-40,Bài 40: Doanh nghiệp Nhật Bản</t>
-  </si>
-  <si>
-    <t>見積書,みつもりしょ,báo giá,名詞,N2,見積書を送付しました,Tôi đã gửi báo giá,tu-vung-cntt,lesson-40,Bài 40: Doanh nghiệp Nhật Bản</t>
-  </si>
-  <si>
-    <t>請求書,せいきゅうしょ,hóa đơn,名詞,N2,請求書を発行しました,Tôi đã phát hành hóa đơn,tu-vung-cntt,lesson-40,Bài 40: Doanh nghiệp Nhật Bản</t>
-  </si>
-  <si>
-    <t>契約書,けいやくしょ,hợp đồng,名詞,N2,契約書を確認してください,Hãy xác nhận hợp đồng,tu-vung-cntt,lesson-40,Bài 40: Doanh nghiệp Nhật Bản</t>
-  </si>
-  <si>
-    <t>秘密保持契約,ひみつほじけいやく,thỏa thuận bảo mật,名詞,N1,秘密保持契約を締結しました,Chúng tôi đã ký thỏa thuận bảo mật,tu-vung-cntt,lesson-40,Bài 40: Doanh nghiệp Nhật Bản</t>
-  </si>
-  <si>
-    <t>締結する,ていけつする,ký kết,動詞,N1,新しい契約を締結しました,Tôi đã ký kết hợp đồng mới,tu-vung-cntt,lesson-40,Bài 40: Doanh nghiệp Nhật Bản</t>
-  </si>
-  <si>
-    <t>お疲れ様です,おつかれさまです,xin chào đồng nghiệp,表現,N5,お疲れ様です;会議を始めましょう,Xin chào mọi người; chúng ta bắt đầu cuộc họp nhé,tu-vung-cntt,lesson-41,Bài 41: Hội thoại IT trong công ty Nhật</t>
-  </si>
-  <si>
-    <t>よろしくお願いいたします,よろしくおねがいいたします,mong được giúp đỡ,表現,N4,本日もよろしくお願いいたします,Hôm nay cũng mong mọi người giúp đỡ,tu-vung-cntt,lesson-41,Bài 41: Hội thoại IT trong công ty Nhật</t>
-  </si>
-  <si>
-    <t>承知しました,しょうちしました,đã hiểu,表現,N3,内容を承知しました;対応します,Tôi đã hiểu nội dung và sẽ xử lý,tu-vung-cntt,lesson-41,Bài 41: Hội thoại IT trong công ty Nhật</t>
-  </si>
-  <si>
-    <t>かしこまりました,かしこまりました,vâng; tôi đã rõ,表現,N2,かしこまりました;すぐ対応いたします,Vâng; tôi sẽ xử lý ngay,tu-vung-cntt,lesson-41,Bài 41: Hội thoại IT trong công ty Nhật</t>
-  </si>
-  <si>
-    <t>少々お待ちください,しょうしょうおまちください,xin chờ một chút,表現,N4,少々お待ちください;確認いたします,Xin chờ một chút; tôi sẽ kiểm tra,tu-vung-cntt,lesson-41,Bài 41: Hội thoại IT trong công ty Nhật</t>
-  </si>
-  <si>
-    <t>確認いたします,かくにんいたします,tôi sẽ kiểm tra,表現,N3,内容を確認いたします,Tôi sẽ kiểm tra nội dung,tu-vung-cntt,lesson-41,Bài 41: Hội thoại IT trong công ty Nhật</t>
-  </si>
-  <si>
-    <t>対応いたします,たいおういたします,tôi sẽ xử lý,表現,N3,本日中に対応いたします,Tôi sẽ xử lý trong hôm nay,tu-vung-cntt,lesson-41,Bài 41: Hội thoại IT trong công ty Nhật</t>
-  </si>
-  <si>
-    <t>申し訳ございません,もうしわけございません,xin lỗi,表現,N3,ご迷惑をおかけして申し訳ございません,Xin lỗi vì đã gây bất tiện,tu-vung-cntt,lesson-41,Bài 41: Hội thoại IT trong công ty Nhật</t>
-  </si>
-  <si>
-    <t>恐れ入ります,おそれいります,xin làm phiền,表現,N2,恐れ入りますが再度ご確認ください,Xin phiền bạn kiểm tra lại,tu-vung-cntt,lesson-41,Bài 41: Hội thoại IT trong công ty Nhật</t>
-  </si>
-  <si>
-    <t>ご確認ください,ごかくにんください,xin vui lòng xác nhận,表現,N4,添付資料をご確認ください,Xin vui lòng kiểm tra tài liệu đính kèm,tu-vung-cntt,lesson-41,Bài 41: Hội thoại IT trong công ty Nhật</t>
-  </si>
-  <si>
-    <t>ご連絡ください,ごれんらくください,xin vui lòng liên hệ,表現,N4,問題があればご連絡ください,Nếu có vấn đề xin hãy liên hệ,tu-vung-cntt,lesson-41,Bài 41: Hội thoại IT trong công ty Nhật</t>
-  </si>
-  <si>
-    <t>お手数ですが,おてすうですが,xin phiền bạn,表現,N3,お手数ですがご返信ください,Xin phiền bạn phản hồi,tu-vung-cntt,lesson-41,Bài 41: Hội thoại IT trong công ty Nhật</t>
-  </si>
-  <si>
-    <t>念のため,ねんのため,để chắc chắn,副詞,N2,念のためバックアップを作成しました,Để chắc chắn tôi đã tạo bản sao lưu,tu-vung-cntt,lesson-41,Bài 41: Hội thoại IT trong công ty Nhật</t>
-  </si>
-  <si>
-    <t>至急,しきゅう,khẩn cấp,副詞,N2,至急ご対応をお願いいたします,Xin xử lý khẩn cấp,tu-vung-cntt,lesson-41,Bài 41: Hội thoại IT trong công ty Nhật</t>
-  </si>
-  <si>
-    <t>ご協力ありがとうございます,ごきょうりょくありがとうございます,cảm ơn sự hợp tác,表現,N3,ご協力ありがとうございます;作業が完了しました,Cảm ơn sự hợp tác; công việc đã hoàn thành,tu-vung-cntt,lesson-41,Bài 41: Hội thoại IT trong công ty Nhật</t>
-  </si>
-  <si>
-    <t>IoT,あいおーてぃー,Internet vạn vật,名詞,N2,IoT機器を管理しています,Tôi đang quản lý các thiết bị IoT,tu-vung-cntt,lesson-42,Bài 42: Công nghệ hiện đại</t>
-  </si>
-  <si>
-    <t>ビッグデータ,びっぐでーた,dữ liệu lớn,名詞,N2,ビッグデータを分析しています,Tôi đang phân tích dữ liệu lớn,tu-vung-cntt,lesson-42,Bài 42: Công nghệ hiện đại</t>
-  </si>
-  <si>
-    <t>データ分析,でーたぶんせき,phân tích dữ liệu,名詞,N2,データ分析を担当しています,Tôi phụ trách phân tích dữ liệu,tu-vung-cntt,lesson-42,Bài 42: Công nghệ hiện đại</t>
-  </si>
-  <si>
-    <t>データサイエンス,でーたさいえんす,khoa học dữ liệu,名詞,N1,データサイエンスを勉強しています,Tôi đang học khoa học dữ liệu,tu-vung-cntt,lesson-42,Bài 42: Công nghệ hiện đại</t>
-  </si>
-  <si>
-    <t>ブロックチェーン,ぶろっくちぇーん,blockchain,名詞,N1,ブロックチェーン技術を学びます,Tôi học công nghệ blockchain,tu-vung-cntt,lesson-42,Bài 42: Công nghệ hiện đại</t>
-  </si>
-  <si>
-    <t>スマートコントラクト,すまーとこんとらくと,hợp đồng thông minh,名詞,N1,スマートコントラクトを開発しました,Tôi đã phát triển smart contract,tu-vung-cntt,lesson-42,Bài 42: Công nghệ hiện đại</t>
-  </si>
-  <si>
-    <t>生成AI,せいせいえーあい,AI tạo sinh,名詞,N1,生成AIを業務で利用しています,Tôi đang sử dụng AI tạo sinh trong công việc,tu-vung-cntt,lesson-42,Bài 42: Công nghệ hiện đại</t>
-  </si>
-  <si>
-    <t>自然言語処理,しぜんげんごしょり,xử lý ngôn ngữ tự nhiên,名詞,N1,自然言語処理を研究しています,Tôi đang nghiên cứu xử lý ngôn ngữ tự nhiên,tu-vung-cntt,lesson-42,Bài 42: Công nghệ hiện đại</t>
-  </si>
-  <si>
-    <t>画像認識,がぞうにんしき,nhận dạng hình ảnh,名詞,N1,画像認識モデルを改善しました,Tôi đã cải thiện mô hình nhận dạng hình ảnh,tu-vung-cntt,lesson-42,Bài 42: Công nghệ hiện đại</t>
-  </si>
-  <si>
-    <t>音声認識,おんせいにんしき,nhận dạng giọng nói,名詞,N1,音声認識の精度が向上しました,Độ chính xác nhận dạng giọng nói đã tăng,tu-vung-cntt,lesson-42,Bài 42: Công nghệ hiện đại</t>
-  </si>
-  <si>
-    <t>自動運転,じどううんてん,lái xe tự động,名詞,N1,自動運転技術を開発しています,Tôi đang phát triển công nghệ lái xe tự động,tu-vung-cntt,lesson-42,Bài 42: Công nghệ hiện đại</t>
-  </si>
-  <si>
-    <t>エッジコンピューティング,えっじこんぴゅーてぃんぐ,điện toán biên,名詞,N1,エッジコンピューティングを導入しました,Tôi đã triển khai điện toán biên,tu-vung-cntt,lesson-42,Bài 42: Công nghệ hiện đại</t>
-  </si>
-  <si>
-    <t>量子コンピューター,りょうしこんぴゅーたー,máy tính lượng tử,名詞,N1,量子コンピューターを勉強しています,Tôi đang học về máy tính lượng tử,tu-vung-cntt,lesson-42,Bài 42: Công nghệ hiện đại</t>
-  </si>
-  <si>
-    <t>MLOps,えむえるおぷす,MLOps,名詞,N1,MLOps環境を構築しました,Tôi đã xây dựng môi trường MLOps,tu-vung-cntt,lesson-42,Bài 42: Công nghệ hiện đại</t>
-  </si>
-  <si>
-    <t>LLM,えるえるえむ,mô hình ngôn ngữ lớn,名詞,N1,LLMを業務に活用しています,Tôi đang ứng dụng LLM trong công việc,tu-vung-cntt,lesson-42,Bài 42: Công nghệ hiện đại</t>
-  </si>
-  <si>
-    <t>ライセンス,らいせんす,giấy phép phần mềm,名詞,N2,ライセンスを更新しました,Tôi đã gia hạn giấy phép phần mềm,tu-vung-cntt,lesson-43,Bài 43: Quản trị CNTT</t>
-  </si>
-  <si>
-    <t>サブスクリプション,さぶすくりぷしょん,gói thuê bao,名詞,N2,サブスクリプションを管理しています,Tôi đang quản lý các gói thuê bao,tu-vung-cntt,lesson-43,Bài 43: Quản trị CNTT</t>
-  </si>
-  <si>
-    <t>資産管理,しさんかんり,quản lý tài sản CNTT,名詞,N1,資産管理システムを更新しました,Tôi đã cập nhật hệ thống quản lý tài sản,tu-vung-cntt,lesson-43,Bài 43: Quản trị CNTT</t>
-  </si>
-  <si>
-    <t>棚卸し,たなおろし,kiểm kê,名詞,N2,機器の棚卸しを行いました,Tôi đã kiểm kê thiết bị,tu-vung-cntt,lesson-43,Bài 43: Quản trị CNTT</t>
-  </si>
-  <si>
-    <t>端末,たんまつ,thiết bị đầu cuối,名詞,N2,新しい端末を設定しました,Tôi đã cấu hình thiết bị đầu cuối mới,tu-vung-cntt,lesson-43,Bài 43: Quản trị CNTT</t>
-  </si>
-  <si>
-    <t>資産番号,しさんばんごう,mã tài sản,名詞,N1,資産番号を登録してください,Hãy đăng ký mã tài sản,tu-vung-cntt,lesson-43,Bài 43: Quản trị CNTT</t>
-  </si>
-  <si>
-    <t>管理番号,かんりばんごう,mã quản lý,名詞,N2,管理番号を確認しました,Tôi đã kiểm tra mã quản lý,tu-vung-cntt,lesson-43,Bài 43: Quản trị CNTT</t>
-  </si>
-  <si>
-    <t>保証期間,ほしょうきかん,thời gian bảo hành,名詞,N2,保証期間は来月までです,Thời gian bảo hành đến tháng sau,tu-vung-cntt,lesson-43,Bài 43: Quản trị CNTT</t>
-  </si>
-  <si>
-    <t>更新期限,こうしんきげん,hạn gia hạn,名詞,N2,更新期限を確認してください,Hãy kiểm tra hạn gia hạn,tu-vung-cntt,lesson-43,Bài 43: Quản trị CNTT</t>
-  </si>
-  <si>
-    <t>保守契約,ほしゅけいやく,hợp đồng bảo trì,名詞,N1,保守契約を更新しました,Tôi đã gia hạn hợp đồng bảo trì,tu-vung-cntt,lesson-43,Bài 43: Quản trị CNTT</t>
-  </si>
-  <si>
-    <t>障害対応,しょうがいたいおう,xử lý sự cố,名詞,N2,障害対応を開始しました,Tôi đã bắt đầu xử lý sự cố,tu-vung-cntt,lesson-43,Bài 43: Quản trị CNTT</t>
-  </si>
-  <si>
-    <t>保守担当,ほしゅたんとう,nhân viên bảo trì,名詞,N2,保守担当へ連絡しました,Tôi đã liên hệ nhân viên bảo trì,tu-vung-cntt,lesson-43,Bài 43: Quản trị CNTT</t>
-  </si>
-  <si>
-    <t>更新履歴,こうしんりれき,lịch sử cập nhật,名詞,N2,更新履歴を保存しました,Tôi đã lưu lịch sử cập nhật,tu-vung-cntt,lesson-43,Bài 43: Quản trị CNTT</t>
-  </si>
-  <si>
-    <t>運用手順書,うんようてじゅんしょ,tài liệu vận hành,名詞,N1,運用手順書を作成しました,Tôi đã tạo tài liệu vận hành,tu-vung-cntt,lesson-43,Bài 43: Quản trị CNTT</t>
-  </si>
-  <si>
-    <t>監査,かんさ,kiểm toán,名詞,N1,監査に向けて準備しています,Tôi đang chuẩn bị cho đợt kiểm toán,tu-vung-cntt,lesson-43,Bài 43: Quản trị CNTT</t>
-  </si>
-  <si>
-    <t>ベンチマーク,べんちまーく,benchmark,名詞,N1,ベンチマークを実施しました,Tôi đã thực hiện benchmark,tu-vung-cntt,lesson-44,Bài 44: Thuật ngữ IT nâng cao</t>
-  </si>
-  <si>
-    <t>スループット,するーぷっと,thông lượng,名詞,N1,システムのスループットを測定しました,Tôi đã đo thông lượng của hệ thống,tu-vung-cntt,lesson-44,Bài 44: Thuật ngữ IT nâng cao</t>
-  </si>
-  <si>
-    <t>レイテンシ,れいてんし,độ trễ,名詞,N1,レイテンシを改善しました,Tôi đã cải thiện độ trễ,tu-vung-cntt,lesson-44,Bài 44: Thuật ngữ IT nâng cao</t>
-  </si>
-  <si>
-    <t>ボトルネック,ぼとるねっく,điểm nghẽn,名詞,N1,ボトルネックを特定しました,Tôi đã xác định điểm nghẽn,tu-vung-cntt,lesson-44,Bài 44: Thuật ngữ IT nâng cao</t>
-  </si>
-  <si>
-    <t>キャッシュ,きゃっしゅ,bộ nhớ đệm,名詞,N2,キャッシュを削除しました,Tôi đã xóa bộ nhớ đệm,tu-vung-cntt,lesson-44,Bài 44: Thuật ngữ IT nâng cao</t>
-  </si>
-  <si>
-    <t>メモリリーク,めもりりーく,rò rỉ bộ nhớ,名詞,N1,メモリリークを修正しました,Tôi đã sửa lỗi rò rỉ bộ nhớ,tu-vung-cntt,lesson-44,Bài 44: Thuật ngữ IT nâng cao</t>
-  </si>
-  <si>
-    <t>ガベージコレクション,がべーじこれくしょん,thu gom rác,名詞,N1,ガベージコレクションを調整しました,Tôi đã điều chỉnh garbage collection,tu-vung-cntt,lesson-44,Bài 44: Thuật ngữ IT nâng cao</t>
-  </si>
-  <si>
-    <t>並列処理,へいれつしょり,xử lý song song,名詞,N1,並列処理で性能を向上しました,Tôi đã cải thiện hiệu năng bằng xử lý song song,tu-vung-cntt,lesson-44,Bài 44: Thuật ngữ IT nâng cao</t>
-  </si>
-  <si>
-    <t>非同期処理,ひどうきしょり,xử lý bất đồng bộ,名詞,N1,非同期処理を導入しました,Tôi đã triển khai xử lý bất đồng bộ,tu-vung-cntt,lesson-44,Bài 44: Thuật ngữ IT nâng cao</t>
-  </si>
-  <si>
-    <t>マルチスレッド,まるちすれっど,đa luồng,名詞,N1,マルチスレッドで実装しました,Tôi đã triển khai bằng đa luồng,tu-vung-cntt,lesson-44,Bài 44: Thuật ngữ IT nâng cao</t>
-  </si>
-  <si>
-    <t>アルゴリズム,あるごりずむ,thuật toán,名詞,N2,新しいアルゴリズムを実装しました,Tôi đã triển khai thuật toán mới,tu-vung-cntt,lesson-44,Bài 44: Thuật ngữ IT nâng cao</t>
-  </si>
-  <si>
-    <t>計算量,けいさんりょう,độ phức tạp tính toán,名詞,N1,計算量を改善しました,Tôi đã cải thiện độ phức tạp tính toán,tu-vung-cntt,lesson-44,Bài 44: Thuật ngữ IT nâng cao</t>
-  </si>
-  <si>
-    <t>最適解,さいてきかい,lời giải tối ưu,名詞,N1,最適解を見つけました,Tôi đã tìm được lời giải tối ưu,tu-vung-cntt,lesson-44,Bài 44: Thuật ngữ IT nâng cao</t>
-  </si>
-  <si>
-    <t>可読性,かどくせい,tính dễ đọc của mã,名詞,N1,コードの可読性を改善しました,Tôi đã cải thiện tính dễ đọc của mã,tu-vung-cntt,lesson-44,Bài 44: Thuật ngữ IT nâng cao</t>
-  </si>
-  <si>
-    <t>保守性,ほしゅせい,tính dễ bảo trì,名詞,N1,保守性を高めました,Tôi đã nâng cao tính dễ bảo trì của hệ thống,tu-vung-cntt,lesson-44,Bài 44: Thuật ngữ IT nâng cao</t>
+    <t>パソコン,ぱそこん,máy tính,N,N5,会社で毎日パソコンを使って仕事をします,Hằng ngày tôi dùng máy tính để làm việc ở công ty,tu-vung-cntt,lesson-01,Bài 1: Thiết bị và khái niệm cơ bản</t>
+  </si>
+  <si>
+    <t>ファイル,ふぁいる,tệp tin,N,N5,このファイルを先に開いて内容を確認してください,Hãy mở tệp này trước và kiểm tra nội dung,tu-vung-cntt,lesson-01,Bài 1: Thiết bị và khái niệm cơ bản</t>
+  </si>
+  <si>
+    <t>フォルダ,ふぉるだ,thư mục,N,N5,資料はこのフォルダの中に保存してあります,Tài liệu được lưu trong thư mục này,tu-vung-cntt,lesson-01,Bài 1: Thiết bị và khái niệm cơ bản</t>
+  </si>
+  <si>
+    <t>保存,ほぞん,lưu dữ liệu,N,N5,作業が終わったら必ず保存してください,Sau khi làm xong hãy nhớ lưu lại,tu-vung-cntt,lesson-01,Bài 1: Thiết bị và khái niệm cơ bản</t>
+  </si>
+  <si>
+    <t>削除,さくじょ,xóa,N,N4,不要なファイルは昨日全部削除しました,Hôm qua tôi đã xóa toàn bộ tệp không cần thiết,tu-vung-cntt,lesson-01,Bài 1: Thiết bị và khái niệm cơ bản</t>
+  </si>
+  <si>
+    <t>検索,けんさく,tìm kiếm,N,N4,必要な資料を社内システムで検索します,Tôi tìm tài liệu cần thiết trên hệ thống nội bộ,tu-vung-cntt,lesson-01,Bài 1: Thiết bị và khái niệm cơ bản</t>
+  </si>
+  <si>
+    <t>画面,がめん,màn hình,N,N4,画面が暗いので明るさを上げてください,Màn hình tối nên hãy tăng độ sáng,tu-vung-cntt,lesson-01,Bài 1: Thiết bị và khái niệm cơ bản</t>
+  </si>
+  <si>
+    <t>入力,にゅうりょく,nhập dữ liệu,N,N4,名前と住所を正しく入力してください,Hãy nhập đúng họ tên và địa chỉ,tu-vung-cntt,lesson-01,Bài 1: Thiết bị và khái niệm cơ bản</t>
+  </si>
+  <si>
+    <t>出力,しゅつりょく,xuất dữ liệu,N,N4,結果をPDFで出力して共有しました,Tôi đã xuất kết quả thành PDF và chia sẻ,tu-vung-cntt,lesson-01,Bài 1: Thiết bị và khái niệm cơ bản</t>
+  </si>
+  <si>
+    <t>印刷,いんさつ,in,N,N4,この資料を二部印刷してください,Hãy in tài liệu này thành hai bản,tu-vung-cntt,lesson-01,Bài 1: Thiết bị và khái niệm cơ bản</t>
+  </si>
+  <si>
+    <t>接続,せつぞく,kết nối,N,N3,サーバーとの接続をもう一度確認してください,Hãy kiểm tra lại kết nối với máy chủ,tu-vung-cntt,lesson-01,Bài 1: Thiết bị và khái niệm cơ bản</t>
+  </si>
+  <si>
+    <t>更新,こうしん,cập nhật,N,N3,システムを最新の状態に更新しました,Tôi đã cập nhật hệ thống lên phiên bản mới nhất,tu-vung-cntt,lesson-01,Bài 1: Thiết bị và khái niệm cơ bản</t>
+  </si>
+  <si>
+    <t>設定,せってい,cài đặt,N,N3,ネットワークの設定を変更しました,Tôi đã thay đổi cài đặt mạng,tu-vung-cntt,lesson-01,Bài 1: Thiết bị và khái niệm cơ bản</t>
+  </si>
+  <si>
+    <t>共有,きょうゆう,chia sẻ,N,N3,完成した資料をチーム全員へ共有しました,Tôi đã chia sẻ tài liệu hoàn thành cho cả nhóm,tu-vung-cntt,lesson-01,Bài 1: Thiết bị và khái niệm cơ bản</t>
+  </si>
+  <si>
+    <t>管理,かんり,quản lý,N,N3,私は毎日サーバーを管理しています,Tôi quản lý máy chủ mỗi ngày,tu-vung-cntt,lesson-01,Bài 1: Thiết bị và khái niệm cơ bản</t>
+  </si>
+  <si>
+    <t>サーバー,さーばー,máy chủ,N,N3,新しいサーバーは昨日から正常に動いています,Máy chủ mới đã hoạt động bình thường từ hôm qua,tu-vung-cntt,lesson-02,Bài 2: Hệ thống và phát triển phần mềm</t>
+  </si>
+  <si>
+    <t>ネットワーク,ねっとわーく,mạng,N,N3,ネットワークに問題がないか確認してください,Hãy kiểm tra xem mạng có vấn đề không,tu-vung-cntt,lesson-02,Bài 2: Hệ thống và phát triển phần mềm</t>
+  </si>
+  <si>
+    <t>データベース,でーたべーす,cơ sở dữ liệu,N,N3,顧客情報はデータベースに保存されています,Thông tin khách hàng được lưu trong cơ sở dữ liệu,tu-vung-cntt,lesson-02,Bài 2: Hệ thống và phát triển phần mềm</t>
+  </si>
+  <si>
+    <t>プログラム,ぷろぐらむ,chương trình,N,N3,このプログラムは毎朝自動で実行されます,Chương trình này tự động chạy mỗi sáng,tu-vung-cntt,lesson-02,Bài 2: Hệ thống và phát triển phần mềm</t>
+  </si>
+  <si>
+    <t>ソフトウェア,そふとうぇあ,phần mềm,N,N3,新しいソフトウェアを今日インストールしました,Hôm nay tôi đã cài phần mềm mới,tu-vung-cntt,lesson-02,Bài 2: Hệ thống và phát triển phần mềm</t>
+  </si>
+  <si>
+    <t>ハードウェア,はーどうぇあ,phần cứng,N,N3,ハードウェアの故障を詳しく調べています,Chúng tôi đang kiểm tra kỹ lỗi phần cứng,tu-vung-cntt,lesson-02,Bài 2: Hệ thống và phát triển phần mềm</t>
+  </si>
+  <si>
+    <t>開発,かいはつ,phát triển,N,N3,新しいシステムの開発を担当しています,Tôi phụ trách phát triển hệ thống mới,tu-vung-cntt,lesson-02,Bài 2: Hệ thống và phát triển phần mềm</t>
+  </si>
+  <si>
+    <t>運用,うんよう,vận hành,N,N3,サービスの運用は二十四時間続きます,Dịch vụ được vận hành hai mươi bốn giờ,tu-vung-cntt,lesson-02,Bài 2: Hệ thống và phát triển phần mềm</t>
+  </si>
+  <si>
+    <t>障害,しょうがい,sự cố,N,N3,障害が発生したので原因を調査しています,Đã xảy ra sự cố nên đang điều tra nguyên nhân,tu-vung-cntt,lesson-02,Bài 2: Hệ thống và phát triển phần mềm</t>
+  </si>
+  <si>
+    <t>復旧,ふっきゅう,khôi phục,N,N3,システムは一時間で復旧しました,Hệ thống đã được khôi phục trong một giờ,tu-vung-cntt,lesson-02,Bài 2: Hệ thống và phát triển phần mềm</t>
+  </si>
+  <si>
+    <t>保守,ほしゅ,bảo trì,N,N3,毎週日曜日にサーバーを保守します,Mỗi Chủ nhật chúng tôi bảo trì máy chủ,tu-vung-cntt,lesson-02,Bài 2: Hệ thống và phát triển phần mềm</t>
+  </si>
+  <si>
+    <t>暗号化,あんごうか,mã hóa,N,N3,重要なデータは暗号化して送信します,Dữ liệu quan trọng được mã hóa trước khi gửi,tu-vung-cntt,lesson-02,Bài 2: Hệ thống và phát triển phần mềm</t>
+  </si>
+  <si>
+    <t>認証,にんしょう,xác thực,N,N3,利用者は認証の後でログインできます,Người dùng có thể đăng nhập sau khi xác thực,tu-vung-cntt,lesson-02,Bài 2: Hệ thống và phát triển phần mềm</t>
+  </si>
+  <si>
+    <t>監視,かんし,giám sát,N,N3,システムを夜間も継続して監視しています,Chúng tôi tiếp tục giám sát hệ thống cả ban đêm,tu-vung-cntt,lesson-02,Bài 2: Hệ thống và phát triển phần mềm</t>
+  </si>
+  <si>
+    <t>バックアップ,ばっくあっぷ,sao lưu,N,N3,毎日自動でバックアップを作成しています,Hệ thống tự động tạo bản sao lưu mỗi ngày,tu-vung-cntt,lesson-02,Bài 2: Hệ thống và phát triển phần mềm</t>
+  </si>
+  <si>
+    <t>ログイン,ろぐいん,đăng nhập,N,N5,朝会社に着いたらすぐログインします,Sáng đến công ty tôi đăng nhập ngay,tu-vung-cntt,lesson-03,Bài 3: Internet và bảo mật</t>
+  </si>
+  <si>
+    <t>ログアウト,ろぐあうと,đăng xuất,N,N5,帰る前に必ずログアウトしてください,Hãy nhớ đăng xuất trước khi về,tu-vung-cntt,lesson-03,Bài 3: Internet và bảo mật</t>
+  </si>
+  <si>
+    <t>メール,めーる,email,N,N5,お客様からメールが届きました,Tôi đã nhận được email từ khách hàng,tu-vung-cntt,lesson-03,Bài 3: Internet và bảo mật</t>
+  </si>
+  <si>
+    <t>パスワード,ぱすわーど,mật khẩu,N,N5,パスワードは他の人に教えません,Tôi không tiết lộ mật khẩu cho người khác,tu-vung-cntt,lesson-03,Bài 3: Internet và bảo mật</t>
+  </si>
+  <si>
+    <t>ユーザー,ゆーざー,người dùng,N,N4,新しいユーザーを追加しました,Tôi đã thêm người dùng mới,tu-vung-cntt,lesson-03,Bài 3: Internet và bảo mật</t>
+  </si>
+  <si>
+    <t>アカウント,あかうんと,tài khoản,N,N4,このアカウントはまだ利用できます,Tài khoản này vẫn có thể sử dụng,tu-vung-cntt,lesson-03,Bài 3: Internet và bảo mật</t>
+  </si>
+  <si>
+    <t>ブラウザ,ぶらうざ,trình duyệt,N,N4,ブラウザを最新版に更新してください,Hãy cập nhật trình duyệt lên phiên bản mới nhất,tu-vung-cntt,lesson-03,Bài 3: Internet và bảo mật</t>
+  </si>
+  <si>
+    <t>ウェブサイト,うぇぶさいと,trang web,N,N4,会社のウェブサイトを毎日確認します,Tôi kiểm tra trang web công ty mỗi ngày,tu-vung-cntt,lesson-03,Bài 3: Internet và bảo mật</t>
+  </si>
+  <si>
+    <t>ダウンロード,だうんろーど,tải xuống,N,N4,必要な資料をダウンロードしました,Tôi đã tải xuống tài liệu cần thiết,tu-vung-cntt,lesson-03,Bài 3: Internet và bảo mật</t>
+  </si>
+  <si>
+    <t>アップロード,あっぷろーど,tải lên,N,N4,完成したファイルをアップロードしてください,Hãy tải lên tệp đã hoàn thành,tu-vung-cntt,lesson-03,Bài 3: Internet và bảo mật</t>
+  </si>
+  <si>
+    <t>アクセス,あくせす,truy cập,N,N3,このフォルダには誰でもアクセスできます,Mọi người đều có thể truy cập thư mục này,tu-vung-cntt,lesson-03,Bài 3: Internet và bảo mật</t>
+  </si>
+  <si>
+    <t>通信,つうしん,giao tiếp dữ liệu,N,N3,通信速度が急に遅くなりました,Tốc độ truyền dữ liệu đột nhiên chậm lại,tu-vung-cntt,lesson-03,Bài 3: Internet và bảo mật</t>
+  </si>
+  <si>
+    <t>セキュリティ,せきゅりてぃ,bảo mật,N,N3,セキュリティを強化する必要があります,Cần tăng cường bảo mật,tu-vung-cntt,lesson-03,Bài 3: Internet và bảo mật</t>
+  </si>
+  <si>
+    <t>ウイルス,ういるす,vi rút máy tính,N,N3,ウイルスを検出したので削除しました,Tôi đã phát hiện và xóa vi rút,tu-vung-cntt,lesson-03,Bài 3: Internet và bảo mật</t>
+  </si>
+  <si>
+    <t>ファイアウォール,ふぁいあうぉーる,tường lửa,N,N3,ファイアウォールの設定を確認してください,Hãy kiểm tra cài đặt tường lửa,tu-vung-cntt,lesson-03,Bài 3: Internet và bảo mật</t>
+  </si>
+  <si>
+    <t>エラー,えらー,lỗi,N,N5,システムにエラーが表示されました,Hệ thống đã hiển thị lỗi,tu-vung-cntt,lesson-04,Bài 4: Lập trình và xử lý sự cố</t>
+  </si>
+  <si>
+    <t>修正,しゅうせい,sửa chữa,N,N4,見つかった問題をすぐ修正しました,Tôi đã sửa ngay vấn đề được phát hiện,tu-vung-cntt,lesson-04,Bài 4: Lập trình và xử lý sự cố</t>
+  </si>
+  <si>
+    <t>確認,かくにん,kiểm tra xác nhận,N,N4,変更した内容をもう一度確認してください,Hãy kiểm tra lại nội dung đã thay đổi,tu-vung-cntt,lesson-04,Bài 4: Lập trình và xử lý sự cố</t>
+  </si>
+  <si>
+    <t>実行,じっこう,thực thi,N,N4,プログラムを実行して結果を確認します,Tôi chạy chương trình và kiểm tra kết quả,tu-vung-cntt,lesson-04,Bài 4: Lập trình và xử lý sự cố</t>
+  </si>
+  <si>
+    <t>停止,ていし,dừng,N,N4,サービスを一時停止しました,Dịch vụ đã được tạm dừng,tu-vung-cntt,lesson-04,Bài 4: Lập trình và xử lý sự cố</t>
+  </si>
+  <si>
+    <t>再起動,さいきどう,khởi động lại,N,N4,サーバーを再起動してみてください,Hãy thử khởi động lại máy chủ,tu-vung-cntt,lesson-04,Bài 4: Lập trình và xử lý sự cố</t>
+  </si>
+  <si>
+    <t>起動,きどう,khởi động,N,N4,パソコンは正常に起動しました,Máy tính đã khởi động bình thường,tu-vung-cntt,lesson-04,Bài 4: Lập trình và xử lý sự cố</t>
+  </si>
+  <si>
+    <t>終了,しゅうりょう,kết thúc,N,N4,作業が終わったらアプリを終了します,Sau khi xong việc tôi sẽ đóng ứng dụng,tu-vung-cntt,lesson-04,Bài 4: Lập trình và xử lý sự cố</t>
+  </si>
+  <si>
+    <t>処理,しょり,xử lý,N,N3,大量のデータを高速で処理できます,Có thể xử lý lượng lớn dữ liệu với tốc độ cao,tu-vung-cntt,lesson-04,Bài 4: Lập trình và xử lý sự cố</t>
+  </si>
+  <si>
+    <t>自動化,じどうか,tự động hóa,N,N3,定型作業を自動化しました,Tôi đã tự động hóa các công việc lặp lại,tu-vung-cntt,lesson-04,Bài 4: Lập trình và xử lý sự cố</t>
+  </si>
+  <si>
+    <t>最適化,さいてきか,tối ưu hóa,N,N3,システムの性能を最適化しています,Chúng tôi đang tối ưu hiệu năng hệ thống,tu-vung-cntt,lesson-04,Bài 4: Lập trình và xử lý sự cố</t>
+  </si>
+  <si>
+    <t>送信,そうしん,gửi,N,N4,資料をお客様へ送信しました,Tôi đã gửi tài liệu cho khách hàng,tu-vung-cntt,lesson-04,Bài 4: Lập trình và xử lý sự cố</t>
+  </si>
+  <si>
+    <t>受信,じゅしん,nhận,N,N4,新しいデータを正常に受信しました,Hệ thống đã nhận dữ liệu mới thành công,tu-vung-cntt,lesson-04,Bài 4: Lập trình và xử lý sự cố</t>
+  </si>
+  <si>
+    <t>プリンター,ぷりんたー,máy in,N,N5,プリンターで会議資料を印刷しました,Tôi đã in tài liệu cuộc họp bằng máy in,tu-vung-cntt,lesson-05,Bài 5: Thiết bị và văn phòng IT</t>
+  </si>
+  <si>
+    <t>スキャナー,すきゃなー,máy quét,N,N5,契約書をスキャナーで読み取りました,Tôi đã quét hợp đồng bằng máy quét,tu-vung-cntt,lesson-05,Bài 5: Thiết bị và văn phòng IT</t>
+  </si>
+  <si>
+    <t>キーボード,きーぼーど,bàn phím,N,N5,キーボードの一部のキーが反応しません,Một số phím trên bàn phím không phản hồi,tu-vung-cntt,lesson-05,Bài 5: Thiết bị và văn phòng IT</t>
+  </si>
+  <si>
+    <t>マウス,まうす,chuột máy tính,N,N5,新しいマウスはとても使いやすいです,Chuột mới rất dễ sử dụng,tu-vung-cntt,lesson-05,Bài 5: Thiết bị và văn phòng IT</t>
+  </si>
+  <si>
+    <t>ケーブル,けーぶる,cáp,N,N4,ネットワークケーブルを交換してください,Hãy thay dây cáp mạng,tu-vung-cntt,lesson-05,Bài 5: Thiết bị và văn phòng IT</t>
+  </si>
+  <si>
+    <t>モニター,もにたー,màn hình,N,N4,モニターを二台使って作業しています,Tôi làm việc với hai màn hình,tu-vung-cntt,lesson-05,Bài 5: Thiết bị và văn phòng IT</t>
+  </si>
+  <si>
+    <t>電源,でんげん,nguồn điện,N,N4,電源が入らないので確認してください,Hãy kiểm tra vì máy không lên nguồn,tu-vung-cntt,lesson-05,Bài 5: Thiết bị và văn phòng IT</t>
+  </si>
+  <si>
+    <t>故障,こしょう,hỏng hóc,N,N3,プリンターが故障したので修理を依頼しました,Máy in bị hỏng nên tôi đã yêu cầu sửa chữa,tu-vung-cntt,lesson-05,Bài 5: Thiết bị và văn phòng IT</t>
+  </si>
+  <si>
+    <t>交換,こうかん,thay thế,N,N3,古いディスクを新しい物へ交換しました,Tôi đã thay ổ đĩa cũ bằng ổ mới,tu-vung-cntt,lesson-05,Bài 5: Thiết bị và văn phòng IT</t>
+  </si>
+  <si>
+    <t>点検,てんけん,kiểm tra bảo dưỡng,N,N3,毎月機器を点検しています,Chúng tôi kiểm tra thiết bị mỗi tháng,tu-vung-cntt,lesson-05,Bài 5: Thiết bị và văn phòng IT</t>
+  </si>
+  <si>
+    <t>修理,しゅうり,sửa chữa,N,N3,壊れたパソコンを修理しました,Tôi đã sửa chiếc máy tính bị hỏng,tu-vung-cntt,lesson-05,Bài 5: Thiết bị và văn phòng IT</t>
+  </si>
+  <si>
+    <t>部品,ぶひん,linh kiện,N,N3,必要な部品がまだ届いていません,Linh kiện cần thiết vẫn chưa được giao tới,tu-vung-cntt,lesson-05,Bài 5: Thiết bị và văn phòng IT</t>
+  </si>
+  <si>
+    <t>機器,きき,thiết bị,N,N3,新しい機器を会議室へ設置しました,Tôi đã lắp đặt thiết bị mới trong phòng họp,tu-vung-cntt,lesson-05,Bài 5: Thiết bị và văn phòng IT</t>
+  </si>
+  <si>
+    <t>コード,こーど,mã nguồn,N,N4,コードを変更する前に確認してください,Hãy kiểm tra trước khi sửa mã nguồn,tu-vung-cntt,lesson-06,Bài 6: Lập trình và phát triển phần mềm</t>
+  </si>
+  <si>
+    <t>変数,へんすう,biến,N,N3,変数の名前を分かりやすくしてください,Hãy đặt tên biến dễ hiểu hơn,tu-vung-cntt,lesson-06,Bài 6: Lập trình và phát triển phần mềm</t>
+  </si>
+  <si>
+    <t>関数,かんすう,hàm,N,N3,この関数はデータを並べ替えます,Hàm này sắp xếp dữ liệu,tu-vung-cntt,lesson-06,Bài 6: Lập trình và phát triển phần mềm</t>
+  </si>
+  <si>
+    <t>配列,はいれつ,mảng,N,N3,配列の要素を一つずつ表示します,Hiển thị từng phần tử của mảng,tu-vung-cntt,lesson-06,Bài 6: Lập trình và phát triển phần mềm</t>
+  </si>
+  <si>
+    <t>文字列,もじれつ,chuỗi ký tự,N,N3,文字列の長さを確認してください,Hãy kiểm tra độ dài chuỗi ký tự,tu-vung-cntt,lesson-06,Bài 6: Lập trình và phát triển phần mềm</t>
+  </si>
+  <si>
+    <t>仕様,しよう,đặc tả yêu cầu,N,N3,仕様を読んでから開発を始めます,Tôi đọc đặc tả trước khi bắt đầu phát triển,tu-vung-cntt,lesson-06,Bài 6: Lập trình và phát triển phần mềm</t>
+  </si>
+  <si>
+    <t>設計,せっけい,thiết kế,N,N3,設計が終わってから実装します,Sau khi thiết kế xong mới tiến hành lập trình,tu-vung-cntt,lesson-06,Bài 6: Lập trình và phát triển phần mềm</t>
+  </si>
+  <si>
+    <t>実装,じっそう,triển khai lập trình,N,N3,新しい機能を実装しました,Tôi đã triển khai tính năng mới,tu-vung-cntt,lesson-06,Bài 6: Lập trình và phát triển phần mềm</t>
+  </si>
+  <si>
+    <t>試験,しけん,kiểm thử,N,N3,試験の結果に問題はありません,Kết quả kiểm thử không có vấn đề,tu-vung-cntt,lesson-06,Bài 6: Lập trình và phát triển phần mềm</t>
+  </si>
+  <si>
+    <t>デバッグ,でばっぐ,gỡ lỗi,N,N3,一日中デバッグを続けました,Tôi đã gỡ lỗi suốt cả ngày,tu-vung-cntt,lesson-06,Bài 6: Lập trình và phát triển phần mềm</t>
+  </si>
+  <si>
+    <t>不具合,ふぐあい,lỗi phần mềm,N,N3,不具合の原因を調査しています,Chúng tôi đang điều tra nguyên nhân lỗi phần mềm,tu-vung-cntt,lesson-06,Bài 6: Lập trình và phát triển phần mềm</t>
+  </si>
+  <si>
+    <t>品質,ひんしつ,chất lượng,N,N3,品質を高めるために改善します,Chúng tôi cải tiến để nâng cao chất lượng,tu-vung-cntt,lesson-06,Bài 6: Lập trình và phát triển phần mềm</t>
+  </si>
+  <si>
+    <t>納期,のうき,thời hạn giao,N,N3,納期までに作業を完了します,Tôi sẽ hoàn thành công việc trước thời hạn,tu-vung-cntt,lesson-06,Bài 6: Lập trình và phát triển phần mềm</t>
+  </si>
+  <si>
+    <t>担当者,たんとうしゃ,người phụ trách,N,N3,担当者へ直接連絡してください,Hãy liên hệ trực tiếp với người phụ trách,tu-vung-cntt,lesson-06,Bài 6: Lập trình và phát triển phần mềm</t>
+  </si>
+  <si>
+    <t>改善,かいぜん,cải tiến,N,N3,利用者の意見を参考に改善しました,Chúng tôi đã cải tiến dựa trên ý kiến người dùng,tu-vung-cntt,lesson-06,Bài 6: Lập trình và phát triển phần mềm</t>
+  </si>
+  <si>
+    <t>画面共有,がめんきょうゆう,chia sẻ màn hình,N,N4,会議で画面共有を使って説明しました,Tôi đã dùng chia sẻ màn hình để giải thích trong cuộc họp,tu-vung-cntt,lesson-07,Bài 7: Họp trực tuyến và làm việc nhóm</t>
+  </si>
+  <si>
+    <t>オンライン会議,おんらいんかいぎ,họp trực tuyến,N,N4,今日はオンライン会議が三回あります,Hôm nay có ba cuộc họp trực tuyến,tu-vung-cntt,lesson-07,Bài 7: Họp trực tuyến và làm việc nhóm</t>
+  </si>
+  <si>
+    <t>チャット,ちゃっと,trò chuyện trực tuyến,N,N5,分からないことはチャットで質問してください,Nếu không hiểu hãy hỏi qua chat,tu-vung-cntt,lesson-07,Bài 7: Họp trực tuyến và làm việc nhóm</t>
+  </si>
+  <si>
+    <t>通知,つうち,thông báo,N,N4,新しい通知がスマートフォンに届きました,Một thông báo mới đã đến điện thoại,tu-vung-cntt,lesson-07,Bài 7: Họp trực tuyến và làm việc nhóm</t>
+  </si>
+  <si>
+    <t>参加,さんか,tham gia,N,N4,全員が会議に参加しました,Mọi người đều đã tham gia cuộc họp,tu-vung-cntt,lesson-07,Bài 7: Họp trực tuyến và làm việc nhóm</t>
+  </si>
+  <si>
+    <t>退出,たいしゅつ,rời khỏi,N,N3,会議が終わったので退出しました,Cuộc họp kết thúc nên tôi đã rời phòng họp,tu-vung-cntt,lesson-07,Bài 7: Họp trực tuyến và làm việc nhóm</t>
+  </si>
+  <si>
+    <t>招待,しょうたい,lời mời,N,N3,会議の招待をメールで送りました,Tôi đã gửi lời mời họp qua email,tu-vung-cntt,lesson-07,Bài 7: Họp trực tuyến và làm việc nhóm</t>
+  </si>
+  <si>
+    <t>会議室,かいぎしつ,phòng họp,N,N5,午後は会議室で打ち合わせをします,Chiều nay chúng tôi họp tại phòng họp,tu-vung-cntt,lesson-07,Bài 7: Họp trực tuyến và làm việc nhóm</t>
+  </si>
+  <si>
+    <t>録画,ろくが,ghi hình,N,N3,重要な説明を録画しました,Tôi đã ghi hình phần giải thích quan trọng,tu-vung-cntt,lesson-07,Bài 7: Họp trực tuyến và làm việc nhóm</t>
+  </si>
+  <si>
+    <t>録音,ろくおん,ghi âm,N,N3,会議の内容を録音しています,Nội dung cuộc họp đang được ghi âm,tu-vung-cntt,lesson-07,Bài 7: Họp trực tuyến và làm việc nhóm</t>
+  </si>
+  <si>
+    <t>発言,はつげん,phát biểu,N,N3,質問があれば自由に発言してください,Nếu có câu hỏi hãy phát biểu tự do,tu-vung-cntt,lesson-07,Bài 7: Họp trực tuyến và làm việc nhóm</t>
+  </si>
+  <si>
+    <t>議事録,ぎじろく,biên bản cuộc họp,N,N3,議事録を午後までに作成します,Tôi sẽ hoàn thành biên bản cuộc họp trước chiều,tu-vung-cntt,lesson-07,Bài 7: Họp trực tuyến và làm việc nhóm</t>
+  </si>
+  <si>
+    <t>共同作業,きょうどうさぎょう,làm việc nhóm,N,N3,共同作業で効率が上がりました,Làm việc nhóm đã nâng cao hiệu quả,tu-vung-cntt,lesson-07,Bài 7: Họp trực tuyến và làm việc nhóm</t>
+  </si>
+  <si>
+    <t>担当,たんとう,phụ trách,N,N3,私はネットワーク担当です,Tôi phụ trách mảng mạng,tu-vung-cntt,lesson-07,Bài 7: Họp trực tuyến và làm việc nhóm</t>
+  </si>
+  <si>
+    <t>利用者,りようしゃ,người sử dụng,N,N4,利用者から多くの質問が届きました,Đã nhận được nhiều câu hỏi từ người dùng,tu-vung-cntt,lesson-08,Bài 8: Hỗ trợ người dùng</t>
+  </si>
+  <si>
+    <t>問い合わせ,といあわせ,yêu cầu hỗ trợ,N,N3,問い合わせにすぐ対応しました,Tôi đã phản hồi yêu cầu hỗ trợ ngay lập tức,tu-vung-cntt,lesson-08,Bài 8: Hỗ trợ người dùng</t>
+  </si>
+  <si>
+    <t>対応,たいおう,xử lý hỗ trợ,N,N3,問題に迅速に対応してください,Hãy xử lý vấn đề một cách nhanh chóng,tu-vung-cntt,lesson-08,Bài 8: Hỗ trợ người dùng</t>
+  </si>
+  <si>
+    <t>受付,うけつけ,tiếp nhận,N,N3,朝から多くの依頼を受付しました,Từ sáng đã tiếp nhận nhiều yêu cầu,tu-vung-cntt,lesson-08,Bài 8: Hỗ trợ người dùng</t>
+  </si>
+  <si>
+    <t>依頼,いらい,yêu cầu,N,N3,新しい依頼を確認してください,Hãy kiểm tra yêu cầu mới,tu-vung-cntt,lesson-08,Bài 8: Hỗ trợ người dùng</t>
+  </si>
+  <si>
+    <t>解決,かいけつ,giải quyết,N,N3,問題を十分で解決しました,Tôi đã giải quyết vấn đề trong mười phút,tu-vung-cntt,lesson-08,Bài 8: Hỗ trợ người dùng</t>
+  </si>
+  <si>
+    <t>原因,げんいん,nguyên nhân,N,N3,原因を詳しく調査しています,Chúng tôi đang điều tra chi tiết nguyên nhân,tu-vung-cntt,lesson-08,Bài 8: Hỗ trợ người dùng</t>
+  </si>
+  <si>
+    <t>現象,げんしょう,hiện tượng,N,N3,同じ現象が何度も発生しました,Hiện tượng tương tự đã xảy ra nhiều lần,tu-vung-cntt,lesson-08,Bài 8: Hỗ trợ người dùng</t>
+  </si>
+  <si>
+    <t>報告,ほうこく,báo cáo,N,N3,結果を上司へ報告しました,Tôi đã báo cáo kết quả với cấp trên,tu-vung-cntt,lesson-08,Bài 8: Hỗ trợ người dùng</t>
+  </si>
+  <si>
+    <t>連絡,れんらく,liên lạc,N,N4,担当者へすぐ連絡してください,Hãy liên lạc ngay với người phụ trách,tu-vung-cntt,lesson-08,Bài 8: Hỗ trợ người dùng</t>
+  </si>
+  <si>
+    <t>説明,せつめい,giải thích,N,N4,操作方法を分かりやすく説明しました,Tôi đã giải thích cách sử dụng một cách dễ hiểu,tu-vung-cntt,lesson-08,Bài 8: Hỗ trợ người dùng</t>
+  </si>
+  <si>
+    <t>操作,そうさ,thao tác,N,N4,操作はとても簡単です,Thao tác rất đơn giản,tu-vung-cntt,lesson-08,Bài 8: Hỗ trợ người dùng</t>
+  </si>
+  <si>
+    <t>案内,あんない,hướng dẫn,N,N3,利用者へ手順を案内しました,Tôi đã hướng dẫn các bước cho người dùng,tu-vung-cntt,lesson-08,Bài 8: Hỗ trợ người dùng</t>
+  </si>
+  <si>
+    <t>手順,てじゅん,các bước thực hiện,N,N3,手順どおりに設定してください,Hãy cài đặt theo đúng các bước,tu-vung-cntt,lesson-08,Bài 8: Hỗ trợ người dùng</t>
+  </si>
+  <si>
+    <t>完了,かんりょう,hoàn tất,N,N3,設定は予定どおり完了しました,Việc cài đặt đã hoàn tất đúng kế hoạch,tu-vung-cntt,lesson-08,Bài 8: Hỗ trợ người dùng</t>
+  </si>
+  <si>
+    <t>エクスプローラー,えくすぷろーらー,File Explorer,N,N4,エクスプローラーで共有フォルダを開いてください,Hãy mở thư mục chia sẻ bằng File Explorer,tu-vung-cntt,lesson-09,Bài 9: Windows và File Explorer</t>
+  </si>
+  <si>
+    <t>デスクトップ,ですくとっぷ,màn hình Desktop,N,N5,デスクトップに新しいフォルダを作りました,Tôi đã tạo một thư mục mới trên Desktop,tu-vung-cntt,lesson-09,Bài 9: Windows và File Explorer</t>
+  </si>
+  <si>
+    <t>ごみ箱,ごみばこ,thùng rác,N,N5,不要なファイルをごみ箱へ移動しました,Tôi đã chuyển tệp không cần thiết vào thùng rác,tu-vung-cntt,lesson-09,Bài 9: Windows và File Explorer</t>
+  </si>
+  <si>
+    <t>コピー,こぴー,sao chép,N,N5,このファイルをUSBへコピーしてください,Hãy sao chép tệp này vào USB,tu-vung-cntt,lesson-09,Bài 9: Windows và File Explorer</t>
+  </si>
+  <si>
+    <t>貼り付け,はりつけ,dán,N,N4,コピーした内容をここへ貼り付けます,Tôi dán nội dung đã sao chép vào đây,tu-vung-cntt,lesson-09,Bài 9: Windows và File Explorer</t>
+  </si>
+  <si>
+    <t>移動,いどう,di chuyển,N,N4,ファイルを別のフォルダへ移動しました,Tôi đã di chuyển tệp sang thư mục khác,tu-vung-cntt,lesson-09,Bài 9: Windows và File Explorer</t>
+  </si>
+  <si>
+    <t>名前変更,なまえへんこう,đổi tên,N,N3,ファイルの名前変更を行いました,Tôi đã đổi tên tệp,tu-vung-cntt,lesson-09,Bài 9: Windows và File Explorer</t>
+  </si>
+  <si>
+    <t>圧縮,あっしゅく,nén tệp,N,N3,大きなファイルを圧縮しました,Tôi đã nén tệp có dung lượng lớn,tu-vung-cntt,lesson-09,Bài 9: Windows và File Explorer</t>
+  </si>
+  <si>
+    <t>展開,てんかい,giải nén,N,N3,ZIPファイルを展開してください,Hãy giải nén tệp ZIP,tu-vung-cntt,lesson-09,Bài 9: Windows và File Explorer</t>
+  </si>
+  <si>
+    <t>ショートカット,しょーとかっと,lối tắt,N,N4,デスクトップにショートカットを作成しました,Tôi đã tạo lối tắt trên Desktop,tu-vung-cntt,lesson-09,Bài 9: Windows và File Explorer</t>
+  </si>
+  <si>
+    <t>ドライブ,どらいぶ,ổ đĩa,N,N4,Dドライブの空き容量を確認してください,Hãy kiểm tra dung lượng trống của ổ D,tu-vung-cntt,lesson-09,Bài 9: Windows và File Explorer</t>
+  </si>
+  <si>
+    <t>容量,ようりょう,dung lượng,N,N3,ディスクの容量が不足しています,Dung lượng ổ đĩa đang không đủ,tu-vung-cntt,lesson-09,Bài 9: Windows và File Explorer</t>
+  </si>
+  <si>
+    <t>読み取り専用,よみとりせんよう,chỉ đọc,N,N3,このファイルは読み取り専用です,Tệp này đang ở chế độ chỉ đọc,tu-vung-cntt,lesson-09,Bài 9: Windows và File Explorer</t>
+  </si>
+  <si>
+    <t>隠しファイル,かくしふぁいる,tệp ẩn,N,N3,隠しファイルを表示してください,Hãy hiển thị các tệp ẩn,tu-vung-cntt,lesson-09,Bài 9: Windows và File Explorer</t>
+  </si>
+  <si>
+    <t>権限,けんげん,quyền truy cập,N,N3,フォルダの権限を変更しました,Tôi đã thay đổi quyền của thư mục,tu-vung-cntt,lesson-09,Bài 9: Windows và File Explorer</t>
+  </si>
+  <si>
+    <t>ドメイン,どめいん,domain,N,N3,新しいパソコンをドメインへ参加させました,Tôi đã đưa máy tính mới vào domain,tu-vung-cntt,lesson-10,Bài 10: Domain và Active Directory</t>
+  </si>
+  <si>
+    <t>管理者,かんりしゃ,quản trị viên,N,N3,管理者だけ設定を変更できます,Chỉ quản trị viên mới có thể thay đổi cài đặt,tu-vung-cntt,lesson-10,Bài 10: Domain và Active Directory</t>
+  </si>
+  <si>
+    <t>管理者権限,かんりしゃけんげん,quyền quản trị,N,N3,管理者権限で実行してください,Hãy chạy bằng quyền quản trị,tu-vung-cntt,lesson-10,Bài 10: Domain và Active Directory</t>
+  </si>
+  <si>
+    <t>利用権限,りようけんげん,quyền sử dụng,N,N3,利用権限を追加しました,Tôi đã thêm quyền sử dụng,tu-vung-cntt,lesson-10,Bài 10: Domain và Active Directory</t>
+  </si>
+  <si>
+    <t>組織単位,そしきたんい,OU; đơn vị tổ chức,N,N3,利用者を組織単位へ移動しました,Tôi đã chuyển người dùng vào OU,tu-vung-cntt,lesson-10,Bài 10: Domain và Active Directory</t>
+  </si>
+  <si>
+    <t>グループ,ぐるーぷ,nhóm,N,N5,新しいグループを作成しました,Tôi đã tạo một nhóm mới,tu-vung-cntt,lesson-10,Bài 10: Domain và Active Directory</t>
+  </si>
+  <si>
+    <t>追加,ついか,thêm,N,N4,利用者をグループへ追加しました,Tôi đã thêm người dùng vào nhóm,tu-vung-cntt,lesson-10,Bài 10: Domain và Active Directory</t>
+  </si>
+  <si>
+    <t>有効化,ゆうこうか,kích hoạt,N,N3,アカウントを有効化しました,Tôi đã kích hoạt tài khoản,tu-vung-cntt,lesson-10,Bài 10: Domain và Active Directory</t>
+  </si>
+  <si>
+    <t>無効化,むこうか,vô hiệu hóa,N,N3,退職者のアカウントを無効化しました,Tôi đã vô hiệu hóa tài khoản của nhân viên nghỉ việc,tu-vung-cntt,lesson-10,Bài 10: Domain và Active Directory</t>
+  </si>
+  <si>
+    <t>パスワード変更,ぱすわーどへんこう,đổi mật khẩu,N,N4,利用者のパスワード変更を行いました,Tôi đã đổi mật khẩu cho người dùng,tu-vung-cntt,lesson-10,Bài 10: Domain và Active Directory</t>
+  </si>
+  <si>
+    <t>ロック,ろっく,khóa tài khoản,N,N3,アカウントがロックされました,Tài khoản đã bị khóa,tu-vung-cntt,lesson-10,Bài 10: Domain và Active Directory</t>
+  </si>
+  <si>
+    <t>ロック解除,ろっくかいじょ,mở khóa tài khoản,N,N3,管理者がロック解除しました,Quản trị viên đã mở khóa tài khoản,tu-vung-cntt,lesson-10,Bài 10: Domain và Active Directory</t>
+  </si>
+  <si>
+    <t>IPアドレス,あいぴーあどれす,địa chỉ IP,N,N4,IPアドレスを確認してから接続してください,Hãy kiểm tra địa chỉ IP trước khi kết nối,tu-vung-cntt,lesson-11,Bài 11: Mạng máy tính cơ bản</t>
+  </si>
+  <si>
+    <t>DNS,でぃーえぬえす,DNS,N,N3,DNSの設定が正しいか確認しました,Tôi đã kiểm tra cài đặt DNS có đúng hay không,tu-vung-cntt,lesson-11,Bài 11: Mạng máy tính cơ bản</t>
+  </si>
+  <si>
+    <t>DHCP,でぃーえいちしーぴー,DHCP,N,N3,DHCPからIPアドレスを取得しました,Máy đã nhận địa chỉ IP từ DHCP,tu-vung-cntt,lesson-11,Bài 11: Mạng máy tính cơ bản</t>
+  </si>
+  <si>
+    <t>ルーター,るーたー,bộ định tuyến,N,N4,ルーターを再起動してください,Hãy khởi động lại bộ định tuyến,tu-vung-cntt,lesson-11,Bài 11: Mạng máy tính cơ bản</t>
+  </si>
+  <si>
+    <t>スイッチ,すいっち,bộ chuyển mạch,N,N4,新しいスイッチを設置しました,Tôi đã lắp đặt bộ chuyển mạch mới,tu-vung-cntt,lesson-11,Bài 11: Mạng máy tính cơ bản</t>
+  </si>
+  <si>
+    <t>LAN,らん,mạng LAN,N,N4,LANケーブルを交換しました,Tôi đã thay cáp LAN,tu-vung-cntt,lesson-11,Bài 11: Mạng máy tính cơ bản</t>
+  </si>
+  <si>
+    <t>無線LAN,むせんらん,mạng không dây,N,N3,無線LANへ正常に接続できました,Đã kết nối thành công vào mạng không dây,tu-vung-cntt,lesson-11,Bài 11: Mạng máy tính cơ bản</t>
+  </si>
+  <si>
+    <t>有線,ゆうせん,kết nối có dây,N,N3,有線のほうが通信は安定しています,Kết nối có dây ổn định hơn,tu-vung-cntt,lesson-11,Bài 11: Mạng máy tính cơ bản</t>
+  </si>
+  <si>
+    <t>無線,むせん,kết nối không dây,N,N3,無線でインターネットを利用しています,Tôi sử dụng Internet qua kết nối không dây,tu-vung-cntt,lesson-11,Bài 11: Mạng máy tính cơ bản</t>
+  </si>
+  <si>
+    <t>通信速度,つうしんそくど,tốc độ truyền,N,N3,通信速度を測定してください,Hãy đo tốc độ truyền mạng,tu-vung-cntt,lesson-11,Bài 11: Mạng máy tính cơ bản</t>
+  </si>
+  <si>
+    <t>遅延,ちえん,độ trễ,N,N3,遅延が大きいので確認します,Độ trễ cao nên tôi sẽ kiểm tra,tu-vung-cntt,lesson-11,Bài 11: Mạng máy tính cơ bản</t>
+  </si>
+  <si>
+    <t>接続先,せつぞくさき,điểm kết nối,N,N3,接続先を間違えないでください,Hãy đừng nhầm điểm kết nối,tu-vung-cntt,lesson-11,Bài 11: Mạng máy tính cơ bản</t>
+  </si>
+  <si>
+    <t>固定IP,こていあいぴー,IP tĩnh,N,N3,サーバーは固定IPを使用しています,Máy chủ đang dùng IP tĩnh,tu-vung-cntt,lesson-11,Bài 11: Mạng máy tính cơ bản</t>
+  </si>
+  <si>
+    <t>動的IP,どうてきあいぴー,IP động,N,N3,この端末は動的IPです,Thiết bị này sử dụng IP động,tu-vung-cntt,lesson-11,Bài 11: Mạng máy tính cơ bản</t>
+  </si>
+  <si>
+    <t>疎通確認,そつうかくにん,kiểm tra kết nối,N,N3,サーバーとの疎通確認を行いました,Tôi đã kiểm tra kết nối với máy chủ,tu-vung-cntt,lesson-11,Bài 11: Mạng máy tính cơ bản</t>
+  </si>
+  <si>
+    <t>ping,ぴんぐ,lệnh ping,N,N4,pingでサーバーとの通信を確認します,Tôi kiểm tra kết nối tới máy chủ bằng ping,tu-vung-cntt,lesson-12,Bài 12: Công cụ kiểm tra mạng</t>
+  </si>
+  <si>
+    <t>応答,おうとう,phản hồi,N,N3,サーバーから応答がありません,Không có phản hồi từ máy chủ,tu-vung-cntt,lesson-12,Bài 12: Công cụ kiểm tra mạng</t>
+  </si>
+  <si>
+    <t>パケット,ぱけっと,gói tin,N,N3,パケットが途中で失われました,Gói tin đã bị mất trên đường truyền,tu-vung-cntt,lesson-12,Bài 12: Công cụ kiểm tra mạng</t>
+  </si>
+  <si>
+    <t>ポート,ぽーと,cổng mạng,N,N3,ポート番号を確認してください,Hãy kiểm tra số cổng mạng,tu-vung-cntt,lesson-12,Bài 12: Công cụ kiểm tra mạng</t>
+  </si>
+  <si>
+    <t>ポート番号,ぽーとばんごう,số cổng,N,N3,FTPは二十一番のポート番号を使います,FTP sử dụng cổng số hai mươi mốt,tu-vung-cntt,lesson-12,Bài 12: Công cụ kiểm tra mạng</t>
+  </si>
+  <si>
+    <t>タイムアウト,たいむあうと,hết thời gian chờ,N,N3,接続がタイムアウトしました,Kết nối đã bị hết thời gian chờ,tu-vung-cntt,lesson-12,Bài 12: Công cụ kiểm tra mạng</t>
+  </si>
+  <si>
+    <t>経路,けいろ,tuyến đường truyền,N,N3,通信経路を調査しています,Chúng tôi đang kiểm tra tuyến truyền dữ liệu,tu-vung-cntt,lesson-12,Bài 12: Công cụ kiểm tra mạng</t>
+  </si>
+  <si>
+    <t>tracert,とれーさーと,lệnh tracert,N,N3,tracertで通信経路を確認しました,Tôi đã kiểm tra tuyến truyền bằng tracert,tu-vung-cntt,lesson-12,Bài 12: Công cụ kiểm tra mạng</t>
+  </si>
+  <si>
+    <t>nslookup,えぬえするっくあっぷ,lệnh nslookup,N,N3,nslookupでDNSを確認してください,Hãy kiểm tra DNS bằng nslookup,tu-vung-cntt,lesson-12,Bài 12: Công cụ kiểm tra mạng</t>
+  </si>
+  <si>
+    <t>ipconfig,あいぴーこんふぃぐ,lệnh ipconfig,N,N3,ipconfigで設定を確認しました,Tôi đã kiểm tra cấu hình bằng ipconfig,tu-vung-cntt,lesson-12,Bài 12: Công cụ kiểm tra mạng</t>
+  </si>
+  <si>
+    <t>接続不能,せつぞくふのう,không thể kết nối,N,N3,現在サーバーは接続不能です,Hiện tại không thể kết nối tới máy chủ,tu-vung-cntt,lesson-12,Bài 12: Công cụ kiểm tra mạng</t>
+  </si>
+  <si>
+    <t>通信障害,つうしんしょうがい,sự cố mạng,N,N3,通信障害の原因を調査しています,Chúng tôi đang điều tra nguyên nhân sự cố mạng,tu-vung-cntt,lesson-12,Bài 12: Công cụ kiểm tra mạng</t>
+  </si>
+  <si>
+    <t>復旧作業,ふっきゅうさぎょう,công việc khôi phục,N,N3,復旧作業はもうすぐ完了します,Công việc khôi phục sẽ sớm hoàn tất,tu-vung-cntt,lesson-12,Bài 12: Công cụ kiểm tra mạng</t>
+  </si>
+  <si>
+    <t>共有フォルダ,きょうゆうふぉるだ,thư mục chia sẻ,N,N4,共有フォルダへ資料を保存してください,Hãy lưu tài liệu vào thư mục chia sẻ,tu-vung-cntt,lesson-13,Bài 13: File Server và chia sẻ dữ liệu</t>
+  </si>
+  <si>
+    <t>共有設定,きょうゆうせってい,cài đặt chia sẻ,N,N3,共有設定を変更しました,Tôi đã thay đổi cài đặt chia sẻ,tu-vung-cntt,lesson-13,Bài 13: File Server và chia sẻ dữ liệu</t>
+  </si>
+  <si>
+    <t>アクセス権,あくせすけん,quyền truy cập,N,N3,アクセス権を利用者へ追加しました,Tôi đã cấp quyền truy cập cho người dùng,tu-vung-cntt,lesson-13,Bài 13: File Server và chia sẻ dữ liệu</t>
+  </si>
+  <si>
+    <t>読み取り権限,よみとりけんげん,quyền đọc,N,N3,読み取り権限だけ設定しました,Tôi chỉ cấp quyền đọc,tu-vung-cntt,lesson-13,Bài 13: File Server và chia sẻ dữ liệu</t>
+  </si>
+  <si>
+    <t>書き込み権限,かきこみけんげん,quyền ghi,N,N3,書き込み権限を許可してください,Hãy cấp quyền ghi,tu-vung-cntt,lesson-13,Bài 13: File Server và chia sẻ dữ liệu</t>
+  </si>
+  <si>
+    <t>フルコントロール,ふるこんとろーる,toàn quyền,N,N3,管理者にフルコントロールを付与しました,Tôi đã cấp toàn quyền cho quản trị viên,tu-vung-cntt,lesson-13,Bài 13: File Server và chia sẻ dữ liệu</t>
+  </si>
+  <si>
+    <t>アクセス拒否,あくせすきょひ,từ chối truy cập,N,N3,アクセス拒否の設定を確認してください,Hãy kiểm tra cài đặt từ chối truy cập,tu-vung-cntt,lesson-13,Bài 13: File Server và chia sẻ dữ liệu</t>
+  </si>
+  <si>
+    <t>ネットワークドライブ,ねっとわーくどらいぶ,ổ đĩa mạng,N,N3,ネットワークドライブを割り当てました,Tôi đã ánh xạ ổ đĩa mạng,tu-vung-cntt,lesson-13,Bài 13: File Server và chia sẻ dữ liệu</t>
+  </si>
+  <si>
+    <t>ファイルサーバー,ふぁいるさーばー,file server,N,N3,ファイルサーバーへ接続してください,Hãy kết nối tới file server,tu-vung-cntt,lesson-13,Bài 13: File Server và chia sẻ dữ liệu</t>
+  </si>
+  <si>
+    <t>保存先,ほぞんさき,vị trí lưu,N,N3,保存先を間違えないでください,Hãy đừng chọn sai vị trí lưu,tu-vung-cntt,lesson-13,Bài 13: File Server và chia sẻ dữ liệu</t>
+  </si>
+  <si>
+    <t>空き容量,あきようりょう,dung lượng trống,N,N3,空き容量が少なくなっています,Dung lượng trống đang còn ít,tu-vung-cntt,lesson-13,Bài 13: File Server và chia sẻ dữ liệu</t>
+  </si>
+  <si>
+    <t>使用容量,しようようりょう,dung lượng đã dùng,N,N3,使用容量を毎週確認します,Tôi kiểm tra dung lượng đã sử dụng mỗi tuần,tu-vung-cntt,lesson-13,Bài 13: File Server và chia sẻ dữ liệu</t>
+  </si>
+  <si>
+    <t>所有者,しょゆうしゃ,chủ sở hữu,N,N3,フォルダの所有者を変更しました,Tôi đã thay đổi chủ sở hữu thư mục,tu-vung-cntt,lesson-13,Bài 13: File Server và chia sẻ dữ liệu</t>
+  </si>
+  <si>
+    <t>アクセスログ,あくせすろぐ,nhật ký truy cập,N,N3,アクセスログを確認しています,Tôi đang kiểm tra nhật ký truy cập,tu-vung-cntt,lesson-13,Bài 13: File Server và chia sẻ dữ liệu</t>
+  </si>
+  <si>
+    <t>FTP,えふてぃーぴー,FTP,N,N3,FTPでファイルを送信しました,Tôi đã gửi tệp qua FTP,tu-vung-cntt,lesson-14,Bài 14: FTP và truyền tệp</t>
+  </si>
+  <si>
+    <t>FileZilla,ふぁいるじら,FileZilla,N,N3,FileZillaでサーバーへ接続します,Tôi kết nối tới máy chủ bằng FileZilla,tu-vung-cntt,lesson-14,Bài 14: FTP và truyền tệp</t>
+  </si>
+  <si>
+    <t>FTPサーバー,えふてぃーぴーさーばー,máy chủ FTP,N,N3,FTPサーバーが正常に動作しています,Máy chủ FTP đang hoạt động bình thường,tu-vung-cntt,lesson-14,Bài 14: FTP và truyền tệp</t>
+  </si>
+  <si>
+    <t>転送,てんそう,truyền tệp,N,N3,大きなファイルを転送しています,Tôi đang truyền tệp có dung lượng lớn,tu-vung-cntt,lesson-14,Bài 14: FTP và truyền tệp</t>
+  </si>
+  <si>
+    <t>転送速度,てんそうそくど,tốc độ truyền,N,N3,転送速度が遅くなりました,Tốc độ truyền đã chậm lại,tu-vung-cntt,lesson-14,Bài 14: FTP và truyền tệp</t>
+  </si>
+  <si>
+    <t>転送完了,てんそうかんりょう,truyền xong,N,N3,転送完了の通知が表示されました,Thông báo truyền tệp hoàn tất đã hiển thị,tu-vung-cntt,lesson-14,Bài 14: FTP và truyền tệp</t>
+  </si>
+  <si>
+    <t>認証情報,にんしょうじょうほう,thông tin xác thực,N,N3,認証情報を入力してください,Hãy nhập thông tin xác thực,tu-vung-cntt,lesson-14,Bài 14: FTP và truyền tệp</t>
+  </si>
+  <si>
+    <t>接続情報,せつぞくじょうほう,thông tin kết nối,N,N3,接続情報を確認しました,Tôi đã kiểm tra thông tin kết nối,tu-vung-cntt,lesson-14,Bài 14: FTP và truyền tệp</t>
+  </si>
+  <si>
+    <t>ホスト名,ほすとめい,tên máy chủ,N,N3,ホスト名を正しく入力してください,Hãy nhập đúng tên máy chủ,tu-vung-cntt,lesson-14,Bài 14: FTP và truyền tệp</t>
+  </si>
+  <si>
+    <t>ユーザー名,ゆーざーめい,tên người dùng,N,N4,ユーザー名を忘れました,Tôi đã quên tên người dùng,tu-vung-cntt,lesson-14,Bài 14: FTP và truyền tệp</t>
+  </si>
+  <si>
+    <t>接続成功,せつぞくせいこう,kết nối thành công,N,N3,サーバーへの接続成功を確認しました,Tôi đã xác nhận kết nối thành công tới máy chủ,tu-vung-cntt,lesson-14,Bài 14: FTP và truyền tệp</t>
+  </si>
+  <si>
+    <t>接続失敗,せつぞくしっぱい,kết nối thất bại,N,N3,接続失敗の原因を調査しています,Chúng tôi đang điều tra nguyên nhân kết nối thất bại,tu-vung-cntt,lesson-14,Bài 14: FTP và truyền tệp</t>
+  </si>
+  <si>
+    <t>再接続,さいせつぞく,kết nối lại,N,N3,数分後に再接続してください,Hãy kết nối lại sau vài phút,tu-vung-cntt,lesson-14,Bài 14: FTP và truyền tệp</t>
+  </si>
+  <si>
+    <t>Windows Server,うぃんどうずさーばー,Windows Server,N,N3,Windows Serverを再起動しました,Tôi đã khởi động lại Windows Server,tu-vung-cntt,lesson-15,Bài 15: Windows Server cơ bản</t>
+  </si>
+  <si>
+    <t>Active Directory,あくてぃぶでぃれくとり,Active Directory,N,N3,Active Directoryで利用者を管理します,Quản lý người dùng bằng Active Directory,tu-vung-cntt,lesson-15,Bài 15: Windows Server cơ bản</t>
+  </si>
+  <si>
+    <t>ドメインコントローラー,どめいんこんとろーらー,Domain Controller,N,N3,新しいドメインコントローラーを追加しました,Tôi đã thêm Domain Controller mới,tu-vung-cntt,lesson-15,Bài 15: Windows Server cơ bản</t>
+  </si>
+  <si>
+    <t>レプリケーション,れぷりけーしょん,sao chép đồng bộ,N,N3,レプリケーションが正常に完了しました,Việc đồng bộ sao chép đã hoàn tất,tu-vung-cntt,lesson-15,Bài 15: Windows Server cơ bản</t>
+  </si>
+  <si>
+    <t>役割,やくわり,vai trò,N,N3,新しい役割をサーバーへ追加しました,Tôi đã thêm vai trò mới cho máy chủ,tu-vung-cntt,lesson-15,Bài 15: Windows Server cơ bản</t>
+  </si>
+  <si>
+    <t>機能,きのう,tính năng,N,N3,必要な機能を有効化してください,Hãy kích hoạt tính năng cần thiết,tu-vung-cntt,lesson-15,Bài 15: Windows Server cơ bản</t>
+  </si>
+  <si>
+    <t>イベントビューアー,いべんとびゅーあー,Event Viewer,N,N3,イベントビューアーでエラーを確認しました,Tôi đã kiểm tra lỗi bằng Event Viewer,tu-vung-cntt,lesson-15,Bài 15: Windows Server cơ bản</t>
+  </si>
+  <si>
+    <t>イベントログ,いべんとろぐ,nhật ký sự kiện,N,N3,イベントログを毎日確認しています,Tôi kiểm tra nhật ký sự kiện mỗi ngày,tu-vung-cntt,lesson-15,Bài 15: Windows Server cơ bản</t>
+  </si>
+  <si>
+    <t>サービス,さーびす,dịch vụ,N,N4,サービスが停止しています,Dịch vụ đang dừng hoạt động,tu-vung-cntt,lesson-15,Bài 15: Windows Server cơ bản</t>
+  </si>
+  <si>
+    <t>自動起動,じどうきどう,khởi động tự động,N,N3,サービスを自動起動に設定しました,Tôi đã đặt dịch vụ khởi động tự động,tu-vung-cntt,lesson-15,Bài 15: Windows Server cơ bản</t>
+  </si>
+  <si>
+    <t>手動起動,しゅどうきどう,khởi động thủ công,N,N3,このサービスは手動起動です,Dịch vụ này khởi động thủ công,tu-vung-cntt,lesson-15,Bài 15: Windows Server cơ bản</t>
+  </si>
+  <si>
+    <t>サーバー名,さーばーめい,tên máy chủ,N,N3,サーバー名を変更しました,Tôi đã đổi tên máy chủ,tu-vung-cntt,lesson-15,Bài 15: Windows Server cơ bản</t>
+  </si>
+  <si>
+    <t>ホスト,ほすと,máy chủ; host,N,N3,ホストへ正常に接続しました,Tôi đã kết nối thành công tới host,tu-vung-cntt,lesson-15,Bài 15: Windows Server cơ bản</t>
+  </si>
+  <si>
+    <t>リモートデスクトップ,りもーとですくとっぷ,Remote Desktop,N,N3,リモートデスクトップで接続します,Tôi kết nối bằng Remote Desktop,tu-vung-cntt,lesson-16,Bài 16: Quản trị từ xa</t>
+  </si>
+  <si>
+    <t>リモート接続,りもーとせつぞく,kết nối từ xa,N,N3,リモート接続が切断されました,Kết nối từ xa đã bị ngắt,tu-vung-cntt,lesson-16,Bài 16: Quản trị từ xa</t>
+  </si>
+  <si>
+    <t>資格情報,しかくじょうほう,thông tin xác thực,N,N3,資格情報を保存しました,Tôi đã lưu thông tin xác thực,tu-vung-cntt,lesson-16,Bài 16: Quản trị từ xa</t>
+  </si>
+  <si>
+    <t>ログオン,ろぐおん,đăng nhập hệ thống,N,N3,ログオンできませんでした,Không thể đăng nhập hệ thống,tu-vung-cntt,lesson-16,Bài 16: Quản trị từ xa</t>
+  </si>
+  <si>
+    <t>ログオフ,ろぐおふ,đăng xuất hệ thống,N,N3,作業後にログオフしてください,Hãy đăng xuất sau khi hoàn thành công việc,tu-vung-cntt,lesson-16,Bài 16: Quản trị từ xa</t>
+  </si>
+  <si>
+    <t>セッション,せっしょん,phiên làm việc,N,N3,古いセッションを終了しました,Tôi đã kết thúc phiên làm việc cũ,tu-vung-cntt,lesson-16,Bài 16: Quản trị từ xa</t>
+  </si>
+  <si>
+    <t>切断,せつだん,ngắt kết nối,N,N3,ネットワークが突然切断されました,Mạng đã bị ngắt kết nối đột ngột,tu-vung-cntt,lesson-16,Bài 16: Quản trị từ xa</t>
+  </si>
+  <si>
+    <t>管理ツール,かんりつーる,công cụ quản trị,N,N3,管理ツールを開いてください,Hãy mở công cụ quản trị,tu-vung-cntt,lesson-16,Bài 16: Quản trị từ xa</t>
+  </si>
+  <si>
+    <t>サーバーマネージャー,さーばーまねーじゃー,Server Manager,N,N3,サーバーマネージャーで設定を確認します,Tôi kiểm tra cài đặt bằng Server Manager,tu-vung-cntt,lesson-16,Bài 16: Quản trị từ xa</t>
+  </si>
+  <si>
+    <t>PowerShell,ぱわーしぇる,PowerShell,N,N3,PowerShellで設定を変更しました,Tôi đã thay đổi cài đặt bằng PowerShell,tu-vung-cntt,lesson-16,Bài 16: Quản trị từ xa</t>
+  </si>
+  <si>
+    <t>コマンドプロンプト,こまんどぷろんぷと,Command Prompt,N,N3,コマンドプロンプトを管理者で開きます,Tôi mở Command Prompt bằng quyền quản trị,tu-vung-cntt,lesson-16,Bài 16: Quản trị từ xa</t>
+  </si>
+  <si>
+    <t>管理コンソール,かんりこんそーる,bảng điều khiển quản trị,N,N3,管理コンソールへログインしました,Tôi đã đăng nhập vào bảng điều khiển quản trị,tu-vung-cntt,lesson-16,Bài 16: Quản trị từ xa</t>
+  </si>
+  <si>
+    <t>管理画面,かんりがめん,màn hình quản trị,N,N3,管理画面から利用者を追加します,Tôi thêm người dùng từ màn hình quản trị,tu-vung-cntt,lesson-16,Bài 16: Quản trị từ xa</t>
+  </si>
+  <si>
+    <t>接続先サーバー,せつぞくさきさーばー,máy chủ đích,N,N3,接続先サーバーを選択してください,Hãy chọn máy chủ cần kết nối,tu-vung-cntt,lesson-16,Bài 16: Quản trị từ xa</t>
+  </si>
+  <si>
+    <t>Microsoft 365,まいくろそふとさんろくご,Microsoft 365,N,N3,Microsoft 365で毎日の業務を行います,Tôi làm việc hằng ngày bằng Microsoft 365,tu-vung-cntt,lesson-17,Bài 17: Microsoft 365 và Outlook</t>
+  </si>
+  <si>
+    <t>Outlook,あうとるっく,Outlook,N,N3,Outlookで会議の予定を確認しました,Tôi đã kiểm tra lịch họp bằng Outlook,tu-vung-cntt,lesson-17,Bài 17: Microsoft 365 và Outlook</t>
+  </si>
+  <si>
+    <t>受信トレイ,じゅしんとれい,hộp thư đến,N,N3,受信トレイに新しいメールがあります,Có email mới trong hộp thư đến,tu-vung-cntt,lesson-17,Bài 17: Microsoft 365 và Outlook</t>
+  </si>
+  <si>
+    <t>送信済み,そうしんずみ,thư đã gửi,N,N3,送信済みフォルダを確認してください,Hãy kiểm tra thư mục thư đã gửi,tu-vung-cntt,lesson-17,Bài 17: Microsoft 365 và Outlook</t>
+  </si>
+  <si>
+    <t>下書き,したがき,thư nháp,N,N3,メールを下書きとして保存しました,Tôi đã lưu email dưới dạng bản nháp,tu-vung-cntt,lesson-17,Bài 17: Microsoft 365 và Outlook</t>
+  </si>
+  <si>
+    <t>添付ファイル,てんぷふぁいる,tệp đính kèm,N,N3,添付ファイルを忘れないでください,Đừng quên tệp đính kèm,tu-vung-cntt,lesson-17,Bài 17: Microsoft 365 và Outlook</t>
+  </si>
+  <si>
+    <t>件名,けんめい,tiêu đề email,N,N3,件名を分かりやすく書いてください,Hãy viết tiêu đề rõ ràng,tu-vung-cntt,lesson-17,Bài 17: Microsoft 365 và Outlook</t>
+  </si>
+  <si>
+    <t>宛先,あてさき,người nhận,N,N3,宛先を確認して送信してください,Hãy kiểm tra người nhận trước khi gửi,tu-vung-cntt,lesson-17,Bài 17: Microsoft 365 và Outlook</t>
+  </si>
+  <si>
+    <t>CC,しーしー,CC,N,N3,CCに上司を追加しました,Tôi đã thêm cấp trên vào CC,tu-vung-cntt,lesson-17,Bài 17: Microsoft 365 và Outlook</t>
+  </si>
+  <si>
+    <t>BCC,びーしーしー,BCC,N,N3,BCCで送信してください,Hãy gửi bằng BCC,tu-vung-cntt,lesson-17,Bài 17: Microsoft 365 và Outlook</t>
+  </si>
+  <si>
+    <t>予定表,よていひょう,lịch làm việc,N,N3,予定表へ会議を追加しました,Tôi đã thêm cuộc họp vào lịch,tu-vung-cntt,lesson-17,Bài 17: Microsoft 365 và Outlook</t>
+  </si>
+  <si>
+    <t>会議依頼,かいぎいらい,lời mời họp,N,N2,会議依頼を全員へ送りました,Tôi đã gửi lời mời họp cho mọi người,tu-vung-cntt,lesson-17,Bài 17: Microsoft 365 và Outlook</t>
+  </si>
+  <si>
+    <t>予定,よてい,kế hoạch; lịch hẹn,N,N4,午後の予定を変更しました,Tôi đã thay đổi lịch buổi chiều,tu-vung-cntt,lesson-17,Bài 17: Microsoft 365 và Outlook</t>
+  </si>
+  <si>
+    <t>返信,へんしん,trả lời,N,N4,メールへ返信してください,Hãy trả lời email,tu-vung-cntt,lesson-17,Bài 17: Microsoft 365 và Outlook</t>
+  </si>
+  <si>
+    <t>Microsoft Teams,まいくろそふとちーむず,Microsoft Teams,N,N3,Microsoft Teamsで会議を始めます,Tôi bắt đầu cuộc họp bằng Microsoft Teams,tu-vung-cntt,lesson-18,Bài 18: Microsoft Teams</t>
+  </si>
+  <si>
+    <t>チーム,ちーむ,nhóm,N,N5,新しいチームを作成しました,Tôi đã tạo nhóm mới,tu-vung-cntt,lesson-18,Bài 18: Microsoft Teams</t>
+  </si>
+  <si>
+    <t>チャネル,ちゃねる,kênh,N,N3,開発チャネルへ参加しました,Tôi đã tham gia kênh phát triển,tu-vung-cntt,lesson-18,Bài 18: Microsoft Teams</t>
+  </si>
+  <si>
+    <t>投稿,とうこう,bài đăng,N,N3,新しい投稿を確認してください,Hãy kiểm tra bài đăng mới,tu-vung-cntt,lesson-18,Bài 18: Microsoft Teams</t>
+  </si>
+  <si>
+    <t>メンション,めんしょん,nhắc tên,N,N2,重要なのでメンションしました,Vì quan trọng nên tôi đã nhắc tên,tu-vung-cntt,lesson-18,Bài 18: Microsoft Teams</t>
+  </si>
+  <si>
+    <t>既読,きどく,đã đọc,N,N2,メッセージは既読になりました,Tin nhắn đã được đọc,tu-vung-cntt,lesson-18,Bài 18: Microsoft Teams</t>
+  </si>
+  <si>
+    <t>未読,みどく,chưa đọc,N,N2,未読メッセージが五件あります,Có năm tin nhắn chưa đọc,tu-vung-cntt,lesson-18,Bài 18: Microsoft Teams</t>
+  </si>
+  <si>
+    <t>通話,つうわ,cuộc gọi,N,N3,Teamsで通話を開始しました,Tôi đã bắt đầu cuộc gọi trên Teams,tu-vung-cntt,lesson-18,Bài 18: Microsoft Teams</t>
+  </si>
+  <si>
+    <t>ビデオ会議,びでおかいぎ,họp video,N,N3,ビデオ会議に参加してください,Hãy tham gia cuộc họp video,tu-vung-cntt,lesson-18,Bài 18: Microsoft Teams</t>
+  </si>
+  <si>
+    <t>背景,はいけい,hình nền,N,N2,背景をぼかしました,Tôi đã làm mờ hình nền,tu-vung-cntt,lesson-18,Bài 18: Microsoft Teams</t>
+  </si>
+  <si>
+    <t>マイク,まいく,micro,N,N5,マイクをオンにしてください,Hãy bật micro,tu-vung-cntt,lesson-18,Bài 18: Microsoft Teams</t>
+  </si>
+  <si>
+    <t>カメラ,かめら,camera,N,N5,カメラをオフにしました,Tôi đã tắt camera,tu-vung-cntt,lesson-18,Bài 18: Microsoft Teams</t>
+  </si>
+  <si>
+    <t>ミュート,みゅーと,tắt tiếng,N,N3,発表中はミュートにしてください,Hãy tắt tiếng khi người khác trình bày,tu-vung-cntt,lesson-18,Bài 18: Microsoft Teams</t>
+  </si>
+  <si>
+    <t>画面録画,がめんろくが,ghi màn hình,N,N2,画面録画を保存しました,Tôi đã lưu bản ghi màn hình,tu-vung-cntt,lesson-18,Bài 18: Microsoft Teams</t>
+  </si>
+  <si>
+    <t>共同編集,きょうどうへんしゅう,chỉnh sửa cộng tác,N,N2,資料を共同編集しています,Chúng tôi đang cùng chỉnh sửa tài liệu,tu-vung-cntt,lesson-18,Bài 18: Microsoft Teams</t>
+  </si>
+  <si>
+    <t>Google Workspace,ぐーぐるわーくすぺーす,Google Workspace,N,N3,Google Workspaceを会社で利用しています,Công ty đang sử dụng Google Workspace,tu-vung-cntt,lesson-19,Bài 19: Google Workspace</t>
+  </si>
+  <si>
+    <t>Gmail,じーめーる,Gmail,N,N5,Gmailでお客様へ返信しました,Tôi đã trả lời khách hàng bằng Gmail,tu-vung-cntt,lesson-19,Bài 19: Google Workspace</t>
+  </si>
+  <si>
+    <t>Google Drive,ぐーぐるどらいぶ,Google Drive,N,N5,資料をGoogle Driveへ保存しました,Tôi đã lưu tài liệu lên Google Drive,tu-vung-cntt,lesson-19,Bài 19: Google Workspace</t>
+  </si>
+  <si>
+    <t>Google Docs,ぐーぐるどきゅめんと,Google Docs,N,N3,Google Docsで報告書を作成します,Tôi tạo báo cáo bằng Google Docs,tu-vung-cntt,lesson-19,Bài 19: Google Workspace</t>
+  </si>
+  <si>
+    <t>Google Sheets,ぐーぐるしーつ,Google Sheets,N,N3,Google Sheetsで売上を管理しています,Tôi quản lý doanh thu bằng Google Sheets,tu-vung-cntt,lesson-19,Bài 19: Google Workspace</t>
+  </si>
+  <si>
+    <t>Google Slides,ぐーぐるすらいど,Google Slides,N,N3,Google Slidesで発表資料を作りました,Tôi đã tạo slide thuyết trình bằng Google Slides,tu-vung-cntt,lesson-19,Bài 19: Google Workspace</t>
+  </si>
+  <si>
+    <t>Google Meet,ぐーぐるみーと,Google Meet,N,N3,Google Meetで会議を始めます,Tôi bắt đầu cuộc họp bằng Google Meet,tu-vung-cntt,lesson-19,Bài 19: Google Workspace</t>
+  </si>
+  <si>
+    <t>共有リンク,きょうゆうりんく,liên kết chia sẻ,N,N3,共有リンクを送ってください,Hãy gửi liên kết chia sẻ,tu-vung-cntt,lesson-19,Bài 19: Google Workspace</t>
+  </si>
+  <si>
+    <t>閲覧権限,えつらんけんげん,quyền xem,N,N2,閲覧権限だけ設定しました,Tôi chỉ cấp quyền xem,tu-vung-cntt,lesson-19,Bài 19: Google Workspace</t>
+  </si>
+  <si>
+    <t>編集権限,へんしゅうけんげん,quyền chỉnh sửa,N,N2,編集権限を追加しました,Tôi đã cấp quyền chỉnh sửa,tu-vung-cntt,lesson-19,Bài 19: Google Workspace</t>
+  </si>
+  <si>
+    <t>コメント,こめんと,bình luận,N,N4,コメントを追加してください,Hãy thêm bình luận,tu-vung-cntt,lesson-19,Bài 19: Google Workspace</t>
+  </si>
+  <si>
+    <t>履歴,りれき,lịch sử,N,N2,変更履歴を確認しました,Tôi đã kiểm tra lịch sử thay đổi,tu-vung-cntt,lesson-19,Bài 19: Google Workspace</t>
+  </si>
+  <si>
+    <t>版,ばん,phiên bản,N,N2,以前の版へ戻しました,Tôi đã quay lại phiên bản trước,tu-vung-cntt,lesson-19,Bài 19: Google Workspace</t>
+  </si>
+  <si>
+    <t>同期,どうき,đồng bộ,N,N2,ファイルを自動同期しています,Tệp đang được đồng bộ tự động,tu-vung-cntt,lesson-19,Bài 19: Google Workspace</t>
+  </si>
+  <si>
+    <t>オフライン,おふらいん,ngoại tuyến,N,N4,オフラインでも編集できます,Có thể chỉnh sửa ngay cả khi ngoại tuyến,tu-vung-cntt,lesson-19,Bài 19: Google Workspace</t>
+  </si>
+  <si>
+    <t>プリンターキュー,ぷりんたーきゅー,hàng đợi in,N,N2,プリンターキューを確認してください,Hãy kiểm tra hàng đợi in,tu-vung-cntt,lesson-20,Bài 20: Máy in và Scan</t>
+  </si>
+  <si>
+    <t>印刷ジョブ,いんさつじょぶ,tác vụ in,N,N2,印刷ジョブを削除しました,Tôi đã xóa tác vụ in,tu-vung-cntt,lesson-20,Bài 20: Máy in và Scan</t>
+  </si>
+  <si>
+    <t>印刷待ち,いんさつまち,đang chờ in,N,N2,印刷待ちの状態が続いています,Trạng thái chờ in vẫn tiếp tục,tu-vung-cntt,lesson-20,Bài 20: Máy in và Scan</t>
+  </si>
+  <si>
+    <t>紙詰まり,かみづまり,kẹt giấy,N,N2,紙詰まりを取り除きました,Tôi đã xử lý tình trạng kẹt giấy,tu-vung-cntt,lesson-20,Bài 20: Máy in và Scan</t>
+  </si>
+  <si>
+    <t>トナー,となー,mực toner,N,N3,トナーを交換してください,Hãy thay hộp mực toner,tu-vung-cntt,lesson-20,Bài 20: Máy in và Scan</t>
+  </si>
+  <si>
+    <t>インク,いんく,mực in,N,N4,インクがなくなりました,Mực in đã hết,tu-vung-cntt,lesson-20,Bài 20: Máy in và Scan</t>
+  </si>
+  <si>
+    <t>給紙,きゅうし,cấp giấy,N,N2,給紙トレイを確認してください,Hãy kiểm tra khay cấp giấy,tu-vung-cntt,lesson-20,Bài 20: Máy in và Scan</t>
+  </si>
+  <si>
+    <t>両面印刷,りょうめんいんさつ,in hai mặt,N,N2,両面印刷を選択しました,Tôi đã chọn chế độ in hai mặt,tu-vung-cntt,lesson-20,Bài 20: Máy in và Scan</t>
+  </si>
+  <si>
+    <t>カラー印刷,からーいんさつ,in màu,N,N3,カラー印刷は禁止されています,In màu bị cấm,tu-vung-cntt,lesson-20,Bài 20: Máy in và Scan</t>
+  </si>
+  <si>
+    <t>白黒印刷,しろくろいんさつ,in trắng đen,N,N3,白黒印刷を利用してください,Hãy sử dụng chế độ in trắng đen,tu-vung-cntt,lesson-20,Bài 20: Máy in và Scan</t>
+  </si>
+  <si>
+    <t>複合機,ふくごうき,máy đa chức năng,N,N2,複合機でコピーしました,Tôi đã sao chép bằng máy đa chức năng,tu-vung-cntt,lesson-20,Bài 20: Máy in và Scan</t>
+  </si>
+  <si>
+    <t>ADF,えーでぃーえふ,bộ nạp giấy tự động,N,N1,ADFに原稿を入れてください,Hãy đặt tài liệu vào bộ nạp giấy tự động,tu-vung-cntt,lesson-20,Bài 20: Máy in và Scan</t>
+  </si>
+  <si>
+    <t>解像度,かいぞうど,độ phân giải,N,N2,解像度を三百dpiに設定しました,Tôi đã đặt độ phân giải thành ba trăm dpi,tu-vung-cntt,lesson-20,Bài 20: Máy in và Scan</t>
+  </si>
+  <si>
+    <t>OCR,おーしーあー,nhận dạng ký tự quang học,N,N1,OCRで文字を認識しました,Tôi đã nhận dạng văn bản bằng OCR,tu-vung-cntt,lesson-20,Bài 20: Máy in và Scan</t>
+  </si>
+  <si>
+    <t>TWAIN,ついん,chuẩn giao tiếp máy quét,N,N1,TWAINドライバーをインストールしてください,Hãy cài đặt trình điều khiển TWAIN,tu-vung-cntt,lesson-21,Bài 21: Scan và Driver</t>
+  </si>
+  <si>
+    <t>WIA,だぶりゅーあいえー,Windows Image Acquisition,N,N1,WIAサービスを再起動しました,Tôi đã khởi động lại dịch vụ WIA,tu-vung-cntt,lesson-21,Bài 21: Scan và Driver</t>
+  </si>
+  <si>
+    <t>ドライバー,どらいばー,trình điều khiển,N,N3,最新のドライバーをインストールしました,Tôi đã cài đặt trình điều khiển mới nhất,tu-vung-cntt,lesson-21,Bài 21: Scan và Driver</t>
+  </si>
+  <si>
+    <t>プリンタードライバー,ぷりんたーどらいばー,trình điều khiển máy in,N,N2,プリンタードライバーを更新してください,Hãy cập nhật trình điều khiển máy in,tu-vung-cntt,lesson-21,Bài 21: Scan và Driver</t>
+  </si>
+  <si>
+    <t>スキャナードライバー,すきゃなーどらいばー,trình điều khiển máy quét,N,N2,スキャナードライバーを再インストールしました,Tôi đã cài đặt lại trình điều khiển máy quét,tu-vung-cntt,lesson-21,Bài 21: Scan và Driver</t>
+  </si>
+  <si>
+    <t>デバイスマネージャー,でばいすまねーじゃー,Device Manager,N,N2,デバイスマネージャーを開いてください,Hãy mở Device Manager,tu-vung-cntt,lesson-21,Bài 21: Scan và Driver</t>
+  </si>
+  <si>
+    <t>互換性,ごかんせい,tính tương thích,N,N1,互換性を確認してください,Hãy kiểm tra tính tương thích,tu-vung-cntt,lesson-21,Bài 21: Scan và Driver</t>
+  </si>
+  <si>
+    <t>署名,しょめい,chữ ký số,N,N1,署名済みドライバーを使用します,Sử dụng trình điều khiển đã được ký số,tu-vung-cntt,lesson-21,Bài 21: Scan và Driver</t>
+  </si>
+  <si>
+    <t>ファームウェア,ふぁーむうぇあ,firmware,N,N1,ファームウェアを更新しました,Tôi đã cập nhật firmware,tu-vung-cntt,lesson-21,Bài 21: Scan và Driver</t>
+  </si>
+  <si>
+    <t>バージョン,ばーじょん,phiên bản,N,N4,最新版のバージョンを使っています,Tôi đang sử dụng phiên bản mới nhất,tu-vung-cntt,lesson-21,Bài 21: Scan và Driver</t>
+  </si>
+  <si>
+    <t>互換モード,ごかんもーど,chế độ tương thích,N,N1,互換モードで実行しました,Tôi đã chạy ở chế độ tương thích,tu-vung-cntt,lesson-21,Bài 21: Scan và Driver</t>
+  </si>
+  <si>
+    <t>ウイルス,ういるす,virus máy tính,N,N4,ウイルスが検出されました,Đã phát hiện virus máy tính,tu-vung-cntt,lesson-22,Bài 22: Bảo mật và Antivirus</t>
+  </si>
+  <si>
+    <t>マルウェア,まるうぇあ,mã độc,N,N2,マルウェアを削除しました,Tôi đã xóa mã độc,tu-vung-cntt,lesson-22,Bài 22: Bảo mật và Antivirus</t>
+  </si>
+  <si>
+    <t>ランサムウェア,らんさむうぇあ,mã độc tống tiền,N,N1,ランサムウェアの攻撃を受けました,Hệ thống đã bị tấn công bởi ransomware,tu-vung-cntt,lesson-22,Bài 22: Bảo mật và Antivirus</t>
+  </si>
+  <si>
+    <t>スパイウェア,すぱいうぇあ,phần mềm gián điệp,N,N1,スパイウェアが見つかりました,Đã phát hiện phần mềm gián điệp,tu-vung-cntt,lesson-22,Bài 22: Bảo mật và Antivirus</t>
+  </si>
+  <si>
+    <t>ウイルス対策ソフト,ういるすたいさくそふと,phần mềm diệt virus,N,N2,ウイルス対策ソフトを更新しました,Tôi đã cập nhật phần mềm diệt virus,tu-vung-cntt,lesson-22,Bài 22: Bảo mật và Antivirus</t>
+  </si>
+  <si>
+    <t>リアルタイム保護,りあるたいむほご,bảo vệ thời gian thực,N,N1,リアルタイム保護を有効にしました,Tôi đã bật bảo vệ thời gian thực,tu-vung-cntt,lesson-22,Bài 22: Bảo mật và Antivirus</t>
+  </si>
+  <si>
+    <t>感染,かんせん,lây nhiễm,N,N2,システムが感染しました,Hệ thống đã bị lây nhiễm,tu-vung-cntt,lesson-22,Bài 22: Bảo mật và Antivirus</t>
+  </si>
+  <si>
+    <t>脆弱性,ぜいじゃくせい,lỗ hổng bảo mật,N,N1,脆弱性を修正しました,Tôi đã vá lỗ hổng bảo mật,tu-vung-cntt,lesson-22,Bài 22: Bảo mật và Antivirus</t>
+  </si>
+  <si>
+    <t>セキュリティパッチ,せきゅりてぃぱっち,bản vá bảo mật,N,N1,セキュリティパッチを適用しました,Tôi đã áp dụng bản vá bảo mật,tu-vung-cntt,lesson-22,Bài 22: Bảo mật và Antivirus</t>
+  </si>
+  <si>
+    <t>不正アクセス,ふせいあくせす,truy cập trái phép,N,N1,不正アクセスを検知しました,Đã phát hiện truy cập trái phép,tu-vung-cntt,lesson-22,Bài 22: Bảo mật và Antivirus</t>
+  </si>
+  <si>
+    <t>侵入,しんにゅう,xâm nhập,N,N1,外部からの侵入を防ぎます,Ngăn chặn sự xâm nhập từ bên ngoài,tu-vung-cntt,lesson-22,Bài 22: Bảo mật và Antivirus</t>
+  </si>
+  <si>
+    <t>バックアップ,ばっくあっぷ,sao lưu,N,N3,毎日バックアップを実行しています,Tôi thực hiện sao lưu mỗi ngày,tu-vung-cntt,lesson-23,Bài 23: Backup và Recovery</t>
+  </si>
+  <si>
+    <t>復元,ふくげん,khôi phục,N,N2,バックアップから復元しました,Tôi đã khôi phục từ bản sao lưu,tu-vung-cntt,lesson-23,Bài 23: Backup và Recovery</t>
+  </si>
+  <si>
+    <t>リストア,りすとあ,phục hồi dữ liệu,N,N2,データをリストアしています,Tôi đang phục hồi dữ liệu,tu-vung-cntt,lesson-23,Bài 23: Backup và Recovery</t>
+  </si>
+  <si>
+    <t>増分バックアップ,ぞうぶんばっくあっぷ,sao lưu gia tăng,N,N1,増分バックアップを設定しました,Tôi đã cấu hình sao lưu gia tăng,tu-vung-cntt,lesson-23,Bài 23: Backup và Recovery</t>
+  </si>
+  <si>
+    <t>完全バックアップ,かんぜんばっくあっぷ,sao lưu toàn bộ,N,N2,完全バックアップを毎週実行します,Tôi thực hiện sao lưu toàn bộ mỗi tuần,tu-vung-cntt,lesson-23,Bài 23: Backup và Recovery</t>
+  </si>
+  <si>
+    <t>差分バックアップ,さぶんばっくあっぷ,sao lưu khác biệt,N,N1,差分バックアップを利用しています,Tôi đang sử dụng sao lưu khác biệt,tu-vung-cntt,lesson-23,Bài 23: Backup và Recovery</t>
+  </si>
+  <si>
+    <t>復元ポイント,ふくげんぽいんと,điểm khôi phục,N,N2,復元ポイントを作成しました,Tôi đã tạo điểm khôi phục,tu-vung-cntt,lesson-23,Bài 23: Backup và Recovery</t>
+  </si>
+  <si>
+    <t>スナップショット,すなっぷしょっと,ảnh chụp trạng thái,N,N1,仮想マシンのスナップショットを作成しました,Tôi đã tạo snapshot của máy ảo,tu-vung-cntt,lesson-23,Bài 23: Backup và Recovery</t>
+  </si>
+  <si>
+    <t>世代管理,せだいかんり,quản lý phiên bản sao lưu,N,N1,世代管理を有効にしました,Tôi đã bật quản lý phiên bản sao lưu,tu-vung-cntt,lesson-23,Bài 23: Backup và Recovery</t>
+  </si>
+  <si>
+    <t>保存期間,ほぞんきかん,thời gian lưu trữ,N,N2,保存期間を一年に設定しました,Tôi đã đặt thời gian lưu trữ là một năm,tu-vung-cntt,lesson-23,Bài 23: Backup và Recovery</t>
+  </si>
+  <si>
+    <t>バックアップ先,ばっくあっぷさき,vị trí sao lưu,N,N2,バックアップ先を変更してください,Hãy thay đổi nơi lưu bản sao lưu,tu-vung-cntt,lesson-23,Bài 23: Backup và Recovery</t>
+  </si>
+  <si>
+    <t>災害復旧,さいがいふっきゅう,khôi phục sau thảm họa,N,N1,災害復旧計画を作成しました,Tôi đã lập kế hoạch khôi phục sau thảm họa,tu-vung-cntt,lesson-23,Bài 23: Backup và Recovery</t>
+  </si>
+  <si>
+    <t>可用性,かようせい,tính sẵn sàng,N,N1,システムの可用性を向上させます,Nâng cao tính sẵn sàng của hệ thống,tu-vung-cntt,lesson-23,Bài 23: Backup và Recovery</t>
+  </si>
+  <si>
+    <t>冗長化,じょうちょうか,dự phòng hệ thống,N,N1,サーバーを冗長化しました,Tôi đã triển khai dự phòng máy chủ,tu-vung-cntt,lesson-23,Bài 23: Backup và Recovery</t>
+  </si>
+  <si>
+    <t>障害復旧,しょうがいふっきゅう,khôi phục sự cố,N,N1,障害復旧を開始しました,Tôi đã bắt đầu khôi phục sự cố,tu-vung-cntt,lesson-23,Bài 23: Backup và Recovery</t>
+  </si>
+  <si>
+    <t>Git,ぎっと,Git,N,N3,Gitでソースコードを管理します,Tôi quản lý mã nguồn bằng Git,tu-vung-cntt,lesson-24,Bài 24: Git và GitHub</t>
+  </si>
+  <si>
+    <t>GitHub,ぎっとはぶ,GitHub,N,N3,GitHubへコードを公開しました,Tôi đã đưa mã nguồn lên GitHub,tu-vung-cntt,lesson-24,Bài 24: Git và GitHub</t>
+  </si>
+  <si>
+    <t>リポジトリ,りぽじとり,kho mã nguồn,N,N2,新しいリポジトリを作成しました,Tôi đã tạo kho mã nguồn mới,tu-vung-cntt,lesson-24,Bài 24: Git và GitHub</t>
+  </si>
+  <si>
+    <t>コミット,こみっと,commit,N,N3,変更をコミットしました,Tôi đã commit các thay đổi,tu-vung-cntt,lesson-24,Bài 24: Git và GitHub</t>
+  </si>
+  <si>
+    <t>プッシュ,ぷっしゅ,push,N,N3,変更をリモートへプッシュしました,Tôi đã push thay đổi lên máy chủ,tu-vung-cntt,lesson-24,Bài 24: Git và GitHub</t>
+  </si>
+  <si>
+    <t>プル,ぷる,pull,N,N3,最新の変更をプルしてください,Hãy pull các thay đổi mới nhất,tu-vung-cntt,lesson-24,Bài 24: Git và GitHub</t>
+  </si>
+  <si>
+    <t>フェッチ,ふぇっち,fetch,N,N1,リモートからフェッチしました,Tôi đã fetch dữ liệu từ máy chủ,tu-vung-cntt,lesson-24,Bài 24: Git và GitHub</t>
+  </si>
+  <si>
+    <t>ブランチ,ぶらんち,nhánh,N,N3,新しいブランチを作成しました,Tôi đã tạo nhánh mới,tu-vung-cntt,lesson-24,Bài 24: Git và GitHub</t>
+  </si>
+  <si>
+    <t>マージ,まーじ,merge,N,N2,ブランチをマージしました,Tôi đã gộp các nhánh,tu-vung-cntt,lesson-24,Bài 24: Git và GitHub</t>
+  </si>
+  <si>
+    <t>マージコンフリクト,まーじこんふりくと,xung đột khi merge,N,N1,マージコンフリクトを解決しました,Tôi đã giải quyết xung đột khi merge,tu-vung-cntt,lesson-24,Bài 24: Git và GitHub</t>
+  </si>
+  <si>
+    <t>クローン,くろーん,clone,N,N2,リポジトリをクローンしました,Tôi đã clone kho mã nguồn,tu-vung-cntt,lesson-24,Bài 24: Git và GitHub</t>
+  </si>
+  <si>
+    <t>プルリクエスト,ぷるりくえすと,pull request,N,N1,プルリクエストを作成しました,Tôi đã tạo pull request,tu-vung-cntt,lesson-24,Bài 24: Git và GitHub</t>
+  </si>
+  <si>
+    <t>レビュー,れびゅー,review mã nguồn,N,N2,コードレビューをお願いします,Hãy review mã nguồn giúp tôi,tu-vung-cntt,lesson-24,Bài 24: Git và GitHub</t>
+  </si>
+  <si>
+    <t>コンフリクト,こんふりくと,xung đột,N,N2,コンフリクトを修正しました,Tôi đã sửa xung đột,tu-vung-cntt,lesson-24,Bài 24: Git và GitHub</t>
+  </si>
+  <si>
+    <t>チェックアウト,ちぇっくあうと,checkout,N,N1,別のブランチへチェックアウトしました,Tôi đã checkout sang nhánh khác,tu-vung-cntt,lesson-24,Bài 24: Git và GitHub</t>
+  </si>
+  <si>
+    <t>データベース,でーたべーす,cơ sở dữ liệu,N,N3,データベースへ接続しました,Tôi đã kết nối tới cơ sở dữ liệu,tu-vung-cntt,lesson-25,Bài 25: SQL và Database</t>
+  </si>
+  <si>
+    <t>DBMS,でぃーびーえむえす,hệ quản trị cơ sở dữ liệu,N,N1,DBMSを更新しました,Tôi đã cập nhật hệ quản trị cơ sở dữ liệu,tu-vung-cntt,lesson-25,Bài 25: SQL và Database</t>
+  </si>
+  <si>
+    <t>テーブル,てーぶる,bảng dữ liệu,N,N3,新しいテーブルを作成しました,Tôi đã tạo bảng mới,tu-vung-cntt,lesson-25,Bài 25: SQL và Database</t>
+  </si>
+  <si>
+    <t>レコード,れこーど,bản ghi,N,N3,レコードを追加しました,Tôi đã thêm bản ghi,tu-vung-cntt,lesson-25,Bài 25: SQL và Database</t>
+  </si>
+  <si>
+    <t>カラム,からむ,cột dữ liệu,N,N2,カラム名を変更しました,Tôi đã đổi tên cột,tu-vung-cntt,lesson-25,Bài 25: SQL và Database</t>
+  </si>
+  <si>
+    <t>主キー,しゅきー,khóa chính,N,N2,主キーを設定してください,Hãy thiết lập khóa chính,tu-vung-cntt,lesson-25,Bài 25: SQL và Database</t>
+  </si>
+  <si>
+    <t>外部キー,がいぶきー,khóa ngoại,N,N1,外部キーを追加しました,Tôi đã thêm khóa ngoại,tu-vung-cntt,lesson-25,Bài 25: SQL và Database</t>
+  </si>
+  <si>
+    <t>クエリ,くえり,truy vấn,N,N3,クエリを実行しました,Tôi đã thực thi truy vấn,tu-vung-cntt,lesson-25,Bài 25: SQL và Database</t>
+  </si>
+  <si>
+    <t>SQL,えすきゅーえる,SQL,N,N3,SQLを勉強しています,Tôi đang học SQL,tu-vung-cntt,lesson-25,Bài 25: SQL và Database</t>
+  </si>
+  <si>
+    <t>SELECT,せれくと,lệnh SELECT,N,N3,SELECT文を実行しました,Tôi đã chạy câu lệnh SELECT,tu-vung-cntt,lesson-25,Bài 25: SQL và Database</t>
+  </si>
+  <si>
+    <t>INSERT,いんさーと,lệnh INSERT,N,N3,INSERT文でデータを追加しました,Tôi đã thêm dữ liệu bằng INSERT,tu-vung-cntt,lesson-25,Bài 25: SQL và Database</t>
+  </si>
+  <si>
+    <t>UPDATE,あっぷでーと,lệnh UPDATE,N,N3,UPDATE文を実行しました,Tôi đã thực thi câu lệnh UPDATE,tu-vung-cntt,lesson-25,Bài 25: SQL và Database</t>
+  </si>
+  <si>
+    <t>DELETE,でりーと,lệnh DELETE,N,N3,不要なデータをDELETEしました,Tôi đã xóa dữ liệu không cần thiết,tu-vung-cntt,lesson-25,Bài 25: SQL và Database</t>
+  </si>
+  <si>
+    <t>JOIN,じょいん,lệnh JOIN,N,N2,JOINで二つの表を結合しました,Tôi đã nối hai bảng bằng JOIN,tu-vung-cntt,lesson-25,Bài 25: SQL và Database</t>
+  </si>
+  <si>
+    <t>トランザクション,とらんざくしょん,giao dịch,N,N1,トランザクションを開始しました,Tôi đã bắt đầu giao dịch,tu-vung-cntt,lesson-26,Bài 26: SQL nâng cao</t>
+  </si>
+  <si>
+    <t>コミット,こみっと,xác nhận giao dịch,N,N1,トランザクションをコミットしました,Tôi đã commit giao dịch,tu-vung-cntt,lesson-26,Bài 26: SQL nâng cao</t>
+  </si>
+  <si>
+    <t>ロールバック,ろーるばっく,hoàn tác giao dịch,N,N1,ロールバックを実行しました,Tôi đã rollback giao dịch,tu-vung-cntt,lesson-26,Bài 26: SQL nâng cao</t>
+  </si>
+  <si>
+    <t>ビュー,びゅー,khung nhìn,N,N2,ビューを作成しました,Tôi đã tạo view,tu-vung-cntt,lesson-26,Bài 26: SQL nâng cao</t>
+  </si>
+  <si>
+    <t>ストアドプロシージャ,すとあどぷろしーじゃ,stored procedure,N,N1,ストアドプロシージャを実行しました,Tôi đã chạy stored procedure,tu-vung-cntt,lesson-26,Bài 26: SQL nâng cao</t>
+  </si>
+  <si>
+    <t>トリガー,とりがー,trigger,N,N1,トリガーを追加しました,Tôi đã thêm trigger,tu-vung-cntt,lesson-26,Bài 26: SQL nâng cao</t>
+  </si>
+  <si>
+    <t>正規化,せいきか,chuẩn hóa dữ liệu,N,N1,データベースを正規化しました,Tôi đã chuẩn hóa cơ sở dữ liệu,tu-vung-cntt,lesson-26,Bài 26: SQL nâng cao</t>
+  </si>
+  <si>
+    <t>制約,せいやく,ràng buộc,N,N2,制約を追加してください,Hãy thêm ràng buộc,tu-vung-cntt,lesson-26,Bài 26: SQL nâng cao</t>
+  </si>
+  <si>
+    <t>一意制約,ゆいいせいやく,ràng buộc duy nhất,N,N1,一意制約を設定しました,Tôi đã thiết lập ràng buộc duy nhất,tu-vung-cntt,lesson-26,Bài 26: SQL nâng cao</t>
+  </si>
+  <si>
+    <t>NULL,なる,giá trị NULL,N,N2,NULLは許可されていません,Không cho phép giá trị NULL,tu-vung-cntt,lesson-26,Bài 26: SQL nâng cao</t>
+  </si>
+  <si>
+    <t>デッドロック,でっどろっく,bế tắc giao dịch,N,N1,デッドロックが発生しました,Đã xảy ra deadlock,tu-vung-cntt,lesson-26,Bài 26: SQL nâng cao</t>
+  </si>
+  <si>
+    <t>最適化,さいてきか,tối ưu hóa,N,N1,クエリを最適化しました,Tôi đã tối ưu hóa truy vấn,tu-vung-cntt,lesson-26,Bài 26: SQL nâng cao</t>
+  </si>
+  <si>
+    <t>実行計画,じっこうけいかく,kế hoạch thực thi,N,N1,実行計画を分析しました,Tôi đã phân tích execution plan,tu-vung-cntt,lesson-26,Bài 26: SQL nâng cao</t>
+  </si>
+  <si>
+    <t>Linux,りなっくす,Linux,N,N3,Linuxサーバーを管理しています,Tôi đang quản lý máy chủ Linux,tu-vung-cntt,lesson-27,Bài 27: Linux cơ bản</t>
+  </si>
+  <si>
+    <t>ディストリビューション,でぃすとりびゅーしょん,bản phân phối Linux,N,N1,Ubuntuは人気のディストリビューションです,Ubuntu là bản phân phối phổ biến,tu-vung-cntt,lesson-27,Bài 27: Linux cơ bản</t>
+  </si>
+  <si>
+    <t>Ubuntu,うぶんとぅ,Ubuntu,N,N3,Ubuntuをインストールしました,Tôi đã cài Ubuntu,tu-vung-cntt,lesson-27,Bài 27: Linux cơ bản</t>
+  </si>
+  <si>
+    <t>CentOS,せんとおーえす,CentOS,N,N2,CentOSを使用しています,Tôi đang sử dụng CentOS,tu-vung-cntt,lesson-27,Bài 27: Linux cơ bản</t>
+  </si>
+  <si>
+    <t>ターミナル,たーみなる,terminal,N,N3,ターミナルを開いてください,Hãy mở terminal,tu-vung-cntt,lesson-27,Bài 27: Linux cơ bản</t>
+  </si>
+  <si>
+    <t>シェル,しぇる,shell,N,N2,Bashシェルを使っています,Tôi đang sử dụng Bash shell,tu-vung-cntt,lesson-27,Bài 27: Linux cơ bản</t>
+  </si>
+  <si>
+    <t>Bash,ばっしゅ,Bash,N,N2,Bashでスクリプトを書きます,Tôi viết script bằng Bash,tu-vung-cntt,lesson-27,Bài 27: Linux cơ bản</t>
+  </si>
+  <si>
+    <t>コマンド,こまんど,lệnh,N,N5,コマンドを入力してください,Hãy nhập lệnh,tu-vung-cntt,lesson-27,Bài 27: Linux cơ bản</t>
+  </si>
+  <si>
+    <t>ディレクトリ,でぃれくとり,thư mục,N,N3,ディレクトリを移動しました,Tôi đã chuyển thư mục,tu-vung-cntt,lesson-27,Bài 27: Linux cơ bản</t>
+  </si>
+  <si>
+    <t>カレントディレクトリ,かれんとでぃれくとり,thư mục hiện tại,N,N2,カレントディレクトリを確認します,Tôi kiểm tra thư mục hiện tại,tu-vung-cntt,lesson-27,Bài 27: Linux cơ bản</t>
+  </si>
+  <si>
+    <t>権限,けんげん,quyền,N,N3,権限を変更しました,Tôi đã thay đổi quyền,tu-vung-cntt,lesson-27,Bài 27: Linux cơ bản</t>
+  </si>
+  <si>
+    <t>所有者,しょゆうしゃ,chủ sở hữu,N,N3,所有者を変更してください,Hãy thay đổi chủ sở hữu,tu-vung-cntt,lesson-27,Bài 27: Linux cơ bản</t>
+  </si>
+  <si>
+    <t>chmod,ちゃもっど,lệnh chmod,N,N2,chmodで権限を変更しました,Tôi đã thay đổi quyền bằng chmod,tu-vung-cntt,lesson-27,Bài 27: Linux cơ bản</t>
+  </si>
+  <si>
+    <t>chown,ちゃうん,lệnh chown,N,N2,chownを実行しました,Tôi đã thực hiện lệnh chown,tu-vung-cntt,lesson-27,Bài 27: Linux cơ bản</t>
+  </si>
+  <si>
+    <t>sudo,すどう,lệnh sudo,N,N3,sudoでコマンドを実行しました,Tôi đã chạy lệnh bằng sudo,tu-vung-cntt,lesson-27,Bài 27: Linux cơ bản</t>
+  </si>
+  <si>
+    <t>root,るーと,tài khoản root,N,N3,rootでログインしました,Tôi đã đăng nhập bằng tài khoản root,tu-vung-cntt,lesson-28,Bài 28: Linux nâng cao</t>
+  </si>
+  <si>
+    <t>パーミッション,ぱーみっしょん,permission,N,N2,パーミッションを確認しました,Tôi đã kiểm tra permission,tu-vung-cntt,lesson-28,Bài 28: Linux nâng cao</t>
+  </si>
+  <si>
+    <t>プロセス,ぷろせす,tiến trình,N,N2,不要なプロセスを終了しました,Tôi đã kết thúc tiến trình không cần thiết,tu-vung-cntt,lesson-28,Bài 28: Linux nâng cao</t>
+  </si>
+  <si>
+    <t>デーモン,でーもん,daemon,N,N1,デーモンが起動しています,Daemon đang chạy,tu-vung-cntt,lesson-28,Bài 28: Linux nâng cao</t>
+  </si>
+  <si>
+    <t>systemctl,しすてむしーてぃーえる,lệnh systemctl,N,N1,systemctlでサービスを再起動しました,Tôi đã khởi động lại dịch vụ bằng systemctl,tu-vung-cntt,lesson-28,Bài 28: Linux nâng cao</t>
+  </si>
+  <si>
+    <t>cron,くろん,cron,N,N1,cronで自動実行を設定しました,Tôi đã thiết lập chạy tự động bằng cron,tu-vung-cntt,lesson-28,Bài 28: Linux nâng cao</t>
+  </si>
+  <si>
+    <t>crontab,くろんたぶ,bảng lịch cron,N,N1,crontabを編集しました,Tôi đã chỉnh sửa crontab,tu-vung-cntt,lesson-28,Bài 28: Linux nâng cao</t>
+  </si>
+  <si>
+    <t>grep,ぐれっぷ,lệnh grep,N,N2,grepで文字列を検索しました,Tôi đã tìm chuỗi bằng grep,tu-vung-cntt,lesson-28,Bài 28: Linux nâng cao</t>
+  </si>
+  <si>
+    <t>find,ふぁいんど,lệnh find,N,N3,findでファイルを検索しました,Tôi đã tìm tệp bằng find,tu-vung-cntt,lesson-28,Bài 28: Linux nâng cao</t>
+  </si>
+  <si>
+    <t>vi,ゔぃーあい,trình soạn thảo vi,N,N2,viで設定ファイルを編集しました,Tôi đã chỉnh sửa tệp cấu hình bằng vi,tu-vung-cntt,lesson-28,Bài 28: Linux nâng cao</t>
+  </si>
+  <si>
+    <t>vim,ゔぃむ,trình soạn thảo Vim,N,N2,vimでスクリプトを書いています,Tôi đang viết script bằng Vim,tu-vung-cntt,lesson-28,Bài 28: Linux nâng cao</t>
+  </si>
+  <si>
+    <t>シンボリックリンク,しんぼりっくりんく,liên kết tượng trưng,N,N1,シンボリックリンクを作成しました,Tôi đã tạo symbolic link,tu-vung-cntt,lesson-28,Bài 28: Linux nâng cao</t>
+  </si>
+  <si>
+    <t>パイプ,ぱいぷ,pipe,N,N2,パイプで結果を渡しました,Tôi đã truyền kết quả bằng pipe,tu-vung-cntt,lesson-28,Bài 28: Linux nâng cao</t>
+  </si>
+  <si>
+    <t>リダイレクト,りだいれくと,chuyển hướng,N,N2,出力をファイルへリダイレクトしました,Tôi đã chuyển hướng đầu ra vào tệp,tu-vung-cntt,lesson-28,Bài 28: Linux nâng cao</t>
+  </si>
+  <si>
+    <t>AWS,えーだぶりゅーえす,AWS,N,N3,AWSでシステムを運用しています,Tôi đang vận hành hệ thống trên AWS,tu-vung-cntt,lesson-29,Bài 29: Cloud Computing</t>
+  </si>
+  <si>
+    <t>Microsoft Azure,まいくろそふとあじゅーる,Microsoft Azure,N,N3,Azureへ仮想マシンを作成しました,Tôi đã tạo máy ảo trên Azure,tu-vung-cntt,lesson-29,Bài 29: Cloud Computing</t>
+  </si>
+  <si>
+    <t>Google Cloud,ぐーぐるくらうど,Google Cloud,N,N3,Google Cloudを勉強しています,Tôi đang học Google Cloud,tu-vung-cntt,lesson-29,Bài 29: Cloud Computing</t>
+  </si>
+  <si>
+    <t>クラウド,くらうど,điện toán đám mây,N,N3,クラウドへデータを移行しました,Tôi đã chuyển dữ liệu lên đám mây,tu-vung-cntt,lesson-29,Bài 29: Cloud Computing</t>
+  </si>
+  <si>
+    <t>オンプレミス,おんぷれみす,hạ tầng tại chỗ,N,N1,オンプレミス環境を運用しています,Tôi đang vận hành hạ tầng tại chỗ,tu-vung-cntt,lesson-29,Bài 29: Cloud Computing</t>
+  </si>
+  <si>
+    <t>仮想マシン,かそうましん,máy ảo,N,N2,仮想マシンを起動しました,Tôi đã khởi động máy ảo,tu-vung-cntt,lesson-29,Bài 29: Cloud Computing</t>
+  </si>
+  <si>
+    <t>インスタンス,いんすたんす,instance,N,N2,新しいインスタンスを作成しました,Tôi đã tạo instance mới,tu-vung-cntt,lesson-29,Bài 29: Cloud Computing</t>
+  </si>
+  <si>
+    <t>ストレージ,すとれーじ,lưu trữ,N,N3,クラウドストレージを利用しています,Tôi đang sử dụng lưu trữ đám mây,tu-vung-cntt,lesson-29,Bài 29: Cloud Computing</t>
+  </si>
+  <si>
+    <t>オブジェクトストレージ,おぶじぇくとすとれーじ,lưu trữ đối tượng,N,N1,オブジェクトストレージへ保存しました,Tôi đã lưu vào object storage,tu-vung-cntt,lesson-29,Bài 29: Cloud Computing</t>
+  </si>
+  <si>
+    <t>バケット,ばけっと,bucket,N,N1,新しいバケットを作成しました,Tôi đã tạo bucket mới,tu-vung-cntt,lesson-29,Bài 29: Cloud Computing</t>
+  </si>
+  <si>
+    <t>リージョン,りーじょん,vùng dữ liệu,N,N2,東京リージョンを選択しました,Tôi đã chọn vùng Tokyo,tu-vung-cntt,lesson-29,Bài 29: Cloud Computing</t>
+  </si>
+  <si>
+    <t>アベイラビリティゾーン,あべいらびりてぃぞーん,vùng khả dụng,N,N1,別のアベイラビリティゾーンへ配置しました,Tôi đã triển khai sang vùng khả dụng khác,tu-vung-cntt,lesson-29,Bài 29: Cloud Computing</t>
+  </si>
+  <si>
+    <t>スケーリング,すけーりんぐ,mở rộng quy mô,N,N1,自動スケーリングを設定しました,Tôi đã thiết lập tự động mở rộng,tu-vung-cntt,lesson-29,Bài 29: Cloud Computing</t>
+  </si>
+  <si>
+    <t>ロードバランサー,ろーどばらんさー,bộ cân bằng tải,N,N1,ロードバランサーを導入しました,Tôi đã triển khai bộ cân bằng tải,tu-vung-cntt,lesson-29,Bài 29: Cloud Computing</t>
+  </si>
+  <si>
+    <t>クラウド移行,くらうどいこう,di chuyển lên cloud,N,N1,クラウド移行を計画しています,Tôi đang lên kế hoạch chuyển lên cloud,tu-vung-cntt,lesson-29,Bài 29: Cloud Computing</t>
+  </si>
+  <si>
+    <t>AI,えーあい,trí tuệ nhân tạo,N,N4,AIを仕事で活用しています,Tôi đang ứng dụng AI trong công việc,tu-vung-cntt,lesson-30,Bài 30: AI và Machine Learning</t>
+  </si>
+  <si>
+    <t>人工知能,じんこうちのう,trí tuệ nhân tạo,N,N2,人工知能について学んでいます,Tôi đang học về trí tuệ nhân tạo,tu-vung-cntt,lesson-30,Bài 30: AI và Machine Learning</t>
+  </si>
+  <si>
+    <t>機械学習,きかいがくしゅう,máy học,N,N2,機械学習モデルを開発しました,Tôi đã phát triển mô hình machine learning,tu-vung-cntt,lesson-30,Bài 30: AI và Machine Learning</t>
+  </si>
+  <si>
+    <t>深層学習,しんそうがくしゅう,học sâu,N,N1,深層学習を研究しています,Tôi đang nghiên cứu deep learning,tu-vung-cntt,lesson-30,Bài 30: AI và Machine Learning</t>
+  </si>
+  <si>
+    <t>ニューラルネットワーク,にゅーらるねっとわーく,mạng nơ ron,N,N1,ニューラルネットワークを学習しました,Tôi đã huấn luyện mạng nơ ron,tu-vung-cntt,lesson-30,Bài 30: AI và Machine Learning</t>
+  </si>
+  <si>
+    <t>モデル,もでる,mô hình,N,N3,新しいモデルを評価しました,Tôi đã đánh giá mô hình mới,tu-vung-cntt,lesson-30,Bài 30: AI và Machine Learning</t>
+  </si>
+  <si>
+    <t>学習データ,がくしゅうでーた,dữ liệu huấn luyện,N,N2,学習データを追加しました,Tôi đã bổ sung dữ liệu huấn luyện,tu-vung-cntt,lesson-30,Bài 30: AI và Machine Learning</t>
+  </si>
+  <si>
+    <t>推論,すいろん,suy luận AI,N,N1,モデルで推論を実行しました,Tôi đã chạy suy luận bằng mô hình,tu-vung-cntt,lesson-30,Bài 30: AI và Machine Learning</t>
+  </si>
+  <si>
+    <t>精度,せいど,độ chính xác,N,N2,モデルの精度が向上しました,Độ chính xác của mô hình đã được cải thiện,tu-vung-cntt,lesson-30,Bài 30: AI và Machine Learning</t>
+  </si>
+  <si>
+    <t>特徴量,とくちょうりょう,đặc trưng dữ liệu,N,N1,特徴量を抽出しました,Tôi đã trích xuất đặc trưng dữ liệu,tu-vung-cntt,lesson-30,Bài 30: AI và Machine Learning</t>
+  </si>
+  <si>
+    <t>データセット,でーたせっと,tập dữ liệu,N,N2,データセットを分割しました,Tôi đã chia tập dữ liệu,tu-vung-cntt,lesson-30,Bài 30: AI và Machine Learning</t>
+  </si>
+  <si>
+    <t>過学習,かがくしゅう,quá khớp,N,N1,モデルが過学習しています,Mô hình đang bị overfitting,tu-vung-cntt,lesson-30,Bài 30: AI và Machine Learning</t>
+  </si>
+  <si>
+    <t>汎化性能,はんかせいのう,khả năng tổng quát hóa,N,N1,汎化性能を改善しました,Tôi đã cải thiện khả năng tổng quát hóa,tu-vung-cntt,lesson-30,Bài 30: AI và Machine Learning</t>
+  </si>
+  <si>
+    <t>フロントエンド,ふろんとえんど,frontend,N,N2,フロントエンドを担当しています,Tôi phụ trách frontend,tu-vung-cntt,lesson-31,Bài 31: Phát triển phần mềm hiện đại</t>
+  </si>
+  <si>
+    <t>バックエンド,ばっくえんど,backend,N,N2,バックエンドを開発しています,Tôi đang phát triển backend,tu-vung-cntt,lesson-31,Bài 31: Phát triển phần mềm hiện đại</t>
+  </si>
+  <si>
+    <t>フルスタック,ふるすたっく,full stack,N,N1,フルスタック開発者を目指しています,Tôi đang hướng tới trở thành full stack developer,tu-vung-cntt,lesson-31,Bài 31: Phát triển phần mềm hiện đại</t>
+  </si>
+  <si>
+    <t>API,えーぴーあい,API,N,N3,APIを利用して連携しました,Tôi đã tích hợp bằng API,tu-vung-cntt,lesson-31,Bài 31: Phát triển phần mềm hiện đại</t>
+  </si>
+  <si>
+    <t>REST API,れすとえーぴーあい,REST API,N,N2,REST APIを設計しました,Tôi đã thiết kế REST API,tu-vung-cntt,lesson-31,Bài 31: Phát triển phần mềm hiện đại</t>
+  </si>
+  <si>
+    <t>JSON,じぇいそん,JSON,N,N3,JSON形式で送信しました,Tôi đã gửi dưới định dạng JSON,tu-vung-cntt,lesson-31,Bài 31: Phát triển phần mềm hiện đại</t>
+  </si>
+  <si>
+    <t>XML,えっくすえむえる,XML,N,N2,XMLファイルを解析しました,Tôi đã phân tích tệp XML,tu-vung-cntt,lesson-31,Bài 31: Phát triển phần mềm hiện đại</t>
+  </si>
+  <si>
+    <t>SDK,えすでぃーけー,SDK,N,N2,SDKを導入しました,Tôi đã tích hợp SDK,tu-vung-cntt,lesson-31,Bài 31: Phát triển phần mềm hiện đại</t>
+  </si>
+  <si>
+    <t>ライブラリ,らいぶらり,thư viện,N,N3,新しいライブラリを追加しました,Tôi đã thêm thư viện mới,tu-vung-cntt,lesson-31,Bài 31: Phát triển phần mềm hiện đại</t>
+  </si>
+  <si>
+    <t>フレームワーク,ふれーむわーく,framework,N,N2,新しいフレームワークを勉強しています,Tôi đang học framework mới,tu-vung-cntt,lesson-31,Bài 31: Phát triển phần mềm hiện đại</t>
+  </si>
+  <si>
+    <t>デバッグ,でばっぐ,gỡ lỗi,N,N3,プログラムをデバッグしました,Tôi đã gỡ lỗi chương trình,tu-vung-cntt,lesson-31,Bài 31: Phát triển phần mềm hiện đại</t>
+  </si>
+  <si>
+    <t>ビルド,びるど,build,N,N2,プロジェクトをビルドしました,Tôi đã build dự án,tu-vung-cntt,lesson-31,Bài 31: Phát triển phần mềm hiện đại</t>
+  </si>
+  <si>
+    <t>デプロイ,でぷろい,triển khai,N,N2,本番環境へデプロイしました,Tôi đã triển khai lên môi trường production,tu-vung-cntt,lesson-31,Bài 31: Phát triển phần mềm hiện đại</t>
+  </si>
+  <si>
+    <t>CI,しーあい,Continuous Integration,N,N1,CIを導入しました,Tôi đã triển khai CI,tu-vung-cntt,lesson-31,Bài 31: Phát triển phần mềm hiện đại</t>
+  </si>
+  <si>
+    <t>CD,しーでぃー,Continuous Delivery,N,N1,CDを自動化しました,Tôi đã tự động hóa CD,tu-vung-cntt,lesson-31,Bài 31: Phát triển phần mềm hiện đại</t>
+  </si>
+  <si>
+    <t>DevOps,でぶおぷす,DevOps,N,N1,DevOpsを実践しています,Tôi đang áp dụng DevOps,tu-vung-cntt,lesson-32,Bài 32: DevOps và Container</t>
+  </si>
+  <si>
+    <t>Docker,どっかー,Docker,N,N2,Dockerで環境を構築しました,Tôi đã xây dựng môi trường bằng Docker,tu-vung-cntt,lesson-32,Bài 32: DevOps và Container</t>
+  </si>
+  <si>
+    <t>コンテナ,こんてな,container,N,N2,コンテナを起動しました,Tôi đã khởi động container,tu-vung-cntt,lesson-32,Bài 32: DevOps và Container</t>
+  </si>
+  <si>
+    <t>Kubernetes,くばねてす,Kubernetes,N,N1,Kubernetesを学習しています,Tôi đang học Kubernetes,tu-vung-cntt,lesson-32,Bài 32: DevOps và Container</t>
+  </si>
+  <si>
+    <t>イメージ,いめーじ,image Docker,N,N2,Dockerイメージを作成しました,Tôi đã tạo Docker image,tu-vung-cntt,lesson-32,Bài 32: DevOps và Container</t>
+  </si>
+  <si>
+    <t>レジストリ,れじすとり,registry,N,N1,レジストリへイメージを保存しました,Tôi đã lưu image vào registry,tu-vung-cntt,lesson-32,Bài 32: DevOps và Container</t>
+  </si>
+  <si>
+    <t>パイプライン,ぱいぷらいん,pipeline,N,N1,CIパイプラインを作成しました,Tôi đã tạo pipeline CI,tu-vung-cntt,lesson-32,Bài 32: DevOps và Container</t>
+  </si>
+  <si>
+    <t>自動化,じどうか,tự động hóa,N,N2,業務を自動化しています,Tôi đang tự động hóa công việc,tu-vung-cntt,lesson-32,Bài 32: DevOps và Container</t>
+  </si>
+  <si>
+    <t>監視,かんし,giám sát,N,N2,サーバーを二十四時間監視しています,Tôi giám sát máy chủ hai mươi bốn giờ,tu-vung-cntt,lesson-32,Bài 32: DevOps và Container</t>
+  </si>
+  <si>
+    <t>ログ収集,ろぐしゅうしゅう,thu thập log,N,N1,ログ収集を自動化しました,Tôi đã tự động hóa việc thu thập log,tu-vung-cntt,lesson-32,Bài 32: DevOps và Container</t>
+  </si>
+  <si>
+    <t>アラート,あらーと,cảnh báo,N,N2,障害アラートを受信しました,Tôi đã nhận cảnh báo sự cố,tu-vung-cntt,lesson-32,Bài 32: DevOps và Container</t>
+  </si>
+  <si>
+    <t>Prometheus,ぷろめてうす,Prometheus,N,N1,Prometheusで監視しています,Tôi đang giám sát bằng Prometheus,tu-vung-cntt,lesson-32,Bài 32: DevOps và Container</t>
+  </si>
+  <si>
+    <t>Grafana,ぐらふぁな,Grafana,N,N1,Grafanaでダッシュボードを表示します,Tôi hiển thị dashboard bằng Grafana,tu-vung-cntt,lesson-32,Bài 32: DevOps và Container</t>
+  </si>
+  <si>
+    <t>Ansible,あんしぶる,Ansible,N,N1,Ansibleで構成管理を行います,Tôi quản lý cấu hình bằng Ansible,tu-vung-cntt,lesson-32,Bài 32: DevOps và Container</t>
+  </si>
+  <si>
+    <t>Terraform,てらふぉーむ,Terraform,N,N1,Terraformで環境を構築しました,Tôi đã xây dựng hạ tầng bằng Terraform,tu-vung-cntt,lesson-32,Bài 32: DevOps và Container</t>
+  </si>
+  <si>
+    <t>要件定義,ようけんていぎ,phân tích yêu cầu,N,N2,要件定義を開始しました,Tôi đã bắt đầu phân tích yêu cầu,tu-vung-cntt,lesson-33,Bài 33: Quy trình phát triển phần mềm</t>
+  </si>
+  <si>
+    <t>基本設計,きほんせっけい,thiết kế cơ bản,N,N2,基本設計を作成しました,Tôi đã hoàn thành thiết kế cơ bản,tu-vung-cntt,lesson-33,Bài 33: Quy trình phát triển phần mềm</t>
+  </si>
+  <si>
+    <t>詳細設計,しょうさいせっけい,thiết kế chi tiết,N,N2,詳細設計を確認してください,Hãy kiểm tra thiết kế chi tiết,tu-vung-cntt,lesson-33,Bài 33: Quy trình phát triển phần mềm</t>
+  </si>
+  <si>
+    <t>実装,じっそう,triển khai lập trình,N,N2,実装を担当しています,Tôi phụ trách triển khai lập trình,tu-vung-cntt,lesson-33,Bài 33: Quy trình phát triển phần mềm</t>
+  </si>
+  <si>
+    <t>単体テスト,たんたいてすと,kiểm thử đơn vị,N,N2,単体テストを実施しました,Tôi đã thực hiện kiểm thử đơn vị,tu-vung-cntt,lesson-33,Bài 33: Quy trình phát triển phần mềm</t>
+  </si>
+  <si>
+    <t>結合テスト,けつごうてすと,kiểm thử tích hợp,N,N2,結合テストを開始しました,Tôi đã bắt đầu kiểm thử tích hợp,tu-vung-cntt,lesson-33,Bài 33: Quy trình phát triển phần mềm</t>
+  </si>
+  <si>
+    <t>総合テスト,そうごうてすと,kiểm thử hệ thống,N,N2,総合テストを完了しました,Tôi đã hoàn thành kiểm thử hệ thống,tu-vung-cntt,lesson-33,Bài 33: Quy trình phát triển phần mềm</t>
+  </si>
+  <si>
+    <t>受け入れテスト,うけいれてすと,kiểm thử chấp nhận,N,N1,受け入れテストを実施しました,Tôi đã thực hiện kiểm thử chấp nhận,tu-vung-cntt,lesson-33,Bài 33: Quy trình phát triển phần mềm</t>
+  </si>
+  <si>
+    <t>リリース,りりーす,phát hành,N,N3,来週システムをリリースします,Tuần sau sẽ phát hành hệ thống,tu-vung-cntt,lesson-33,Bài 33: Quy trình phát triển phần mềm</t>
+  </si>
+  <si>
+    <t>保守,ほしゅ,bảo trì,N,N2,システム保守を担当しています,Tôi phụ trách bảo trì hệ thống,tu-vung-cntt,lesson-33,Bài 33: Quy trình phát triển phần mềm</t>
+  </si>
+  <si>
+    <t>運用,うんよう,vận hành,N,N2,本番環境を運用しています,Tôi đang vận hành môi trường production,tu-vung-cntt,lesson-33,Bài 33: Quy trình phát triển phần mềm</t>
+  </si>
+  <si>
+    <t>改修,かいしゅう,cải tiến hệ thống,N,N1,システムを改修しました,Tôi đã cải tiến hệ thống,tu-vung-cntt,lesson-33,Bài 33: Quy trình phát triển phần mềm</t>
+  </si>
+  <si>
+    <t>仕様書,しようしょ,tài liệu đặc tả,N,N2,仕様書を更新しました,Tôi đã cập nhật tài liệu đặc tả,tu-vung-cntt,lesson-33,Bài 33: Quy trình phát triển phần mềm</t>
+  </si>
+  <si>
+    <t>設計書,せっけいしょ,tài liệu thiết kế,N,N2,設計書を共有しました,Tôi đã chia sẻ tài liệu thiết kế,tu-vung-cntt,lesson-33,Bài 33: Quy trình phát triển phần mềm</t>
+  </si>
+  <si>
+    <t>納品,のうひん,bàn giao sản phẩm,N,N1,予定通り納品しました,Tôi đã bàn giao đúng tiến độ,tu-vung-cntt,lesson-33,Bài 33: Quy trình phát triển phần mềm</t>
+  </si>
+  <si>
+    <t>アジャイル,あじゃいる,Agile,N,N2,アジャイル開発を採用しています,Tôi đang áp dụng phát triển Agile,tu-vung-cntt,lesson-34,Bài 34: Agile và Scrum</t>
+  </si>
+  <si>
+    <t>スクラム,すくらむ,Scrum,N,N2,スクラムで開発しています,Tôi phát triển theo Scrum,tu-vung-cntt,lesson-34,Bài 34: Agile và Scrum</t>
+  </si>
+  <si>
+    <t>スプリント,すぷりんと,sprint,N,N2,二週間のスプリントを開始しました,Tôi đã bắt đầu sprint hai tuần,tu-vung-cntt,lesson-34,Bài 34: Agile và Scrum</t>
+  </si>
+  <si>
+    <t>プロダクトバックログ,ぷろだくとばっくろぐ,product backlog,N,N1,バックログを更新しました,Tôi đã cập nhật product backlog,tu-vung-cntt,lesson-34,Bài 34: Agile và Scrum</t>
+  </si>
+  <si>
+    <t>スプリントバックログ,すぷりんとばっくろぐ,sprint backlog,N,N1,スプリントバックログを確認します,Tôi kiểm tra sprint backlog,tu-vung-cntt,lesson-34,Bài 34: Agile và Scrum</t>
+  </si>
+  <si>
+    <t>ユーザーストーリー,ゆーざーすとーりー,user story,N,N1,ユーザーストーリーを書きました,Tôi đã viết user story,tu-vung-cntt,lesson-34,Bài 34: Agile và Scrum</t>
+  </si>
+  <si>
+    <t>タスク,たすく,công việc,N,N5,今日のタスクを終えました,Tôi đã hoàn thành công việc hôm nay,tu-vung-cntt,lesson-34,Bài 34: Agile và Scrum</t>
+  </si>
+  <si>
+    <t>進捗,しんちょく,tiến độ,N,N2,進捗を毎日報告します,Tôi báo cáo tiến độ hằng ngày,tu-vung-cntt,lesson-34,Bài 34: Agile và Scrum</t>
+  </si>
+  <si>
+    <t>朝会,あさかい,họp đầu ngày,N,N2,朝会に参加してください,Hãy tham gia cuộc họp đầu ngày,tu-vung-cntt,lesson-34,Bài 34: Agile và Scrum</t>
+  </si>
+  <si>
+    <t>ふりかえり,ふりかえり,họp retrospective,N,N2,スプリント後にふりかえりを行います,Chúng tôi họp retrospective sau sprint,tu-vung-cntt,lesson-34,Bài 34: Agile và Scrum</t>
+  </si>
+  <si>
+    <t>優先順位,ゆうせんじゅんい,mức ưu tiên,N,N2,優先順位を変更しました,Tôi đã thay đổi mức ưu tiên,tu-vung-cntt,lesson-34,Bài 34: Agile và Scrum</t>
+  </si>
+  <si>
+    <t>見積もり,みつもり,ước lượng,N,N2,工数を見積もりました,Tôi đã ước lượng khối lượng công việc,tu-vung-cntt,lesson-34,Bài 34: Agile và Scrum</t>
+  </si>
+  <si>
+    <t>工数,こうすう,khối lượng công việc,N,N1,工数を削減しました,Tôi đã giảm khối lượng công việc,tu-vung-cntt,lesson-34,Bài 34: Agile và Scrum</t>
+  </si>
+  <si>
+    <t>バーンダウンチャート,ばーんだうんちゃーと,biểu đồ burndown,N,N1,バーンダウンチャートを確認しました,Tôi đã kiểm tra biểu đồ burndown,tu-vung-cntt,lesson-34,Bài 34: Agile và Scrum</t>
+  </si>
+  <si>
+    <t>スクラムマスター,すくらむますたー,Scrum Master,N,N1,スクラムマスターと相談しました,Tôi đã trao đổi với Scrum Master,tu-vung-cntt,lesson-34,Bài 34: Agile và Scrum</t>
+  </si>
+  <si>
+    <t>ブリッジSE,ぶりっじえすいー,BrSE,N,N2,ブリッジSEとして働いています,Tôi làm việc với vai trò BrSE,tu-vung-cntt,lesson-35,Bài 35: Thuật ngữ IT công ty Nhật</t>
+  </si>
+  <si>
+    <t>オフショア,おふしょあ,offshore,N,N2,オフショア開発を担当しています,Tôi phụ trách phát triển offshore,tu-vung-cntt,lesson-35,Bài 35: Thuật ngữ IT công ty Nhật</t>
+  </si>
+  <si>
+    <t>ニアショア,にあしょあ,nearshore,N,N1,ニアショア開発を検討しています,Chúng tôi đang xem xét phát triển nearshore,tu-vung-cntt,lesson-35,Bài 35: Thuật ngữ IT công ty Nhật</t>
+  </si>
+  <si>
+    <t>客先,きゃくさき,khách hàng,N,N2,客先へ訪問しました,Tôi đã đến công ty khách hàng,tu-vung-cntt,lesson-35,Bài 35: Thuật ngữ IT công ty Nhật</t>
+  </si>
+  <si>
+    <t>顧客,こきゃく,khách hàng,N,N3,顧客へ報告しました,Tôi đã báo cáo với khách hàng,tu-vung-cntt,lesson-35,Bài 35: Thuật ngữ IT công ty Nhật</t>
+  </si>
+  <si>
+    <t>仕様変更,しようへんこう,thay đổi yêu cầu,N,N2,仕様変更がありました,Yêu cầu đã có thay đổi,tu-vung-cntt,lesson-35,Bài 35: Thuật ngữ IT công ty Nhật</t>
+  </si>
+  <si>
+    <t>障害票,しょうがいひょう,phiếu lỗi,N,N1,障害票を登録しました,Tôi đã tạo phiếu lỗi,tu-vung-cntt,lesson-35,Bài 35: Thuật ngữ IT công ty Nhật</t>
+  </si>
+  <si>
+    <t>課題管理,かだいかんり,quản lý vấn đề,N,N1,課題管理を行っています,Tôi đang quản lý các vấn đề,tu-vung-cntt,lesson-35,Bài 35: Thuật ngữ IT công ty Nhật</t>
+  </si>
+  <si>
+    <t>担当者,たんとうしゃ,người phụ trách,N,N3,担当者へ連絡しました,Tôi đã liên hệ người phụ trách,tu-vung-cntt,lesson-35,Bài 35: Thuật ngữ IT công ty Nhật</t>
+  </si>
+  <si>
+    <t>承認,しょうにん,phê duyệt,N,N2,上司の承認を受けました,Tôi đã nhận được phê duyệt của cấp trên,tu-vung-cntt,lesson-35,Bài 35: Thuật ngữ IT công ty Nhật</t>
+  </si>
+  <si>
+    <t>稼働,かどう,vận hành,N,N1,システムが正常に稼働しています,Hệ thống đang vận hành bình thường,tu-vung-cntt,lesson-35,Bài 35: Thuật ngữ IT công ty Nhật</t>
+  </si>
+  <si>
+    <t>納期,のうき,hạn giao hàng,N,N2,納期を守ってください,Hãy đảm bảo đúng thời hạn giao hàng,tu-vung-cntt,lesson-35,Bài 35: Thuật ngữ IT công ty Nhật</t>
+  </si>
+  <si>
+    <t>品質保証,ひんしつほしょう,đảm bảo chất lượng,N,N1,品質保証を強化しました,Tôi đã tăng cường đảm bảo chất lượng,tu-vung-cntt,lesson-35,Bài 35: Thuật ngữ IT công ty Nhật</t>
+  </si>
+  <si>
+    <t>品質管理,ひんしつかんり,quản lý chất lượng,N,N1,品質管理を担当しています,Tôi phụ trách quản lý chất lượng,tu-vung-cntt,lesson-35,Bài 35: Thuật ngữ IT công ty Nhật</t>
+  </si>
+  <si>
+    <t>検収,けんしゅう,nghiệm thu,N,N1,検収が完了しました,Việc nghiệm thu đã hoàn tất,tu-vung-cntt,lesson-35,Bài 35: Thuật ngữ IT công ty Nhật</t>
+  </si>
+  <si>
+    <t>報告,ほうこく,báo cáo,N,N4,毎日進捗を報告します,Tôi báo cáo tiến độ hằng ngày,tu-vung-cntt,lesson-36,Bài 36: Giao tiếp trong công ty IT Nhật</t>
+  </si>
+  <si>
+    <t>連絡,れんらく,liên lạc,N,N4,問題があれば連絡してください,Hãy liên lạc nếu có vấn đề,tu-vung-cntt,lesson-36,Bài 36: Giao tiếp trong công ty IT Nhật</t>
+  </si>
+  <si>
+    <t>相談,そうだん,trao đổi; tham khảo ý kiến,N,N4,困ったら相談してください,Hãy trao đổi nếu gặp khó khăn,tu-vung-cntt,lesson-36,Bài 36: Giao tiếp trong công ty IT Nhật</t>
+  </si>
+  <si>
+    <t>確認,かくにん,xác nhận,N,N4,内容を確認してください,Hãy xác nhận nội dung,tu-vung-cntt,lesson-36,Bài 36: Giao tiếp trong công ty IT Nhật</t>
+  </si>
+  <si>
+    <t>依頼,いらい,yêu cầu,N,N3,作業を依頼しました,Tôi đã yêu cầu thực hiện công việc,tu-vung-cntt,lesson-36,Bài 36: Giao tiếp trong công ty IT Nhật</t>
+  </si>
+  <si>
+    <t>対応,たいおう,xử lý; ứng phó,N,N3,すぐに対応します,Tôi sẽ xử lý ngay lập tức,tu-vung-cntt,lesson-36,Bài 36: Giao tiếp trong công ty IT Nhật</t>
+  </si>
+  <si>
+    <t>共有,きょうゆう,chia sẻ,N,N3,情報を共有してください,Hãy chia sẻ thông tin,tu-vung-cntt,lesson-36,Bài 36: Giao tiếp trong công ty IT Nhật</t>
+  </si>
+  <si>
+    <t>引き継ぎ,ひきつぎ,bàn giao công việc,N,N2,引き継ぎ資料を作成しました,Tôi đã tạo tài liệu bàn giao,tu-vung-cntt,lesson-36,Bài 36: Giao tiếp trong công ty IT Nhật</t>
+  </si>
+  <si>
+    <t>期限,きげん,hạn chót,N,N3,期限までに提出してください,Hãy nộp trước thời hạn,tu-vung-cntt,lesson-36,Bài 36: Giao tiếp trong công ty IT Nhật</t>
+  </si>
+  <si>
+    <t>進行状況,しんこうじょうきょう,tình hình tiến độ,N,N2,進行状況を確認しました,Tôi đã kiểm tra tình hình tiến độ,tu-vung-cntt,lesson-36,Bài 36: Giao tiếp trong công ty IT Nhật</t>
+  </si>
+  <si>
+    <t>遅延,ちえん,chậm tiến độ,N,N2,納期に遅延が発生しました,Đã xảy ra chậm tiến độ giao hàng,tu-vung-cntt,lesson-36,Bài 36: Giao tiếp trong công ty IT Nhật</t>
+  </si>
+  <si>
+    <t>原因,げんいん,nguyên nhân,N,N3,原因を調査しています,Tôi đang điều tra nguyên nhân,tu-vung-cntt,lesson-36,Bài 36: Giao tiếp trong công ty IT Nhật</t>
+  </si>
+  <si>
+    <t>対策,たいさく,biện pháp đối phó,N,N2,再発防止の対策を考えます,Chúng tôi sẽ đưa ra biện pháp ngăn tái diễn,tu-vung-cntt,lesson-36,Bài 36: Giao tiếp trong công ty IT Nhật</t>
+  </si>
+  <si>
+    <t>再発防止,さいはつぼうし,ngăn tái diễn,N,N1,再発防止策を実施しました,Tôi đã thực hiện biện pháp ngăn tái diễn,tu-vung-cntt,lesson-36,Bài 36: Giao tiếp trong công ty IT Nhật</t>
+  </si>
+  <si>
+    <t>議事録,ぎじろく,biên bản cuộc họp,N,N2,議事録を全員へ共有しました,Tôi đã chia sẻ biên bản cuộc họp cho mọi người,tu-vung-cntt,lesson-36,Bài 36: Giao tiếp trong công ty IT Nhật</t>
+  </si>
+  <si>
+    <t>リファクタリング,りふぁくたりんぐ,tái cấu trúc mã nguồn,N,N1,コードをリファクタリングしました,Tôi đã tái cấu trúc mã nguồn,tu-vung-cntt,lesson-37,Bài 37: Chất lượng phần mềm</t>
+  </si>
+  <si>
+    <t>技術的負債,ぎじゅつてきふさい,nợ kỹ thuật,N,N1,技術的負債を減らします,Chúng tôi sẽ giảm nợ kỹ thuật,tu-vung-cntt,lesson-37,Bài 37: Chất lượng phần mềm</t>
+  </si>
+  <si>
+    <t>コードレビュー,こーどれびゅー,review mã nguồn,N,N2,コードレビューを実施しました,Tôi đã thực hiện review mã nguồn,tu-vung-cntt,lesson-37,Bài 37: Chất lượng phần mềm</t>
+  </si>
+  <si>
+    <t>静的解析,せいてきかいせき,phân tích tĩnh,N,N1,静的解析ツールを実行しました,Tôi đã chạy công cụ phân tích tĩnh,tu-vung-cntt,lesson-37,Bài 37: Chất lượng phần mềm</t>
+  </si>
+  <si>
+    <t>単体試験,たんたいしけん,kiểm thử đơn vị,N,N2,単体試験を自動化しました,Tôi đã tự động hóa kiểm thử đơn vị,tu-vung-cntt,lesson-37,Bài 37: Chất lượng phần mềm</t>
+  </si>
+  <si>
+    <t>回帰テスト,かいきてすと,kiểm thử hồi quy,N,N1,回帰テストを実施しました,Tôi đã thực hiện kiểm thử hồi quy,tu-vung-cntt,lesson-37,Bài 37: Chất lượng phần mềm</t>
+  </si>
+  <si>
+    <t>品質,ひんしつ,chất lượng,N,N3,品質を改善しています,Tôi đang cải thiện chất lượng,tu-vung-cntt,lesson-37,Bài 37: Chất lượng phần mềm</t>
+  </si>
+  <si>
+    <t>保守性,ほしゅせい,khả năng bảo trì,N,N1,保守性を向上させました,Tôi đã nâng cao khả năng bảo trì,tu-vung-cntt,lesson-37,Bài 37: Chất lượng phần mềm</t>
+  </si>
+  <si>
+    <t>可読性,かどくせい,khả năng đọc hiểu mã,N,N1,コードの可読性を高めました,Tôi đã cải thiện khả năng đọc của mã,tu-vung-cntt,lesson-37,Bài 37: Chất lượng phần mềm</t>
+  </si>
+  <si>
+    <t>再利用性,さいりようせい,khả năng tái sử dụng,N,N1,再利用性を意識して設計しました,Tôi thiết kế chú trọng khả năng tái sử dụng,tu-vung-cntt,lesson-37,Bài 37: Chất lượng phần mềm</t>
+  </si>
+  <si>
+    <t>例外処理,れいがいしょり,xử lý ngoại lệ,N,N1,例外処理を追加しました,Tôi đã bổ sung xử lý ngoại lệ,tu-vung-cntt,lesson-37,Bài 37: Chất lượng phần mềm</t>
+  </si>
+  <si>
+    <t>ログ出力,ろぐしゅつりょく,xuất log,N,N2,ログ出力を有効にしました,Tôi đã bật ghi log,tu-vung-cntt,lesson-37,Bài 37: Chất lượng phần mềm</t>
+  </si>
+  <si>
+    <t>コーディング規約,こーでぃんぐきやく,quy chuẩn lập trình,N,N1,コーディング規約を守ってください,Hãy tuân thủ quy chuẩn lập trình,tu-vung-cntt,lesson-37,Bài 37: Chất lượng phần mềm</t>
+  </si>
+  <si>
+    <t>テストケース,てすとけーす,test case,N,N2,テストケースを追加しました,Tôi đã bổ sung test case,tu-vung-cntt,lesson-37,Bài 37: Chất lượng phần mềm</t>
+  </si>
+  <si>
+    <t>不具合修正,ふぐあいしゅうせい,sửa lỗi,N,N2,不具合修正が完了しました,Việc sửa lỗi đã hoàn tất,tu-vung-cntt,lesson-37,Bài 37: Chất lượng phần mềm</t>
+  </si>
+  <si>
+    <t>マイクロサービス,まいくろさーびす,microservice,N,N1,マイクロサービスへ移行しました,Tôi đã chuyển sang kiến trúc microservice,tu-vung-cntt,lesson-38,Bài 38: Kiến trúc hệ thống</t>
+  </si>
+  <si>
+    <t>モノリス,ものりす,monolith,N,N1,モノリス構成を採用しています,Tôi đang sử dụng kiến trúc monolith,tu-vung-cntt,lesson-38,Bài 38: Kiến trúc hệ thống</t>
+  </si>
+  <si>
+    <t>アーキテクチャ,あーきてくちゃ,kiến trúc hệ thống,N,N2,システムアーキテクチャを設計しました,Tôi đã thiết kế kiến trúc hệ thống,tu-vung-cntt,lesson-38,Bài 38: Kiến trúc hệ thống</t>
+  </si>
+  <si>
+    <t>モジュール,もじゅーる,module,N,N2,モジュールを分割しました,Tôi đã tách các module,tu-vung-cntt,lesson-38,Bài 38: Kiến trúc hệ thống</t>
+  </si>
+  <si>
+    <t>ミドルウェア,みどるうぇあ,middleware,N,N1,ミドルウェアを更新しました,Tôi đã cập nhật middleware,tu-vung-cntt,lesson-38,Bài 38: Kiến trúc hệ thống</t>
+  </si>
+  <si>
+    <t>キャッシュ,きゃっしゅ,bộ nhớ đệm,N,N2,キャッシュを削除しました,Tôi đã xóa bộ nhớ đệm,tu-vung-cntt,lesson-38,Bài 38: Kiến trúc hệ thống</t>
+  </si>
+  <si>
+    <t>メッセージキュー,めっせーじきゅー,hàng đợi thông điệp,N,N1,メッセージキューを導入しました,Tôi đã triển khai message queue,tu-vung-cntt,lesson-38,Bài 38: Kiến trúc hệ thống</t>
+  </si>
+  <si>
+    <t>負荷分散,ふかぶんさん,cân bằng tải,N,N1,負荷分散を設定しました,Tôi đã cấu hình cân bằng tải,tu-vung-cntt,lesson-38,Bài 38: Kiến trúc hệ thống</t>
+  </si>
+  <si>
+    <t>冗長構成,じょうちょうこうせい,kiến trúc dự phòng,N,N1,冗長構成を構築しました,Tôi đã xây dựng kiến trúc dự phòng,tu-vung-cntt,lesson-38,Bài 38: Kiến trúc hệ thống</t>
+  </si>
+  <si>
+    <t>高可用性,こうかようせい,tính sẵn sàng cao,N,N1,高可用性を実現しました,Tôi đã đạt được tính sẵn sàng cao,tu-vung-cntt,lesson-38,Bài 38: Kiến trúc hệ thống</t>
+  </si>
+  <si>
+    <t>スループット,するーぷっと,thông lượng,N,N1,スループットを改善しました,Tôi đã cải thiện thông lượng,tu-vung-cntt,lesson-38,Bài 38: Kiến trúc hệ thống</t>
+  </si>
+  <si>
+    <t>レイテンシ,れいてんし,độ trễ,N,N1,レイテンシが増加しました,Độ trễ đã tăng lên,tu-vung-cntt,lesson-38,Bài 38: Kiến trúc hệ thống</t>
+  </si>
+  <si>
+    <t>ボトルネック,ぼとるねっく,điểm nghẽn,N,N1,ボトルネックを特定しました,Tôi đã xác định điểm nghẽn,tu-vung-cntt,lesson-38,Bài 38: Kiến trúc hệ thống</t>
+  </si>
+  <si>
+    <t>スケーラビリティ,すけーらびりてぃ,khả năng mở rộng,N,N1,スケーラビリティを向上させました,Tôi đã nâng cao khả năng mở rộng,tu-vung-cntt,lesson-38,Bài 38: Kiến trúc hệ thống</t>
+  </si>
+  <si>
+    <t>可観測性,かかんそくせい,khả năng quan sát hệ thống,N,N1,可観測性を強化しました,Tôi đã tăng cường khả năng quan sát hệ thống,tu-vung-cntt,lesson-38,Bài 38: Kiến trúc hệ thống</t>
+  </si>
+  <si>
+    <t>敬語,けいご,kính ngữ,N,N3,敬語を正しく使ってください,Hãy sử dụng kính ngữ đúng cách,tu-vung-cntt,lesson-39,Bài 39: Giao tiếp với khách hàng Nhật</t>
+  </si>
+  <si>
+    <t>ご回答,ごかいとう,phản hồi,N,N2,ご回答をお待ちしております,Chúng tôi đang chờ phản hồi,tu-vung-cntt,lesson-39,Bài 39: Giao tiếp với khách hàng Nhật</t>
+  </si>
+  <si>
+    <t>ご協力,ごきょうりょく,sự hợp tác,N,N3,ご協力ありがとうございます,Cảm ơn sự hợp tác của quý vị,tu-vung-cntt,lesson-39,Bài 39: Giao tiếp với khách hàng Nhật</t>
+  </si>
+  <si>
+    <t>折り返し,おりかえし,gọi lại; phản hồi lại,N,N2,折り返しご連絡します,Tôi sẽ liên hệ lại,tu-vung-cntt,lesson-39,Bài 39: Giao tiếp với khách hàng Nhật</t>
+  </si>
+  <si>
+    <t>稟議,りんぎ,đề xuất phê duyệt nội bộ,N,N1,稟議を提出しました,Tôi đã gửi đề xuất phê duyệt,tu-vung-cntt,lesson-40,Bài 40: Doanh nghiệp Nhật Bản</t>
+  </si>
+  <si>
+    <t>稟議書,りんぎしょ,tài liệu xin phê duyệt,N,N1,稟議書を作成しました,Tôi đã tạo tài liệu xin phê duyệt,tu-vung-cntt,lesson-40,Bài 40: Doanh nghiệp Nhật Bản</t>
+  </si>
+  <si>
+    <t>決裁,けっさい,phê duyệt cuối cùng,N,N1,決裁が完了しました,Việc phê duyệt cuối cùng đã hoàn tất,tu-vung-cntt,lesson-40,Bài 40: Doanh nghiệp Nhật Bản</t>
+  </si>
+  <si>
+    <t>承認フロー,しょうにんふろー,quy trình phê duyệt,N,N1,承認フローを変更しました,Tôi đã thay đổi quy trình phê duyệt,tu-vung-cntt,lesson-40,Bài 40: Doanh nghiệp Nhật Bản</t>
+  </si>
+  <si>
+    <t>業務改善,ぎょうむかいぜん,cải tiến nghiệp vụ,N,N1,業務改善を提案しました,Tôi đã đề xuất cải tiến nghiệp vụ,tu-vung-cntt,lesson-40,Bài 40: Doanh nghiệp Nhật Bản</t>
+  </si>
+  <si>
+    <t>標準化,ひょうじゅんか,tiêu chuẩn hóa,N,N1,業務を標準化しました,Tôi đã tiêu chuẩn hóa quy trình,tu-vung-cntt,lesson-40,Bài 40: Doanh nghiệp Nhật Bản</t>
+  </si>
+  <si>
+    <t>手順書,てじゅんしょ,tài liệu hướng dẫn quy trình,N,N2,手順書を更新しました,Tôi đã cập nhật tài liệu hướng dẫn,tu-vung-cntt,lesson-40,Bài 40: Doanh nghiệp Nhật Bản</t>
+  </si>
+  <si>
+    <t>業務フロー,ぎょうむふろー,quy trình nghiệp vụ,N,N1,業務フローを見直しました,Tôi đã rà soát quy trình nghiệp vụ,tu-vung-cntt,lesson-40,Bài 40: Doanh nghiệp Nhật Bản</t>
+  </si>
+  <si>
+    <t>標準手順書,ひょうじゅんてじゅんしょ,tài liệu quy trình chuẩn,N,N1,標準手順書を共有しました,Tôi đã chia sẻ tài liệu quy trình chuẩn,tu-vung-cntt,lesson-40,Bài 40: Doanh nghiệp Nhật Bản</t>
+  </si>
+  <si>
+    <t>引合い,ひきあい,yêu cầu báo giá,N,N1,新しい引合いが届きました,Đã nhận được yêu cầu báo giá mới,tu-vung-cntt,lesson-40,Bài 40: Doanh nghiệp Nhật Bản</t>
+  </si>
+  <si>
+    <t>見積書,みつもりしょ,báo giá,N,N2,見積書を送付しました,Tôi đã gửi báo giá,tu-vung-cntt,lesson-40,Bài 40: Doanh nghiệp Nhật Bản</t>
+  </si>
+  <si>
+    <t>請求書,せいきゅうしょ,hóa đơn,N,N2,請求書を発行しました,Tôi đã phát hành hóa đơn,tu-vung-cntt,lesson-40,Bài 40: Doanh nghiệp Nhật Bản</t>
+  </si>
+  <si>
+    <t>契約書,けいやくしょ,hợp đồng,N,N2,契約書を確認してください,Hãy xác nhận hợp đồng,tu-vung-cntt,lesson-40,Bài 40: Doanh nghiệp Nhật Bản</t>
+  </si>
+  <si>
+    <t>秘密保持契約,ひみつほじけいやく,thỏa thuận bảo mật,N,N1,秘密保持契約を締結しました,Chúng tôi đã ký thỏa thuận bảo mật,tu-vung-cntt,lesson-40,Bài 40: Doanh nghiệp Nhật Bản</t>
+  </si>
+  <si>
+    <t>IoT,あいおーてぃー,Internet vạn vật,N,N2,IoT機器を管理しています,Tôi đang quản lý các thiết bị IoT,tu-vung-cntt,lesson-42,Bài 42: Công nghệ hiện đại</t>
+  </si>
+  <si>
+    <t>ビッグデータ,びっぐでーた,dữ liệu lớn,N,N2,ビッグデータを分析しています,Tôi đang phân tích dữ liệu lớn,tu-vung-cntt,lesson-42,Bài 42: Công nghệ hiện đại</t>
+  </si>
+  <si>
+    <t>データ分析,でーたぶんせき,phân tích dữ liệu,N,N2,データ分析を担当しています,Tôi phụ trách phân tích dữ liệu,tu-vung-cntt,lesson-42,Bài 42: Công nghệ hiện đại</t>
+  </si>
+  <si>
+    <t>データサイエンス,でーたさいえんす,khoa học dữ liệu,N,N1,データサイエンスを勉強しています,Tôi đang học khoa học dữ liệu,tu-vung-cntt,lesson-42,Bài 42: Công nghệ hiện đại</t>
+  </si>
+  <si>
+    <t>ブロックチェーン,ぶろっくちぇーん,blockchain,N,N1,ブロックチェーン技術を学びます,Tôi học công nghệ blockchain,tu-vung-cntt,lesson-42,Bài 42: Công nghệ hiện đại</t>
+  </si>
+  <si>
+    <t>スマートコントラクト,すまーとこんとらくと,hợp đồng thông minh,N,N1,スマートコントラクトを開発しました,Tôi đã phát triển smart contract,tu-vung-cntt,lesson-42,Bài 42: Công nghệ hiện đại</t>
+  </si>
+  <si>
+    <t>生成AI,せいせいえーあい,AI tạo sinh,N,N1,生成AIを業務で利用しています,Tôi đang sử dụng AI tạo sinh trong công việc,tu-vung-cntt,lesson-42,Bài 42: Công nghệ hiện đại</t>
+  </si>
+  <si>
+    <t>自然言語処理,しぜんげんごしょり,xử lý ngôn ngữ tự nhiên,N,N1,自然言語処理を研究しています,Tôi đang nghiên cứu xử lý ngôn ngữ tự nhiên,tu-vung-cntt,lesson-42,Bài 42: Công nghệ hiện đại</t>
+  </si>
+  <si>
+    <t>画像認識,がぞうにんしき,nhận dạng hình ảnh,N,N1,画像認識モデルを改善しました,Tôi đã cải thiện mô hình nhận dạng hình ảnh,tu-vung-cntt,lesson-42,Bài 42: Công nghệ hiện đại</t>
+  </si>
+  <si>
+    <t>音声認識,おんせいにんしき,nhận dạng giọng nói,N,N1,音声認識の精度が向上しました,Độ chính xác nhận dạng giọng nói đã tăng,tu-vung-cntt,lesson-42,Bài 42: Công nghệ hiện đại</t>
+  </si>
+  <si>
+    <t>自動運転,じどううんてん,lái xe tự động,N,N1,自動運転技術を開発しています,Tôi đang phát triển công nghệ lái xe tự động,tu-vung-cntt,lesson-42,Bài 42: Công nghệ hiện đại</t>
+  </si>
+  <si>
+    <t>エッジコンピューティング,えっじこんぴゅーてぃんぐ,điện toán biên,N,N1,エッジコンピューティングを導入しました,Tôi đã triển khai điện toán biên,tu-vung-cntt,lesson-42,Bài 42: Công nghệ hiện đại</t>
+  </si>
+  <si>
+    <t>量子コンピューター,りょうしこんぴゅーたー,máy tính lượng tử,N,N1,量子コンピューターを勉強しています,Tôi đang học về máy tính lượng tử,tu-vung-cntt,lesson-42,Bài 42: Công nghệ hiện đại</t>
+  </si>
+  <si>
+    <t>MLOps,えむえるおぷす,MLOps,N,N1,MLOps環境を構築しました,Tôi đã xây dựng môi trường MLOps,tu-vung-cntt,lesson-42,Bài 42: Công nghệ hiện đại</t>
+  </si>
+  <si>
+    <t>LLM,えるえるえむ,mô hình ngôn ngữ lớn,N,N1,LLMを業務に活用しています,Tôi đang ứng dụng LLM trong công việc,tu-vung-cntt,lesson-42,Bài 42: Công nghệ hiện đại</t>
+  </si>
+  <si>
+    <t>ライセンス,らいせんす,giấy phép phần mềm,N,N2,ライセンスを更新しました,Tôi đã gia hạn giấy phép phần mềm,tu-vung-cntt,lesson-43,Bài 43: Quản trị CNTT</t>
+  </si>
+  <si>
+    <t>サブスクリプション,さぶすくりぷしょん,gói thuê bao,N,N2,サブスクリプションを管理しています,Tôi đang quản lý các gói thuê bao,tu-vung-cntt,lesson-43,Bài 43: Quản trị CNTT</t>
+  </si>
+  <si>
+    <t>資産管理,しさんかんり,quản lý tài sản CNTT,N,N1,資産管理システムを更新しました,Tôi đã cập nhật hệ thống quản lý tài sản,tu-vung-cntt,lesson-43,Bài 43: Quản trị CNTT</t>
+  </si>
+  <si>
+    <t>棚卸し,たなおろし,kiểm kê,N,N2,機器の棚卸しを行いました,Tôi đã kiểm kê thiết bị,tu-vung-cntt,lesson-43,Bài 43: Quản trị CNTT</t>
+  </si>
+  <si>
+    <t>端末,たんまつ,thiết bị đầu cuối,N,N2,新しい端末を設定しました,Tôi đã cấu hình thiết bị đầu cuối mới,tu-vung-cntt,lesson-43,Bài 43: Quản trị CNTT</t>
+  </si>
+  <si>
+    <t>資産番号,しさんばんごう,mã tài sản,N,N1,資産番号を登録してください,Hãy đăng ký mã tài sản,tu-vung-cntt,lesson-43,Bài 43: Quản trị CNTT</t>
+  </si>
+  <si>
+    <t>管理番号,かんりばんごう,mã quản lý,N,N2,管理番号を確認しました,Tôi đã kiểm tra mã quản lý,tu-vung-cntt,lesson-43,Bài 43: Quản trị CNTT</t>
+  </si>
+  <si>
+    <t>保証期間,ほしょうきかん,thời gian bảo hành,N,N2,保証期間は来月までです,Thời gian bảo hành đến tháng sau,tu-vung-cntt,lesson-43,Bài 43: Quản trị CNTT</t>
+  </si>
+  <si>
+    <t>更新期限,こうしんきげん,hạn gia hạn,N,N2,更新期限を確認してください,Hãy kiểm tra hạn gia hạn,tu-vung-cntt,lesson-43,Bài 43: Quản trị CNTT</t>
+  </si>
+  <si>
+    <t>保守契約,ほしゅけいやく,hợp đồng bảo trì,N,N1,保守契約を更新しました,Tôi đã gia hạn hợp đồng bảo trì,tu-vung-cntt,lesson-43,Bài 43: Quản trị CNTT</t>
+  </si>
+  <si>
+    <t>障害対応,しょうがいたいおう,xử lý sự cố,N,N2,障害対応を開始しました,Tôi đã bắt đầu xử lý sự cố,tu-vung-cntt,lesson-43,Bài 43: Quản trị CNTT</t>
+  </si>
+  <si>
+    <t>保守担当,ほしゅたんとう,nhân viên bảo trì,N,N2,保守担当へ連絡しました,Tôi đã liên hệ nhân viên bảo trì,tu-vung-cntt,lesson-43,Bài 43: Quản trị CNTT</t>
+  </si>
+  <si>
+    <t>更新履歴,こうしんりれき,lịch sử cập nhật,N,N2,更新履歴を保存しました,Tôi đã lưu lịch sử cập nhật,tu-vung-cntt,lesson-43,Bài 43: Quản trị CNTT</t>
+  </si>
+  <si>
+    <t>運用手順書,うんようてじゅんしょ,tài liệu vận hành,N,N1,運用手順書を作成しました,Tôi đã tạo tài liệu vận hành,tu-vung-cntt,lesson-43,Bài 43: Quản trị CNTT</t>
+  </si>
+  <si>
+    <t>監査,かんさ,kiểm toán,N,N1,監査に向けて準備しています,Tôi đang chuẩn bị cho đợt kiểm toán,tu-vung-cntt,lesson-43,Bài 43: Quản trị CNTT</t>
+  </si>
+  <si>
+    <t>ベンチマーク,べんちまーく,benchmark,N,N1,ベンチマークを実施しました,Tôi đã thực hiện benchmark,tu-vung-cntt,lesson-44,Bài 44: Thuật ngữ IT nâng cao</t>
+  </si>
+  <si>
+    <t>スループット,するーぷっと,thông lượng,N,N1,システムのスループットを測定しました,Tôi đã đo thông lượng của hệ thống,tu-vung-cntt,lesson-44,Bài 44: Thuật ngữ IT nâng cao</t>
+  </si>
+  <si>
+    <t>レイテンシ,れいてんし,độ trễ,N,N1,レイテンシを改善しました,Tôi đã cải thiện độ trễ,tu-vung-cntt,lesson-44,Bài 44: Thuật ngữ IT nâng cao</t>
+  </si>
+  <si>
+    <t>ボトルネック,ぼとるねっく,điểm nghẽn,N,N1,ボトルネックを特定しました,Tôi đã xác định điểm nghẽn,tu-vung-cntt,lesson-44,Bài 44: Thuật ngữ IT nâng cao</t>
+  </si>
+  <si>
+    <t>キャッシュ,きゃっしゅ,bộ nhớ đệm,N,N2,キャッシュを削除しました,Tôi đã xóa bộ nhớ đệm,tu-vung-cntt,lesson-44,Bài 44: Thuật ngữ IT nâng cao</t>
+  </si>
+  <si>
+    <t>メモリリーク,めもりりーく,rò rỉ bộ nhớ,N,N1,メモリリークを修正しました,Tôi đã sửa lỗi rò rỉ bộ nhớ,tu-vung-cntt,lesson-44,Bài 44: Thuật ngữ IT nâng cao</t>
+  </si>
+  <si>
+    <t>ガベージコレクション,がべーじこれくしょん,thu gom rác,N,N1,ガベージコレクションを調整しました,Tôi đã điều chỉnh garbage collection,tu-vung-cntt,lesson-44,Bài 44: Thuật ngữ IT nâng cao</t>
+  </si>
+  <si>
+    <t>並列処理,へいれつしょり,xử lý song song,N,N1,並列処理で性能を向上しました,Tôi đã cải thiện hiệu năng bằng xử lý song song,tu-vung-cntt,lesson-44,Bài 44: Thuật ngữ IT nâng cao</t>
+  </si>
+  <si>
+    <t>非同期処理,ひどうきしょり,xử lý bất đồng bộ,N,N1,非同期処理を導入しました,Tôi đã triển khai xử lý bất đồng bộ,tu-vung-cntt,lesson-44,Bài 44: Thuật ngữ IT nâng cao</t>
+  </si>
+  <si>
+    <t>マルチスレッド,まるちすれっど,đa luồng,N,N1,マルチスレッドで実装しました,Tôi đã triển khai bằng đa luồng,tu-vung-cntt,lesson-44,Bài 44: Thuật ngữ IT nâng cao</t>
+  </si>
+  <si>
+    <t>アルゴリズム,あるごりずむ,thuật toán,N,N2,新しいアルゴリズムを実装しました,Tôi đã triển khai thuật toán mới,tu-vung-cntt,lesson-44,Bài 44: Thuật ngữ IT nâng cao</t>
+  </si>
+  <si>
+    <t>計算量,けいさんりょう,độ phức tạp tính toán,N,N1,計算量を改善しました,Tôi đã cải thiện độ phức tạp tính toán,tu-vung-cntt,lesson-44,Bài 44: Thuật ngữ IT nâng cao</t>
+  </si>
+  <si>
+    <t>最適解,さいてきかい,lời giải tối ưu,N,N1,最適解を見つけました,Tôi đã tìm được lời giải tối ưu,tu-vung-cntt,lesson-44,Bài 44: Thuật ngữ IT nâng cao</t>
+  </si>
+  <si>
+    <t>可読性,かどくせい,tính dễ đọc của mã,N,N1,コードの可読性を改善しました,Tôi đã cải thiện tính dễ đọc của mã,tu-vung-cntt,lesson-44,Bài 44: Thuật ngữ IT nâng cao</t>
+  </si>
+  <si>
+    <t>保守性,ほしゅせい,tính dễ bảo trì,N,N1,保守性を高めました,Tôi đã nâng cao tính dễ bảo trì của hệ thống,tu-vung-cntt,lesson-44,Bài 44: Thuật ngữ IT nâng cao</t>
+  </si>
+  <si>
+    <t>参加する,さんかする,tham gia,V,N4,パソコンを会社のドメインへ参加します,Tôi sẽ cho máy tính tham gia domain của công ty,tu-vung-cntt,lesson-10,Bài 10: Domain và Active Directory</t>
+  </si>
+  <si>
+    <t>離脱する,りだつする,rời khỏi,V,N3,古いパソコンをドメインから離脱しました,Tôi đã đưa máy tính cũ ra khỏi domain,tu-vung-cntt,lesson-10,Bài 10: Domain và Active Directory</t>
+  </si>
+  <si>
+    <t>開く,ひらく,mở,V,N5,このファイルを開いて内容を読んでください,Hãy mở tệp này và đọc nội dung,tu-vung-cntt,lesson-04,Bài 4: Lập trình và xử lý sự cố</t>
+  </si>
+  <si>
+    <t>閉じる,とじる,đóng,V,N5,使い終わったら画面を閉じてください,Sau khi dùng xong hãy đóng màn hình,tu-vung-cntt,lesson-04,Bài 4: Lập trình và xử lý sự cố</t>
+  </si>
+  <si>
+    <t>共有する,きょうゆうする,chia sẻ,V,N4,資料を全員と共有してください,Hãy chia sẻ tài liệu với mọi người,tu-vung-cntt,lesson-07,Bài 7: Họp trực tuyến và làm việc nhóm</t>
+  </si>
+  <si>
+    <t>削除する,さくじょする,xóa,V,N4,不要なアカウントを削除しました,Tôi đã xóa tài khoản không cần thiết,tu-vung-cntt,lesson-10,Bài 10: Domain và Active Directory</t>
+  </si>
+  <si>
+    <t>更新する,こうしんする,làm mới,V,N4,IPアドレスを更新してください,Hãy làm mới địa chỉ IP,tu-vung-cntt,lesson-12,Bài 12: Công cụ kiểm tra mạng</t>
+  </si>
+  <si>
+    <t>解放する,かいほうする,giải phóng,V,N3,現在のIPアドレスを解放しました,Tôi đã giải phóng địa chỉ IP hiện tại,tu-vung-cntt,lesson-12,Bài 12: Công cụ kiểm tra mạng</t>
+  </si>
+  <si>
+    <t>割り当てる,わりあてる,ánh xạ; gán,V,N3,Zドライブを割り当てました,Tôi đã ánh xạ ổ Z,tu-vung-cntt,lesson-13,Bài 13: File Server và chia sẻ dữ liệu</t>
+  </si>
+  <si>
+    <t>アップロードする,あっぷろーどする,tải lên,V,N4,ファイルをサーバーへアップロードしました,Tôi đã tải tệp lên máy chủ,tu-vung-cntt,lesson-14,Bài 14: FTP và truyền tệp</t>
+  </si>
+  <si>
+    <t>ダウンロードする,だうんろーどする,tải xuống,V,N4,最新の資料をダウンロードしました,Tôi đã tải xuống tài liệu mới nhất,tu-vung-cntt,lesson-14,Bài 14: FTP và truyền tệp</t>
+  </si>
+  <si>
+    <t>開始する,かいしする,khởi động,V,N4,サービスを開始してください,Hãy khởi động dịch vụ,tu-vung-cntt,lesson-15,Bài 15: Windows Server cơ bản</t>
+  </si>
+  <si>
+    <t>停止する,ていしする,dừng,V,N4,不要なサービスを停止しました,Tôi đã dừng dịch vụ không cần thiết,tu-vung-cntt,lesson-15,Bài 15: Windows Server cơ bản</t>
+  </si>
+  <si>
+    <t>再接続する,さいせつぞくする,kết nối lại,V,N3,数分後に再接続してください,Hãy kết nối lại sau vài phút,tu-vung-cntt,lesson-16,Bài 16: Quản trị từ xa</t>
+  </si>
+  <si>
+    <t>実行する,じっこうする,thực thi,V,N4,このコマンドを実行してください,Hãy thực thi lệnh này,tu-vung-cntt,lesson-16,Bài 16: Quản trị từ xa</t>
+  </si>
+  <si>
+    <t>転送する,てんそうする,chuyển tiếp,V,N4,このメールを転送してください,Hãy chuyển tiếp email này,tu-vung-cntt,lesson-17,Bài 17: Microsoft 365 và Outlook</t>
+  </si>
+  <si>
+    <t>スキャンする,すきゃんする,quét tài liệu,V,N4,契約書をPDFへスキャンしました,Tôi đã quét hợp đồng thành PDF,tu-vung-cntt,lesson-20,Bài 20: Máy in và Scan</t>
+  </si>
+  <si>
+    <t>認識する,にんしきする,nhận diện,V,N3,パソコンが機器を認識しません,Máy tính không nhận diện thiết bị,tu-vung-cntt,lesson-21,Bài 21: Scan và Driver</t>
+  </si>
+  <si>
+    <t>検出する,けんしゅつする,phát hiện,V,N2,新しい機器を検出しました,Tôi đã phát hiện thiết bị mới,tu-vung-cntt,lesson-21,Bài 21: Scan và Driver</t>
+  </si>
+  <si>
+    <t>更新する,こうしんする,cập nhật,V,N4,ドライバーを更新してください,Hãy cập nhật trình điều khiển,tu-vung-cntt,lesson-21,Bài 21: Scan và Driver</t>
+  </si>
+  <si>
+    <t>再インストールする,さいいんすとーるする,cài đặt lại,V,N3,ソフトを再インストールしました,Tôi đã cài đặt lại phần mềm,tu-vung-cntt,lesson-21,Bài 21: Scan và Driver</t>
+  </si>
+  <si>
+    <t>隔離する,かくりする,cách ly,V,N2,感染したファイルを隔離しました,Tôi đã cách ly tệp bị nhiễm,tu-vung-cntt,lesson-22,Bài 22: Bảo mật và Antivirus</t>
+  </si>
+  <si>
+    <t>駆除する,くじょする,loại bỏ; diệt,V,N1,ウイルスを完全に駆除しました,Tôi đã loại bỏ hoàn toàn virus,tu-vung-cntt,lesson-22,Bài 22: Bảo mật và Antivirus</t>
+  </si>
+  <si>
+    <t>暗号化する,あんごうかする,mã hóa,V,N2,重要なデータを暗号化しました,Tôi đã mã hóa dữ liệu quan trọng,tu-vung-cntt,lesson-22,Bài 22: Bảo mật và Antivirus</t>
+  </si>
+  <si>
+    <t>復号する,ふくごうする,giải mã,V,N1,暗号を復号できません,Không thể giải mã dữ liệu đã mã hóa,tu-vung-cntt,lesson-22,Bài 22: Bảo mật và Antivirus</t>
+  </si>
+  <si>
+    <t>訓練する,くんれんする,huấn luyện,V,N2,モデルを訓練しています,Tôi đang huấn luyện mô hình,tu-vung-cntt,lesson-30,Bài 30: AI và Machine Learning</t>
+  </si>
+  <si>
+    <t>推論する,すいろんする,suy luận,V,N1,画像から結果を推論しました,Tôi đã suy luận kết quả từ hình ảnh,tu-vung-cntt,lesson-30,Bài 30: AI và Machine Learning</t>
+  </si>
+  <si>
+    <t>締結する,ていけつする,ký kết,V,N1,新しい契約を締結しました,Tôi đã ký kết hợp đồng mới,tu-vung-cntt,lesson-40,Bài 40: Doanh nghiệp Nhật Bản</t>
+  </si>
+  <si>
+    <t>至急,しきゅう,khẩn cấp,Phó từ,N2,至急ご対応をお願いいたします,Xin xử lý khẩn cấp,tu-vung-cntt,lesson-41,Bài 41: Hội thoại IT trong công ty Nhật</t>
+  </si>
+  <si>
+    <t>至急,しきゅう,khẩn cấp,Phó từ,N2,至急ご対応をお願いいたします,Xin vui lòng xử lý khẩn cấp,tu-vung-cntt,lesson-39,Bài 39: Giao tiếp với khách hàng Nhật</t>
+  </si>
+  <si>
+    <t>念のため,ねんのため,để chắc chắn,Phó từ,N2,念のためバックアップを作成しました,Để chắc chắn tôi đã tạo bản sao lưu,tu-vung-cntt,lesson-41,Bài 41: Hội thoại IT trong công ty Nhật</t>
+  </si>
+  <si>
+    <t>電源を入れる,でんげんをいれる,bật nguồn,Mẫu câu,N4,作業を始める前に電源を入れてください,Hãy bật nguồn trước khi bắt đầu làm việc,tu-vung-cntt,lesson-05,Bài 5: Thiết bị và văn phòng IT</t>
+  </si>
+  <si>
+    <t>電源を切る,でんげんをきる,tắt nguồn,Mẫu câu,N4,帰る前に電源を切ってください,Hãy tắt nguồn trước khi ra về,tu-vung-cntt,lesson-05,Bài 5: Thiết bị và văn phòng IT</t>
+  </si>
+  <si>
+    <t>お世話になっております,おせわになっております,Xin cảm ơn quý vị luôn hỗ trợ,Mẫu câu,N3,お世話になっておりますよろしくお願いいたします,Xin cảm ơn quý vị đã luôn hỗ trợ,tu-vung-cntt,lesson-39,Bài 39: Giao tiếp với khách hàng Nhật</t>
+  </si>
+  <si>
+    <t>承知しました,しょうちしました,Đã hiểu,Mẫu câu,N3,内容を承知しました,Tôi đã hiểu nội dung,tu-vung-cntt,lesson-39,Bài 39: Giao tiếp với khách hàng Nhật</t>
+  </si>
+  <si>
+    <t>かしこまりました,かしこまりました,Vâng tôi đã rõ,Mẫu câu,N2,かしこまりました対応いたします,Vâng tôi sẽ xử lý,tu-vung-cntt,lesson-39,Bài 39: Giao tiếp với khách hàng Nhật</t>
+  </si>
+  <si>
+    <t>恐れ入ります,おそれいります,Xin phép; làm phiền,Mẫu câu,N2,恐れ入りますがご確認ください,Xin phiền quý vị xác nhận,tu-vung-cntt,lesson-39,Bài 39: Giao tiếp với khách hàng Nhật</t>
+  </si>
+  <si>
+    <t>申し訳ございません,もうしわけございません,Thành thật xin lỗi,Mẫu câu,N2,申し訳ございませんすぐ対応します,Thành thật xin lỗi chúng tôi sẽ xử lý ngay,tu-vung-cntt,lesson-39,Bài 39: Giao tiếp với khách hàng Nhật</t>
+  </si>
+  <si>
+    <t>ご確認ください,ごかくにんください,Xin vui lòng xác nhận,Mẫu câu,N3,添付資料をご確認ください,Xin vui lòng xác nhận tài liệu đính kèm,tu-vung-cntt,lesson-39,Bài 39: Giao tiếp với khách hàng Nhật</t>
+  </si>
+  <si>
+    <t>ご対応ありがとうございます,ごたいおうありがとうございます,Cảm ơn đã hỗ trợ,Mẫu câu,N2,ご対応ありがとうございます,Cảm ơn vì đã hỗ trợ,tu-vung-cntt,lesson-39,Bài 39: Giao tiếp với khách hàng Nhật</t>
+  </si>
+  <si>
+    <t>少々お待ちください,しょうしょうおまちください,Xin vui lòng chờ một chút,Mẫu câu,N3,少々お待ちください確認します,Xin vui lòng chờ tôi kiểm tra,tu-vung-cntt,lesson-39,Bài 39: Giao tiếp với khách hàng Nhật</t>
+  </si>
+  <si>
+    <t>よろしくお願いいたします,よろしくおねがいいたします,Mong nhận được sự giúp đỡ,Mẫu câu,N4,今後ともよろしくお願いいたします,Mong tiếp tục nhận được sự hỗ trợ,tu-vung-cntt,lesson-39,Bài 39: Giao tiếp với khách hàng Nhật</t>
+  </si>
+  <si>
+    <t>ご連絡いたします,ごれんらくいたします,Tôi sẽ liên hệ,Mẫu câu,N2,後ほどご連絡いたします,Tôi sẽ liên hệ sau,tu-vung-cntt,lesson-39,Bài 39: Giao tiếp với khách hàng Nhật</t>
+  </si>
+  <si>
+    <t>お疲れ様です,おつかれさまです,xin chào đồng nghiệp,Mẫu câu,N5,お疲れ様です;会議を始めましょう,Xin chào mọi người; chúng ta bắt đầu cuộc họp nhé,tu-vung-cntt,lesson-41,Bài 41: Hội thoại IT trong công ty Nhật</t>
+  </si>
+  <si>
+    <t>よろしくお願いいたします,よろしくおねがいいたします,mong được giúp đỡ,Mẫu câu,N4,本日もよろしくお願いいたします,Hôm nay cũng mong mọi người giúp đỡ,tu-vung-cntt,lesson-41,Bài 41: Hội thoại IT trong công ty Nhật</t>
+  </si>
+  <si>
+    <t>承知しました,しょうちしました,đã hiểu,Mẫu câu,N3,内容を承知しました;対応します,Tôi đã hiểu nội dung và sẽ xử lý,tu-vung-cntt,lesson-41,Bài 41: Hội thoại IT trong công ty Nhật</t>
+  </si>
+  <si>
+    <t>かしこまりました,かしこまりました,vâng; tôi đã rõ,Mẫu câu,N2,かしこまりました;すぐ対応いたします,Vâng; tôi sẽ xử lý ngay,tu-vung-cntt,lesson-41,Bài 41: Hội thoại IT trong công ty Nhật</t>
+  </si>
+  <si>
+    <t>少々お待ちください,しょうしょうおまちください,xin chờ một chút,Mẫu câu,N4,少々お待ちください;確認いたします,Xin chờ một chút; tôi sẽ kiểm tra,tu-vung-cntt,lesson-41,Bài 41: Hội thoại IT trong công ty Nhật</t>
+  </si>
+  <si>
+    <t>確認いたします,かくにんいたします,tôi sẽ kiểm tra,Mẫu câu,N3,内容を確認いたします,Tôi sẽ kiểm tra nội dung,tu-vung-cntt,lesson-41,Bài 41: Hội thoại IT trong công ty Nhật</t>
+  </si>
+  <si>
+    <t>対応いたします,たいおういたします,tôi sẽ xử lý,Mẫu câu,N3,本日中に対応いたします,Tôi sẽ xử lý trong hôm nay,tu-vung-cntt,lesson-41,Bài 41: Hội thoại IT trong công ty Nhật</t>
+  </si>
+  <si>
+    <t>申し訳ございません,もうしわけございません,xin lỗi,Mẫu câu,N3,ご迷惑をおかけして申し訳ございません,Xin lỗi vì đã gây bất tiện,tu-vung-cntt,lesson-41,Bài 41: Hội thoại IT trong công ty Nhật</t>
+  </si>
+  <si>
+    <t>恐れ入ります,おそれいります,xin làm phiền,Mẫu câu,N2,恐れ入りますが再度ご確認ください,Xin phiền bạn kiểm tra lại,tu-vung-cntt,lesson-41,Bài 41: Hội thoại IT trong công ty Nhật</t>
+  </si>
+  <si>
+    <t>ご確認ください,ごかくにんください,xin vui lòng xác nhận,Mẫu câu,N4,添付資料をご確認ください,Xin vui lòng kiểm tra tài liệu đính kèm,tu-vung-cntt,lesson-41,Bài 41: Hội thoại IT trong công ty Nhật</t>
+  </si>
+  <si>
+    <t>ご連絡ください,ごれんらくください,xin vui lòng liên hệ,Mẫu câu,N4,問題があればご連絡ください,Nếu có vấn đề xin hãy liên hệ,tu-vung-cntt,lesson-41,Bài 41: Hội thoại IT trong công ty Nhật</t>
+  </si>
+  <si>
+    <t>お手数ですが,おてすうですが,xin phiền bạn,Mẫu câu,N3,お手数ですがご返信ください,Xin phiền bạn phản hồi,tu-vung-cntt,lesson-41,Bài 41: Hội thoại IT trong công ty Nhật</t>
+  </si>
+  <si>
+    <t>ご協力ありがとうございます,ごきょうりょくありがとうございます,cảm ơn sự hợp tác,Mẫu câu,N3,ご協力ありがとうございます;作業が完了しました,Cảm ơn sự hợp tác; công việc đã hoàn thành,tu-vung-cntt,lesson-41,Bài 41: Hội thoại IT trong công ty Nhật</t>
+  </si>
+  <si>
+    <t>インデックス,インデックス,chỉ mục,N,N2,インデックスを作成しました,Tôi đã tạo chỉ mục,tu-vung-cntt,lesson-25,Bài 25: SQL và Database</t>
   </si>
 </sst>
 </file>
@@ -2315,6 +2315,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:A659"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="103.5703125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
@@ -2603,3012 +2606,3012 @@
     </row>
     <row r="58" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>57</v>
+        <v>604</v>
       </c>
     </row>
     <row r="59" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>58</v>
+        <v>605</v>
       </c>
     </row>
     <row r="60" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="61" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="62" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="63" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="64" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="65" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="66" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="67" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="68" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="69" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>68</v>
+        <v>633</v>
       </c>
     </row>
     <row r="70" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>69</v>
+        <v>634</v>
       </c>
     </row>
     <row r="71" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
     </row>
     <row r="72" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
     </row>
     <row r="73" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
     </row>
     <row r="74" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
     </row>
     <row r="75" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
     </row>
     <row r="76" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
     </row>
     <row r="77" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
     </row>
     <row r="78" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
     </row>
     <row r="79" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
     </row>
     <row r="80" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
     </row>
     <row r="81" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
     </row>
     <row r="82" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
     </row>
     <row r="83" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
     <row r="84" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
     </row>
     <row r="85" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
     </row>
     <row r="86" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
     </row>
     <row r="87" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
     </row>
     <row r="88" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
     </row>
     <row r="89" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
     </row>
     <row r="90" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
     </row>
     <row r="91" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
     </row>
     <row r="92" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
     </row>
     <row r="93" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
     </row>
     <row r="94" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
     </row>
     <row r="95" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
     </row>
     <row r="96" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
     </row>
     <row r="97" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
     </row>
     <row r="98" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>97</v>
+        <v>606</v>
       </c>
     </row>
     <row r="99" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
     </row>
     <row r="100" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
     </row>
     <row r="101" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
     </row>
     <row r="102" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
     </row>
     <row r="103" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
     </row>
     <row r="104" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
     </row>
     <row r="105" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
     </row>
     <row r="106" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
     </row>
     <row r="107" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
     </row>
     <row r="108" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
     </row>
     <row r="109" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
     </row>
     <row r="110" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
     </row>
     <row r="111" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
     </row>
     <row r="112" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
     </row>
     <row r="113" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="114" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
     </row>
     <row r="115" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
     </row>
     <row r="116" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
     </row>
     <row r="117" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
     </row>
     <row r="118" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
     </row>
     <row r="119" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
     </row>
     <row r="120" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
     </row>
     <row r="121" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
     </row>
     <row r="122" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
     </row>
     <row r="123" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
     </row>
     <row r="124" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
     </row>
     <row r="125" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="126" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
     </row>
     <row r="127" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
     </row>
     <row r="128" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
     </row>
     <row r="129" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
     </row>
     <row r="130" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="131" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
     </row>
     <row r="132" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
     </row>
     <row r="133" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
     </row>
     <row r="134" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
     </row>
     <row r="135" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
     </row>
     <row r="136" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
     </row>
     <row r="137" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
     </row>
     <row r="138" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>137</v>
+        <v>602</v>
       </c>
     </row>
     <row r="139" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>138</v>
+        <v>603</v>
       </c>
     </row>
     <row r="140" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
     </row>
     <row r="141" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
     </row>
     <row r="142" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
     </row>
     <row r="143" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
     </row>
     <row r="144" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
     </row>
     <row r="145" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
     </row>
     <row r="146" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>145</v>
+        <v>607</v>
       </c>
     </row>
     <row r="147" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>146</v>
+        <v>138</v>
       </c>
     </row>
     <row r="148" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>147</v>
+        <v>139</v>
       </c>
     </row>
     <row r="149" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>148</v>
+        <v>140</v>
       </c>
     </row>
     <row r="150" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>149</v>
+        <v>141</v>
       </c>
     </row>
     <row r="151" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>150</v>
+        <v>142</v>
       </c>
     </row>
     <row r="152" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
     </row>
     <row r="153" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
     </row>
     <row r="154" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
     </row>
     <row r="155" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
     </row>
     <row r="156" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
     </row>
     <row r="157" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
     </row>
     <row r="158" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
     </row>
     <row r="159" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
     </row>
     <row r="160" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>159</v>
+        <v>151</v>
       </c>
     </row>
     <row r="161" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
     </row>
     <row r="162" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>161</v>
+        <v>153</v>
       </c>
     </row>
     <row r="163" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>162</v>
+        <v>154</v>
       </c>
     </row>
     <row r="164" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>163</v>
+        <v>155</v>
       </c>
     </row>
     <row r="165" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
     </row>
     <row r="166" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
-        <v>165</v>
+        <v>157</v>
       </c>
     </row>
     <row r="167" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
     </row>
     <row r="168" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
     </row>
     <row r="169" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
     </row>
     <row r="170" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
-        <v>169</v>
+        <v>161</v>
       </c>
     </row>
     <row r="171" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
     </row>
     <row r="172" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>171</v>
+        <v>163</v>
       </c>
     </row>
     <row r="173" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
     </row>
     <row r="174" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
-        <v>173</v>
+        <v>165</v>
       </c>
     </row>
     <row r="175" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
-        <v>174</v>
+        <v>166</v>
       </c>
     </row>
     <row r="176" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
-        <v>175</v>
+        <v>167</v>
       </c>
     </row>
     <row r="177" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
-        <v>176</v>
+        <v>608</v>
       </c>
     </row>
     <row r="178" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
-        <v>177</v>
+        <v>609</v>
       </c>
     </row>
     <row r="179" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
-        <v>178</v>
+        <v>168</v>
       </c>
     </row>
     <row r="180" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
-        <v>179</v>
+        <v>169</v>
       </c>
     </row>
     <row r="181" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
-        <v>180</v>
+        <v>170</v>
       </c>
     </row>
     <row r="182" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
-        <v>181</v>
+        <v>171</v>
       </c>
     </row>
     <row r="183" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
     </row>
     <row r="184" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
-        <v>183</v>
+        <v>173</v>
       </c>
     </row>
     <row r="185" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
-        <v>184</v>
+        <v>174</v>
       </c>
     </row>
     <row r="186" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
-        <v>185</v>
+        <v>175</v>
       </c>
     </row>
     <row r="187" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
-        <v>186</v>
+        <v>176</v>
       </c>
     </row>
     <row r="188" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
-        <v>187</v>
+        <v>177</v>
       </c>
     </row>
     <row r="189" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
-        <v>188</v>
+        <v>178</v>
       </c>
     </row>
     <row r="190" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
-        <v>189</v>
+        <v>610</v>
       </c>
     </row>
     <row r="191" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
-        <v>190</v>
+        <v>179</v>
       </c>
     </row>
     <row r="192" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
-        <v>191</v>
+        <v>180</v>
       </c>
     </row>
     <row r="193" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
-        <v>192</v>
+        <v>181</v>
       </c>
     </row>
     <row r="194" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
-        <v>193</v>
+        <v>182</v>
       </c>
     </row>
     <row r="195" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
-        <v>194</v>
+        <v>183</v>
       </c>
     </row>
     <row r="196" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
-        <v>195</v>
+        <v>184</v>
       </c>
     </row>
     <row r="197" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
-        <v>196</v>
+        <v>185</v>
       </c>
     </row>
     <row r="198" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
-        <v>197</v>
+        <v>186</v>
       </c>
     </row>
     <row r="199" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
-        <v>198</v>
+        <v>187</v>
       </c>
     </row>
     <row r="200" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
-        <v>199</v>
+        <v>188</v>
       </c>
     </row>
     <row r="201" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
-        <v>200</v>
+        <v>189</v>
       </c>
     </row>
     <row r="202" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
-        <v>201</v>
+        <v>611</v>
       </c>
     </row>
     <row r="203" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
-        <v>202</v>
+        <v>612</v>
       </c>
     </row>
     <row r="204" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
-        <v>203</v>
+        <v>190</v>
       </c>
     </row>
     <row r="205" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
-        <v>204</v>
+        <v>191</v>
       </c>
     </row>
     <row r="206" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
-        <v>205</v>
+        <v>192</v>
       </c>
     </row>
     <row r="207" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
-        <v>206</v>
+        <v>193</v>
       </c>
     </row>
     <row r="208" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
-        <v>207</v>
+        <v>194</v>
       </c>
     </row>
     <row r="209" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
-        <v>208</v>
+        <v>195</v>
       </c>
     </row>
     <row r="210" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
-        <v>209</v>
+        <v>196</v>
       </c>
     </row>
     <row r="211" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
-        <v>210</v>
+        <v>197</v>
       </c>
     </row>
     <row r="212" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
-        <v>211</v>
+        <v>198</v>
       </c>
     </row>
     <row r="213" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
-        <v>212</v>
+        <v>199</v>
       </c>
     </row>
     <row r="214" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
-        <v>213</v>
+        <v>200</v>
       </c>
     </row>
     <row r="215" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
-        <v>214</v>
+        <v>201</v>
       </c>
     </row>
     <row r="216" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
-        <v>215</v>
+        <v>202</v>
       </c>
     </row>
     <row r="217" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
-        <v>216</v>
+        <v>203</v>
       </c>
     </row>
     <row r="218" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
-        <v>217</v>
+        <v>204</v>
       </c>
     </row>
     <row r="219" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
-        <v>218</v>
+        <v>205</v>
       </c>
     </row>
     <row r="220" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
-        <v>219</v>
+        <v>206</v>
       </c>
     </row>
     <row r="221" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
-        <v>220</v>
+        <v>613</v>
       </c>
     </row>
     <row r="222" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
-        <v>221</v>
+        <v>614</v>
       </c>
     </row>
     <row r="223" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
-        <v>222</v>
+        <v>207</v>
       </c>
     </row>
     <row r="224" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
-        <v>223</v>
+        <v>208</v>
       </c>
     </row>
     <row r="225" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
-        <v>224</v>
+        <v>209</v>
       </c>
     </row>
     <row r="226" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
-        <v>225</v>
+        <v>210</v>
       </c>
     </row>
     <row r="227" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
-        <v>226</v>
+        <v>211</v>
       </c>
     </row>
     <row r="228" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
-        <v>227</v>
+        <v>212</v>
       </c>
     </row>
     <row r="229" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
-        <v>228</v>
+        <v>213</v>
       </c>
     </row>
     <row r="230" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
-        <v>229</v>
+        <v>214</v>
       </c>
     </row>
     <row r="231" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
-        <v>230</v>
+        <v>215</v>
       </c>
     </row>
     <row r="232" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
-        <v>231</v>
+        <v>216</v>
       </c>
     </row>
     <row r="233" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
-        <v>232</v>
+        <v>217</v>
       </c>
     </row>
     <row r="234" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
-        <v>233</v>
+        <v>615</v>
       </c>
     </row>
     <row r="235" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
-        <v>234</v>
+        <v>218</v>
       </c>
     </row>
     <row r="236" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
-        <v>235</v>
+        <v>219</v>
       </c>
     </row>
     <row r="237" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
-        <v>236</v>
+        <v>220</v>
       </c>
     </row>
     <row r="238" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
-        <v>237</v>
+        <v>221</v>
       </c>
     </row>
     <row r="239" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
-        <v>238</v>
+        <v>616</v>
       </c>
     </row>
     <row r="240" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
-        <v>239</v>
+        <v>222</v>
       </c>
     </row>
     <row r="241" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
-        <v>240</v>
+        <v>223</v>
       </c>
     </row>
     <row r="242" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
-        <v>241</v>
+        <v>224</v>
       </c>
     </row>
     <row r="243" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
-        <v>242</v>
+        <v>225</v>
       </c>
     </row>
     <row r="244" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
-        <v>243</v>
+        <v>226</v>
       </c>
     </row>
     <row r="245" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
-        <v>244</v>
+        <v>227</v>
       </c>
     </row>
     <row r="246" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
-        <v>245</v>
+        <v>228</v>
       </c>
     </row>
     <row r="247" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
-        <v>246</v>
+        <v>229</v>
       </c>
     </row>
     <row r="248" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
-        <v>247</v>
+        <v>230</v>
       </c>
     </row>
     <row r="249" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
-        <v>248</v>
+        <v>231</v>
       </c>
     </row>
     <row r="250" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
-        <v>249</v>
+        <v>232</v>
       </c>
     </row>
     <row r="251" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
-        <v>250</v>
+        <v>233</v>
       </c>
     </row>
     <row r="252" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
-        <v>251</v>
+        <v>234</v>
       </c>
     </row>
     <row r="253" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
-        <v>252</v>
+        <v>235</v>
       </c>
     </row>
     <row r="254" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
-        <v>253</v>
+        <v>236</v>
       </c>
     </row>
     <row r="255" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
-        <v>254</v>
+        <v>237</v>
       </c>
     </row>
     <row r="256" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
-        <v>255</v>
+        <v>238</v>
       </c>
     </row>
     <row r="257" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
-        <v>256</v>
+        <v>617</v>
       </c>
     </row>
     <row r="258" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
-        <v>257</v>
+        <v>239</v>
       </c>
     </row>
     <row r="259" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
-        <v>258</v>
+        <v>240</v>
       </c>
     </row>
     <row r="260" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
-        <v>259</v>
+        <v>241</v>
       </c>
     </row>
     <row r="261" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
-        <v>260</v>
+        <v>242</v>
       </c>
     </row>
     <row r="262" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
-        <v>261</v>
+        <v>243</v>
       </c>
     </row>
     <row r="263" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
-        <v>262</v>
+        <v>244</v>
       </c>
     </row>
     <row r="264" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
-        <v>263</v>
+        <v>245</v>
       </c>
     </row>
     <row r="265" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
-        <v>264</v>
+        <v>246</v>
       </c>
     </row>
     <row r="266" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
-        <v>265</v>
+        <v>247</v>
       </c>
     </row>
     <row r="267" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
-        <v>266</v>
+        <v>248</v>
       </c>
     </row>
     <row r="268" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
-        <v>267</v>
+        <v>249</v>
       </c>
     </row>
     <row r="269" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
-        <v>268</v>
+        <v>250</v>
       </c>
     </row>
     <row r="270" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
-        <v>269</v>
+        <v>251</v>
       </c>
     </row>
     <row r="271" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
-        <v>270</v>
+        <v>252</v>
       </c>
     </row>
     <row r="272" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
-        <v>271</v>
+        <v>253</v>
       </c>
     </row>
     <row r="273" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
-        <v>272</v>
+        <v>254</v>
       </c>
     </row>
     <row r="274" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
-        <v>273</v>
+        <v>255</v>
       </c>
     </row>
     <row r="275" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
-        <v>274</v>
+        <v>256</v>
       </c>
     </row>
     <row r="276" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
-        <v>275</v>
+        <v>257</v>
       </c>
     </row>
     <row r="277" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
-        <v>276</v>
+        <v>258</v>
       </c>
     </row>
     <row r="278" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
-        <v>277</v>
+        <v>259</v>
       </c>
     </row>
     <row r="279" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
-        <v>278</v>
+        <v>260</v>
       </c>
     </row>
     <row r="280" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
-        <v>279</v>
+        <v>261</v>
       </c>
     </row>
     <row r="281" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
-        <v>280</v>
+        <v>262</v>
       </c>
     </row>
     <row r="282" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
-        <v>281</v>
+        <v>263</v>
       </c>
     </row>
     <row r="283" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
-        <v>282</v>
+        <v>264</v>
       </c>
     </row>
     <row r="284" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
-        <v>283</v>
+        <v>265</v>
       </c>
     </row>
     <row r="285" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
-        <v>284</v>
+        <v>266</v>
       </c>
     </row>
     <row r="286" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
-        <v>285</v>
+        <v>267</v>
       </c>
     </row>
     <row r="287" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
-        <v>286</v>
+        <v>268</v>
       </c>
     </row>
     <row r="288" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
-        <v>287</v>
+        <v>269</v>
       </c>
     </row>
     <row r="289" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
-        <v>288</v>
+        <v>270</v>
       </c>
     </row>
     <row r="290" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
-        <v>289</v>
+        <v>271</v>
       </c>
     </row>
     <row r="291" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
-        <v>290</v>
+        <v>272</v>
       </c>
     </row>
     <row r="292" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
-        <v>291</v>
+        <v>273</v>
       </c>
     </row>
     <row r="293" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
-        <v>292</v>
+        <v>274</v>
       </c>
     </row>
     <row r="294" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
-        <v>293</v>
+        <v>275</v>
       </c>
     </row>
     <row r="295" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
-        <v>294</v>
+        <v>276</v>
       </c>
     </row>
     <row r="296" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
-        <v>295</v>
+        <v>277</v>
       </c>
     </row>
     <row r="297" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
-        <v>296</v>
+        <v>278</v>
       </c>
     </row>
     <row r="298" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
-        <v>297</v>
+        <v>279</v>
       </c>
     </row>
     <row r="299" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
-        <v>298</v>
+        <v>618</v>
       </c>
     </row>
     <row r="300" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
-        <v>299</v>
+        <v>280</v>
       </c>
     </row>
     <row r="301" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
-        <v>300</v>
+        <v>281</v>
       </c>
     </row>
     <row r="302" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
-        <v>301</v>
+        <v>282</v>
       </c>
     </row>
     <row r="303" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A303" t="s">
-        <v>302</v>
+        <v>283</v>
       </c>
     </row>
     <row r="304" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A304" t="s">
-        <v>303</v>
+        <v>284</v>
       </c>
     </row>
     <row r="305" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A305" t="s">
-        <v>304</v>
+        <v>285</v>
       </c>
     </row>
     <row r="306" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A306" t="s">
-        <v>305</v>
+        <v>286</v>
       </c>
     </row>
     <row r="307" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A307" t="s">
-        <v>306</v>
+        <v>287</v>
       </c>
     </row>
     <row r="308" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A308" t="s">
-        <v>307</v>
+        <v>288</v>
       </c>
     </row>
     <row r="309" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A309" t="s">
-        <v>308</v>
+        <v>619</v>
       </c>
     </row>
     <row r="310" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A310" t="s">
-        <v>309</v>
+        <v>620</v>
       </c>
     </row>
     <row r="311" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A311" t="s">
-        <v>310</v>
+        <v>621</v>
       </c>
     </row>
     <row r="312" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A312" t="s">
-        <v>311</v>
+        <v>622</v>
       </c>
     </row>
     <row r="313" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A313" t="s">
-        <v>312</v>
+        <v>289</v>
       </c>
     </row>
     <row r="314" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A314" t="s">
-        <v>313</v>
+        <v>290</v>
       </c>
     </row>
     <row r="315" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A315" t="s">
-        <v>314</v>
+        <v>291</v>
       </c>
     </row>
     <row r="316" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A316" t="s">
-        <v>315</v>
+        <v>292</v>
       </c>
     </row>
     <row r="317" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A317" t="s">
-        <v>316</v>
+        <v>293</v>
       </c>
     </row>
     <row r="318" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A318" t="s">
-        <v>317</v>
+        <v>294</v>
       </c>
     </row>
     <row r="319" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A319" t="s">
-        <v>318</v>
+        <v>295</v>
       </c>
     </row>
     <row r="320" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A320" t="s">
-        <v>319</v>
+        <v>296</v>
       </c>
     </row>
     <row r="321" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A321" t="s">
-        <v>320</v>
+        <v>297</v>
       </c>
     </row>
     <row r="322" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A322" t="s">
-        <v>321</v>
+        <v>298</v>
       </c>
     </row>
     <row r="323" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A323" t="s">
-        <v>322</v>
+        <v>299</v>
       </c>
     </row>
     <row r="324" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A324" t="s">
-        <v>323</v>
+        <v>623</v>
       </c>
     </row>
     <row r="325" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A325" t="s">
-        <v>324</v>
+        <v>300</v>
       </c>
     </row>
     <row r="326" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A326" t="s">
-        <v>325</v>
+        <v>624</v>
       </c>
     </row>
     <row r="327" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A327" t="s">
-        <v>326</v>
+        <v>301</v>
       </c>
     </row>
     <row r="328" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A328" t="s">
-        <v>327</v>
+        <v>302</v>
       </c>
     </row>
     <row r="329" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A329" t="s">
-        <v>328</v>
+        <v>303</v>
       </c>
     </row>
     <row r="330" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A330" t="s">
-        <v>329</v>
+        <v>304</v>
       </c>
     </row>
     <row r="331" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A331" t="s">
-        <v>330</v>
+        <v>625</v>
       </c>
     </row>
     <row r="332" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A332" t="s">
-        <v>331</v>
+        <v>626</v>
       </c>
     </row>
     <row r="333" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A333" t="s">
-        <v>332</v>
+        <v>305</v>
       </c>
     </row>
     <row r="334" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A334" t="s">
-        <v>333</v>
+        <v>306</v>
       </c>
     </row>
     <row r="335" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A335" t="s">
-        <v>334</v>
+        <v>307</v>
       </c>
     </row>
     <row r="336" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A336" t="s">
-        <v>335</v>
+        <v>308</v>
       </c>
     </row>
     <row r="337" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A337" t="s">
-        <v>336</v>
+        <v>309</v>
       </c>
     </row>
     <row r="338" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A338" t="s">
-        <v>337</v>
+        <v>310</v>
       </c>
     </row>
     <row r="339" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A339" t="s">
-        <v>338</v>
+        <v>311</v>
       </c>
     </row>
     <row r="340" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A340" t="s">
-        <v>339</v>
+        <v>312</v>
       </c>
     </row>
     <row r="341" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A341" t="s">
-        <v>340</v>
+        <v>313</v>
       </c>
     </row>
     <row r="342" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A342" t="s">
-        <v>341</v>
+        <v>314</v>
       </c>
     </row>
     <row r="343" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A343" t="s">
-        <v>342</v>
+        <v>315</v>
       </c>
     </row>
     <row r="344" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A344" t="s">
-        <v>343</v>
+        <v>316</v>
       </c>
     </row>
     <row r="345" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A345" t="s">
-        <v>344</v>
+        <v>317</v>
       </c>
     </row>
     <row r="346" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A346" t="s">
-        <v>345</v>
+        <v>318</v>
       </c>
     </row>
     <row r="347" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A347" t="s">
-        <v>346</v>
+        <v>319</v>
       </c>
     </row>
     <row r="348" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A348" t="s">
-        <v>347</v>
+        <v>320</v>
       </c>
     </row>
     <row r="349" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A349" t="s">
-        <v>348</v>
+        <v>321</v>
       </c>
     </row>
     <row r="350" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A350" t="s">
-        <v>349</v>
+        <v>322</v>
       </c>
     </row>
     <row r="351" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A351" t="s">
-        <v>350</v>
+        <v>323</v>
       </c>
     </row>
     <row r="352" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A352" t="s">
-        <v>351</v>
+        <v>324</v>
       </c>
     </row>
     <row r="353" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A353" t="s">
-        <v>352</v>
+        <v>325</v>
       </c>
     </row>
     <row r="354" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A354" t="s">
-        <v>353</v>
+        <v>326</v>
       </c>
     </row>
     <row r="355" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A355" t="s">
-        <v>354</v>
+        <v>327</v>
       </c>
     </row>
     <row r="356" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A356" t="s">
-        <v>355</v>
+        <v>328</v>
       </c>
     </row>
     <row r="357" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A357" t="s">
-        <v>356</v>
+        <v>329</v>
       </c>
     </row>
     <row r="358" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A358" t="s">
-        <v>357</v>
+        <v>330</v>
       </c>
     </row>
     <row r="359" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A359" t="s">
-        <v>358</v>
+        <v>331</v>
       </c>
     </row>
     <row r="360" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A360" t="s">
-        <v>359</v>
+        <v>332</v>
       </c>
     </row>
     <row r="361" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A361" t="s">
-        <v>360</v>
+        <v>333</v>
       </c>
     </row>
     <row r="362" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A362" t="s">
-        <v>361</v>
+        <v>334</v>
       </c>
     </row>
     <row r="363" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A363" t="s">
-        <v>362</v>
+        <v>335</v>
       </c>
     </row>
     <row r="364" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A364" t="s">
-        <v>363</v>
+        <v>336</v>
       </c>
     </row>
     <row r="365" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A365" t="s">
-        <v>364</v>
+        <v>337</v>
       </c>
     </row>
     <row r="366" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A366" t="s">
-        <v>365</v>
+        <v>338</v>
       </c>
     </row>
     <row r="367" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A367" t="s">
-        <v>366</v>
+        <v>339</v>
       </c>
     </row>
     <row r="368" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A368" t="s">
-        <v>367</v>
+        <v>340</v>
       </c>
     </row>
     <row r="369" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A369" t="s">
-        <v>368</v>
+        <v>341</v>
       </c>
     </row>
     <row r="370" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A370" t="s">
-        <v>369</v>
+        <v>658</v>
       </c>
     </row>
     <row r="371" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A371" t="s">
-        <v>370</v>
+        <v>342</v>
       </c>
     </row>
     <row r="372" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A372" t="s">
-        <v>371</v>
+        <v>343</v>
       </c>
     </row>
     <row r="373" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A373" t="s">
-        <v>372</v>
+        <v>344</v>
       </c>
     </row>
     <row r="374" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A374" t="s">
-        <v>373</v>
+        <v>345</v>
       </c>
     </row>
     <row r="375" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A375" t="s">
-        <v>374</v>
+        <v>346</v>
       </c>
     </row>
     <row r="376" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A376" t="s">
-        <v>375</v>
+        <v>347</v>
       </c>
     </row>
     <row r="377" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A377" t="s">
-        <v>376</v>
+        <v>348</v>
       </c>
     </row>
     <row r="378" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A378" t="s">
-        <v>377</v>
+        <v>349</v>
       </c>
     </row>
     <row r="379" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A379" t="s">
-        <v>378</v>
+        <v>350</v>
       </c>
     </row>
     <row r="380" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A380" t="s">
-        <v>379</v>
+        <v>351</v>
       </c>
     </row>
     <row r="381" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A381" t="s">
-        <v>380</v>
+        <v>352</v>
       </c>
     </row>
     <row r="382" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A382" t="s">
-        <v>381</v>
+        <v>353</v>
       </c>
     </row>
     <row r="383" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A383" t="s">
-        <v>382</v>
+        <v>354</v>
       </c>
     </row>
     <row r="384" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A384" t="s">
-        <v>383</v>
+        <v>355</v>
       </c>
     </row>
     <row r="385" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A385" t="s">
-        <v>384</v>
+        <v>356</v>
       </c>
     </row>
     <row r="386" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A386" t="s">
-        <v>385</v>
+        <v>357</v>
       </c>
     </row>
     <row r="387" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A387" t="s">
-        <v>386</v>
+        <v>358</v>
       </c>
     </row>
     <row r="388" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A388" t="s">
-        <v>387</v>
+        <v>359</v>
       </c>
     </row>
     <row r="389" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A389" t="s">
-        <v>388</v>
+        <v>360</v>
       </c>
     </row>
     <row r="390" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A390" t="s">
-        <v>389</v>
+        <v>361</v>
       </c>
     </row>
     <row r="391" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A391" t="s">
-        <v>390</v>
+        <v>362</v>
       </c>
     </row>
     <row r="392" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A392" t="s">
-        <v>391</v>
+        <v>363</v>
       </c>
     </row>
     <row r="393" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A393" t="s">
-        <v>392</v>
+        <v>364</v>
       </c>
     </row>
     <row r="394" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A394" t="s">
-        <v>393</v>
+        <v>365</v>
       </c>
     </row>
     <row r="395" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A395" t="s">
-        <v>394</v>
+        <v>366</v>
       </c>
     </row>
     <row r="396" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A396" t="s">
-        <v>395</v>
+        <v>367</v>
       </c>
     </row>
     <row r="397" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A397" t="s">
-        <v>396</v>
+        <v>368</v>
       </c>
     </row>
     <row r="398" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A398" t="s">
-        <v>397</v>
+        <v>369</v>
       </c>
     </row>
     <row r="399" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A399" t="s">
-        <v>398</v>
+        <v>370</v>
       </c>
     </row>
     <row r="400" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A400" t="s">
-        <v>399</v>
+        <v>371</v>
       </c>
     </row>
     <row r="401" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A401" t="s">
-        <v>400</v>
+        <v>372</v>
       </c>
     </row>
     <row r="402" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A402" t="s">
-        <v>401</v>
+        <v>373</v>
       </c>
     </row>
     <row r="403" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A403" t="s">
-        <v>402</v>
+        <v>374</v>
       </c>
     </row>
     <row r="404" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A404" t="s">
-        <v>403</v>
+        <v>375</v>
       </c>
     </row>
     <row r="405" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A405" t="s">
-        <v>404</v>
+        <v>376</v>
       </c>
     </row>
     <row r="406" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A406" t="s">
-        <v>405</v>
+        <v>377</v>
       </c>
     </row>
     <row r="407" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A407" t="s">
-        <v>406</v>
+        <v>378</v>
       </c>
     </row>
     <row r="408" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A408" t="s">
-        <v>407</v>
+        <v>379</v>
       </c>
     </row>
     <row r="409" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A409" t="s">
-        <v>408</v>
+        <v>380</v>
       </c>
     </row>
     <row r="410" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A410" t="s">
-        <v>409</v>
+        <v>381</v>
       </c>
     </row>
     <row r="411" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A411" t="s">
-        <v>410</v>
+        <v>382</v>
       </c>
     </row>
     <row r="412" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A412" t="s">
-        <v>411</v>
+        <v>383</v>
       </c>
     </row>
     <row r="413" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A413" t="s">
-        <v>412</v>
+        <v>384</v>
       </c>
     </row>
     <row r="414" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A414" t="s">
-        <v>413</v>
+        <v>385</v>
       </c>
     </row>
     <row r="415" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A415" t="s">
-        <v>414</v>
+        <v>386</v>
       </c>
     </row>
     <row r="416" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A416" t="s">
-        <v>415</v>
+        <v>387</v>
       </c>
     </row>
     <row r="417" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A417" t="s">
-        <v>416</v>
+        <v>388</v>
       </c>
     </row>
     <row r="418" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A418" t="s">
-        <v>417</v>
+        <v>389</v>
       </c>
     </row>
     <row r="419" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A419" t="s">
-        <v>418</v>
+        <v>390</v>
       </c>
     </row>
     <row r="420" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A420" t="s">
-        <v>419</v>
+        <v>391</v>
       </c>
     </row>
     <row r="421" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A421" t="s">
-        <v>420</v>
+        <v>392</v>
       </c>
     </row>
     <row r="422" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A422" t="s">
-        <v>421</v>
+        <v>393</v>
       </c>
     </row>
     <row r="423" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A423" t="s">
-        <v>422</v>
+        <v>394</v>
       </c>
     </row>
     <row r="424" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A424" t="s">
-        <v>423</v>
+        <v>395</v>
       </c>
     </row>
     <row r="425" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A425" t="s">
-        <v>424</v>
+        <v>396</v>
       </c>
     </row>
     <row r="426" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A426" t="s">
-        <v>425</v>
+        <v>397</v>
       </c>
     </row>
     <row r="427" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A427" t="s">
-        <v>426</v>
+        <v>398</v>
       </c>
     </row>
     <row r="428" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A428" t="s">
-        <v>427</v>
+        <v>399</v>
       </c>
     </row>
     <row r="429" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A429" t="s">
-        <v>428</v>
+        <v>400</v>
       </c>
     </row>
     <row r="430" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A430" t="s">
-        <v>429</v>
+        <v>401</v>
       </c>
     </row>
     <row r="431" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A431" t="s">
-        <v>430</v>
+        <v>402</v>
       </c>
     </row>
     <row r="432" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A432" t="s">
-        <v>431</v>
+        <v>403</v>
       </c>
     </row>
     <row r="433" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A433" t="s">
-        <v>432</v>
+        <v>404</v>
       </c>
     </row>
     <row r="434" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A434" t="s">
-        <v>433</v>
+        <v>405</v>
       </c>
     </row>
     <row r="435" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A435" t="s">
-        <v>434</v>
+        <v>406</v>
       </c>
     </row>
     <row r="436" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A436" t="s">
-        <v>435</v>
+        <v>407</v>
       </c>
     </row>
     <row r="437" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A437" t="s">
-        <v>436</v>
+        <v>408</v>
       </c>
     </row>
     <row r="438" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A438" t="s">
-        <v>437</v>
+        <v>409</v>
       </c>
     </row>
     <row r="439" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A439" t="s">
-        <v>438</v>
+        <v>410</v>
       </c>
     </row>
     <row r="440" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A440" t="s">
-        <v>439</v>
+        <v>411</v>
       </c>
     </row>
     <row r="441" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A441" t="s">
-        <v>440</v>
+        <v>412</v>
       </c>
     </row>
     <row r="442" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A442" t="s">
-        <v>441</v>
+        <v>413</v>
       </c>
     </row>
     <row r="443" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A443" t="s">
-        <v>442</v>
+        <v>414</v>
       </c>
     </row>
     <row r="444" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A444" t="s">
-        <v>443</v>
+        <v>627</v>
       </c>
     </row>
     <row r="445" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A445" t="s">
-        <v>444</v>
+        <v>628</v>
       </c>
     </row>
     <row r="446" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A446" t="s">
-        <v>445</v>
+        <v>415</v>
       </c>
     </row>
     <row r="447" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A447" t="s">
-        <v>446</v>
+        <v>416</v>
       </c>
     </row>
     <row r="448" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A448" t="s">
-        <v>447</v>
+        <v>417</v>
       </c>
     </row>
     <row r="449" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A449" t="s">
-        <v>448</v>
+        <v>418</v>
       </c>
     </row>
     <row r="450" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A450" t="s">
-        <v>449</v>
+        <v>419</v>
       </c>
     </row>
     <row r="451" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A451" t="s">
-        <v>450</v>
+        <v>420</v>
       </c>
     </row>
     <row r="452" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A452" t="s">
-        <v>451</v>
+        <v>421</v>
       </c>
     </row>
     <row r="453" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A453" t="s">
-        <v>452</v>
+        <v>422</v>
       </c>
     </row>
     <row r="454" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A454" t="s">
-        <v>453</v>
+        <v>423</v>
       </c>
     </row>
     <row r="455" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A455" t="s">
-        <v>454</v>
+        <v>424</v>
       </c>
     </row>
     <row r="456" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A456" t="s">
-        <v>455</v>
+        <v>425</v>
       </c>
     </row>
     <row r="457" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A457" t="s">
-        <v>456</v>
+        <v>426</v>
       </c>
     </row>
     <row r="458" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A458" t="s">
-        <v>457</v>
+        <v>427</v>
       </c>
     </row>
     <row r="459" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A459" t="s">
-        <v>458</v>
+        <v>428</v>
       </c>
     </row>
     <row r="460" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A460" t="s">
-        <v>459</v>
+        <v>429</v>
       </c>
     </row>
     <row r="461" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A461" t="s">
-        <v>460</v>
+        <v>430</v>
       </c>
     </row>
     <row r="462" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A462" t="s">
-        <v>461</v>
+        <v>431</v>
       </c>
     </row>
     <row r="463" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A463" t="s">
-        <v>462</v>
+        <v>432</v>
       </c>
     </row>
     <row r="464" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A464" t="s">
-        <v>463</v>
+        <v>433</v>
       </c>
     </row>
     <row r="465" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A465" t="s">
-        <v>464</v>
+        <v>434</v>
       </c>
     </row>
     <row r="466" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A466" t="s">
-        <v>465</v>
+        <v>435</v>
       </c>
     </row>
     <row r="467" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A467" t="s">
-        <v>466</v>
+        <v>436</v>
       </c>
     </row>
     <row r="468" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A468" t="s">
-        <v>467</v>
+        <v>437</v>
       </c>
     </row>
     <row r="469" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A469" t="s">
-        <v>468</v>
+        <v>438</v>
       </c>
     </row>
     <row r="470" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A470" t="s">
-        <v>469</v>
+        <v>439</v>
       </c>
     </row>
     <row r="471" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A471" t="s">
-        <v>470</v>
+        <v>440</v>
       </c>
     </row>
     <row r="472" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A472" t="s">
-        <v>471</v>
+        <v>441</v>
       </c>
     </row>
     <row r="473" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A473" t="s">
-        <v>472</v>
+        <v>442</v>
       </c>
     </row>
     <row r="474" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A474" t="s">
-        <v>473</v>
+        <v>443</v>
       </c>
     </row>
     <row r="475" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A475" t="s">
-        <v>474</v>
+        <v>444</v>
       </c>
     </row>
     <row r="476" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A476" t="s">
-        <v>475</v>
+        <v>445</v>
       </c>
     </row>
     <row r="477" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A477" t="s">
-        <v>476</v>
+        <v>446</v>
       </c>
     </row>
     <row r="478" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A478" t="s">
-        <v>477</v>
+        <v>447</v>
       </c>
     </row>
     <row r="479" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A479" t="s">
-        <v>478</v>
+        <v>448</v>
       </c>
     </row>
     <row r="480" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A480" t="s">
-        <v>479</v>
+        <v>449</v>
       </c>
     </row>
     <row r="481" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A481" t="s">
-        <v>480</v>
+        <v>450</v>
       </c>
     </row>
     <row r="482" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A482" t="s">
-        <v>481</v>
+        <v>451</v>
       </c>
     </row>
     <row r="483" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A483" t="s">
-        <v>482</v>
+        <v>452</v>
       </c>
     </row>
     <row r="484" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A484" t="s">
-        <v>483</v>
+        <v>453</v>
       </c>
     </row>
     <row r="485" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A485" t="s">
-        <v>484</v>
+        <v>454</v>
       </c>
     </row>
     <row r="486" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A486" t="s">
-        <v>485</v>
+        <v>455</v>
       </c>
     </row>
     <row r="487" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A487" t="s">
-        <v>486</v>
+        <v>456</v>
       </c>
     </row>
     <row r="488" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A488" t="s">
-        <v>487</v>
+        <v>457</v>
       </c>
     </row>
     <row r="489" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A489" t="s">
-        <v>488</v>
+        <v>458</v>
       </c>
     </row>
     <row r="490" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A490" t="s">
-        <v>489</v>
+        <v>459</v>
       </c>
     </row>
     <row r="491" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A491" t="s">
-        <v>490</v>
+        <v>460</v>
       </c>
     </row>
     <row r="492" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A492" t="s">
-        <v>491</v>
+        <v>461</v>
       </c>
     </row>
     <row r="493" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A493" t="s">
-        <v>492</v>
+        <v>462</v>
       </c>
     </row>
     <row r="494" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A494" t="s">
-        <v>493</v>
+        <v>463</v>
       </c>
     </row>
     <row r="495" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A495" t="s">
-        <v>494</v>
+        <v>464</v>
       </c>
     </row>
     <row r="496" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A496" t="s">
-        <v>495</v>
+        <v>465</v>
       </c>
     </row>
     <row r="497" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A497" t="s">
-        <v>496</v>
+        <v>466</v>
       </c>
     </row>
     <row r="498" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A498" t="s">
-        <v>497</v>
+        <v>467</v>
       </c>
     </row>
     <row r="499" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A499" t="s">
-        <v>498</v>
+        <v>468</v>
       </c>
     </row>
     <row r="500" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A500" t="s">
-        <v>499</v>
+        <v>469</v>
       </c>
     </row>
     <row r="501" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A501" t="s">
-        <v>500</v>
+        <v>470</v>
       </c>
     </row>
     <row r="502" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A502" t="s">
-        <v>501</v>
+        <v>471</v>
       </c>
     </row>
     <row r="503" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A503" t="s">
-        <v>502</v>
+        <v>472</v>
       </c>
     </row>
     <row r="504" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A504" t="s">
-        <v>503</v>
+        <v>473</v>
       </c>
     </row>
     <row r="505" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A505" t="s">
-        <v>504</v>
+        <v>474</v>
       </c>
     </row>
     <row r="506" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A506" t="s">
-        <v>505</v>
+        <v>475</v>
       </c>
     </row>
     <row r="507" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A507" t="s">
-        <v>506</v>
+        <v>476</v>
       </c>
     </row>
     <row r="508" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A508" t="s">
-        <v>507</v>
+        <v>477</v>
       </c>
     </row>
     <row r="509" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A509" t="s">
-        <v>508</v>
+        <v>478</v>
       </c>
     </row>
     <row r="510" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A510" t="s">
-        <v>509</v>
+        <v>479</v>
       </c>
     </row>
     <row r="511" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A511" t="s">
-        <v>510</v>
+        <v>480</v>
       </c>
     </row>
     <row r="512" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A512" t="s">
-        <v>511</v>
+        <v>481</v>
       </c>
     </row>
     <row r="513" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A513" t="s">
-        <v>512</v>
+        <v>482</v>
       </c>
     </row>
     <row r="514" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A514" t="s">
-        <v>513</v>
+        <v>483</v>
       </c>
     </row>
     <row r="515" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A515" t="s">
-        <v>514</v>
+        <v>484</v>
       </c>
     </row>
     <row r="516" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A516" t="s">
-        <v>515</v>
+        <v>485</v>
       </c>
     </row>
     <row r="517" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A517" t="s">
-        <v>516</v>
+        <v>486</v>
       </c>
     </row>
     <row r="518" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A518" t="s">
-        <v>517</v>
+        <v>487</v>
       </c>
     </row>
     <row r="519" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A519" t="s">
-        <v>518</v>
+        <v>488</v>
       </c>
     </row>
     <row r="520" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A520" t="s">
-        <v>519</v>
+        <v>489</v>
       </c>
     </row>
     <row r="521" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A521" t="s">
-        <v>520</v>
+        <v>490</v>
       </c>
     </row>
     <row r="522" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A522" t="s">
-        <v>521</v>
+        <v>491</v>
       </c>
     </row>
     <row r="523" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A523" t="s">
-        <v>522</v>
+        <v>492</v>
       </c>
     </row>
     <row r="524" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A524" t="s">
-        <v>523</v>
+        <v>493</v>
       </c>
     </row>
     <row r="525" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A525" t="s">
-        <v>524</v>
+        <v>494</v>
       </c>
     </row>
     <row r="526" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A526" t="s">
-        <v>525</v>
+        <v>495</v>
       </c>
     </row>
     <row r="527" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A527" t="s">
-        <v>526</v>
+        <v>496</v>
       </c>
     </row>
     <row r="528" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A528" t="s">
-        <v>527</v>
+        <v>497</v>
       </c>
     </row>
     <row r="529" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A529" t="s">
-        <v>528</v>
+        <v>498</v>
       </c>
     </row>
     <row r="530" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A530" t="s">
-        <v>529</v>
+        <v>499</v>
       </c>
     </row>
     <row r="531" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A531" t="s">
-        <v>530</v>
+        <v>500</v>
       </c>
     </row>
     <row r="532" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A532" t="s">
-        <v>531</v>
+        <v>501</v>
       </c>
     </row>
     <row r="533" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A533" t="s">
-        <v>532</v>
+        <v>502</v>
       </c>
     </row>
     <row r="534" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A534" t="s">
-        <v>533</v>
+        <v>503</v>
       </c>
     </row>
     <row r="535" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A535" t="s">
-        <v>534</v>
+        <v>504</v>
       </c>
     </row>
     <row r="536" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A536" t="s">
-        <v>535</v>
+        <v>505</v>
       </c>
     </row>
     <row r="537" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A537" t="s">
-        <v>536</v>
+        <v>506</v>
       </c>
     </row>
     <row r="538" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A538" t="s">
-        <v>537</v>
+        <v>507</v>
       </c>
     </row>
     <row r="539" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A539" t="s">
-        <v>538</v>
+        <v>508</v>
       </c>
     </row>
     <row r="540" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A540" t="s">
-        <v>539</v>
+        <v>509</v>
       </c>
     </row>
     <row r="541" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A541" t="s">
-        <v>540</v>
+        <v>510</v>
       </c>
     </row>
     <row r="542" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A542" t="s">
-        <v>541</v>
+        <v>511</v>
       </c>
     </row>
     <row r="543" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A543" t="s">
-        <v>542</v>
+        <v>512</v>
       </c>
     </row>
     <row r="544" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A544" t="s">
-        <v>543</v>
+        <v>513</v>
       </c>
     </row>
     <row r="545" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A545" t="s">
-        <v>544</v>
+        <v>514</v>
       </c>
     </row>
     <row r="546" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A546" t="s">
-        <v>545</v>
+        <v>515</v>
       </c>
     </row>
     <row r="547" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A547" t="s">
-        <v>546</v>
+        <v>516</v>
       </c>
     </row>
     <row r="548" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A548" t="s">
-        <v>547</v>
+        <v>517</v>
       </c>
     </row>
     <row r="549" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A549" t="s">
-        <v>548</v>
+        <v>518</v>
       </c>
     </row>
     <row r="550" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A550" t="s">
-        <v>549</v>
+        <v>519</v>
       </c>
     </row>
     <row r="551" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A551" t="s">
-        <v>550</v>
+        <v>520</v>
       </c>
     </row>
     <row r="552" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A552" t="s">
-        <v>551</v>
+        <v>521</v>
       </c>
     </row>
     <row r="553" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A553" t="s">
-        <v>552</v>
+        <v>522</v>
       </c>
     </row>
     <row r="554" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A554" t="s">
-        <v>553</v>
+        <v>523</v>
       </c>
     </row>
     <row r="555" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A555" t="s">
-        <v>554</v>
+        <v>524</v>
       </c>
     </row>
     <row r="556" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A556" t="s">
-        <v>555</v>
+        <v>525</v>
       </c>
     </row>
     <row r="557" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A557" t="s">
-        <v>556</v>
+        <v>526</v>
       </c>
     </row>
     <row r="558" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A558" t="s">
-        <v>557</v>
+        <v>527</v>
       </c>
     </row>
     <row r="559" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A559" t="s">
-        <v>558</v>
+        <v>528</v>
       </c>
     </row>
     <row r="560" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A560" t="s">
-        <v>559</v>
+        <v>529</v>
       </c>
     </row>
     <row r="561" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A561" t="s">
-        <v>560</v>
+        <v>530</v>
       </c>
     </row>
     <row r="562" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A562" t="s">
-        <v>561</v>
+        <v>531</v>
       </c>
     </row>
     <row r="563" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A563" t="s">
-        <v>562</v>
+        <v>532</v>
       </c>
     </row>
     <row r="564" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A564" t="s">
-        <v>563</v>
+        <v>533</v>
       </c>
     </row>
     <row r="565" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A565" t="s">
-        <v>564</v>
+        <v>534</v>
       </c>
     </row>
     <row r="566" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A566" t="s">
-        <v>565</v>
+        <v>535</v>
       </c>
     </row>
     <row r="567" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A567" t="s">
-        <v>566</v>
+        <v>536</v>
       </c>
     </row>
     <row r="568" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A568" t="s">
-        <v>567</v>
+        <v>537</v>
       </c>
     </row>
     <row r="569" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A569" t="s">
-        <v>568</v>
+        <v>538</v>
       </c>
     </row>
     <row r="570" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A570" t="s">
-        <v>569</v>
+        <v>539</v>
       </c>
     </row>
     <row r="571" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A571" t="s">
-        <v>570</v>
+        <v>635</v>
       </c>
     </row>
     <row r="572" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A572" t="s">
-        <v>571</v>
+        <v>636</v>
       </c>
     </row>
     <row r="573" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A573" t="s">
-        <v>572</v>
+        <v>637</v>
       </c>
     </row>
     <row r="574" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A574" t="s">
-        <v>573</v>
+        <v>638</v>
       </c>
     </row>
     <row r="575" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A575" t="s">
-        <v>574</v>
+        <v>639</v>
       </c>
     </row>
     <row r="576" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A576" t="s">
-        <v>575</v>
+        <v>640</v>
       </c>
     </row>
     <row r="577" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A577" t="s">
-        <v>576</v>
+        <v>641</v>
       </c>
     </row>
     <row r="578" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A578" t="s">
-        <v>577</v>
+        <v>642</v>
       </c>
     </row>
     <row r="579" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A579" t="s">
-        <v>578</v>
+        <v>643</v>
       </c>
     </row>
     <row r="580" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A580" t="s">
-        <v>579</v>
+        <v>644</v>
       </c>
     </row>
     <row r="581" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A581" t="s">
-        <v>580</v>
+        <v>540</v>
       </c>
     </row>
     <row r="582" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A582" t="s">
-        <v>581</v>
+        <v>541</v>
       </c>
     </row>
     <row r="583" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A583" t="s">
-        <v>582</v>
+        <v>631</v>
       </c>
     </row>
     <row r="584" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A584" t="s">
-        <v>583</v>
+        <v>542</v>
       </c>
     </row>
     <row r="585" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A585" t="s">
-        <v>584</v>
+        <v>543</v>
       </c>
     </row>
     <row r="586" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A586" t="s">
-        <v>585</v>
+        <v>544</v>
       </c>
     </row>
     <row r="587" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A587" t="s">
-        <v>586</v>
+        <v>545</v>
       </c>
     </row>
     <row r="588" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A588" t="s">
-        <v>587</v>
+        <v>546</v>
       </c>
     </row>
     <row r="589" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A589" t="s">
-        <v>588</v>
+        <v>547</v>
       </c>
     </row>
     <row r="590" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A590" t="s">
-        <v>589</v>
+        <v>548</v>
       </c>
     </row>
     <row r="591" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A591" t="s">
-        <v>590</v>
+        <v>549</v>
       </c>
     </row>
     <row r="592" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A592" t="s">
-        <v>591</v>
+        <v>550</v>
       </c>
     </row>
     <row r="593" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A593" t="s">
-        <v>592</v>
+        <v>551</v>
       </c>
     </row>
     <row r="594" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A594" t="s">
-        <v>593</v>
+        <v>552</v>
       </c>
     </row>
     <row r="595" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A595" t="s">
-        <v>594</v>
+        <v>553</v>
       </c>
     </row>
     <row r="596" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A596" t="s">
-        <v>595</v>
+        <v>554</v>
       </c>
     </row>
     <row r="597" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A597" t="s">
-        <v>596</v>
+        <v>555</v>
       </c>
     </row>
     <row r="598" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A598" t="s">
-        <v>597</v>
+        <v>556</v>
       </c>
     </row>
     <row r="599" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A599" t="s">
-        <v>598</v>
+        <v>629</v>
       </c>
     </row>
     <row r="600" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A600" t="s">
-        <v>599</v>
+        <v>645</v>
       </c>
     </row>
     <row r="601" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A601" t="s">
-        <v>600</v>
+        <v>646</v>
       </c>
     </row>
     <row r="602" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A602" t="s">
-        <v>601</v>
+        <v>647</v>
       </c>
     </row>
     <row r="603" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A603" t="s">
-        <v>602</v>
+        <v>648</v>
       </c>
     </row>
     <row r="604" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A604" t="s">
-        <v>603</v>
+        <v>649</v>
       </c>
     </row>
     <row r="605" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A605" t="s">
-        <v>604</v>
+        <v>650</v>
       </c>
     </row>
     <row r="606" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A606" t="s">
-        <v>605</v>
+        <v>651</v>
       </c>
     </row>
     <row r="607" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A607" t="s">
-        <v>606</v>
+        <v>652</v>
       </c>
     </row>
     <row r="608" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A608" t="s">
-        <v>607</v>
+        <v>653</v>
       </c>
     </row>
     <row r="609" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A609" t="s">
-        <v>608</v>
+        <v>654</v>
       </c>
     </row>
     <row r="610" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A610" t="s">
-        <v>609</v>
+        <v>655</v>
       </c>
     </row>
     <row r="611" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A611" t="s">
-        <v>610</v>
+        <v>656</v>
       </c>
     </row>
     <row r="612" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A612" t="s">
-        <v>611</v>
+        <v>632</v>
       </c>
     </row>
     <row r="613" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A613" t="s">
-        <v>612</v>
+        <v>630</v>
       </c>
     </row>
     <row r="614" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A614" t="s">
-        <v>613</v>
+        <v>657</v>
       </c>
     </row>
     <row r="615" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A615" t="s">
-        <v>614</v>
+        <v>557</v>
       </c>
     </row>
     <row r="616" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A616" t="s">
-        <v>615</v>
+        <v>558</v>
       </c>
     </row>
     <row r="617" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A617" t="s">
-        <v>616</v>
+        <v>559</v>
       </c>
     </row>
     <row r="618" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A618" t="s">
-        <v>617</v>
+        <v>560</v>
       </c>
     </row>
     <row r="619" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A619" t="s">
-        <v>618</v>
+        <v>561</v>
       </c>
     </row>
     <row r="620" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A620" t="s">
-        <v>619</v>
+        <v>562</v>
       </c>
     </row>
     <row r="621" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A621" t="s">
-        <v>620</v>
+        <v>563</v>
       </c>
     </row>
     <row r="622" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A622" t="s">
-        <v>621</v>
+        <v>564</v>
       </c>
     </row>
     <row r="623" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A623" t="s">
-        <v>622</v>
+        <v>565</v>
       </c>
     </row>
     <row r="624" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A624" t="s">
-        <v>623</v>
+        <v>566</v>
       </c>
     </row>
     <row r="625" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A625" t="s">
-        <v>624</v>
+        <v>567</v>
       </c>
     </row>
     <row r="626" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A626" t="s">
-        <v>625</v>
+        <v>568</v>
       </c>
     </row>
     <row r="627" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A627" t="s">
-        <v>626</v>
+        <v>569</v>
       </c>
     </row>
     <row r="628" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A628" t="s">
-        <v>627</v>
+        <v>570</v>
       </c>
     </row>
     <row r="629" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A629" t="s">
-        <v>628</v>
+        <v>571</v>
       </c>
     </row>
     <row r="630" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A630" t="s">
-        <v>629</v>
+        <v>572</v>
       </c>
     </row>
     <row r="631" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A631" t="s">
-        <v>630</v>
+        <v>573</v>
       </c>
     </row>
     <row r="632" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A632" t="s">
-        <v>631</v>
+        <v>574</v>
       </c>
     </row>
     <row r="633" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A633" t="s">
-        <v>632</v>
+        <v>575</v>
       </c>
     </row>
     <row r="634" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A634" t="s">
-        <v>633</v>
+        <v>576</v>
       </c>
     </row>
     <row r="635" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A635" t="s">
-        <v>634</v>
+        <v>577</v>
       </c>
     </row>
     <row r="636" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A636" t="s">
-        <v>635</v>
+        <v>578</v>
       </c>
     </row>
     <row r="637" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A637" t="s">
-        <v>636</v>
+        <v>579</v>
       </c>
     </row>
     <row r="638" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A638" t="s">
-        <v>637</v>
+        <v>580</v>
       </c>
     </row>
     <row r="639" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A639" t="s">
-        <v>638</v>
+        <v>581</v>
       </c>
     </row>
     <row r="640" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A640" t="s">
-        <v>639</v>
+        <v>582</v>
       </c>
     </row>
     <row r="641" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A641" t="s">
-        <v>640</v>
+        <v>583</v>
       </c>
     </row>
     <row r="642" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A642" t="s">
-        <v>641</v>
+        <v>584</v>
       </c>
     </row>
     <row r="643" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A643" t="s">
-        <v>642</v>
+        <v>585</v>
       </c>
     </row>
     <row r="644" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A644" t="s">
-        <v>643</v>
+        <v>586</v>
       </c>
     </row>
     <row r="645" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A645" t="s">
-        <v>644</v>
+        <v>587</v>
       </c>
     </row>
     <row r="646" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A646" t="s">
-        <v>645</v>
+        <v>588</v>
       </c>
     </row>
     <row r="647" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A647" t="s">
-        <v>646</v>
+        <v>589</v>
       </c>
     </row>
     <row r="648" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A648" t="s">
-        <v>647</v>
+        <v>590</v>
       </c>
     </row>
     <row r="649" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A649" t="s">
-        <v>648</v>
+        <v>591</v>
       </c>
     </row>
     <row r="650" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A650" t="s">
-        <v>649</v>
+        <v>592</v>
       </c>
     </row>
     <row r="651" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A651" t="s">
-        <v>650</v>
+        <v>593</v>
       </c>
     </row>
     <row r="652" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A652" t="s">
-        <v>651</v>
+        <v>594</v>
       </c>
     </row>
     <row r="653" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A653" t="s">
-        <v>652</v>
+        <v>595</v>
       </c>
     </row>
     <row r="654" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A654" t="s">
-        <v>653</v>
+        <v>596</v>
       </c>
     </row>
     <row r="655" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A655" t="s">
-        <v>654</v>
+        <v>597</v>
       </c>
     </row>
     <row r="656" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A656" t="s">
-        <v>655</v>
+        <v>598</v>
       </c>
     </row>
     <row r="657" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A657" t="s">
-        <v>656</v>
+        <v>599</v>
       </c>
     </row>
     <row r="658" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A658" t="s">
-        <v>657</v>
+        <v>600</v>
       </c>
     </row>
     <row r="659" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A659" t="s">
-        <v>658</v>
+        <v>601</v>
       </c>
     </row>
   </sheetData>
